--- a/Projects/MISQ/MISQ round 2/afterSEmeeting260624_results, theory and LR.xlsx
+++ b/Projects/MISQ/MISQ round 2/afterSEmeeting260624_results, theory and LR.xlsx
@@ -1,30 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dylanchen/Desktop/geek-community/Projects/MISQ/MISQ round 2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7052D50D-7C9E-8F4D-B2CD-DB2A60902E93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EE90A10-09AB-9B47-8D30-D39EA99452E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19540" xr2:uid="{30F402B7-E6D8-E34B-8063-713AC97DE139}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19420" activeTab="1" xr2:uid="{30F402B7-E6D8-E34B-8063-713AC97DE139}"/>
   </bookViews>
   <sheets>
-    <sheet name="Results" sheetId="7" r:id="rId1"/>
-    <sheet name="Theory" sheetId="8" r:id="rId2"/>
-    <sheet name="Literature Review" sheetId="9" r:id="rId3"/>
-    <sheet name="interaction plot (20260608)" sheetId="6" r:id="rId4"/>
-    <sheet name="table in paper" sheetId="3" r:id="rId5"/>
-    <sheet name="Sheet1" sheetId="1" r:id="rId6"/>
-    <sheet name="Sheet3" sheetId="5" r:id="rId7"/>
-    <sheet name="interaction plot" sheetId="2" r:id="rId8"/>
+    <sheet name="Theory" sheetId="8" r:id="rId1"/>
+    <sheet name="Result" sheetId="10" r:id="rId2"/>
+    <sheet name="Results (with table)" sheetId="7" r:id="rId3"/>
+    <sheet name="Literature Review" sheetId="9" r:id="rId4"/>
+    <sheet name="interaction plot (20260608)" sheetId="6" r:id="rId5"/>
+    <sheet name="table in paper" sheetId="3" r:id="rId6"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId7"/>
+    <sheet name="Sheet3" sheetId="5" r:id="rId8"/>
+    <sheet name="interaction plot" sheetId="2" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_Ref194135344" localSheetId="0">Results!$N$26</definedName>
-    <definedName name="_Ref210225085" localSheetId="0">Results!$D$42</definedName>
+    <definedName name="_Hlk194498603" localSheetId="3">'Literature Review'!$A$15</definedName>
+    <definedName name="_Ref194135344" localSheetId="2">'Results (with table)'!$N$26</definedName>
+    <definedName name="_Ref210225085" localSheetId="2">'Results (with table)'!$D$42</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -50,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1160" uniqueCount="482">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1270" uniqueCount="546">
   <si>
     <t>DV: # human answers</t>
   </si>
@@ -1515,14 +1517,6 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">(Goal Setting Theory)
-AI answer quality is a slow-processed cue because it requires deliberate reading. Per Goal Setting Theory, the most difficult goals produce the highest performance. Once experts recognize the AI answer is high quality, it becomes a challenging benchmark. This triggers greater effort and raises human answer quality. </t>
-  </si>
-  <si>
-    <t>(Competitive Arousal Theory)
-The AI label is a fast-processed cue, and contribution is a fast, quantity-based decision. Per Competitive Arousal Theory, the mere presence of a rival triggers arousal that drives action. Answerer perceive AI as a weak competitor (because they think they are more experienced in tehcnical question domain like SegmentFault) with high winning probability, so arousal converts directly into increased contribution.</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">H2: </t>
     </r>
@@ -1536,14 +1530,6 @@
       </rPr>
       <t>reverses H1</t>
     </r>
-  </si>
-  <si>
-    <t>(Competitive Dynamics Theory)
-Answer length is a fast-processed heuristic cue, and contribution remains a fast decision. Per Competitive Dynamics Theory, when a response requires substantial resource commitment, answerer are less likely to act. A longer AI answer signals higher entry cost without deep reading, which demotivate the arousal-driven contribution.</t>
-  </si>
-  <si>
-    <t>(Downward Social Comparison Theory)
-The AI label, though a fast-processed cue, establishes a persistent comparison reference point for the quality-production stage. Answer quality is a slow, effort-intensive outcome. Per Downward Social Comparison Theory, comparing with a weaker target substitutes for instrumental action. This downward social comparison with weak competitor replaces actual effort paid into cultivating answer quality, so answer quality decreases.</t>
   </si>
   <si>
     <t>Log(answer number in 7 days)</t>
@@ -1642,27 +1628,6 @@
     </r>
   </si>
   <si>
-    <t>0.030**</t>
-  </si>
-  <si>
-    <t>0.024*</t>
-  </si>
-  <si>
-    <t>0.016*</t>
-  </si>
-  <si>
-    <t>controls</t>
-  </si>
-  <si>
-    <t>whether the answer contains personal experience</t>
-  </si>
-  <si>
-    <t>whether the answer contains opinionated insights</t>
-  </si>
-  <si>
-    <t>whether the answer contains alternative solutions</t>
-  </si>
-  <si>
     <t>OLS</t>
   </si>
   <si>
@@ -1746,9 +1711,6 @@
     <t>Robustness checks: alternative model specifications for human answer supply</t>
   </si>
   <si>
-    <t>Human answerers’ response to AI-generated answers</t>
-  </si>
-  <si>
     <t>The impact of AI-generated answers on the answer supply and answer quality</t>
   </si>
   <si>
@@ -2060,26 +2022,282 @@
     <t>additional analysis</t>
   </si>
   <si>
-    <t>LI Xin's list</t>
-  </si>
-  <si>
-    <t>setup 1 下不同的10个LLM DV</t>
-  </si>
-  <si>
-    <t>deepen insights</t>
-  </si>
-  <si>
-    <t>strnegth interpretation</t>
-  </si>
-  <si>
-    <t>expand insights</t>
+    <t>Other DV</t>
+  </si>
+  <si>
+    <t>strength interpretation</t>
+  </si>
+  <si>
+    <t>verify weak competitor</t>
+  </si>
+  <si>
+    <t>verify "Fast Signal → Fast Outcome"</t>
+  </si>
+  <si>
+    <t>AI label increase human contribution
+AI length decrease human contribution</t>
+  </si>
+  <si>
+    <t>AI lael decrease first human quality
+AI quality increase first human quality</t>
+  </si>
+  <si>
+    <t>AI label 加速first human的到来
+AI length 减速first human的到来
+AI quality 没有影响</t>
+  </si>
+  <si>
+    <t>verify AI label generate affect/emotion that continuously impact quality</t>
+  </si>
+  <si>
+    <t>AI lael decrease second human quality
+AI length 不显著（length产生的judgement已过期）
+AI quality increase second human quality</t>
+  </si>
+  <si>
+    <t>Extend or Deepen Insights</t>
+  </si>
+  <si>
+    <t>first human quality increase on what?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">different differientiation direction? </t>
+  </si>
+  <si>
+    <t>AI quality increase Similarity(fisrt human, AI) in AI group</t>
+  </si>
+  <si>
+    <t>question difficulty as moderator</t>
+  </si>
+  <si>
+    <t>other parties: questioner &amp; viewer</t>
+  </si>
+  <si>
+    <t>no impact on questioners and viewers</t>
+  </si>
+  <si>
+    <t>AI lebel 更多地 increase high repuration expert contribution</t>
+  </si>
+  <si>
+    <t>AI label 更多地 decrease high repuration expert quality
+AI quality 更多地 increase  high repuration expert quality  (out of surprise)</t>
+  </si>
+  <si>
+    <t>quality increase, how about recognition?</t>
+  </si>
+  <si>
+    <t>netlike decrease, due to elevated expectation</t>
+  </si>
+  <si>
+    <r>
+      <t>Contribution = System 1 decision; Quality = System 2 outcome.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Whether to participate is a binary, low-load call that System 1 resolves in seconds. Producing a quality answer requires sustained reading, reasoning, and drafting—a protracted System 2 process.</t>
+    </r>
+  </si>
+  <si>
+    <t>另外我们能不能做个model free画一下两种问题随着时间平均回答数目和qulaity的变化</t>
+  </si>
+  <si>
+    <t>大模型打分的quality能不能和viwer likes 算个correlation，没有AI只有人，看看face validity</t>
+  </si>
+  <si>
+    <t>AI回答长度比人长，但是质量跟高端人差不多，我们看了对质量影响，有没有必要看看对长度影响？</t>
+  </si>
+  <si>
+    <t>Reputation analysis 可不可以直接做哪些人的质量和长度和AI差不多</t>
+  </si>
+  <si>
+    <t>Study</t>
+  </si>
+  <si>
+    <t>Community</t>
+  </si>
+  <si>
+    <t>AI Examined</t>
+  </si>
+  <si>
+    <t>Event</t>
+  </si>
+  <si>
+    <t>Research Design</t>
+  </si>
+  <si>
+    <t>User Group Examined</t>
+  </si>
+  <si>
+    <t>Unit of Analysis</t>
+  </si>
+  <si>
+    <t>GenAI Effect</t>
+  </si>
+  <si>
+    <t>Borwankar et al., 2023</t>
+  </si>
+  <si>
+    <t>Stack Overflow</t>
+  </si>
+  <si>
+    <t>ChatGPT</t>
+  </si>
+  <si>
+    <t>GenAI ban</t>
+  </si>
+  <si>
+    <t>Natural Experiment</t>
+  </si>
+  <si>
+    <t>Answerer, Viewer</t>
+  </si>
+  <si>
+    <t>answer-user-day</t>
+  </si>
+  <si>
+    <t>Decrease # of likes</t>
+  </si>
+  <si>
+    <t>Burtch et al., 2023</t>
+  </si>
+  <si>
+    <t>GenAI introduction</t>
+  </si>
+  <si>
+    <t>Questioner</t>
+  </si>
+  <si>
+    <t>topic-week</t>
+  </si>
+  <si>
+    <t>Reduce # of questions</t>
+  </si>
+  <si>
+    <t>del Rio-Chanona et al., 2023</t>
+  </si>
+  <si>
+    <t>Quinn &amp; Gutt, 2023</t>
+  </si>
+  <si>
+    <t>Stack Exchange</t>
+  </si>
+  <si>
+    <t>Sanatizadeh et al., 2023</t>
+  </si>
+  <si>
+    <t>Questioner, Answerer, Viewer</t>
+  </si>
+  <si>
+    <t>post-day</t>
+  </si>
+  <si>
+    <t>Reduce # of views; increase # of likes</t>
+  </si>
+  <si>
+    <t>Shan &amp; Qiu, 2023</t>
+  </si>
+  <si>
+    <t>Answerer</t>
+  </si>
+  <si>
+    <t>user-day</t>
+  </si>
+  <si>
+    <t>Su et al., 2023</t>
+  </si>
+  <si>
+    <t>Quora</t>
+  </si>
+  <si>
+    <t>Internal GenAI</t>
+  </si>
+  <si>
+    <t>question-week</t>
+  </si>
+  <si>
+    <t>Xue et al., 2023</t>
+  </si>
+  <si>
+    <t>topic-day</t>
+  </si>
+  <si>
+    <t>Li &amp; Kim, 2024</t>
+  </si>
+  <si>
+    <t>Reduce # of answers</t>
+  </si>
+  <si>
+    <t>Reduce # of likes</t>
+  </si>
+  <si>
+    <t>Wang &amp; Zheng, 2024</t>
+  </si>
+  <si>
+    <t>Increase # of questions</t>
+  </si>
+  <si>
+    <t>Increase # of views</t>
+  </si>
+  <si>
+    <t>Increase # of answers; make answers shorter and easier to read</t>
+  </si>
+  <si>
+    <t>Make answers shorter, more negative and harder to read</t>
+  </si>
+  <si>
+    <t>Reduce # of questions; make questions more difficult to read</t>
+  </si>
+  <si>
+    <t>Reduce # of answers; make answers longer, more difficult to read</t>
+  </si>
+  <si>
+    <t>Reduce # of questions; make questions longer, more difficult to read</t>
+  </si>
+  <si>
+    <t>Increase # of answers; make answers longer and similar to AI answers</t>
+  </si>
+  <si>
+    <t>Increase # of answers; increase acceptance ratio of answers</t>
+  </si>
+  <si>
+    <t>Reduce # of questions; make questions higher quality (simpler questions disappear)</t>
+  </si>
+  <si>
+    <t>Increase question quality</t>
+  </si>
+  <si>
+    <t>- Length is a fast signal (routine assessment) 
+- "Intensity matching" converts physical volume into perceived barrier.
+- When perceived cost exceeds perceived benefit, System 1 flips</t>
+  </si>
+  <si>
+    <t>- AI Label is a fast signal, zero-cost "routine assessment". 
+- Cause negative emotion (new competitor -&gt; threat, low-quality AI at the time as "availability heuristic" -&gt; 不屑)
+- "exaggerated emotional coherence" -&gt; weak competitor
+- what's more? "Overconfidence"</t>
+  </si>
+  <si>
+    <t>- AI label through system 1 output negative affect towards AI. Affect persists as continuous background "mood".
+- "Law of least effort" lowers the effort.
+- "Anchoring prevents sufficient adjustment", even for slow decision</t>
+  </si>
+  <si>
+    <t>- Quality is a slow signal—inaccessible without deliberate reading. 
+- High quality triggers "surprise", forcing System 2 to override.
+- what's more, professional identity threat is "sufficiently important" to activate System 2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="29" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -2224,6 +2442,61 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FFFFC000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -2263,7 +2536,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -2380,11 +2653,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="156">
+  <cellXfs count="168">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -2462,8 +2746,243 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="6" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
@@ -2471,17 +2990,116 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2494,6 +3112,18 @@
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2513,320 +3143,6 @@
     <xf numFmtId="49" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="6" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -16972,6 +17288,432 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>88900</xdr:colOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4097" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8AA38731-6B98-D316-7D19-E478C0C611A6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:clrChange>
+            <a:clrFrom>
+              <a:srgbClr val="FFFFFF"/>
+            </a:clrFrom>
+            <a:clrTo>
+              <a:srgbClr val="FFFFFF">
+                <a:alpha val="0"/>
+              </a:srgbClr>
+            </a:clrTo>
+          </a:clrChange>
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="15049500" y="21082000"/>
+          <a:ext cx="88900" cy="177800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4098" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6F967735-B6DA-8C2D-8489-66D2AB2A2822}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
+          <a:clrChange>
+            <a:clrFrom>
+              <a:srgbClr val="FFFFFF"/>
+            </a:clrFrom>
+            <a:clrTo>
+              <a:srgbClr val="FFFFFF">
+                <a:alpha val="0"/>
+              </a:srgbClr>
+            </a:clrTo>
+          </a:clrChange>
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="16484600" y="20802600"/>
+          <a:ext cx="152400" cy="165100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>279400</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4099" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C320F611-D4C3-D5B1-576D-AD226F99FCA3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5">
+          <a:clrChange>
+            <a:clrFrom>
+              <a:srgbClr val="FFFFFF"/>
+            </a:clrFrom>
+            <a:clrTo>
+              <a:srgbClr val="FFFFFF">
+                <a:alpha val="0"/>
+              </a:srgbClr>
+            </a:clrTo>
+          </a:clrChange>
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="17919700" y="20802600"/>
+          <a:ext cx="279400" cy="165100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>139700</xdr:colOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4100" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7BD0F9AF-A9E3-E1AC-21CC-1C13E3D40B99}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6">
+          <a:clrChange>
+            <a:clrFrom>
+              <a:srgbClr val="FFFFFF"/>
+            </a:clrFrom>
+            <a:clrTo>
+              <a:srgbClr val="FFFFFF">
+                <a:alpha val="0"/>
+              </a:srgbClr>
+            </a:clrTo>
+          </a:clrChange>
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="19596100" y="21082000"/>
+          <a:ext cx="139700" cy="165100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4101" name="Picture 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1B6428B2-AD1D-D7E2-C3AE-F4B51B77B8A2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7">
+          <a:clrChange>
+            <a:clrFrom>
+              <a:srgbClr val="FFFFFF"/>
+            </a:clrFrom>
+            <a:clrTo>
+              <a:srgbClr val="FFFFFF">
+                <a:alpha val="0"/>
+              </a:srgbClr>
+            </a:clrTo>
+          </a:clrChange>
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="21424900" y="20802600"/>
+          <a:ext cx="76200" cy="165100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>279400</xdr:colOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4102" name="Picture 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CD7D4A9A-CAB4-1732-EF96-11269777887F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8">
+          <a:clrChange>
+            <a:clrFrom>
+              <a:srgbClr val="FFFFFF"/>
+            </a:clrFrom>
+            <a:clrTo>
+              <a:srgbClr val="FFFFFF">
+                <a:alpha val="0"/>
+              </a:srgbClr>
+            </a:clrTo>
+          </a:clrChange>
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="21424900" y="21082000"/>
+          <a:ext cx="279400" cy="165100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -18066,1386 +18808,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FD1D18A-C464-364C-95F7-F927C76322D3}">
-  <dimension ref="B2:AI89"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="22" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="10.83203125" style="48"/>
-    <col min="2" max="2" width="21.83203125" style="154" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.6640625" style="62" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="21.6640625" style="62" customWidth="1"/>
-    <col min="6" max="7" width="18.83203125" style="62" customWidth="1"/>
-    <col min="8" max="9" width="21.6640625" style="62" customWidth="1"/>
-    <col min="10" max="12" width="18.83203125" style="62" customWidth="1"/>
-    <col min="13" max="13" width="22" style="116" customWidth="1"/>
-    <col min="14" max="14" width="24" style="116" customWidth="1"/>
-    <col min="15" max="16" width="21.6640625" style="116" customWidth="1"/>
-    <col min="17" max="18" width="18.83203125" style="116" customWidth="1"/>
-    <col min="19" max="19" width="10.83203125" style="54"/>
-    <col min="20" max="20" width="14.33203125" style="54" bestFit="1" customWidth="1"/>
-    <col min="21" max="26" width="10.83203125" style="54"/>
-    <col min="27" max="27" width="10.83203125" style="136"/>
-    <col min="28" max="35" width="10.83203125" style="52"/>
-    <col min="36" max="16384" width="10.83203125" style="48"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:27" x14ac:dyDescent="0.2">
-      <c r="B2" s="50" t="s">
-        <v>388</v>
-      </c>
-      <c r="C2" s="59" t="s">
-        <v>389</v>
-      </c>
-      <c r="D2" s="59"/>
-      <c r="E2" s="59"/>
-      <c r="F2" s="59"/>
-      <c r="G2" s="59"/>
-      <c r="H2" s="59"/>
-      <c r="I2" s="59"/>
-      <c r="J2" s="59"/>
-      <c r="K2" s="59"/>
-      <c r="L2" s="59"/>
-      <c r="M2" s="111" t="s">
-        <v>390</v>
-      </c>
-      <c r="N2" s="111"/>
-      <c r="O2" s="111"/>
-      <c r="P2" s="111"/>
-      <c r="Q2" s="111"/>
-      <c r="R2" s="111"/>
-      <c r="S2" s="53" t="s">
-        <v>473</v>
-      </c>
-      <c r="T2" s="53"/>
-      <c r="U2" s="53"/>
-      <c r="V2" s="53"/>
-      <c r="W2" s="53"/>
-      <c r="X2" s="53"/>
-      <c r="Y2" s="53"/>
-      <c r="Z2" s="53"/>
-      <c r="AA2" s="53"/>
-    </row>
-    <row r="3" spans="2:27" ht="21" x14ac:dyDescent="0.2">
-      <c r="B3" s="152" t="s">
-        <v>474</v>
-      </c>
-      <c r="C3" s="60"/>
-      <c r="D3" s="60"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="60"/>
-      <c r="G3" s="60"/>
-      <c r="H3" s="60"/>
-      <c r="I3" s="60"/>
-      <c r="J3" s="60"/>
-      <c r="K3" s="60"/>
-      <c r="L3" s="60"/>
-      <c r="M3" s="112"/>
-      <c r="N3" s="112"/>
-      <c r="O3" s="112"/>
-      <c r="P3" s="112"/>
-      <c r="Q3" s="112"/>
-      <c r="R3" s="112"/>
-    </row>
-    <row r="4" spans="2:27" ht="21" x14ac:dyDescent="0.2">
-      <c r="B4" s="49"/>
-      <c r="C4" s="60"/>
-      <c r="D4" s="61"/>
-      <c r="E4" s="61"/>
-      <c r="F4" s="61"/>
-      <c r="G4" s="61"/>
-      <c r="H4" s="61"/>
-      <c r="J4" s="63" t="s">
-        <v>433</v>
-      </c>
-      <c r="K4" s="61"/>
-      <c r="L4" s="61"/>
-      <c r="M4" s="113"/>
-      <c r="N4" s="113"/>
-      <c r="O4" s="112"/>
-      <c r="P4" s="112"/>
-      <c r="Q4" s="112"/>
-      <c r="R4" s="112"/>
-      <c r="T4" s="56" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="5" spans="2:27" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="49"/>
-      <c r="C5" s="60"/>
-      <c r="D5" s="61"/>
-      <c r="E5" s="61"/>
-      <c r="F5" s="61"/>
-      <c r="G5" s="61"/>
-      <c r="H5" s="61"/>
-      <c r="J5" s="64"/>
-      <c r="K5" s="65" t="s">
-        <v>340</v>
-      </c>
-      <c r="L5" s="65" t="s">
-        <v>341</v>
-      </c>
-      <c r="M5" s="114" t="s">
-        <v>342</v>
-      </c>
-      <c r="N5" s="114" t="s">
-        <v>343</v>
-      </c>
-      <c r="O5" s="112"/>
-      <c r="P5" s="112"/>
-      <c r="Q5" s="112"/>
-      <c r="R5" s="112"/>
-      <c r="T5" s="137"/>
-      <c r="U5" s="57" t="s">
-        <v>340</v>
-      </c>
-      <c r="V5" s="57" t="s">
-        <v>341</v>
-      </c>
-      <c r="W5" s="57" t="s">
-        <v>342</v>
-      </c>
-      <c r="X5" s="57" t="s">
-        <v>343</v>
-      </c>
-      <c r="Y5" s="57" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="6" spans="2:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="49"/>
-      <c r="D6" s="61"/>
-      <c r="E6" s="61"/>
-      <c r="F6" s="61"/>
-      <c r="G6" s="61"/>
-      <c r="H6" s="61"/>
-      <c r="J6" s="66" t="s">
-        <v>388</v>
-      </c>
-      <c r="K6" s="67" t="s">
-        <v>403</v>
-      </c>
-      <c r="L6" s="67"/>
-      <c r="M6" s="115" t="s">
-        <v>404</v>
-      </c>
-      <c r="N6" s="115"/>
-      <c r="T6" s="138" t="s">
-        <v>345</v>
-      </c>
-      <c r="U6" s="139" t="s">
-        <v>470</v>
-      </c>
-      <c r="V6" s="139"/>
-      <c r="W6" s="139"/>
-      <c r="X6" s="140" t="s">
-        <v>471</v>
-      </c>
-      <c r="Y6" s="140" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="7" spans="2:27" ht="16" x14ac:dyDescent="0.2">
-      <c r="B7" s="49"/>
-      <c r="D7" s="61"/>
-      <c r="E7" s="61"/>
-      <c r="F7" s="61"/>
-      <c r="G7" s="61"/>
-      <c r="H7" s="61"/>
-      <c r="J7" s="68" t="s">
-        <v>334</v>
-      </c>
-      <c r="K7" s="69" t="s">
-        <v>6</v>
-      </c>
-      <c r="L7" s="69" t="s">
-        <v>67</v>
-      </c>
-      <c r="M7" s="117" t="s">
-        <v>41</v>
-      </c>
-      <c r="N7" s="117" t="s">
-        <v>387</v>
-      </c>
-      <c r="T7" s="138"/>
-      <c r="U7" s="141" t="s">
-        <v>461</v>
-      </c>
-      <c r="V7" s="58" t="s">
-        <v>462</v>
-      </c>
-      <c r="W7" s="58" t="s">
-        <v>463</v>
-      </c>
-      <c r="X7" s="142"/>
-      <c r="Y7" s="142"/>
-    </row>
-    <row r="8" spans="2:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="49"/>
-      <c r="D8" s="61"/>
-      <c r="E8" s="61"/>
-      <c r="F8" s="61"/>
-      <c r="G8" s="61"/>
-      <c r="H8" s="61"/>
-      <c r="J8" s="68"/>
-      <c r="K8" s="69" t="s">
-        <v>16</v>
-      </c>
-      <c r="L8" s="69" t="s">
-        <v>30</v>
-      </c>
-      <c r="M8" s="117" t="s">
-        <v>383</v>
-      </c>
-      <c r="N8" s="117" t="s">
-        <v>88</v>
-      </c>
-      <c r="T8" s="143" t="s">
-        <v>407</v>
-      </c>
-      <c r="U8" s="140">
-        <v>-0.01</v>
-      </c>
-      <c r="V8" s="144">
-        <v>-2E-3</v>
-      </c>
-      <c r="W8" s="144">
-        <v>-8.9999999999999993E-3</v>
-      </c>
-      <c r="X8" s="140">
-        <v>-3.9E-2</v>
-      </c>
-      <c r="Y8" s="140">
-        <v>-8.9999999999999993E-3</v>
-      </c>
-    </row>
-    <row r="9" spans="2:27" ht="16" x14ac:dyDescent="0.2">
-      <c r="B9" s="49"/>
-      <c r="D9" s="61"/>
-      <c r="E9" s="61"/>
-      <c r="F9" s="61"/>
-      <c r="G9" s="61"/>
-      <c r="H9" s="61"/>
-      <c r="J9" s="68" t="s">
-        <v>405</v>
-      </c>
-      <c r="K9" s="69"/>
-      <c r="L9" s="69" t="s">
-        <v>76</v>
-      </c>
-      <c r="M9" s="117"/>
-      <c r="N9" s="117" t="s">
-        <v>384</v>
-      </c>
-      <c r="T9" s="145"/>
-      <c r="U9" s="146" t="s">
-        <v>465</v>
-      </c>
-      <c r="V9" s="147" t="s">
-        <v>466</v>
-      </c>
-      <c r="W9" s="147" t="s">
-        <v>466</v>
-      </c>
-      <c r="X9" s="146" t="s">
-        <v>222</v>
-      </c>
-      <c r="Y9" s="146" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="10" spans="2:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="49"/>
-      <c r="D10" s="61"/>
-      <c r="E10" s="61"/>
-      <c r="F10" s="61"/>
-      <c r="G10" s="61"/>
-      <c r="H10" s="61"/>
-      <c r="J10" s="68"/>
-      <c r="K10" s="69"/>
-      <c r="L10" s="69" t="s">
-        <v>26</v>
-      </c>
-      <c r="M10" s="117"/>
-      <c r="N10" s="117" t="s">
-        <v>16</v>
-      </c>
-      <c r="T10" s="148" t="s">
-        <v>338</v>
-      </c>
-      <c r="U10" s="140" t="s">
-        <v>336</v>
-      </c>
-      <c r="V10" s="140" t="s">
-        <v>336</v>
-      </c>
-      <c r="W10" s="140" t="s">
-        <v>336</v>
-      </c>
-      <c r="X10" s="140" t="s">
-        <v>336</v>
-      </c>
-      <c r="Y10" s="140" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="11" spans="2:27" ht="16" x14ac:dyDescent="0.2">
-      <c r="B11" s="49"/>
-      <c r="D11" s="61"/>
-      <c r="E11" s="61"/>
-      <c r="F11" s="61"/>
-      <c r="G11" s="61"/>
-      <c r="H11" s="61"/>
-      <c r="J11" s="68" t="s">
-        <v>406</v>
-      </c>
-      <c r="K11" s="69"/>
-      <c r="L11" s="69" t="s">
-        <v>80</v>
-      </c>
-      <c r="M11" s="117"/>
-      <c r="N11" s="117" t="s">
-        <v>385</v>
-      </c>
-      <c r="T11" s="149" t="s">
-        <v>423</v>
-      </c>
-      <c r="U11" s="141" t="s">
-        <v>336</v>
-      </c>
-      <c r="V11" s="141" t="s">
-        <v>336</v>
-      </c>
-      <c r="W11" s="141" t="s">
-        <v>336</v>
-      </c>
-      <c r="X11" s="141" t="s">
-        <v>336</v>
-      </c>
-      <c r="Y11" s="141" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="12" spans="2:27" ht="16" x14ac:dyDescent="0.2">
-      <c r="B12" s="49"/>
-      <c r="D12" s="61"/>
-      <c r="E12" s="61"/>
-      <c r="F12" s="61"/>
-      <c r="G12" s="61"/>
-      <c r="H12" s="61"/>
-      <c r="J12" s="70"/>
-      <c r="K12" s="71"/>
-      <c r="L12" s="71" t="s">
-        <v>85</v>
-      </c>
-      <c r="M12" s="118"/>
-      <c r="N12" s="118" t="s">
-        <v>99</v>
-      </c>
-      <c r="T12" s="149" t="s">
-        <v>339</v>
-      </c>
-      <c r="U12" s="150">
-        <v>3613</v>
-      </c>
-      <c r="V12" s="150">
-        <v>3613</v>
-      </c>
-      <c r="W12" s="150">
-        <v>3613</v>
-      </c>
-      <c r="X12" s="150">
-        <v>2748</v>
-      </c>
-      <c r="Y12" s="150">
-        <v>3613</v>
-      </c>
-    </row>
-    <row r="13" spans="2:27" ht="16" x14ac:dyDescent="0.2">
-      <c r="B13" s="49"/>
-      <c r="D13" s="61"/>
-      <c r="E13" s="61"/>
-      <c r="F13" s="61"/>
-      <c r="G13" s="61"/>
-      <c r="H13" s="61"/>
-      <c r="J13" s="72" t="s">
-        <v>335</v>
-      </c>
-      <c r="K13" s="69" t="s">
-        <v>336</v>
-      </c>
-      <c r="L13" s="69" t="s">
-        <v>336</v>
-      </c>
-      <c r="M13" s="117" t="s">
-        <v>336</v>
-      </c>
-      <c r="N13" s="117" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="14" spans="2:27" ht="16" x14ac:dyDescent="0.2">
-      <c r="B14" s="49"/>
-      <c r="D14" s="61"/>
-      <c r="E14" s="61"/>
-      <c r="F14" s="61"/>
-      <c r="G14" s="61"/>
-      <c r="H14" s="61"/>
-      <c r="J14" s="72" t="s">
-        <v>337</v>
-      </c>
-      <c r="K14" s="69" t="s">
-        <v>336</v>
-      </c>
-      <c r="L14" s="69" t="s">
-        <v>336</v>
-      </c>
-      <c r="M14" s="117" t="s">
-        <v>336</v>
-      </c>
-      <c r="N14" s="117" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="15" spans="2:27" ht="16" x14ac:dyDescent="0.2">
-      <c r="B15" s="49"/>
-      <c r="D15" s="61"/>
-      <c r="E15" s="61"/>
-      <c r="F15" s="61"/>
-      <c r="G15" s="61"/>
-      <c r="H15" s="61"/>
-      <c r="J15" s="72" t="s">
-        <v>338</v>
-      </c>
-      <c r="K15" s="69" t="s">
-        <v>336</v>
-      </c>
-      <c r="L15" s="69" t="s">
-        <v>336</v>
-      </c>
-      <c r="M15" s="117" t="s">
-        <v>336</v>
-      </c>
-      <c r="N15" s="117" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="16" spans="2:27" ht="16" x14ac:dyDescent="0.2">
-      <c r="B16" s="49"/>
-      <c r="J16" s="73" t="s">
-        <v>339</v>
-      </c>
-      <c r="K16" s="71" t="s">
-        <v>344</v>
-      </c>
-      <c r="L16" s="71" t="s">
-        <v>347</v>
-      </c>
-      <c r="M16" s="118" t="s">
-        <v>386</v>
-      </c>
-      <c r="N16" s="118" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="17" spans="2:35" ht="16" x14ac:dyDescent="0.2">
-      <c r="B17" s="49"/>
-    </row>
-    <row r="18" spans="2:35" ht="16" x14ac:dyDescent="0.2">
-      <c r="B18" s="49"/>
-    </row>
-    <row r="19" spans="2:35" ht="16" x14ac:dyDescent="0.2">
-      <c r="B19" s="49"/>
-    </row>
-    <row r="20" spans="2:35" ht="16" x14ac:dyDescent="0.2">
-      <c r="B20" s="49"/>
-    </row>
-    <row r="21" spans="2:35" ht="16" x14ac:dyDescent="0.2">
-      <c r="B21" s="49"/>
-    </row>
-    <row r="22" spans="2:35" ht="16" x14ac:dyDescent="0.2">
-      <c r="B22" s="49"/>
-    </row>
-    <row r="23" spans="2:35" ht="16" x14ac:dyDescent="0.2">
-      <c r="B23" s="49"/>
-    </row>
-    <row r="24" spans="2:35" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="153" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="25" spans="2:35" ht="16" x14ac:dyDescent="0.2">
-      <c r="B25" s="153"/>
-    </row>
-    <row r="26" spans="2:35" ht="16" x14ac:dyDescent="0.2">
-      <c r="B26" s="153"/>
-      <c r="N26" s="119" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="27" spans="2:35" ht="16" x14ac:dyDescent="0.2">
-      <c r="B27" s="153"/>
-      <c r="N27" s="120"/>
-      <c r="O27" s="114" t="s">
-        <v>340</v>
-      </c>
-      <c r="P27" s="114" t="s">
-        <v>341</v>
-      </c>
-      <c r="Q27" s="114" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="28" spans="2:35" s="47" customFormat="1" ht="42" x14ac:dyDescent="0.2">
-      <c r="B28" s="153"/>
-      <c r="C28" s="62"/>
-      <c r="D28" s="62"/>
-      <c r="E28" s="62"/>
-      <c r="F28" s="62"/>
-      <c r="G28" s="62"/>
-      <c r="H28" s="62"/>
-      <c r="I28" s="62"/>
-      <c r="J28" s="62"/>
-      <c r="K28" s="62"/>
-      <c r="L28" s="62"/>
-      <c r="M28" s="116"/>
-      <c r="N28" s="121" t="s">
-        <v>388</v>
-      </c>
-      <c r="O28" s="122" t="s">
-        <v>412</v>
-      </c>
-      <c r="P28" s="122" t="s">
-        <v>413</v>
-      </c>
-      <c r="Q28" s="123" t="s">
-        <v>414</v>
-      </c>
-      <c r="R28" s="116"/>
-      <c r="S28" s="55"/>
-      <c r="T28" s="55"/>
-      <c r="U28" s="55"/>
-      <c r="V28" s="55"/>
-      <c r="W28" s="55"/>
-      <c r="X28" s="55"/>
-      <c r="Y28" s="55"/>
-      <c r="Z28" s="55"/>
-      <c r="AA28" s="151"/>
-      <c r="AB28" s="51"/>
-      <c r="AC28" s="51"/>
-      <c r="AD28" s="51"/>
-      <c r="AE28" s="51"/>
-      <c r="AF28" s="51"/>
-      <c r="AG28" s="51"/>
-      <c r="AH28" s="51"/>
-      <c r="AI28" s="51"/>
-    </row>
-    <row r="29" spans="2:35" ht="16" x14ac:dyDescent="0.2">
-      <c r="B29" s="153"/>
-      <c r="N29" s="124" t="s">
-        <v>407</v>
-      </c>
-      <c r="O29" s="125" t="s">
-        <v>408</v>
-      </c>
-      <c r="P29" s="125" t="s">
-        <v>409</v>
-      </c>
-      <c r="Q29" s="125" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="30" spans="2:35" ht="16" x14ac:dyDescent="0.2">
-      <c r="B30" s="153"/>
-      <c r="N30" s="124"/>
-      <c r="O30" s="126" t="s">
-        <v>16</v>
-      </c>
-      <c r="P30" s="126" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q30" s="126" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="31" spans="2:35" ht="16" x14ac:dyDescent="0.2">
-      <c r="B31" s="153"/>
-      <c r="N31" s="127" t="s">
-        <v>338</v>
-      </c>
-      <c r="O31" s="125" t="s">
-        <v>336</v>
-      </c>
-      <c r="P31" s="125" t="s">
-        <v>336</v>
-      </c>
-      <c r="Q31" s="125" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="32" spans="2:35" ht="16" x14ac:dyDescent="0.2">
-      <c r="B32" s="153"/>
-      <c r="N32" s="127" t="s">
-        <v>411</v>
-      </c>
-      <c r="O32" s="125" t="s">
-        <v>336</v>
-      </c>
-      <c r="P32" s="125" t="s">
-        <v>336</v>
-      </c>
-      <c r="Q32" s="125" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="33" spans="2:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="B33" s="153"/>
-      <c r="N33" s="128" t="s">
-        <v>339</v>
-      </c>
-      <c r="O33" s="129">
-        <v>4634</v>
-      </c>
-      <c r="P33" s="129">
-        <v>4634</v>
-      </c>
-      <c r="Q33" s="129">
-        <v>4634</v>
-      </c>
-    </row>
-    <row r="34" spans="2:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="B34" s="153"/>
-    </row>
-    <row r="35" spans="2:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="B35" s="153"/>
-    </row>
-    <row r="36" spans="2:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="B36" s="153"/>
-    </row>
-    <row r="37" spans="2:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="B37" s="153"/>
-    </row>
-    <row r="38" spans="2:17" ht="17" x14ac:dyDescent="0.2">
-      <c r="B38" s="153"/>
-      <c r="L38" s="62" t="s">
-        <v>481</v>
-      </c>
-      <c r="M38" s="116" t="s">
-        <v>479</v>
-      </c>
-      <c r="N38" s="155" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="39" spans="2:17" ht="17" x14ac:dyDescent="0.2">
-      <c r="B39" s="153"/>
-      <c r="M39" s="116" t="s">
-        <v>480</v>
-      </c>
-      <c r="N39" s="116" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="40" spans="2:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="B40" s="153"/>
-    </row>
-    <row r="41" spans="2:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="B41" s="153"/>
-    </row>
-    <row r="42" spans="2:17" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B42" s="153" t="s">
-        <v>475</v>
-      </c>
-      <c r="D42" s="63" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="43" spans="2:17" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B43" s="153"/>
-      <c r="D43" s="74"/>
-      <c r="E43" s="74" t="s">
-        <v>415</v>
-      </c>
-      <c r="F43" s="74"/>
-      <c r="G43" s="75" t="s">
-        <v>416</v>
-      </c>
-      <c r="H43" s="75" t="s">
-        <v>417</v>
-      </c>
-      <c r="I43" s="75" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="44" spans="2:17" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B44" s="153"/>
-      <c r="D44" s="76"/>
-      <c r="E44" s="77" t="s">
-        <v>340</v>
-      </c>
-      <c r="F44" s="77" t="s">
-        <v>341</v>
-      </c>
-      <c r="G44" s="77" t="s">
-        <v>342</v>
-      </c>
-      <c r="H44" s="78" t="s">
-        <v>343</v>
-      </c>
-      <c r="I44" s="78" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="45" spans="2:17" ht="26" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B45" s="153"/>
-      <c r="D45" s="76"/>
-      <c r="E45" s="79" t="s">
-        <v>419</v>
-      </c>
-      <c r="F45" s="79"/>
-      <c r="G45" s="79" t="s">
-        <v>420</v>
-      </c>
-      <c r="H45" s="79"/>
-      <c r="I45" s="79"/>
-    </row>
-    <row r="46" spans="2:17" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B46" s="153"/>
-      <c r="D46" s="80" t="s">
-        <v>407</v>
-      </c>
-      <c r="E46" s="81" t="s">
-        <v>6</v>
-      </c>
-      <c r="F46" s="81" t="s">
-        <v>421</v>
-      </c>
-      <c r="G46" s="81" t="s">
-        <v>422</v>
-      </c>
-      <c r="H46" s="81" t="s">
-        <v>422</v>
-      </c>
-      <c r="I46" s="81" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="47" spans="2:17" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B47" s="153"/>
-      <c r="D47" s="80"/>
-      <c r="E47" s="82" t="s">
-        <v>16</v>
-      </c>
-      <c r="F47" s="82" t="s">
-        <v>213</v>
-      </c>
-      <c r="G47" s="82" t="s">
-        <v>467</v>
-      </c>
-      <c r="H47" s="82" t="s">
-        <v>469</v>
-      </c>
-      <c r="I47" s="82" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="48" spans="2:17" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B48" s="153"/>
-      <c r="D48" s="83" t="s">
-        <v>423</v>
-      </c>
-      <c r="E48" s="77" t="s">
-        <v>336</v>
-      </c>
-      <c r="F48" s="77" t="s">
-        <v>336</v>
-      </c>
-      <c r="G48" s="77" t="s">
-        <v>336</v>
-      </c>
-      <c r="H48" s="77" t="s">
-        <v>336</v>
-      </c>
-      <c r="I48" s="77" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="49" spans="2:11" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="153"/>
-      <c r="D49" s="83" t="s">
-        <v>338</v>
-      </c>
-      <c r="E49" s="77" t="s">
-        <v>336</v>
-      </c>
-      <c r="F49" s="77" t="s">
-        <v>336</v>
-      </c>
-      <c r="G49" s="77" t="s">
-        <v>336</v>
-      </c>
-      <c r="H49" s="77" t="s">
-        <v>336</v>
-      </c>
-      <c r="I49" s="77" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="50" spans="2:11" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B50" s="153"/>
-      <c r="D50" s="84" t="s">
-        <v>424</v>
-      </c>
-      <c r="E50" s="85"/>
-      <c r="F50" s="86" t="s">
-        <v>336</v>
-      </c>
-      <c r="G50" s="85"/>
-      <c r="H50" s="85"/>
-      <c r="I50" s="85"/>
-    </row>
-    <row r="51" spans="2:11" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B51" s="153"/>
-      <c r="D51" s="87" t="s">
-        <v>339</v>
-      </c>
-      <c r="E51" s="88">
-        <v>3613</v>
-      </c>
-      <c r="F51" s="88">
-        <v>3613</v>
-      </c>
-      <c r="G51" s="88">
-        <v>3613</v>
-      </c>
-      <c r="H51" s="88">
-        <v>3613</v>
-      </c>
-      <c r="I51" s="88">
-        <v>3613</v>
-      </c>
-    </row>
-    <row r="52" spans="2:11" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B52" s="153"/>
-      <c r="D52" s="87" t="s">
-        <v>425</v>
-      </c>
-      <c r="E52" s="89"/>
-      <c r="F52" s="81">
-        <v>2730.402</v>
-      </c>
-      <c r="G52" s="89"/>
-      <c r="H52" s="81">
-        <v>10115.514999999999</v>
-      </c>
-      <c r="I52" s="81">
-        <v>10117.514999999999</v>
-      </c>
-    </row>
-    <row r="53" spans="2:11" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B53" s="153"/>
-      <c r="D53" s="87" t="s">
-        <v>426</v>
-      </c>
-      <c r="E53" s="89"/>
-      <c r="F53" s="81">
-        <v>3900.7449999999999</v>
-      </c>
-      <c r="G53" s="89"/>
-      <c r="H53" s="89"/>
-      <c r="I53" s="89"/>
-    </row>
-    <row r="54" spans="2:11" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B54" s="153"/>
-      <c r="D54" s="87" t="s">
-        <v>427</v>
-      </c>
-      <c r="E54" s="89"/>
-      <c r="F54" s="81">
-        <v>-1176.201</v>
-      </c>
-      <c r="G54" s="81">
-        <v>-4869.7579999999998</v>
-      </c>
-      <c r="H54" s="81">
-        <v>-4869.7579999999998</v>
-      </c>
-      <c r="I54" s="81">
-        <v>-4869.7579999999998</v>
-      </c>
-    </row>
-    <row r="55" spans="2:11" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B55" s="153"/>
-      <c r="D55" s="87" t="s">
-        <v>428</v>
-      </c>
-      <c r="E55" s="89"/>
-      <c r="F55" s="89"/>
-      <c r="G55" s="81">
-        <v>3545.797</v>
-      </c>
-      <c r="H55" s="89"/>
-      <c r="I55" s="89"/>
-    </row>
-    <row r="56" spans="2:11" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B56" s="153"/>
-      <c r="D56" s="84" t="s">
-        <v>429</v>
-      </c>
-      <c r="E56" s="85"/>
-      <c r="F56" s="85"/>
-      <c r="G56" s="85">
-        <v>1.4E-2</v>
-      </c>
-      <c r="H56" s="85"/>
-      <c r="I56" s="85"/>
-    </row>
-    <row r="57" spans="2:11" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B57" s="153"/>
-      <c r="D57" s="87"/>
-      <c r="E57" s="81"/>
-      <c r="F57" s="81"/>
-      <c r="G57" s="81"/>
-      <c r="H57" s="81"/>
-      <c r="I57" s="81"/>
-    </row>
-    <row r="58" spans="2:11" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B58" s="153"/>
-      <c r="D58" s="87"/>
-      <c r="E58" s="81"/>
-      <c r="F58" s="81"/>
-      <c r="G58" s="81"/>
-      <c r="H58" s="81"/>
-      <c r="I58" s="81"/>
-    </row>
-    <row r="59" spans="2:11" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B59" s="153"/>
-    </row>
-    <row r="60" spans="2:11" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B60" s="153"/>
-      <c r="D60" s="90" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="61" spans="2:11" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B61" s="153"/>
-      <c r="D61" s="74"/>
-      <c r="E61" s="65" t="s">
-        <v>340</v>
-      </c>
-      <c r="F61" s="65" t="s">
-        <v>341</v>
-      </c>
-      <c r="G61" s="65" t="s">
-        <v>342</v>
-      </c>
-      <c r="H61" s="65" t="s">
-        <v>343</v>
-      </c>
-      <c r="I61" s="65" t="s">
-        <v>430</v>
-      </c>
-      <c r="J61" s="65" t="s">
-        <v>445</v>
-      </c>
-      <c r="K61" s="65" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="62" spans="2:11" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B62" s="153"/>
-      <c r="D62" s="76"/>
-      <c r="E62" s="91" t="s">
-        <v>434</v>
-      </c>
-      <c r="F62" s="91" t="s">
-        <v>435</v>
-      </c>
-      <c r="G62" s="91"/>
-      <c r="H62" s="91"/>
-      <c r="I62" s="91" t="s">
-        <v>436</v>
-      </c>
-      <c r="J62" s="91"/>
-      <c r="K62" s="91"/>
-    </row>
-    <row r="63" spans="2:11" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B63" s="153"/>
-      <c r="D63" s="76"/>
-      <c r="E63" s="79"/>
-      <c r="F63" s="92" t="s">
-        <v>437</v>
-      </c>
-      <c r="G63" s="92" t="s">
-        <v>438</v>
-      </c>
-      <c r="H63" s="92" t="s">
-        <v>439</v>
-      </c>
-      <c r="I63" s="93"/>
-      <c r="J63" s="93"/>
-      <c r="K63" s="93"/>
-    </row>
-    <row r="64" spans="2:11" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B64" s="153"/>
-      <c r="D64" s="80" t="s">
-        <v>407</v>
-      </c>
-      <c r="E64" s="81" t="s">
-        <v>440</v>
-      </c>
-      <c r="F64" s="81" t="s">
-        <v>441</v>
-      </c>
-      <c r="G64" s="81" t="s">
-        <v>6</v>
-      </c>
-      <c r="H64" s="81" t="s">
-        <v>442</v>
-      </c>
-      <c r="I64" s="81">
-        <v>-2.5999999999999999E-2</v>
-      </c>
-      <c r="J64" s="81" t="s">
-        <v>443</v>
-      </c>
-      <c r="K64" s="81" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="65" spans="2:13" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B65" s="153"/>
-      <c r="D65" s="94"/>
-      <c r="E65" s="71" t="s">
-        <v>29</v>
-      </c>
-      <c r="F65" s="71" t="s">
-        <v>16</v>
-      </c>
-      <c r="G65" s="71" t="s">
-        <v>16</v>
-      </c>
-      <c r="H65" s="71" t="s">
-        <v>16</v>
-      </c>
-      <c r="I65" s="71" t="s">
-        <v>298</v>
-      </c>
-      <c r="J65" s="71" t="s">
-        <v>28</v>
-      </c>
-      <c r="K65" s="71" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="66" spans="2:13" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B66" s="153"/>
-      <c r="D66" s="95" t="s">
-        <v>338</v>
-      </c>
-      <c r="E66" s="75" t="s">
-        <v>336</v>
-      </c>
-      <c r="F66" s="75" t="s">
-        <v>336</v>
-      </c>
-      <c r="G66" s="75" t="s">
-        <v>336</v>
-      </c>
-      <c r="H66" s="75" t="s">
-        <v>336</v>
-      </c>
-      <c r="I66" s="75" t="s">
-        <v>336</v>
-      </c>
-      <c r="J66" s="75" t="s">
-        <v>336</v>
-      </c>
-      <c r="K66" s="75" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="67" spans="2:13" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B67" s="153"/>
-      <c r="D67" s="96" t="s">
-        <v>423</v>
-      </c>
-      <c r="E67" s="85" t="s">
-        <v>336</v>
-      </c>
-      <c r="F67" s="85" t="s">
-        <v>336</v>
-      </c>
-      <c r="G67" s="85" t="s">
-        <v>336</v>
-      </c>
-      <c r="H67" s="85" t="s">
-        <v>336</v>
-      </c>
-      <c r="I67" s="85" t="s">
-        <v>336</v>
-      </c>
-      <c r="J67" s="85" t="s">
-        <v>336</v>
-      </c>
-      <c r="K67" s="85" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="68" spans="2:13" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B68" s="153"/>
-      <c r="D68" s="96" t="s">
-        <v>339</v>
-      </c>
-      <c r="E68" s="97">
-        <v>3613</v>
-      </c>
-      <c r="F68" s="97">
-        <v>3613</v>
-      </c>
-      <c r="G68" s="97">
-        <v>3613</v>
-      </c>
-      <c r="H68" s="97">
-        <v>3613</v>
-      </c>
-      <c r="I68" s="85">
-        <v>838</v>
-      </c>
-      <c r="J68" s="98">
-        <v>1607</v>
-      </c>
-      <c r="K68" s="98">
-        <v>2413</v>
-      </c>
-    </row>
-    <row r="69" spans="2:13" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B69" s="153"/>
-    </row>
-    <row r="70" spans="2:13" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B70" s="153"/>
-    </row>
-    <row r="71" spans="2:13" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B71" s="153"/>
-    </row>
-    <row r="72" spans="2:13" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B72" s="153"/>
-      <c r="K72" s="90" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="73" spans="2:13" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B73" s="153"/>
-      <c r="K73" s="99"/>
-      <c r="L73" s="65" t="s">
-        <v>340</v>
-      </c>
-      <c r="M73" s="114" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="74" spans="2:13" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B74" s="153"/>
-      <c r="K74" s="77"/>
-      <c r="L74" s="86" t="s">
-        <v>448</v>
-      </c>
-      <c r="M74" s="130" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="75" spans="2:13" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B75" s="153"/>
-      <c r="K75" s="100" t="s">
-        <v>450</v>
-      </c>
-      <c r="L75" s="77">
-        <v>-2.1999999999999999E-2</v>
-      </c>
-      <c r="M75" s="125">
-        <v>-1.6E-2</v>
-      </c>
-    </row>
-    <row r="76" spans="2:13" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B76" s="153"/>
-      <c r="K76" s="101"/>
-      <c r="L76" s="102" t="s">
-        <v>224</v>
-      </c>
-      <c r="M76" s="131" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="77" spans="2:13" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B77" s="153"/>
-      <c r="K77" s="83" t="s">
-        <v>451</v>
-      </c>
-      <c r="L77" s="77" t="s">
-        <v>336</v>
-      </c>
-      <c r="M77" s="125" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="78" spans="2:13" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B78" s="153"/>
-      <c r="K78" s="96" t="s">
-        <v>423</v>
-      </c>
-      <c r="L78" s="86" t="s">
-        <v>336</v>
-      </c>
-      <c r="M78" s="130" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="79" spans="2:13" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B79" s="153"/>
-      <c r="K79" s="96" t="s">
-        <v>339</v>
-      </c>
-      <c r="L79" s="97">
-        <v>5984</v>
-      </c>
-      <c r="M79" s="129">
-        <v>8961</v>
-      </c>
-    </row>
-    <row r="80" spans="2:13" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B80" s="153"/>
-    </row>
-    <row r="81" spans="2:15" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B81" s="153"/>
-    </row>
-    <row r="82" spans="2:15" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B82" s="153"/>
-    </row>
-    <row r="83" spans="2:15" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B83" s="153"/>
-      <c r="J83" s="90" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="84" spans="2:15" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B84" s="153"/>
-      <c r="J84" s="103"/>
-      <c r="K84" s="104" t="s">
-        <v>454</v>
-      </c>
-      <c r="L84" s="104" t="s">
-        <v>458</v>
-      </c>
-      <c r="M84" s="132" t="s">
-        <v>459</v>
-      </c>
-      <c r="N84" s="132" t="s">
-        <v>455</v>
-      </c>
-      <c r="O84" s="132" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="85" spans="2:15" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B85" s="153"/>
-      <c r="J85" s="105"/>
-      <c r="K85" s="106"/>
-      <c r="L85" s="106"/>
-      <c r="M85" s="133"/>
-      <c r="N85" s="133"/>
-      <c r="O85" s="133"/>
-    </row>
-    <row r="86" spans="2:15" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B86" s="153"/>
-      <c r="J86" s="107" t="s">
-        <v>457</v>
-      </c>
-      <c r="K86" s="108">
-        <v>-4.5999999999999999E-2</v>
-      </c>
-      <c r="L86" s="108">
-        <v>9.2999999999999999E-2</v>
-      </c>
-      <c r="M86" s="134">
-        <v>0.121</v>
-      </c>
-      <c r="N86" s="134">
-        <v>-4.4999999999999998E-2</v>
-      </c>
-      <c r="O86" s="134">
-        <v>39.719000000000001</v>
-      </c>
-    </row>
-    <row r="87" spans="2:15" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B87" s="153"/>
-      <c r="J87" s="109" t="s">
-        <v>449</v>
-      </c>
-      <c r="K87" s="110">
-        <v>-4.5999999999999999E-2</v>
-      </c>
-      <c r="L87" s="110">
-        <v>3.3000000000000002E-2</v>
-      </c>
-      <c r="M87" s="135">
-        <v>4.2999999999999997E-2</v>
-      </c>
-      <c r="N87" s="135">
-        <v>-4.3999999999999997E-2</v>
-      </c>
-      <c r="O87" s="135">
-        <v>26.744</v>
-      </c>
-    </row>
-    <row r="88" spans="2:15" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B88" s="153"/>
-    </row>
-    <row r="89" spans="2:15" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B89" s="153"/>
-    </row>
-  </sheetData>
-  <mergeCells count="32">
-    <mergeCell ref="B3:B23"/>
-    <mergeCell ref="B24:B41"/>
-    <mergeCell ref="B42:B89"/>
-    <mergeCell ref="S2:AA2"/>
-    <mergeCell ref="M84:M85"/>
-    <mergeCell ref="N84:N85"/>
-    <mergeCell ref="O84:O85"/>
-    <mergeCell ref="T6:T7"/>
-    <mergeCell ref="U6:W6"/>
-    <mergeCell ref="T8:T9"/>
-    <mergeCell ref="D64:D65"/>
-    <mergeCell ref="I62:K62"/>
-    <mergeCell ref="K75:K76"/>
-    <mergeCell ref="J84:J85"/>
-    <mergeCell ref="K84:K85"/>
-    <mergeCell ref="L84:L85"/>
-    <mergeCell ref="G45:I45"/>
-    <mergeCell ref="D46:D47"/>
-    <mergeCell ref="D61:D63"/>
-    <mergeCell ref="E62:E63"/>
-    <mergeCell ref="F62:H62"/>
-    <mergeCell ref="J11:J12"/>
-    <mergeCell ref="N29:N30"/>
-    <mergeCell ref="D43:D45"/>
-    <mergeCell ref="E43:F43"/>
-    <mergeCell ref="E45:F45"/>
-    <mergeCell ref="C2:L2"/>
-    <mergeCell ref="M2:R2"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="J9:J10"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{662C8392-57F3-DA44-A638-CAE1AE9DCA0E}">
-  <dimension ref="B1:D8"/>
+  <dimension ref="B2:D11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="26"/>
@@ -19455,96 +18819,2034 @@
     <col min="5" max="16384" width="10.83203125" style="26"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:4" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="2:4" ht="23" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="27" t="s">
+    <row r="2" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="C2" s="105" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="2:4" ht="23" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="27" t="s">
         <v>388</v>
       </c>
-      <c r="C2" s="27" t="s">
+      <c r="C5" s="27" t="s">
         <v>389</v>
       </c>
-      <c r="D2" s="27" t="s">
+      <c r="D5" s="27" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="3" spans="2:4" ht="22" x14ac:dyDescent="0.2">
-      <c r="B3" s="30" t="s">
+    <row r="6" spans="2:4" ht="22" x14ac:dyDescent="0.2">
+      <c r="B6" s="115" t="s">
         <v>391</v>
       </c>
-      <c r="C3" s="28" t="s">
+      <c r="C6" s="28" t="s">
         <v>392</v>
       </c>
-      <c r="D3" s="28" t="s">
+      <c r="D6" s="28" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="4" spans="2:4" ht="221" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="31"/>
-      <c r="C4" s="29" t="s">
-        <v>399</v>
-      </c>
-      <c r="D4" s="29" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="5" spans="2:4" ht="22" x14ac:dyDescent="0.2">
-      <c r="B5" s="30" t="s">
+    <row r="7" spans="2:4" ht="111" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="116"/>
+      <c r="C7" s="104" t="s">
+        <v>543</v>
+      </c>
+      <c r="D7" s="104" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" ht="22" x14ac:dyDescent="0.2">
+      <c r="B8" s="115" t="s">
         <v>394</v>
       </c>
-      <c r="C5" s="28" t="s">
-        <v>400</v>
-      </c>
-      <c r="D5" s="30" t="s">
+      <c r="C8" s="28" t="s">
+        <v>398</v>
+      </c>
+      <c r="D8" s="115" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="6" spans="2:4" ht="177" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="31"/>
-      <c r="C6" s="29" t="s">
-        <v>401</v>
-      </c>
-      <c r="D6" s="31"/>
-    </row>
-    <row r="7" spans="2:4" ht="22" x14ac:dyDescent="0.2">
-      <c r="B7" s="30" t="s">
+    <row r="9" spans="2:4" ht="89" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="116"/>
+      <c r="C9" s="104" t="s">
+        <v>542</v>
+      </c>
+      <c r="D9" s="116"/>
+    </row>
+    <row r="10" spans="2:4" ht="22" x14ac:dyDescent="0.2">
+      <c r="B10" s="115" t="s">
         <v>396</v>
       </c>
-      <c r="C7" s="30" t="s">
+      <c r="C10" s="115" t="s">
         <v>395</v>
       </c>
-      <c r="D7" s="28" t="s">
+      <c r="D10" s="28" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="8" spans="2:4" ht="155" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="31"/>
-      <c r="C8" s="31"/>
-      <c r="D8" s="29" t="s">
-        <v>398</v>
+    <row r="11" spans="2:4" ht="89" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="116"/>
+      <c r="C11" s="116"/>
+      <c r="D11" s="104" t="s">
+        <v>545</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8750E32-A59B-9548-9A1A-62B4C8E80AF6}">
+  <dimension ref="B2:F22"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="22" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10.83203125" style="97"/>
+    <col min="2" max="2" width="22.1640625" style="97" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="45" style="97" customWidth="1"/>
+    <col min="4" max="4" width="77" style="96" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="80.1640625" style="96" customWidth="1"/>
+    <col min="6" max="6" width="89.5" style="97" customWidth="1"/>
+    <col min="7" max="16384" width="10.83203125" style="97"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B2" s="120"/>
+      <c r="C2" s="120"/>
+      <c r="D2" s="103" t="s">
+        <v>389</v>
+      </c>
+      <c r="E2" s="103" t="s">
+        <v>390</v>
+      </c>
+      <c r="F2" s="103" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="3" spans="2:6" ht="46" x14ac:dyDescent="0.3">
+      <c r="B3" s="117" t="s">
+        <v>462</v>
+      </c>
+      <c r="C3" s="117"/>
+      <c r="D3" s="98" t="s">
+        <v>469</v>
+      </c>
+      <c r="E3" s="98" t="s">
+        <v>470</v>
+      </c>
+      <c r="F3" s="99"/>
+    </row>
+    <row r="4" spans="2:6" ht="46" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="119" t="s">
+        <v>466</v>
+      </c>
+      <c r="C4" s="99" t="s">
+        <v>467</v>
+      </c>
+      <c r="D4" s="100" t="s">
+        <v>481</v>
+      </c>
+      <c r="E4" s="100" t="s">
+        <v>482</v>
+      </c>
+      <c r="F4" s="99"/>
+    </row>
+    <row r="5" spans="2:6" ht="69" x14ac:dyDescent="0.3">
+      <c r="B5" s="119"/>
+      <c r="C5" s="99" t="s">
+        <v>468</v>
+      </c>
+      <c r="D5" s="98" t="s">
+        <v>471</v>
+      </c>
+      <c r="E5" s="100"/>
+      <c r="F5" s="99"/>
+    </row>
+    <row r="6" spans="2:6" ht="46" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="119"/>
+      <c r="C6" s="100" t="s">
+        <v>472</v>
+      </c>
+      <c r="D6" s="100"/>
+      <c r="E6" s="100" t="s">
+        <v>473</v>
+      </c>
+      <c r="F6" s="99"/>
+    </row>
+    <row r="7" spans="2:6" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="121" t="s">
+        <v>474</v>
+      </c>
+      <c r="C7" s="118" t="s">
+        <v>475</v>
+      </c>
+      <c r="D7" s="100"/>
+      <c r="E7" s="101" t="s">
+        <v>476</v>
+      </c>
+      <c r="F7" s="99"/>
+    </row>
+    <row r="8" spans="2:6" ht="23" x14ac:dyDescent="0.3">
+      <c r="B8" s="121"/>
+      <c r="C8" s="118"/>
+      <c r="D8" s="100"/>
+      <c r="E8" s="98" t="s">
+        <v>477</v>
+      </c>
+      <c r="F8" s="99"/>
+    </row>
+    <row r="9" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B9" s="121"/>
+      <c r="C9" s="99" t="s">
+        <v>478</v>
+      </c>
+      <c r="D9" s="100"/>
+      <c r="E9" s="100"/>
+      <c r="F9" s="99"/>
+    </row>
+    <row r="10" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B10" s="121"/>
+      <c r="C10" s="99" t="s">
+        <v>479</v>
+      </c>
+      <c r="D10" s="100"/>
+      <c r="E10" s="100"/>
+      <c r="F10" s="102" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B11" s="121"/>
+      <c r="C11" s="99" t="s">
+        <v>483</v>
+      </c>
+      <c r="D11" s="100"/>
+      <c r="E11" s="100"/>
+      <c r="F11" s="102" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B12" s="121"/>
+      <c r="C12" s="99"/>
+      <c r="D12" s="106" t="s">
+        <v>486</v>
+      </c>
+      <c r="E12" s="100"/>
+      <c r="F12" s="99"/>
+    </row>
+    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B13" s="121"/>
+      <c r="C13" s="99"/>
+      <c r="D13" s="100"/>
+      <c r="E13" s="106" t="s">
+        <v>487</v>
+      </c>
+      <c r="F13" s="99"/>
+    </row>
+    <row r="14" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B14" s="121"/>
+      <c r="C14" s="99"/>
+      <c r="D14" s="100"/>
+      <c r="E14" s="100"/>
+      <c r="F14" s="106" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B15" s="121"/>
+      <c r="C15" s="99"/>
+      <c r="D15" s="106" t="s">
+        <v>489</v>
+      </c>
+      <c r="E15" s="100"/>
+      <c r="F15" s="99"/>
+    </row>
+    <row r="22" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D22"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="B3:C3"/>
     <mergeCell ref="C7:C8"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B7:B15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06B7323D-B2F5-BD40-8E81-C2419FFBC224}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FD1D18A-C464-364C-95F7-F927C76322D3}">
+  <dimension ref="B2:AI89"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="22" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="21.83203125" style="96" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.6640625" style="39" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="21.6640625" style="39" customWidth="1"/>
+    <col min="6" max="7" width="18.83203125" style="39" customWidth="1"/>
+    <col min="8" max="9" width="21.6640625" style="39" customWidth="1"/>
+    <col min="10" max="12" width="18.83203125" style="39" customWidth="1"/>
+    <col min="13" max="13" width="22" style="75" customWidth="1"/>
+    <col min="14" max="14" width="24" style="75" customWidth="1"/>
+    <col min="15" max="16" width="21.6640625" style="75" customWidth="1"/>
+    <col min="17" max="18" width="18.83203125" style="75" customWidth="1"/>
+    <col min="19" max="19" width="10.83203125" style="32"/>
+    <col min="20" max="20" width="14.33203125" style="32" bestFit="1" customWidth="1"/>
+    <col min="21" max="26" width="10.83203125" style="32"/>
+    <col min="27" max="27" width="10.83203125" style="84"/>
+    <col min="28" max="35" width="10.83203125" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="B2" s="30" t="s">
+        <v>388</v>
+      </c>
+      <c r="C2" s="146" t="s">
+        <v>389</v>
+      </c>
+      <c r="D2" s="146"/>
+      <c r="E2" s="146"/>
+      <c r="F2" s="146"/>
+      <c r="G2" s="146"/>
+      <c r="H2" s="146"/>
+      <c r="I2" s="146"/>
+      <c r="J2" s="146"/>
+      <c r="K2" s="146"/>
+      <c r="L2" s="146"/>
+      <c r="M2" s="147" t="s">
+        <v>390</v>
+      </c>
+      <c r="N2" s="147"/>
+      <c r="O2" s="147"/>
+      <c r="P2" s="147"/>
+      <c r="Q2" s="147"/>
+      <c r="R2" s="147"/>
+      <c r="S2" s="129" t="s">
+        <v>461</v>
+      </c>
+      <c r="T2" s="129"/>
+      <c r="U2" s="129"/>
+      <c r="V2" s="129"/>
+      <c r="W2" s="129"/>
+      <c r="X2" s="129"/>
+      <c r="Y2" s="129"/>
+      <c r="Z2" s="129"/>
+      <c r="AA2" s="129"/>
+    </row>
+    <row r="3" spans="2:27" ht="21" x14ac:dyDescent="0.2">
+      <c r="B3" s="140" t="s">
+        <v>462</v>
+      </c>
+      <c r="C3" s="37"/>
+      <c r="D3" s="37"/>
+      <c r="E3" s="37"/>
+      <c r="F3" s="37"/>
+      <c r="G3" s="37"/>
+      <c r="H3" s="37"/>
+      <c r="I3" s="37"/>
+      <c r="J3" s="37"/>
+      <c r="K3" s="37"/>
+      <c r="L3" s="37"/>
+      <c r="M3" s="72"/>
+      <c r="N3" s="72"/>
+      <c r="O3" s="72"/>
+      <c r="P3" s="72"/>
+      <c r="Q3" s="72"/>
+      <c r="R3" s="72"/>
+    </row>
+    <row r="4" spans="2:27" ht="21" x14ac:dyDescent="0.2">
+      <c r="B4" s="141"/>
+      <c r="C4" s="37"/>
+      <c r="D4" s="38"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="38"/>
+      <c r="G4" s="38"/>
+      <c r="H4" s="38"/>
+      <c r="J4" s="40" t="s">
+        <v>421</v>
+      </c>
+      <c r="K4" s="38"/>
+      <c r="L4" s="38"/>
+      <c r="M4" s="73"/>
+      <c r="N4" s="73"/>
+      <c r="O4" s="72"/>
+      <c r="P4" s="72"/>
+      <c r="Q4" s="72"/>
+      <c r="R4" s="72"/>
+      <c r="T4" s="34" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="5" spans="2:27" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="141"/>
+      <c r="C5" s="37"/>
+      <c r="D5" s="38"/>
+      <c r="E5" s="38"/>
+      <c r="F5" s="38"/>
+      <c r="G5" s="38"/>
+      <c r="H5" s="38"/>
+      <c r="J5" s="41"/>
+      <c r="K5" s="42" t="s">
+        <v>340</v>
+      </c>
+      <c r="L5" s="42" t="s">
+        <v>341</v>
+      </c>
+      <c r="M5" s="74" t="s">
+        <v>342</v>
+      </c>
+      <c r="N5" s="74" t="s">
+        <v>343</v>
+      </c>
+      <c r="O5" s="72"/>
+      <c r="P5" s="72"/>
+      <c r="Q5" s="72"/>
+      <c r="R5" s="72"/>
+      <c r="T5" s="85"/>
+      <c r="U5" s="35" t="s">
+        <v>340</v>
+      </c>
+      <c r="V5" s="35" t="s">
+        <v>341</v>
+      </c>
+      <c r="W5" s="35" t="s">
+        <v>342</v>
+      </c>
+      <c r="X5" s="35" t="s">
+        <v>343</v>
+      </c>
+      <c r="Y5" s="35" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="6" spans="2:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B6" s="141"/>
+      <c r="D6" s="38"/>
+      <c r="E6" s="38"/>
+      <c r="F6" s="38"/>
+      <c r="G6" s="38"/>
+      <c r="H6" s="38"/>
+      <c r="J6" s="43" t="s">
+        <v>388</v>
+      </c>
+      <c r="K6" s="148" t="s">
+        <v>399</v>
+      </c>
+      <c r="L6" s="148"/>
+      <c r="M6" s="149" t="s">
+        <v>400</v>
+      </c>
+      <c r="N6" s="149"/>
+      <c r="T6" s="132" t="s">
+        <v>345</v>
+      </c>
+      <c r="U6" s="133" t="s">
+        <v>458</v>
+      </c>
+      <c r="V6" s="133"/>
+      <c r="W6" s="133"/>
+      <c r="X6" s="86" t="s">
+        <v>459</v>
+      </c>
+      <c r="Y6" s="86" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="7" spans="2:27" ht="16" x14ac:dyDescent="0.2">
+      <c r="B7" s="141"/>
+      <c r="D7" s="38"/>
+      <c r="E7" s="38"/>
+      <c r="F7" s="38"/>
+      <c r="G7" s="38"/>
+      <c r="H7" s="38"/>
+      <c r="J7" s="144" t="s">
+        <v>334</v>
+      </c>
+      <c r="K7" s="44" t="s">
+        <v>6</v>
+      </c>
+      <c r="L7" s="44" t="s">
+        <v>67</v>
+      </c>
+      <c r="M7" s="76" t="s">
+        <v>41</v>
+      </c>
+      <c r="N7" s="76" t="s">
+        <v>387</v>
+      </c>
+      <c r="T7" s="132"/>
+      <c r="U7" s="87" t="s">
+        <v>449</v>
+      </c>
+      <c r="V7" s="36" t="s">
+        <v>450</v>
+      </c>
+      <c r="W7" s="36" t="s">
+        <v>451</v>
+      </c>
+      <c r="X7" s="88"/>
+      <c r="Y7" s="88"/>
+    </row>
+    <row r="8" spans="2:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B8" s="141"/>
+      <c r="D8" s="38"/>
+      <c r="E8" s="38"/>
+      <c r="F8" s="38"/>
+      <c r="G8" s="38"/>
+      <c r="H8" s="38"/>
+      <c r="J8" s="144"/>
+      <c r="K8" s="44" t="s">
+        <v>16</v>
+      </c>
+      <c r="L8" s="44" t="s">
+        <v>30</v>
+      </c>
+      <c r="M8" s="76" t="s">
+        <v>383</v>
+      </c>
+      <c r="N8" s="76" t="s">
+        <v>88</v>
+      </c>
+      <c r="T8" s="134" t="s">
+        <v>403</v>
+      </c>
+      <c r="U8" s="86">
+        <v>-0.01</v>
+      </c>
+      <c r="V8" s="89">
+        <v>-2E-3</v>
+      </c>
+      <c r="W8" s="89">
+        <v>-8.9999999999999993E-3</v>
+      </c>
+      <c r="X8" s="86">
+        <v>-3.9E-2</v>
+      </c>
+      <c r="Y8" s="86">
+        <v>-8.9999999999999993E-3</v>
+      </c>
+    </row>
+    <row r="9" spans="2:27" ht="16" x14ac:dyDescent="0.2">
+      <c r="B9" s="141"/>
+      <c r="D9" s="38"/>
+      <c r="E9" s="38"/>
+      <c r="F9" s="38"/>
+      <c r="G9" s="38"/>
+      <c r="H9" s="38"/>
+      <c r="J9" s="144" t="s">
+        <v>401</v>
+      </c>
+      <c r="K9" s="44"/>
+      <c r="L9" s="44" t="s">
+        <v>76</v>
+      </c>
+      <c r="M9" s="76"/>
+      <c r="N9" s="76" t="s">
+        <v>384</v>
+      </c>
+      <c r="T9" s="135"/>
+      <c r="U9" s="90" t="s">
+        <v>453</v>
+      </c>
+      <c r="V9" s="91" t="s">
+        <v>454</v>
+      </c>
+      <c r="W9" s="91" t="s">
+        <v>454</v>
+      </c>
+      <c r="X9" s="90" t="s">
+        <v>222</v>
+      </c>
+      <c r="Y9" s="90" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="2:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="141"/>
+      <c r="D10" s="38"/>
+      <c r="E10" s="38"/>
+      <c r="F10" s="38"/>
+      <c r="G10" s="38"/>
+      <c r="H10" s="38"/>
+      <c r="J10" s="144"/>
+      <c r="K10" s="44"/>
+      <c r="L10" s="44" t="s">
+        <v>26</v>
+      </c>
+      <c r="M10" s="76"/>
+      <c r="N10" s="76" t="s">
+        <v>16</v>
+      </c>
+      <c r="T10" s="92" t="s">
+        <v>338</v>
+      </c>
+      <c r="U10" s="86" t="s">
+        <v>336</v>
+      </c>
+      <c r="V10" s="86" t="s">
+        <v>336</v>
+      </c>
+      <c r="W10" s="86" t="s">
+        <v>336</v>
+      </c>
+      <c r="X10" s="86" t="s">
+        <v>336</v>
+      </c>
+      <c r="Y10" s="86" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="11" spans="2:27" ht="16" x14ac:dyDescent="0.2">
+      <c r="B11" s="141"/>
+      <c r="D11" s="38"/>
+      <c r="E11" s="38"/>
+      <c r="F11" s="38"/>
+      <c r="G11" s="38"/>
+      <c r="H11" s="38"/>
+      <c r="J11" s="144" t="s">
+        <v>402</v>
+      </c>
+      <c r="K11" s="44"/>
+      <c r="L11" s="44" t="s">
+        <v>80</v>
+      </c>
+      <c r="M11" s="76"/>
+      <c r="N11" s="76" t="s">
+        <v>385</v>
+      </c>
+      <c r="T11" s="93" t="s">
+        <v>412</v>
+      </c>
+      <c r="U11" s="87" t="s">
+        <v>336</v>
+      </c>
+      <c r="V11" s="87" t="s">
+        <v>336</v>
+      </c>
+      <c r="W11" s="87" t="s">
+        <v>336</v>
+      </c>
+      <c r="X11" s="87" t="s">
+        <v>336</v>
+      </c>
+      <c r="Y11" s="87" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="12" spans="2:27" ht="16" x14ac:dyDescent="0.2">
+      <c r="B12" s="141"/>
+      <c r="D12" s="38"/>
+      <c r="E12" s="38"/>
+      <c r="F12" s="38"/>
+      <c r="G12" s="38"/>
+      <c r="H12" s="38"/>
+      <c r="J12" s="145"/>
+      <c r="K12" s="45"/>
+      <c r="L12" s="45" t="s">
+        <v>85</v>
+      </c>
+      <c r="M12" s="77"/>
+      <c r="N12" s="77" t="s">
+        <v>99</v>
+      </c>
+      <c r="T12" s="93" t="s">
+        <v>339</v>
+      </c>
+      <c r="U12" s="94">
+        <v>3613</v>
+      </c>
+      <c r="V12" s="94">
+        <v>3613</v>
+      </c>
+      <c r="W12" s="94">
+        <v>3613</v>
+      </c>
+      <c r="X12" s="94">
+        <v>2748</v>
+      </c>
+      <c r="Y12" s="94">
+        <v>3613</v>
+      </c>
+    </row>
+    <row r="13" spans="2:27" ht="16" x14ac:dyDescent="0.2">
+      <c r="B13" s="141"/>
+      <c r="D13" s="38"/>
+      <c r="E13" s="38"/>
+      <c r="F13" s="38"/>
+      <c r="G13" s="38"/>
+      <c r="H13" s="38"/>
+      <c r="J13" s="46" t="s">
+        <v>335</v>
+      </c>
+      <c r="K13" s="44" t="s">
+        <v>336</v>
+      </c>
+      <c r="L13" s="44" t="s">
+        <v>336</v>
+      </c>
+      <c r="M13" s="76" t="s">
+        <v>336</v>
+      </c>
+      <c r="N13" s="76" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="14" spans="2:27" ht="16" x14ac:dyDescent="0.2">
+      <c r="B14" s="141"/>
+      <c r="D14" s="38"/>
+      <c r="E14" s="38"/>
+      <c r="F14" s="38"/>
+      <c r="G14" s="38"/>
+      <c r="H14" s="38"/>
+      <c r="J14" s="46" t="s">
+        <v>337</v>
+      </c>
+      <c r="K14" s="44" t="s">
+        <v>336</v>
+      </c>
+      <c r="L14" s="44" t="s">
+        <v>336</v>
+      </c>
+      <c r="M14" s="76" t="s">
+        <v>336</v>
+      </c>
+      <c r="N14" s="76" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="15" spans="2:27" ht="16" x14ac:dyDescent="0.2">
+      <c r="B15" s="141"/>
+      <c r="D15" s="38"/>
+      <c r="E15" s="38"/>
+      <c r="F15" s="38"/>
+      <c r="G15" s="38"/>
+      <c r="H15" s="38"/>
+      <c r="J15" s="46" t="s">
+        <v>338</v>
+      </c>
+      <c r="K15" s="44" t="s">
+        <v>336</v>
+      </c>
+      <c r="L15" s="44" t="s">
+        <v>336</v>
+      </c>
+      <c r="M15" s="76" t="s">
+        <v>336</v>
+      </c>
+      <c r="N15" s="76" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="16" spans="2:27" ht="16" x14ac:dyDescent="0.2">
+      <c r="B16" s="141"/>
+      <c r="J16" s="47" t="s">
+        <v>339</v>
+      </c>
+      <c r="K16" s="45" t="s">
+        <v>344</v>
+      </c>
+      <c r="L16" s="45" t="s">
+        <v>347</v>
+      </c>
+      <c r="M16" s="77" t="s">
+        <v>386</v>
+      </c>
+      <c r="N16" s="77" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="17" spans="2:35" ht="16" x14ac:dyDescent="0.2">
+      <c r="B17" s="141"/>
+    </row>
+    <row r="18" spans="2:35" ht="16" x14ac:dyDescent="0.2">
+      <c r="B18" s="141"/>
+    </row>
+    <row r="19" spans="2:35" ht="16" x14ac:dyDescent="0.2">
+      <c r="B19" s="141"/>
+    </row>
+    <row r="20" spans="2:35" ht="16" x14ac:dyDescent="0.2">
+      <c r="B20" s="141"/>
+    </row>
+    <row r="21" spans="2:35" ht="16" x14ac:dyDescent="0.2">
+      <c r="B21" s="141"/>
+    </row>
+    <row r="22" spans="2:35" ht="16" x14ac:dyDescent="0.2">
+      <c r="B22" s="141"/>
+    </row>
+    <row r="23" spans="2:35" ht="16" x14ac:dyDescent="0.2">
+      <c r="B23" s="141"/>
+    </row>
+    <row r="24" spans="2:35" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B24" s="142" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="25" spans="2:35" ht="16" x14ac:dyDescent="0.2">
+      <c r="B25" s="142"/>
+    </row>
+    <row r="26" spans="2:35" ht="16" x14ac:dyDescent="0.2">
+      <c r="B26" s="142"/>
+    </row>
+    <row r="27" spans="2:35" ht="16" x14ac:dyDescent="0.2">
+      <c r="B27" s="142"/>
+      <c r="N27" s="73"/>
+    </row>
+    <row r="28" spans="2:35" s="26" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="B28" s="142"/>
+      <c r="C28" s="39"/>
+      <c r="D28" s="39"/>
+      <c r="E28" s="39"/>
+      <c r="F28" s="39"/>
+      <c r="G28" s="39"/>
+      <c r="H28" s="39"/>
+      <c r="I28" s="39"/>
+      <c r="J28" s="39"/>
+      <c r="K28" s="39"/>
+      <c r="L28" s="39"/>
+      <c r="M28" s="75"/>
+      <c r="N28" s="75"/>
+      <c r="O28" s="75"/>
+      <c r="P28" s="75"/>
+      <c r="Q28" s="75"/>
+      <c r="R28" s="75"/>
+      <c r="S28" s="33"/>
+      <c r="T28" s="33"/>
+      <c r="U28" s="33"/>
+      <c r="V28" s="33"/>
+      <c r="W28" s="33"/>
+      <c r="X28" s="33"/>
+      <c r="Y28" s="33"/>
+      <c r="Z28" s="33"/>
+      <c r="AA28" s="95"/>
+      <c r="AB28" s="31"/>
+      <c r="AC28" s="31"/>
+      <c r="AD28" s="31"/>
+      <c r="AE28" s="31"/>
+      <c r="AF28" s="31"/>
+      <c r="AG28" s="31"/>
+      <c r="AH28" s="31"/>
+      <c r="AI28" s="31"/>
+    </row>
+    <row r="29" spans="2:35" ht="16" x14ac:dyDescent="0.2">
+      <c r="B29" s="142"/>
+    </row>
+    <row r="30" spans="2:35" ht="16" x14ac:dyDescent="0.2">
+      <c r="B30" s="142"/>
+    </row>
+    <row r="31" spans="2:35" ht="16" x14ac:dyDescent="0.2">
+      <c r="B31" s="142"/>
+    </row>
+    <row r="32" spans="2:35" ht="16" x14ac:dyDescent="0.2">
+      <c r="B32" s="142"/>
+    </row>
+    <row r="33" spans="2:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="B33" s="142"/>
+    </row>
+    <row r="34" spans="2:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="B34" s="142"/>
+    </row>
+    <row r="35" spans="2:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="B35" s="142"/>
+    </row>
+    <row r="36" spans="2:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="B36" s="142"/>
+    </row>
+    <row r="37" spans="2:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="B37" s="142"/>
+    </row>
+    <row r="38" spans="2:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="B38" s="142"/>
+      <c r="N38" s="73"/>
+    </row>
+    <row r="39" spans="2:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="B39" s="142"/>
+    </row>
+    <row r="40" spans="2:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="B40" s="142"/>
+    </row>
+    <row r="41" spans="2:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="B41" s="142"/>
+    </row>
+    <row r="42" spans="2:14" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B42" s="142" t="s">
+        <v>463</v>
+      </c>
+      <c r="D42" s="40" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="43" spans="2:14" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B43" s="142"/>
+      <c r="D43" s="137"/>
+      <c r="E43" s="137" t="s">
+        <v>404</v>
+      </c>
+      <c r="F43" s="137"/>
+      <c r="G43" s="48" t="s">
+        <v>405</v>
+      </c>
+      <c r="H43" s="48" t="s">
+        <v>406</v>
+      </c>
+      <c r="I43" s="48" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="44" spans="2:14" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B44" s="142"/>
+      <c r="D44" s="138"/>
+      <c r="E44" s="50" t="s">
+        <v>340</v>
+      </c>
+      <c r="F44" s="50" t="s">
+        <v>341</v>
+      </c>
+      <c r="G44" s="50" t="s">
+        <v>342</v>
+      </c>
+      <c r="H44" s="51" t="s">
+        <v>343</v>
+      </c>
+      <c r="I44" s="51" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="45" spans="2:14" ht="26" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B45" s="142"/>
+      <c r="D45" s="138"/>
+      <c r="E45" s="139" t="s">
+        <v>408</v>
+      </c>
+      <c r="F45" s="139"/>
+      <c r="G45" s="139" t="s">
+        <v>409</v>
+      </c>
+      <c r="H45" s="139"/>
+      <c r="I45" s="139"/>
+    </row>
+    <row r="46" spans="2:14" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B46" s="142"/>
+      <c r="D46" s="136" t="s">
+        <v>403</v>
+      </c>
+      <c r="E46" s="49" t="s">
+        <v>6</v>
+      </c>
+      <c r="F46" s="49" t="s">
+        <v>410</v>
+      </c>
+      <c r="G46" s="49" t="s">
+        <v>411</v>
+      </c>
+      <c r="H46" s="49" t="s">
+        <v>411</v>
+      </c>
+      <c r="I46" s="49" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="47" spans="2:14" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B47" s="142"/>
+      <c r="D47" s="136"/>
+      <c r="E47" s="44" t="s">
+        <v>16</v>
+      </c>
+      <c r="F47" s="44" t="s">
+        <v>213</v>
+      </c>
+      <c r="G47" s="44" t="s">
+        <v>455</v>
+      </c>
+      <c r="H47" s="44" t="s">
+        <v>457</v>
+      </c>
+      <c r="I47" s="44" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="48" spans="2:14" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B48" s="142"/>
+      <c r="D48" s="53" t="s">
+        <v>412</v>
+      </c>
+      <c r="E48" s="50" t="s">
+        <v>336</v>
+      </c>
+      <c r="F48" s="50" t="s">
+        <v>336</v>
+      </c>
+      <c r="G48" s="50" t="s">
+        <v>336</v>
+      </c>
+      <c r="H48" s="50" t="s">
+        <v>336</v>
+      </c>
+      <c r="I48" s="50" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="49" spans="2:11" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B49" s="142"/>
+      <c r="D49" s="53" t="s">
+        <v>338</v>
+      </c>
+      <c r="E49" s="50" t="s">
+        <v>336</v>
+      </c>
+      <c r="F49" s="50" t="s">
+        <v>336</v>
+      </c>
+      <c r="G49" s="50" t="s">
+        <v>336</v>
+      </c>
+      <c r="H49" s="50" t="s">
+        <v>336</v>
+      </c>
+      <c r="I49" s="50" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="50" spans="2:11" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B50" s="142"/>
+      <c r="D50" s="54" t="s">
+        <v>413</v>
+      </c>
+      <c r="E50" s="55"/>
+      <c r="F50" s="56" t="s">
+        <v>336</v>
+      </c>
+      <c r="G50" s="55"/>
+      <c r="H50" s="55"/>
+      <c r="I50" s="55"/>
+    </row>
+    <row r="51" spans="2:11" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B51" s="142"/>
+      <c r="D51" s="57" t="s">
+        <v>339</v>
+      </c>
+      <c r="E51" s="58">
+        <v>3613</v>
+      </c>
+      <c r="F51" s="58">
+        <v>3613</v>
+      </c>
+      <c r="G51" s="58">
+        <v>3613</v>
+      </c>
+      <c r="H51" s="58">
+        <v>3613</v>
+      </c>
+      <c r="I51" s="58">
+        <v>3613</v>
+      </c>
+    </row>
+    <row r="52" spans="2:11" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B52" s="142"/>
+      <c r="D52" s="57" t="s">
+        <v>414</v>
+      </c>
+      <c r="E52" s="59"/>
+      <c r="F52" s="49">
+        <v>2730.402</v>
+      </c>
+      <c r="G52" s="59"/>
+      <c r="H52" s="49">
+        <v>10115.514999999999</v>
+      </c>
+      <c r="I52" s="49">
+        <v>10117.514999999999</v>
+      </c>
+    </row>
+    <row r="53" spans="2:11" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B53" s="142"/>
+      <c r="D53" s="57" t="s">
+        <v>415</v>
+      </c>
+      <c r="E53" s="59"/>
+      <c r="F53" s="49">
+        <v>3900.7449999999999</v>
+      </c>
+      <c r="G53" s="59"/>
+      <c r="H53" s="59"/>
+      <c r="I53" s="59"/>
+    </row>
+    <row r="54" spans="2:11" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B54" s="142"/>
+      <c r="D54" s="57" t="s">
+        <v>416</v>
+      </c>
+      <c r="E54" s="59"/>
+      <c r="F54" s="49">
+        <v>-1176.201</v>
+      </c>
+      <c r="G54" s="49">
+        <v>-4869.7579999999998</v>
+      </c>
+      <c r="H54" s="49">
+        <v>-4869.7579999999998</v>
+      </c>
+      <c r="I54" s="49">
+        <v>-4869.7579999999998</v>
+      </c>
+    </row>
+    <row r="55" spans="2:11" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B55" s="142"/>
+      <c r="D55" s="57" t="s">
+        <v>417</v>
+      </c>
+      <c r="E55" s="59"/>
+      <c r="F55" s="59"/>
+      <c r="G55" s="49">
+        <v>3545.797</v>
+      </c>
+      <c r="H55" s="59"/>
+      <c r="I55" s="59"/>
+    </row>
+    <row r="56" spans="2:11" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B56" s="142"/>
+      <c r="D56" s="54" t="s">
+        <v>418</v>
+      </c>
+      <c r="E56" s="55"/>
+      <c r="F56" s="55"/>
+      <c r="G56" s="55">
+        <v>1.4E-2</v>
+      </c>
+      <c r="H56" s="55"/>
+      <c r="I56" s="55"/>
+    </row>
+    <row r="57" spans="2:11" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B57" s="142"/>
+      <c r="D57" s="57"/>
+      <c r="E57" s="49"/>
+      <c r="F57" s="49"/>
+      <c r="G57" s="49"/>
+      <c r="H57" s="49"/>
+      <c r="I57" s="49"/>
+    </row>
+    <row r="58" spans="2:11" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B58" s="142"/>
+      <c r="D58" s="57"/>
+      <c r="E58" s="49"/>
+      <c r="F58" s="49"/>
+      <c r="G58" s="49"/>
+      <c r="H58" s="49"/>
+      <c r="I58" s="49"/>
+    </row>
+    <row r="59" spans="2:11" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B59" s="142"/>
+    </row>
+    <row r="60" spans="2:11" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B60" s="142"/>
+      <c r="D60" s="60" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="61" spans="2:11" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B61" s="142"/>
+      <c r="D61" s="137"/>
+      <c r="E61" s="42" t="s">
+        <v>340</v>
+      </c>
+      <c r="F61" s="42" t="s">
+        <v>341</v>
+      </c>
+      <c r="G61" s="42" t="s">
+        <v>342</v>
+      </c>
+      <c r="H61" s="42" t="s">
+        <v>343</v>
+      </c>
+      <c r="I61" s="42" t="s">
+        <v>419</v>
+      </c>
+      <c r="J61" s="42" t="s">
+        <v>433</v>
+      </c>
+      <c r="K61" s="42" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="62" spans="2:11" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B62" s="142"/>
+      <c r="D62" s="138"/>
+      <c r="E62" s="122" t="s">
+        <v>422</v>
+      </c>
+      <c r="F62" s="122" t="s">
+        <v>423</v>
+      </c>
+      <c r="G62" s="122"/>
+      <c r="H62" s="122"/>
+      <c r="I62" s="122" t="s">
+        <v>424</v>
+      </c>
+      <c r="J62" s="122"/>
+      <c r="K62" s="122"/>
+    </row>
+    <row r="63" spans="2:11" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B63" s="142"/>
+      <c r="D63" s="138"/>
+      <c r="E63" s="139"/>
+      <c r="F63" s="52" t="s">
+        <v>425</v>
+      </c>
+      <c r="G63" s="52" t="s">
+        <v>426</v>
+      </c>
+      <c r="H63" s="52" t="s">
+        <v>427</v>
+      </c>
+      <c r="I63" s="61"/>
+      <c r="J63" s="61"/>
+      <c r="K63" s="61"/>
+    </row>
+    <row r="64" spans="2:11" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B64" s="142"/>
+      <c r="D64" s="136" t="s">
+        <v>403</v>
+      </c>
+      <c r="E64" s="49" t="s">
+        <v>428</v>
+      </c>
+      <c r="F64" s="49" t="s">
+        <v>429</v>
+      </c>
+      <c r="G64" s="49" t="s">
+        <v>6</v>
+      </c>
+      <c r="H64" s="49" t="s">
+        <v>430</v>
+      </c>
+      <c r="I64" s="49">
+        <v>-2.5999999999999999E-2</v>
+      </c>
+      <c r="J64" s="49" t="s">
+        <v>431</v>
+      </c>
+      <c r="K64" s="49" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="65" spans="2:13" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B65" s="142"/>
+      <c r="D65" s="143"/>
+      <c r="E65" s="45" t="s">
+        <v>29</v>
+      </c>
+      <c r="F65" s="45" t="s">
+        <v>16</v>
+      </c>
+      <c r="G65" s="45" t="s">
+        <v>16</v>
+      </c>
+      <c r="H65" s="45" t="s">
+        <v>16</v>
+      </c>
+      <c r="I65" s="45" t="s">
+        <v>298</v>
+      </c>
+      <c r="J65" s="45" t="s">
+        <v>28</v>
+      </c>
+      <c r="K65" s="45" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="66" spans="2:13" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B66" s="142"/>
+      <c r="D66" s="62" t="s">
+        <v>338</v>
+      </c>
+      <c r="E66" s="48" t="s">
+        <v>336</v>
+      </c>
+      <c r="F66" s="48" t="s">
+        <v>336</v>
+      </c>
+      <c r="G66" s="48" t="s">
+        <v>336</v>
+      </c>
+      <c r="H66" s="48" t="s">
+        <v>336</v>
+      </c>
+      <c r="I66" s="48" t="s">
+        <v>336</v>
+      </c>
+      <c r="J66" s="48" t="s">
+        <v>336</v>
+      </c>
+      <c r="K66" s="48" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="67" spans="2:13" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B67" s="142"/>
+      <c r="D67" s="63" t="s">
+        <v>412</v>
+      </c>
+      <c r="E67" s="55" t="s">
+        <v>336</v>
+      </c>
+      <c r="F67" s="55" t="s">
+        <v>336</v>
+      </c>
+      <c r="G67" s="55" t="s">
+        <v>336</v>
+      </c>
+      <c r="H67" s="55" t="s">
+        <v>336</v>
+      </c>
+      <c r="I67" s="55" t="s">
+        <v>336</v>
+      </c>
+      <c r="J67" s="55" t="s">
+        <v>336</v>
+      </c>
+      <c r="K67" s="55" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="68" spans="2:13" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B68" s="142"/>
+      <c r="D68" s="63" t="s">
+        <v>339</v>
+      </c>
+      <c r="E68" s="64">
+        <v>3613</v>
+      </c>
+      <c r="F68" s="64">
+        <v>3613</v>
+      </c>
+      <c r="G68" s="64">
+        <v>3613</v>
+      </c>
+      <c r="H68" s="64">
+        <v>3613</v>
+      </c>
+      <c r="I68" s="55">
+        <v>838</v>
+      </c>
+      <c r="J68" s="65">
+        <v>1607</v>
+      </c>
+      <c r="K68" s="65">
+        <v>2413</v>
+      </c>
+    </row>
+    <row r="69" spans="2:13" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B69" s="142"/>
+    </row>
+    <row r="70" spans="2:13" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B70" s="142"/>
+    </row>
+    <row r="71" spans="2:13" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B71" s="142"/>
+    </row>
+    <row r="72" spans="2:13" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B72" s="142"/>
+      <c r="K72" s="60" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="73" spans="2:13" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B73" s="142"/>
+      <c r="K73" s="66"/>
+      <c r="L73" s="42" t="s">
+        <v>340</v>
+      </c>
+      <c r="M73" s="74" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="74" spans="2:13" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B74" s="142"/>
+      <c r="K74" s="50"/>
+      <c r="L74" s="56" t="s">
+        <v>436</v>
+      </c>
+      <c r="M74" s="80" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="75" spans="2:13" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B75" s="142"/>
+      <c r="K75" s="123" t="s">
+        <v>438</v>
+      </c>
+      <c r="L75" s="50">
+        <v>-2.1999999999999999E-2</v>
+      </c>
+      <c r="M75" s="78">
+        <v>-1.6E-2</v>
+      </c>
+    </row>
+    <row r="76" spans="2:13" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B76" s="142"/>
+      <c r="K76" s="124"/>
+      <c r="L76" s="67" t="s">
+        <v>224</v>
+      </c>
+      <c r="M76" s="81" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="77" spans="2:13" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B77" s="142"/>
+      <c r="K77" s="53" t="s">
+        <v>439</v>
+      </c>
+      <c r="L77" s="50" t="s">
+        <v>336</v>
+      </c>
+      <c r="M77" s="78" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="78" spans="2:13" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B78" s="142"/>
+      <c r="K78" s="63" t="s">
+        <v>412</v>
+      </c>
+      <c r="L78" s="56" t="s">
+        <v>336</v>
+      </c>
+      <c r="M78" s="80" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="79" spans="2:13" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B79" s="142"/>
+      <c r="K79" s="63" t="s">
+        <v>339</v>
+      </c>
+      <c r="L79" s="64">
+        <v>5984</v>
+      </c>
+      <c r="M79" s="79">
+        <v>8961</v>
+      </c>
+    </row>
+    <row r="80" spans="2:13" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B80" s="142"/>
+    </row>
+    <row r="81" spans="2:15" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B81" s="142"/>
+    </row>
+    <row r="82" spans="2:15" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B82" s="142"/>
+    </row>
+    <row r="83" spans="2:15" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B83" s="142"/>
+      <c r="J83" s="60" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="84" spans="2:15" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B84" s="142"/>
+      <c r="J84" s="125"/>
+      <c r="K84" s="127" t="s">
+        <v>442</v>
+      </c>
+      <c r="L84" s="127" t="s">
+        <v>446</v>
+      </c>
+      <c r="M84" s="130" t="s">
+        <v>447</v>
+      </c>
+      <c r="N84" s="130" t="s">
+        <v>443</v>
+      </c>
+      <c r="O84" s="130" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="85" spans="2:15" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B85" s="142"/>
+      <c r="J85" s="126"/>
+      <c r="K85" s="128"/>
+      <c r="L85" s="128"/>
+      <c r="M85" s="131"/>
+      <c r="N85" s="131"/>
+      <c r="O85" s="131"/>
+    </row>
+    <row r="86" spans="2:15" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B86" s="142"/>
+      <c r="J86" s="69" t="s">
+        <v>445</v>
+      </c>
+      <c r="K86" s="70">
+        <v>-4.5999999999999999E-2</v>
+      </c>
+      <c r="L86" s="70">
+        <v>9.2999999999999999E-2</v>
+      </c>
+      <c r="M86" s="83">
+        <v>0.121</v>
+      </c>
+      <c r="N86" s="83">
+        <v>-4.4999999999999998E-2</v>
+      </c>
+      <c r="O86" s="83">
+        <v>39.719000000000001</v>
+      </c>
+    </row>
+    <row r="87" spans="2:15" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B87" s="142"/>
+      <c r="J87" s="71" t="s">
+        <v>437</v>
+      </c>
+      <c r="K87" s="68">
+        <v>-4.5999999999999999E-2</v>
+      </c>
+      <c r="L87" s="68">
+        <v>3.3000000000000002E-2</v>
+      </c>
+      <c r="M87" s="82">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="N87" s="82">
+        <v>-4.3999999999999997E-2</v>
+      </c>
+      <c r="O87" s="82">
+        <v>26.744</v>
+      </c>
+    </row>
+    <row r="88" spans="2:15" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B88" s="142"/>
+    </row>
+    <row r="89" spans="2:15" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B89" s="142"/>
+    </row>
+  </sheetData>
+  <mergeCells count="31">
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="C2:L2"/>
+    <mergeCell ref="M2:R2"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="D43:D45"/>
+    <mergeCell ref="E43:F43"/>
+    <mergeCell ref="E45:F45"/>
+    <mergeCell ref="G45:I45"/>
+    <mergeCell ref="D46:D47"/>
+    <mergeCell ref="D61:D63"/>
+    <mergeCell ref="E62:E63"/>
+    <mergeCell ref="F62:H62"/>
+    <mergeCell ref="B3:B23"/>
+    <mergeCell ref="B24:B41"/>
+    <mergeCell ref="B42:B89"/>
+    <mergeCell ref="D64:D65"/>
+    <mergeCell ref="S2:AA2"/>
+    <mergeCell ref="M84:M85"/>
+    <mergeCell ref="N84:N85"/>
+    <mergeCell ref="O84:O85"/>
+    <mergeCell ref="T6:T7"/>
+    <mergeCell ref="U6:W6"/>
+    <mergeCell ref="T8:T9"/>
+    <mergeCell ref="I62:K62"/>
+    <mergeCell ref="K75:K76"/>
+    <mergeCell ref="J84:J85"/>
+    <mergeCell ref="K84:K85"/>
+    <mergeCell ref="L84:L85"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06B7323D-B2F5-BD40-8E81-C2419FFBC224}">
+  <dimension ref="B2:I21"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="20.1640625" customWidth="1"/>
+    <col min="5" max="5" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="55" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B2" s="110" t="s">
+        <v>490</v>
+      </c>
+      <c r="C2" s="110" t="s">
+        <v>491</v>
+      </c>
+      <c r="D2" s="110" t="s">
+        <v>492</v>
+      </c>
+      <c r="E2" s="110" t="s">
+        <v>493</v>
+      </c>
+      <c r="F2" s="110" t="s">
+        <v>494</v>
+      </c>
+      <c r="G2" s="110" t="s">
+        <v>495</v>
+      </c>
+      <c r="H2" s="110" t="s">
+        <v>496</v>
+      </c>
+      <c r="I2" s="110" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B3" s="152" t="s">
+        <v>498</v>
+      </c>
+      <c r="C3" s="151" t="s">
+        <v>499</v>
+      </c>
+      <c r="D3" s="151" t="s">
+        <v>500</v>
+      </c>
+      <c r="E3" s="151" t="s">
+        <v>501</v>
+      </c>
+      <c r="F3" s="151" t="s">
+        <v>502</v>
+      </c>
+      <c r="G3" s="151" t="s">
+        <v>503</v>
+      </c>
+      <c r="H3" s="151" t="s">
+        <v>504</v>
+      </c>
+      <c r="I3" s="107" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B4" s="152"/>
+      <c r="C4" s="151"/>
+      <c r="D4" s="151"/>
+      <c r="E4" s="151"/>
+      <c r="F4" s="151"/>
+      <c r="G4" s="151"/>
+      <c r="H4" s="151"/>
+      <c r="I4" s="107" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B5" s="108" t="s">
+        <v>506</v>
+      </c>
+      <c r="C5" s="109" t="s">
+        <v>499</v>
+      </c>
+      <c r="D5" s="109" t="s">
+        <v>500</v>
+      </c>
+      <c r="E5" s="109" t="s">
+        <v>507</v>
+      </c>
+      <c r="F5" s="109" t="s">
+        <v>502</v>
+      </c>
+      <c r="G5" s="109" t="s">
+        <v>508</v>
+      </c>
+      <c r="H5" s="109" t="s">
+        <v>509</v>
+      </c>
+      <c r="I5" s="107" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B6" s="108" t="s">
+        <v>511</v>
+      </c>
+      <c r="C6" s="109" t="s">
+        <v>499</v>
+      </c>
+      <c r="D6" s="109" t="s">
+        <v>500</v>
+      </c>
+      <c r="E6" s="109" t="s">
+        <v>507</v>
+      </c>
+      <c r="F6" s="109" t="s">
+        <v>502</v>
+      </c>
+      <c r="G6" s="109" t="s">
+        <v>508</v>
+      </c>
+      <c r="H6" s="109" t="s">
+        <v>509</v>
+      </c>
+      <c r="I6" s="107" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B7" s="108" t="s">
+        <v>512</v>
+      </c>
+      <c r="C7" s="109" t="s">
+        <v>513</v>
+      </c>
+      <c r="D7" s="109" t="s">
+        <v>500</v>
+      </c>
+      <c r="E7" s="109" t="s">
+        <v>507</v>
+      </c>
+      <c r="F7" s="109" t="s">
+        <v>502</v>
+      </c>
+      <c r="G7" s="109" t="s">
+        <v>508</v>
+      </c>
+      <c r="H7" s="109" t="s">
+        <v>509</v>
+      </c>
+      <c r="I7" s="107" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B8" s="152" t="s">
+        <v>514</v>
+      </c>
+      <c r="C8" s="151" t="s">
+        <v>513</v>
+      </c>
+      <c r="D8" s="151" t="s">
+        <v>500</v>
+      </c>
+      <c r="E8" s="151" t="s">
+        <v>507</v>
+      </c>
+      <c r="F8" s="151" t="s">
+        <v>502</v>
+      </c>
+      <c r="G8" s="151" t="s">
+        <v>515</v>
+      </c>
+      <c r="H8" s="151" t="s">
+        <v>516</v>
+      </c>
+      <c r="I8" s="107" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B9" s="152"/>
+      <c r="C9" s="151"/>
+      <c r="D9" s="151"/>
+      <c r="E9" s="151"/>
+      <c r="F9" s="151"/>
+      <c r="G9" s="151"/>
+      <c r="H9" s="151"/>
+      <c r="I9" s="107" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B10" s="152"/>
+      <c r="C10" s="151"/>
+      <c r="D10" s="151"/>
+      <c r="E10" s="151"/>
+      <c r="F10" s="151"/>
+      <c r="G10" s="151"/>
+      <c r="H10" s="151"/>
+      <c r="I10" s="107" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B11" s="108" t="s">
+        <v>518</v>
+      </c>
+      <c r="C11" s="109" t="s">
+        <v>499</v>
+      </c>
+      <c r="D11" s="109" t="s">
+        <v>500</v>
+      </c>
+      <c r="E11" s="109" t="s">
+        <v>507</v>
+      </c>
+      <c r="F11" s="109" t="s">
+        <v>502</v>
+      </c>
+      <c r="G11" s="109" t="s">
+        <v>519</v>
+      </c>
+      <c r="H11" s="109" t="s">
+        <v>520</v>
+      </c>
+      <c r="I11" s="107" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="12" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B12" s="108" t="s">
+        <v>521</v>
+      </c>
+      <c r="C12" s="109" t="s">
+        <v>522</v>
+      </c>
+      <c r="D12" s="109" t="s">
+        <v>523</v>
+      </c>
+      <c r="E12" s="109" t="s">
+        <v>507</v>
+      </c>
+      <c r="F12" s="109" t="s">
+        <v>502</v>
+      </c>
+      <c r="G12" s="109" t="s">
+        <v>519</v>
+      </c>
+      <c r="H12" s="109" t="s">
+        <v>524</v>
+      </c>
+      <c r="I12" s="107" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B13" s="108" t="s">
+        <v>525</v>
+      </c>
+      <c r="C13" s="109" t="s">
+        <v>499</v>
+      </c>
+      <c r="D13" s="109" t="s">
+        <v>500</v>
+      </c>
+      <c r="E13" s="109" t="s">
+        <v>507</v>
+      </c>
+      <c r="F13" s="109" t="s">
+        <v>502</v>
+      </c>
+      <c r="G13" s="109" t="s">
+        <v>508</v>
+      </c>
+      <c r="H13" s="109" t="s">
+        <v>526</v>
+      </c>
+      <c r="I13" s="107" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B14" s="152" t="s">
+        <v>527</v>
+      </c>
+      <c r="C14" s="151" t="s">
+        <v>513</v>
+      </c>
+      <c r="D14" s="151" t="s">
+        <v>500</v>
+      </c>
+      <c r="E14" s="151" t="s">
+        <v>507</v>
+      </c>
+      <c r="F14" s="151" t="s">
+        <v>502</v>
+      </c>
+      <c r="G14" s="151" t="s">
+        <v>503</v>
+      </c>
+      <c r="H14" s="151" t="s">
+        <v>520</v>
+      </c>
+      <c r="I14" s="107" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B15" s="152"/>
+      <c r="C15" s="151"/>
+      <c r="D15" s="151"/>
+      <c r="E15" s="151"/>
+      <c r="F15" s="151"/>
+      <c r="G15" s="151"/>
+      <c r="H15" s="151"/>
+      <c r="I15" s="107" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B16" s="152" t="s">
+        <v>530</v>
+      </c>
+      <c r="C16" s="151" t="s">
+        <v>513</v>
+      </c>
+      <c r="D16" s="151" t="s">
+        <v>500</v>
+      </c>
+      <c r="E16" s="151" t="s">
+        <v>501</v>
+      </c>
+      <c r="F16" s="151" t="s">
+        <v>502</v>
+      </c>
+      <c r="G16" s="151" t="s">
+        <v>515</v>
+      </c>
+      <c r="H16" s="151" t="s">
+        <v>509</v>
+      </c>
+      <c r="I16" s="107" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B17" s="152"/>
+      <c r="C17" s="151"/>
+      <c r="D17" s="151"/>
+      <c r="E17" s="151"/>
+      <c r="F17" s="151"/>
+      <c r="G17" s="151"/>
+      <c r="H17" s="151"/>
+      <c r="I17" s="107" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B18" s="152"/>
+      <c r="C18" s="151"/>
+      <c r="D18" s="151"/>
+      <c r="E18" s="151"/>
+      <c r="F18" s="151"/>
+      <c r="G18" s="151"/>
+      <c r="H18" s="151"/>
+      <c r="I18" s="107" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B19" s="153" t="s">
+        <v>525</v>
+      </c>
+      <c r="C19" s="150" t="s">
+        <v>499</v>
+      </c>
+      <c r="D19" s="150" t="s">
+        <v>500</v>
+      </c>
+      <c r="E19" s="150" t="s">
+        <v>507</v>
+      </c>
+      <c r="F19" s="150" t="s">
+        <v>502</v>
+      </c>
+      <c r="G19" s="150" t="s">
+        <v>508</v>
+      </c>
+      <c r="H19" s="150" t="s">
+        <v>526</v>
+      </c>
+      <c r="I19" s="111" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B20" s="153"/>
+      <c r="C20" s="150"/>
+      <c r="D20" s="150"/>
+      <c r="E20" s="150"/>
+      <c r="F20" s="150"/>
+      <c r="G20" s="150"/>
+      <c r="H20" s="150"/>
+      <c r="I20" s="111" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B21" s="112" t="s">
+        <v>518</v>
+      </c>
+      <c r="C21" s="113" t="s">
+        <v>499</v>
+      </c>
+      <c r="D21" s="113" t="s">
+        <v>500</v>
+      </c>
+      <c r="E21" s="113" t="s">
+        <v>507</v>
+      </c>
+      <c r="F21" s="113" t="s">
+        <v>502</v>
+      </c>
+      <c r="G21" s="113" t="s">
+        <v>519</v>
+      </c>
+      <c r="H21" s="113" t="s">
+        <v>520</v>
+      </c>
+      <c r="I21" s="114" t="s">
+        <v>533</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="35">
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="E19:E20"/>
+    <mergeCell ref="F19:F20"/>
+    <mergeCell ref="G19:G20"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="C8:C10"/>
+    <mergeCell ref="D8:D10"/>
+    <mergeCell ref="E8:E10"/>
+    <mergeCell ref="F8:F10"/>
+    <mergeCell ref="G8:G10"/>
+    <mergeCell ref="H8:H10"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="H19:H20"/>
+    <mergeCell ref="F16:F18"/>
+    <mergeCell ref="G16:G18"/>
+    <mergeCell ref="H16:H18"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="B16:B18"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="D16:D18"/>
+    <mergeCell ref="E16:E18"/>
+    <mergeCell ref="B19:B20"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8DD9CDF-8D3B-4C4F-9F1C-C65D2EB3343E}">
   <dimension ref="A1:M49"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -20083,7 +21385,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2940A11-14E0-5242-BAF0-2DDD4FA2A627}">
   <dimension ref="B2:P61"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -20142,35 +21444,35 @@
       <c r="B3" s="15" t="s">
         <v>345</v>
       </c>
-      <c r="C3" s="36" t="s">
+      <c r="C3" s="154" t="s">
         <v>346</v>
       </c>
-      <c r="D3" s="36"/>
-      <c r="E3" s="36" t="s">
+      <c r="D3" s="154"/>
+      <c r="E3" s="154" t="s">
         <v>348</v>
       </c>
-      <c r="F3" s="36"/>
+      <c r="F3" s="154"/>
       <c r="H3" s="15" t="s">
         <v>345</v>
       </c>
-      <c r="I3" s="36" t="s">
+      <c r="I3" s="154" t="s">
         <v>349</v>
       </c>
-      <c r="J3" s="36"/>
-      <c r="K3" s="36" t="s">
+      <c r="J3" s="154"/>
+      <c r="K3" s="154" t="s">
         <v>350</v>
       </c>
-      <c r="L3" s="36"/>
+      <c r="L3" s="154"/>
       <c r="N3" s="15" t="s">
         <v>345</v>
       </c>
-      <c r="O3" s="36" t="s">
+      <c r="O3" s="154" t="s">
         <v>352</v>
       </c>
-      <c r="P3" s="36"/>
+      <c r="P3" s="154"/>
     </row>
     <row r="4" spans="2:16" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="37" t="s">
+      <c r="B4" s="155" t="s">
         <v>334</v>
       </c>
       <c r="C4" s="13" t="s">
@@ -20185,7 +21487,7 @@
       <c r="F4" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="H4" s="37" t="s">
+      <c r="H4" s="155" t="s">
         <v>334</v>
       </c>
       <c r="I4" s="13" t="s">
@@ -20200,7 +21502,7 @@
       <c r="L4" s="13" t="s">
         <v>260</v>
       </c>
-      <c r="N4" s="37" t="s">
+      <c r="N4" s="155" t="s">
         <v>334</v>
       </c>
       <c r="O4" s="13" t="s">
@@ -20211,7 +21513,7 @@
       </c>
     </row>
     <row r="5" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B5" s="37"/>
+      <c r="B5" s="155"/>
       <c r="C5" s="13" t="s">
         <v>16</v>
       </c>
@@ -20224,7 +21526,7 @@
       <c r="F5" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="H5" s="37"/>
+      <c r="H5" s="155"/>
       <c r="I5" s="13" t="s">
         <v>29</v>
       </c>
@@ -20237,7 +21539,7 @@
       <c r="L5" s="13" t="s">
         <v>263</v>
       </c>
-      <c r="N5" s="37"/>
+      <c r="N5" s="155"/>
       <c r="O5" s="13" t="s">
         <v>65</v>
       </c>
@@ -20246,7 +21548,7 @@
       </c>
     </row>
     <row r="6" spans="2:16" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="37" t="s">
+      <c r="B6" s="155" t="s">
         <v>364</v>
       </c>
       <c r="C6" s="13"/>
@@ -20257,7 +21559,7 @@
       <c r="F6" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="H6" s="37" t="s">
+      <c r="H6" s="155" t="s">
         <v>360</v>
       </c>
       <c r="J6" s="13" t="s">
@@ -20267,7 +21569,7 @@
       <c r="L6" s="13" t="s">
         <v>266</v>
       </c>
-      <c r="N6" s="37" t="s">
+      <c r="N6" s="155" t="s">
         <v>360</v>
       </c>
       <c r="P6" s="13" t="s">
@@ -20275,7 +21577,7 @@
       </c>
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B7" s="37"/>
+      <c r="B7" s="155"/>
       <c r="C7" s="13"/>
       <c r="D7" s="13" t="s">
         <v>26</v>
@@ -20284,7 +21586,7 @@
       <c r="F7" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="H7" s="37"/>
+      <c r="H7" s="155"/>
       <c r="J7" s="13" t="s">
         <v>213</v>
       </c>
@@ -20292,13 +21594,13 @@
       <c r="L7" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="N7" s="37"/>
+      <c r="N7" s="155"/>
       <c r="P7" s="13" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="8" spans="2:16" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="37" t="s">
+      <c r="B8" s="155" t="s">
         <v>365</v>
       </c>
       <c r="C8" s="13"/>
@@ -20309,7 +21611,7 @@
       <c r="F8" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="H8" s="37" t="s">
+      <c r="H8" s="155" t="s">
         <v>361</v>
       </c>
       <c r="J8" s="13" t="s">
@@ -20319,7 +21621,7 @@
       <c r="L8" s="13" t="s">
         <v>269</v>
       </c>
-      <c r="N8" s="37" t="s">
+      <c r="N8" s="155" t="s">
         <v>361</v>
       </c>
       <c r="P8" s="13" t="s">
@@ -20327,7 +21629,7 @@
       </c>
     </row>
     <row r="9" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B9" s="38"/>
+      <c r="B9" s="156"/>
       <c r="C9" s="16"/>
       <c r="D9" s="16" t="s">
         <v>85</v>
@@ -20336,7 +21638,7 @@
       <c r="F9" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="H9" s="37"/>
+      <c r="H9" s="155"/>
       <c r="J9" s="13" t="s">
         <v>163</v>
       </c>
@@ -20344,7 +21646,7 @@
       <c r="L9" s="13" t="s">
         <v>274</v>
       </c>
-      <c r="N9" s="37"/>
+      <c r="N9" s="155"/>
       <c r="P9" s="13" t="s">
         <v>217</v>
       </c>
@@ -20365,7 +21667,7 @@
       <c r="F10" s="13" t="s">
         <v>336</v>
       </c>
-      <c r="H10" s="37" t="s">
+      <c r="H10" s="155" t="s">
         <v>362</v>
       </c>
       <c r="I10" s="13"/>
@@ -20376,7 +21678,7 @@
       <c r="L10" s="13" t="s">
         <v>277</v>
       </c>
-      <c r="N10" s="37" t="s">
+      <c r="N10" s="155" t="s">
         <v>362</v>
       </c>
       <c r="O10" s="13"/>
@@ -20400,7 +21702,7 @@
       <c r="F11" s="13" t="s">
         <v>336</v>
       </c>
-      <c r="H11" s="37"/>
+      <c r="H11" s="155"/>
       <c r="I11" s="13"/>
       <c r="J11" s="13" t="s">
         <v>251</v>
@@ -20409,7 +21711,7 @@
       <c r="L11" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="N11" s="37"/>
+      <c r="N11" s="155"/>
       <c r="O11" s="13"/>
       <c r="P11" s="13" t="s">
         <v>213</v>
@@ -20431,7 +21733,7 @@
       <c r="F12" s="13" t="s">
         <v>336</v>
       </c>
-      <c r="H12" s="37" t="s">
+      <c r="H12" s="155" t="s">
         <v>363</v>
       </c>
       <c r="I12" s="13"/>
@@ -20442,7 +21744,7 @@
       <c r="L12" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="N12" s="37" t="s">
+      <c r="N12" s="155" t="s">
         <v>363</v>
       </c>
       <c r="O12" s="13"/>
@@ -20466,7 +21768,7 @@
       <c r="F13" s="16" t="s">
         <v>347</v>
       </c>
-      <c r="H13" s="38"/>
+      <c r="H13" s="156"/>
       <c r="I13" s="16"/>
       <c r="J13" s="16" t="s">
         <v>210</v>
@@ -20475,7 +21777,7 @@
       <c r="L13" s="16" t="s">
         <v>286</v>
       </c>
-      <c r="N13" s="38"/>
+      <c r="N13" s="156"/>
       <c r="O13" s="16"/>
       <c r="P13" s="16" t="s">
         <v>60</v>
@@ -20605,20 +21907,20 @@
       </c>
     </row>
     <row r="20" spans="2:16" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="46" t="s">
+      <c r="B20" s="29" t="s">
         <v>388</v>
       </c>
-      <c r="C20" s="36" t="s">
-        <v>403</v>
-      </c>
-      <c r="D20" s="36"/>
-      <c r="E20" s="36" t="s">
-        <v>404</v>
-      </c>
-      <c r="F20" s="36"/>
+      <c r="C20" s="154" t="s">
+        <v>399</v>
+      </c>
+      <c r="D20" s="154"/>
+      <c r="E20" s="154" t="s">
+        <v>400</v>
+      </c>
+      <c r="F20" s="154"/>
     </row>
     <row r="21" spans="2:16" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="37" t="s">
+      <c r="B21" s="155" t="s">
         <v>334</v>
       </c>
       <c r="C21" s="13" t="s">
@@ -20635,7 +21937,7 @@
       </c>
     </row>
     <row r="22" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B22" s="37"/>
+      <c r="B22" s="155"/>
       <c r="C22" s="13" t="s">
         <v>16</v>
       </c>
@@ -20650,8 +21952,8 @@
       </c>
     </row>
     <row r="23" spans="2:16" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="37" t="s">
-        <v>405</v>
+      <c r="B23" s="155" t="s">
+        <v>401</v>
       </c>
       <c r="C23" s="13"/>
       <c r="D23" s="13" t="s">
@@ -20663,7 +21965,7 @@
       </c>
     </row>
     <row r="24" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B24" s="37"/>
+      <c r="B24" s="155"/>
       <c r="C24" s="13"/>
       <c r="D24" s="13" t="s">
         <v>26</v>
@@ -20674,8 +21976,8 @@
       </c>
     </row>
     <row r="25" spans="2:16" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="37" t="s">
-        <v>406</v>
+      <c r="B25" s="155" t="s">
+        <v>402</v>
       </c>
       <c r="C25" s="13"/>
       <c r="D25" s="13" t="s">
@@ -20687,7 +21989,7 @@
       </c>
     </row>
     <row r="26" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B26" s="38"/>
+      <c r="B26" s="156"/>
       <c r="C26" s="16"/>
       <c r="D26" s="16" t="s">
         <v>85</v>
@@ -20768,23 +22070,23 @@
     <row r="32" spans="2:16" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="34" spans="2:7" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="44" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B44" s="39" t="s">
+      <c r="B44" s="157" t="s">
         <v>324</v>
       </c>
-      <c r="C44" s="39" t="s">
+      <c r="C44" s="157" t="s">
         <v>325</v>
       </c>
-      <c r="D44" s="39"/>
-      <c r="E44" s="39"/>
-      <c r="F44" s="39" t="s">
+      <c r="D44" s="157"/>
+      <c r="E44" s="157"/>
+      <c r="F44" s="157" t="s">
         <v>326</v>
       </c>
-      <c r="G44" s="39" t="s">
+      <c r="G44" s="157" t="s">
         <v>327</v>
       </c>
     </row>
     <row r="45" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B45" s="33"/>
+      <c r="B45" s="158"/>
       <c r="C45" s="19" t="s">
         <v>328</v>
       </c>
@@ -20794,11 +22096,11 @@
       <c r="E45" s="19" t="s">
         <v>330</v>
       </c>
-      <c r="F45" s="35"/>
-      <c r="G45" s="35"/>
+      <c r="F45" s="160"/>
+      <c r="G45" s="160"/>
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B46" s="32" t="s">
+      <c r="B46" s="159" t="s">
         <v>331</v>
       </c>
       <c r="C46" s="17" t="str">
@@ -20813,17 +22115,17 @@
         <f>"89.272"</f>
         <v>89.272</v>
       </c>
-      <c r="F46" s="33" t="str">
+      <c r="F46" s="158" t="str">
         <f>"0.000"</f>
         <v>0.000</v>
       </c>
-      <c r="G46" s="33" t="str">
+      <c r="G46" s="158" t="str">
         <f>"2702.000"</f>
         <v>2702.000</v>
       </c>
     </row>
     <row r="47" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B47" s="32"/>
+      <c r="B47" s="159"/>
       <c r="C47" s="17" t="str">
         <f>"(113.981)"</f>
         <v>(113.981)</v>
@@ -20836,11 +22138,11 @@
         <f>"(133.323)"</f>
         <v>(133.323)</v>
       </c>
-      <c r="F47" s="33"/>
-      <c r="G47" s="33"/>
+      <c r="F47" s="158"/>
+      <c r="G47" s="158"/>
     </row>
     <row r="48" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B48" s="32" t="s">
+      <c r="B48" s="159" t="s">
         <v>332</v>
       </c>
       <c r="C48" s="17" t="str">
@@ -20855,17 +22157,17 @@
         <f>"1.372"</f>
         <v>1.372</v>
       </c>
-      <c r="F48" s="33" t="str">
+      <c r="F48" s="158" t="str">
         <f>"0.000"</f>
         <v>0.000</v>
       </c>
-      <c r="G48" s="33" t="str">
+      <c r="G48" s="158" t="str">
         <f>"8.000"</f>
         <v>8.000</v>
       </c>
     </row>
     <row r="49" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B49" s="32"/>
+      <c r="B49" s="159"/>
       <c r="C49" s="17" t="str">
         <f>"(1.166)"</f>
         <v>(1.166)</v>
@@ -20878,11 +22180,11 @@
         <f>"(1.192)"</f>
         <v>(1.192)</v>
       </c>
-      <c r="F49" s="33"/>
-      <c r="G49" s="33"/>
+      <c r="F49" s="158"/>
+      <c r="G49" s="158"/>
     </row>
     <row r="50" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B50" s="32" t="s">
+      <c r="B50" s="159" t="s">
         <v>355</v>
       </c>
       <c r="C50" s="17" t="str">
@@ -20897,17 +22199,17 @@
         <f>"0.397"</f>
         <v>0.397</v>
       </c>
-      <c r="F50" s="33" t="str">
+      <c r="F50" s="158" t="str">
         <f>"-0.048"</f>
         <v>-0.048</v>
       </c>
-      <c r="G50" s="33" t="str">
+      <c r="G50" s="158" t="str">
         <f>"0.991"</f>
         <v>0.991</v>
       </c>
     </row>
     <row r="51" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B51" s="32"/>
+      <c r="B51" s="159"/>
       <c r="C51" s="17" t="str">
         <f>"(0.181)"</f>
         <v>(0.181)</v>
@@ -20920,11 +22222,11 @@
         <f>"(0.188)"</f>
         <v>(0.188)</v>
       </c>
-      <c r="F51" s="33"/>
-      <c r="G51" s="33"/>
+      <c r="F51" s="158"/>
+      <c r="G51" s="158"/>
     </row>
     <row r="52" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B52" s="32" t="s">
+      <c r="B52" s="159" t="s">
         <v>333</v>
       </c>
       <c r="C52" s="17" t="str">
@@ -20939,17 +22241,17 @@
         <f>"0.536"</f>
         <v>0.536</v>
       </c>
-      <c r="F52" s="33" t="str">
+      <c r="F52" s="158" t="str">
         <f>"-3.000"</f>
         <v>-3.000</v>
       </c>
-      <c r="G52" s="33" t="str">
+      <c r="G52" s="158" t="str">
         <f>"14.000"</f>
         <v>14.000</v>
       </c>
     </row>
     <row r="53" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B53" s="32"/>
+      <c r="B53" s="159"/>
       <c r="C53" s="17" t="str">
         <f>"(1.096)"</f>
         <v>(1.096)</v>
@@ -20962,11 +22264,11 @@
         <f>"(1.140)"</f>
         <v>(1.140)</v>
       </c>
-      <c r="F53" s="33"/>
-      <c r="G53" s="33"/>
+      <c r="F53" s="158"/>
+      <c r="G53" s="158"/>
     </row>
     <row r="54" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B54" s="32" t="s">
+      <c r="B54" s="159" t="s">
         <v>357</v>
       </c>
       <c r="C54" s="17" t="str">
@@ -20981,17 +22283,17 @@
         <f>"0.000"</f>
         <v>0.000</v>
       </c>
-      <c r="F54" s="33" t="str">
+      <c r="F54" s="158" t="str">
         <f>"0.000"</f>
         <v>0.000</v>
       </c>
-      <c r="G54" s="33" t="str">
+      <c r="G54" s="158" t="str">
         <f>"6.977"</f>
         <v>6.977</v>
       </c>
     </row>
     <row r="55" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B55" s="32"/>
+      <c r="B55" s="159"/>
       <c r="C55" s="17" t="str">
         <f>"(2.864)"</f>
         <v>(2.864)</v>
@@ -21004,11 +22306,11 @@
         <f>"(0.000)"</f>
         <v>(0.000)</v>
       </c>
-      <c r="F55" s="33"/>
-      <c r="G55" s="33"/>
+      <c r="F55" s="158"/>
+      <c r="G55" s="158"/>
     </row>
     <row r="56" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B56" s="32" t="s">
+      <c r="B56" s="159" t="s">
         <v>359</v>
       </c>
       <c r="C56" s="17" t="str">
@@ -21023,17 +22325,17 @@
         <f>"0.000"</f>
         <v>0.000</v>
       </c>
-      <c r="F56" s="33" t="str">
+      <c r="F56" s="158" t="str">
         <f>"0.000"</f>
         <v>0.000</v>
       </c>
-      <c r="G56" s="33" t="str">
+      <c r="G56" s="158" t="str">
         <f>"0.891"</f>
         <v>0.891</v>
       </c>
     </row>
     <row r="57" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B57" s="32"/>
+      <c r="B57" s="159"/>
       <c r="C57" s="17" t="str">
         <f>"(0.297)"</f>
         <v>(0.297)</v>
@@ -21046,11 +22348,11 @@
         <f>"(0.000)"</f>
         <v>(0.000)</v>
       </c>
-      <c r="F57" s="33"/>
-      <c r="G57" s="33"/>
+      <c r="F57" s="158"/>
+      <c r="G57" s="158"/>
     </row>
     <row r="58" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B58" s="32" t="s">
+      <c r="B58" s="159" t="s">
         <v>358</v>
       </c>
       <c r="C58" s="17" t="str">
@@ -21065,17 +22367,17 @@
         <f>"3.443"</f>
         <v>3.443</v>
       </c>
-      <c r="F58" s="33" t="str">
+      <c r="F58" s="158" t="str">
         <f>"0.000"</f>
         <v>0.000</v>
       </c>
-      <c r="G58" s="33" t="str">
+      <c r="G58" s="158" t="str">
         <f>"7.912"</f>
         <v>7.912</v>
       </c>
     </row>
     <row r="59" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B59" s="32"/>
+      <c r="B59" s="159"/>
       <c r="C59" s="17" t="str">
         <f>"(1.489)"</f>
         <v>(1.489)</v>
@@ -21088,11 +22390,11 @@
         <f>"(1.338)"</f>
         <v>(1.338)</v>
       </c>
-      <c r="F59" s="33"/>
-      <c r="G59" s="33"/>
+      <c r="F59" s="158"/>
+      <c r="G59" s="158"/>
     </row>
     <row r="60" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B60" s="32" t="s">
+      <c r="B60" s="159" t="s">
         <v>356</v>
       </c>
       <c r="C60" s="17" t="str">
@@ -21107,17 +22409,17 @@
         <f>"0.445"</f>
         <v>0.445</v>
       </c>
-      <c r="F60" s="33" t="str">
+      <c r="F60" s="158" t="str">
         <f>"-0.090"</f>
         <v>-0.090</v>
       </c>
-      <c r="G60" s="33" t="str">
+      <c r="G60" s="158" t="str">
         <f>"0.911"</f>
         <v>0.911</v>
       </c>
     </row>
     <row r="61" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B61" s="34"/>
+      <c r="B61" s="161"/>
       <c r="C61" s="18" t="str">
         <f>"(0.177)"</f>
         <v>(0.177)</v>
@@ -21130,25 +22432,29 @@
         <f>"(0.187)"</f>
         <v>(0.187)</v>
       </c>
-      <c r="F61" s="35"/>
-      <c r="G61" s="35"/>
+      <c r="F61" s="160"/>
+      <c r="G61" s="160"/>
     </row>
   </sheetData>
   <mergeCells count="51">
-    <mergeCell ref="O3:P3"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="N4:N5"/>
-    <mergeCell ref="N6:N7"/>
-    <mergeCell ref="N8:N9"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="G60:G61"/>
+    <mergeCell ref="G54:G55"/>
+    <mergeCell ref="B56:B57"/>
+    <mergeCell ref="F56:F57"/>
+    <mergeCell ref="G56:G57"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="F58:F59"/>
+    <mergeCell ref="G58:G59"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="F54:F55"/>
+    <mergeCell ref="B50:B51"/>
+    <mergeCell ref="F50:F51"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="F60:F61"/>
+    <mergeCell ref="G50:G51"/>
+    <mergeCell ref="B52:B53"/>
+    <mergeCell ref="F52:F53"/>
+    <mergeCell ref="G52:G53"/>
     <mergeCell ref="B48:B49"/>
     <mergeCell ref="F48:F49"/>
     <mergeCell ref="G48:G49"/>
@@ -21165,34 +22471,30 @@
     <mergeCell ref="H12:H13"/>
     <mergeCell ref="C20:D20"/>
     <mergeCell ref="E20:F20"/>
-    <mergeCell ref="B50:B51"/>
-    <mergeCell ref="F50:F51"/>
-    <mergeCell ref="G50:G51"/>
-    <mergeCell ref="B52:B53"/>
-    <mergeCell ref="F52:F53"/>
-    <mergeCell ref="G52:G53"/>
     <mergeCell ref="B21:B22"/>
     <mergeCell ref="B23:B24"/>
     <mergeCell ref="B25:B26"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="F54:F55"/>
-    <mergeCell ref="G54:G55"/>
-    <mergeCell ref="B56:B57"/>
-    <mergeCell ref="F56:F57"/>
-    <mergeCell ref="G56:G57"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="F58:F59"/>
-    <mergeCell ref="G58:G59"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="F60:F61"/>
-    <mergeCell ref="G60:G61"/>
+    <mergeCell ref="O3:P3"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="N4:N5"/>
+    <mergeCell ref="N6:N7"/>
+    <mergeCell ref="N8:N9"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="H8:H9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{985AFA23-5DA6-564F-ADE6-19391318ACD9}">
   <dimension ref="B1:X90"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -21221,18 +22523,18 @@
   <sheetData>
     <row r="1" spans="2:12" hidden="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:12" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="42" t="s">
+      <c r="B2" s="164" t="s">
         <v>179</v>
       </c>
       <c r="C2" s="3"/>
-      <c r="D2" s="44" t="s">
+      <c r="D2" s="166" t="s">
         <v>0</v>
       </c>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44" t="s">
+      <c r="E2" s="166"/>
+      <c r="F2" s="166" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="44"/>
+      <c r="G2" s="166"/>
       <c r="H2" s="8" t="s">
         <v>124</v>
       </c>
@@ -21242,14 +22544,14 @@
       <c r="J2" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="K2" s="44" t="s">
+      <c r="K2" s="166" t="s">
         <v>2</v>
       </c>
-      <c r="L2" s="44"/>
+      <c r="L2" s="166"/>
     </row>
     <row r="3" spans="2:12" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="43"/>
-      <c r="C3" s="40" t="s">
+      <c r="B3" s="165"/>
+      <c r="C3" s="162" t="s">
         <v>5</v>
       </c>
       <c r="D3" s="4" t="s">
@@ -21281,8 +22583,8 @@
       </c>
     </row>
     <row r="4" spans="2:12" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="43"/>
-      <c r="C4" s="41"/>
+      <c r="B4" s="165"/>
+      <c r="C4" s="163"/>
       <c r="D4" s="4" t="s">
         <v>16</v>
       </c>
@@ -21312,8 +22614,8 @@
       </c>
     </row>
     <row r="5" spans="2:12" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="43"/>
-      <c r="C5" s="40" t="s">
+      <c r="B5" s="165"/>
+      <c r="C5" s="162" t="s">
         <v>11</v>
       </c>
       <c r="D5" s="4"/>
@@ -21339,8 +22641,8 @@
       </c>
     </row>
     <row r="6" spans="2:12" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="43"/>
-      <c r="C6" s="41"/>
+      <c r="B6" s="165"/>
+      <c r="C6" s="163"/>
       <c r="D6" s="4"/>
       <c r="E6" s="4" t="s">
         <v>26</v>
@@ -21364,8 +22666,8 @@
       </c>
     </row>
     <row r="7" spans="2:12" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="43"/>
-      <c r="C7" s="40" t="s">
+      <c r="B7" s="165"/>
+      <c r="C7" s="162" t="s">
         <v>13</v>
       </c>
       <c r="D7" s="4"/>
@@ -21391,8 +22693,8 @@
       </c>
     </row>
     <row r="8" spans="2:12" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="43"/>
-      <c r="C8" s="41"/>
+      <c r="B8" s="165"/>
+      <c r="C8" s="163"/>
       <c r="D8" s="4"/>
       <c r="E8" s="4" t="s">
         <v>33</v>
@@ -21416,7 +22718,7 @@
       </c>
     </row>
     <row r="9" spans="2:12" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="43"/>
+      <c r="B9" s="165"/>
       <c r="C9" s="3" t="s">
         <v>14</v>
       </c>
@@ -21450,18 +22752,18 @@
     </row>
     <row r="10" spans="2:12" hidden="1" x14ac:dyDescent="0.2"/>
     <row r="11" spans="2:12" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="42" t="s">
+      <c r="B11" s="164" t="s">
         <v>180</v>
       </c>
       <c r="C11" s="3"/>
-      <c r="D11" s="44" t="s">
+      <c r="D11" s="166" t="s">
         <v>3</v>
       </c>
-      <c r="E11" s="44"/>
-      <c r="F11" s="44" t="s">
+      <c r="E11" s="166"/>
+      <c r="F11" s="166" t="s">
         <v>4</v>
       </c>
-      <c r="G11" s="44"/>
+      <c r="G11" s="166"/>
       <c r="H11" s="8" t="s">
         <v>124</v>
       </c>
@@ -21471,14 +22773,14 @@
       <c r="J11" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="K11" s="44" t="s">
+      <c r="K11" s="166" t="s">
         <v>127</v>
       </c>
-      <c r="L11" s="44"/>
+      <c r="L11" s="166"/>
     </row>
     <row r="12" spans="2:12" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="43"/>
-      <c r="C12" s="40" t="s">
+      <c r="B12" s="165"/>
+      <c r="C12" s="162" t="s">
         <v>5</v>
       </c>
       <c r="D12" s="4" t="s">
@@ -21510,8 +22812,8 @@
       </c>
     </row>
     <row r="13" spans="2:12" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="43"/>
-      <c r="C13" s="41"/>
+      <c r="B13" s="165"/>
+      <c r="C13" s="163"/>
       <c r="D13" s="4" t="s">
         <v>29</v>
       </c>
@@ -21541,8 +22843,8 @@
       </c>
     </row>
     <row r="14" spans="2:12" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="43"/>
-      <c r="C14" s="40" t="s">
+      <c r="B14" s="165"/>
+      <c r="C14" s="162" t="s">
         <v>186</v>
       </c>
       <c r="D14" s="4"/>
@@ -21568,8 +22870,8 @@
       </c>
     </row>
     <row r="15" spans="2:12" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="43"/>
-      <c r="C15" s="41"/>
+      <c r="B15" s="165"/>
+      <c r="C15" s="163"/>
       <c r="D15" s="4"/>
       <c r="E15" s="4" t="s">
         <v>211</v>
@@ -21593,8 +22895,8 @@
       </c>
     </row>
     <row r="16" spans="2:12" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="43"/>
-      <c r="C16" s="40" t="s">
+      <c r="B16" s="165"/>
+      <c r="C16" s="162" t="s">
         <v>228</v>
       </c>
       <c r="D16" s="4"/>
@@ -21620,8 +22922,8 @@
       </c>
     </row>
     <row r="17" spans="2:24" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="43"/>
-      <c r="C17" s="41"/>
+      <c r="B17" s="165"/>
+      <c r="C17" s="163"/>
       <c r="D17" s="4"/>
       <c r="E17" s="4" t="s">
         <v>215</v>
@@ -21645,8 +22947,8 @@
       </c>
     </row>
     <row r="18" spans="2:24" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="43"/>
-      <c r="C18" s="40" t="s">
+      <c r="B18" s="165"/>
+      <c r="C18" s="162" t="s">
         <v>134</v>
       </c>
       <c r="D18" s="4"/>
@@ -21672,8 +22974,8 @@
       </c>
     </row>
     <row r="19" spans="2:24" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="43"/>
-      <c r="C19" s="41"/>
+      <c r="B19" s="165"/>
+      <c r="C19" s="163"/>
       <c r="D19" s="4"/>
       <c r="E19" s="4" t="s">
         <v>222</v>
@@ -21697,8 +22999,8 @@
       </c>
     </row>
     <row r="20" spans="2:24" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="43"/>
-      <c r="C20" s="40" t="s">
+      <c r="B20" s="165"/>
+      <c r="C20" s="162" t="s">
         <v>139</v>
       </c>
       <c r="D20" s="4"/>
@@ -21724,8 +23026,8 @@
       </c>
     </row>
     <row r="21" spans="2:24" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="43"/>
-      <c r="C21" s="41"/>
+      <c r="B21" s="165"/>
+      <c r="C21" s="163"/>
       <c r="D21" s="4"/>
       <c r="E21" s="4" t="s">
         <v>143</v>
@@ -21749,7 +23051,7 @@
       </c>
     </row>
     <row r="22" spans="2:24" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="43"/>
+      <c r="B22" s="165"/>
       <c r="C22" s="3" t="s">
         <v>14</v>
       </c>
@@ -21808,18 +23110,18 @@
       <c r="X24" s="11"/>
     </row>
     <row r="25" spans="2:24" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="42" t="s">
+      <c r="B25" s="164" t="s">
         <v>177</v>
       </c>
       <c r="C25" s="3"/>
-      <c r="D25" s="44" t="s">
+      <c r="D25" s="166" t="s">
         <v>0</v>
       </c>
-      <c r="E25" s="44"/>
-      <c r="F25" s="44" t="s">
+      <c r="E25" s="166"/>
+      <c r="F25" s="166" t="s">
         <v>1</v>
       </c>
-      <c r="G25" s="44"/>
+      <c r="G25" s="166"/>
       <c r="H25" s="8" t="s">
         <v>124</v>
       </c>
@@ -21829,10 +23131,10 @@
       <c r="J25" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="K25" s="44" t="s">
+      <c r="K25" s="166" t="s">
         <v>2</v>
       </c>
-      <c r="L25" s="44"/>
+      <c r="L25" s="166"/>
       <c r="N25" s="10"/>
       <c r="P25" s="2"/>
       <c r="Q25" s="2"/>
@@ -21845,8 +23147,8 @@
       <c r="X25" s="11"/>
     </row>
     <row r="26" spans="2:24" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="43"/>
-      <c r="C26" s="40" t="s">
+      <c r="B26" s="165"/>
+      <c r="C26" s="162" t="s">
         <v>5</v>
       </c>
       <c r="D26" s="4" t="s">
@@ -21888,8 +23190,8 @@
       <c r="X26" s="11"/>
     </row>
     <row r="27" spans="2:24" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B27" s="43"/>
-      <c r="C27" s="41"/>
+      <c r="B27" s="165"/>
+      <c r="C27" s="163"/>
       <c r="D27" s="4" t="s">
         <v>16</v>
       </c>
@@ -21929,8 +23231,8 @@
       <c r="X27" s="11"/>
     </row>
     <row r="28" spans="2:24" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B28" s="43"/>
-      <c r="C28" s="40" t="s">
+      <c r="B28" s="165"/>
+      <c r="C28" s="162" t="s">
         <v>11</v>
       </c>
       <c r="D28" s="4"/>
@@ -21966,8 +23268,8 @@
       <c r="X28" s="11"/>
     </row>
     <row r="29" spans="2:24" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B29" s="43"/>
-      <c r="C29" s="41"/>
+      <c r="B29" s="165"/>
+      <c r="C29" s="163"/>
       <c r="D29" s="4"/>
       <c r="E29" s="4" t="s">
         <v>26</v>
@@ -22001,8 +23303,8 @@
       <c r="X29" s="11"/>
     </row>
     <row r="30" spans="2:24" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B30" s="43"/>
-      <c r="C30" s="40" t="s">
+      <c r="B30" s="165"/>
+      <c r="C30" s="162" t="s">
         <v>13</v>
       </c>
       <c r="D30" s="4"/>
@@ -22038,8 +23340,8 @@
       <c r="X30" s="11"/>
     </row>
     <row r="31" spans="2:24" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B31" s="43"/>
-      <c r="C31" s="41"/>
+      <c r="B31" s="165"/>
+      <c r="C31" s="163"/>
       <c r="D31" s="4"/>
       <c r="E31" s="4" t="s">
         <v>33</v>
@@ -22073,7 +23375,7 @@
       <c r="X31" s="11"/>
     </row>
     <row r="32" spans="2:24" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B32" s="43"/>
+      <c r="B32" s="165"/>
       <c r="C32" s="3" t="s">
         <v>14</v>
       </c>
@@ -22128,18 +23430,18 @@
       <c r="X33" s="11"/>
     </row>
     <row r="34" spans="2:24" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B34" s="42" t="s">
+      <c r="B34" s="164" t="s">
         <v>178</v>
       </c>
       <c r="C34" s="3"/>
-      <c r="D34" s="44" t="s">
+      <c r="D34" s="166" t="s">
         <v>3</v>
       </c>
-      <c r="E34" s="44"/>
-      <c r="F34" s="44" t="s">
+      <c r="E34" s="166"/>
+      <c r="F34" s="166" t="s">
         <v>4</v>
       </c>
-      <c r="G34" s="44"/>
+      <c r="G34" s="166"/>
       <c r="H34" s="8" t="s">
         <v>124</v>
       </c>
@@ -22149,10 +23451,10 @@
       <c r="J34" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="K34" s="44" t="s">
+      <c r="K34" s="166" t="s">
         <v>127</v>
       </c>
-      <c r="L34" s="44"/>
+      <c r="L34" s="166"/>
       <c r="N34" s="10"/>
       <c r="P34" s="2"/>
       <c r="Q34" s="2"/>
@@ -22165,8 +23467,8 @@
       <c r="X34" s="11"/>
     </row>
     <row r="35" spans="2:24" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B35" s="43"/>
-      <c r="C35" s="40" t="s">
+      <c r="B35" s="165"/>
+      <c r="C35" s="162" t="s">
         <v>5</v>
       </c>
       <c r="D35" s="4" t="s">
@@ -22208,8 +23510,8 @@
       <c r="X35" s="11"/>
     </row>
     <row r="36" spans="2:24" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B36" s="43"/>
-      <c r="C36" s="41"/>
+      <c r="B36" s="165"/>
+      <c r="C36" s="163"/>
       <c r="D36" s="4" t="s">
         <v>29</v>
       </c>
@@ -22249,8 +23551,8 @@
       <c r="X36" s="11"/>
     </row>
     <row r="37" spans="2:24" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B37" s="43"/>
-      <c r="C37" s="40" t="s">
+      <c r="B37" s="165"/>
+      <c r="C37" s="162" t="s">
         <v>186</v>
       </c>
       <c r="D37" s="4"/>
@@ -22286,8 +23588,8 @@
       <c r="X37" s="11"/>
     </row>
     <row r="38" spans="2:24" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B38" s="43"/>
-      <c r="C38" s="41"/>
+      <c r="B38" s="165"/>
+      <c r="C38" s="163"/>
       <c r="D38" s="4"/>
       <c r="E38" s="4" t="s">
         <v>211</v>
@@ -22321,8 +23623,8 @@
       <c r="X38" s="11"/>
     </row>
     <row r="39" spans="2:24" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="43"/>
-      <c r="C39" s="40" t="s">
+      <c r="B39" s="165"/>
+      <c r="C39" s="162" t="s">
         <v>228</v>
       </c>
       <c r="D39" s="4"/>
@@ -22358,8 +23660,8 @@
       <c r="X39" s="11"/>
     </row>
     <row r="40" spans="2:24" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B40" s="43"/>
-      <c r="C40" s="41"/>
+      <c r="B40" s="165"/>
+      <c r="C40" s="163"/>
       <c r="D40" s="4"/>
       <c r="E40" s="4" t="s">
         <v>215</v>
@@ -22393,8 +23695,8 @@
       <c r="X40" s="11"/>
     </row>
     <row r="41" spans="2:24" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B41" s="43"/>
-      <c r="C41" s="40" t="s">
+      <c r="B41" s="165"/>
+      <c r="C41" s="162" t="s">
         <v>134</v>
       </c>
       <c r="D41" s="4"/>
@@ -22430,8 +23732,8 @@
       <c r="X41" s="11"/>
     </row>
     <row r="42" spans="2:24" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B42" s="43"/>
-      <c r="C42" s="41"/>
+      <c r="B42" s="165"/>
+      <c r="C42" s="163"/>
       <c r="D42" s="4"/>
       <c r="E42" s="4" t="s">
         <v>222</v>
@@ -22465,8 +23767,8 @@
       <c r="X42" s="11"/>
     </row>
     <row r="43" spans="2:24" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B43" s="43"/>
-      <c r="C43" s="40" t="s">
+      <c r="B43" s="165"/>
+      <c r="C43" s="162" t="s">
         <v>139</v>
       </c>
       <c r="D43" s="4"/>
@@ -22502,8 +23804,8 @@
       <c r="X43" s="11"/>
     </row>
     <row r="44" spans="2:24" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B44" s="43"/>
-      <c r="C44" s="41"/>
+      <c r="B44" s="165"/>
+      <c r="C44" s="163"/>
       <c r="D44" s="4"/>
       <c r="E44" s="4" t="s">
         <v>143</v>
@@ -22537,7 +23839,7 @@
       <c r="X44" s="11"/>
     </row>
     <row r="45" spans="2:24" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B45" s="43"/>
+      <c r="B45" s="165"/>
       <c r="C45" s="3" t="s">
         <v>14</v>
       </c>
@@ -22581,18 +23883,18 @@
     </row>
     <row r="46" spans="2:24" hidden="1" x14ac:dyDescent="0.2"/>
     <row r="47" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B47" s="42" t="s">
+      <c r="B47" s="164" t="s">
         <v>130</v>
       </c>
       <c r="C47" s="3"/>
-      <c r="D47" s="44" t="s">
+      <c r="D47" s="166" t="s">
         <v>0</v>
       </c>
-      <c r="E47" s="44"/>
-      <c r="F47" s="44" t="s">
+      <c r="E47" s="166"/>
+      <c r="F47" s="166" t="s">
         <v>1</v>
       </c>
-      <c r="G47" s="44"/>
+      <c r="G47" s="166"/>
       <c r="H47" s="24" t="s">
         <v>124</v>
       </c>
@@ -22602,14 +23904,14 @@
       <c r="J47" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="K47" s="45" t="s">
+      <c r="K47" s="167" t="s">
         <v>2</v>
       </c>
-      <c r="L47" s="45"/>
+      <c r="L47" s="167"/>
     </row>
     <row r="48" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B48" s="43"/>
-      <c r="C48" s="40" t="s">
+      <c r="B48" s="165"/>
+      <c r="C48" s="162" t="s">
         <v>5</v>
       </c>
       <c r="D48" s="7" t="s">
@@ -22641,8 +23943,8 @@
       </c>
     </row>
     <row r="49" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B49" s="43"/>
-      <c r="C49" s="41"/>
+      <c r="B49" s="165"/>
+      <c r="C49" s="163"/>
       <c r="D49" s="4" t="s">
         <v>16</v>
       </c>
@@ -22672,8 +23974,8 @@
       </c>
     </row>
     <row r="50" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B50" s="43"/>
-      <c r="C50" s="40" t="s">
+      <c r="B50" s="165"/>
+      <c r="C50" s="162" t="s">
         <v>11</v>
       </c>
       <c r="D50" s="4"/>
@@ -22699,8 +24001,8 @@
       </c>
     </row>
     <row r="51" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B51" s="43"/>
-      <c r="C51" s="41"/>
+      <c r="B51" s="165"/>
+      <c r="C51" s="163"/>
       <c r="D51" s="4"/>
       <c r="E51" s="4" t="s">
         <v>26</v>
@@ -22724,8 +24026,8 @@
       </c>
     </row>
     <row r="52" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B52" s="43"/>
-      <c r="C52" s="40" t="s">
+      <c r="B52" s="165"/>
+      <c r="C52" s="162" t="s">
         <v>79</v>
       </c>
       <c r="D52" s="4"/>
@@ -22751,8 +24053,8 @@
       </c>
     </row>
     <row r="53" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B53" s="43"/>
-      <c r="C53" s="41"/>
+      <c r="B53" s="165"/>
+      <c r="C53" s="163"/>
       <c r="D53" s="4"/>
       <c r="E53" s="4" t="s">
         <v>85</v>
@@ -22776,7 +24078,7 @@
       </c>
     </row>
     <row r="54" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B54" s="43"/>
+      <c r="B54" s="165"/>
       <c r="C54" s="3" t="s">
         <v>14</v>
       </c>
@@ -22809,18 +24111,18 @@
       </c>
     </row>
     <row r="56" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B56" s="42" t="s">
+      <c r="B56" s="164" t="s">
         <v>131</v>
       </c>
       <c r="C56" s="3"/>
-      <c r="D56" s="44" t="s">
+      <c r="D56" s="166" t="s">
         <v>3</v>
       </c>
-      <c r="E56" s="44"/>
-      <c r="F56" s="44" t="s">
+      <c r="E56" s="166"/>
+      <c r="F56" s="166" t="s">
         <v>4</v>
       </c>
-      <c r="G56" s="44"/>
+      <c r="G56" s="166"/>
       <c r="H56" s="8" t="s">
         <v>124</v>
       </c>
@@ -22830,14 +24132,14 @@
       <c r="J56" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="K56" s="44" t="s">
+      <c r="K56" s="166" t="s">
         <v>127</v>
       </c>
-      <c r="L56" s="44"/>
+      <c r="L56" s="166"/>
     </row>
     <row r="57" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B57" s="43"/>
-      <c r="C57" s="40" t="s">
+      <c r="B57" s="165"/>
+      <c r="C57" s="162" t="s">
         <v>5</v>
       </c>
       <c r="D57" s="7" t="s">
@@ -22869,8 +24171,8 @@
       </c>
     </row>
     <row r="58" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B58" s="43"/>
-      <c r="C58" s="41"/>
+      <c r="B58" s="165"/>
+      <c r="C58" s="163"/>
       <c r="D58" s="4" t="s">
         <v>29</v>
       </c>
@@ -22900,8 +24202,8 @@
       </c>
     </row>
     <row r="59" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B59" s="43"/>
-      <c r="C59" s="40" t="s">
+      <c r="B59" s="165"/>
+      <c r="C59" s="162" t="s">
         <v>186</v>
       </c>
       <c r="D59" s="4"/>
@@ -22927,8 +24229,8 @@
       </c>
     </row>
     <row r="60" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B60" s="43"/>
-      <c r="C60" s="41"/>
+      <c r="B60" s="165"/>
+      <c r="C60" s="163"/>
       <c r="D60" s="4"/>
       <c r="E60" s="4" t="s">
         <v>213</v>
@@ -22952,8 +24254,8 @@
       </c>
     </row>
     <row r="61" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B61" s="43"/>
-      <c r="C61" s="40" t="s">
+      <c r="B61" s="165"/>
+      <c r="C61" s="162" t="s">
         <v>229</v>
       </c>
       <c r="D61" s="4"/>
@@ -22979,8 +24281,8 @@
       </c>
     </row>
     <row r="62" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B62" s="43"/>
-      <c r="C62" s="41"/>
+      <c r="B62" s="165"/>
+      <c r="C62" s="163"/>
       <c r="D62" s="4"/>
       <c r="E62" s="4" t="s">
         <v>163</v>
@@ -23004,8 +24306,8 @@
       </c>
     </row>
     <row r="63" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B63" s="43"/>
-      <c r="C63" s="40" t="s">
+      <c r="B63" s="165"/>
+      <c r="C63" s="162" t="s">
         <v>134</v>
       </c>
       <c r="D63" s="4"/>
@@ -23031,8 +24333,8 @@
       </c>
     </row>
     <row r="64" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B64" s="43"/>
-      <c r="C64" s="41"/>
+      <c r="B64" s="165"/>
+      <c r="C64" s="163"/>
       <c r="D64" s="4"/>
       <c r="E64" s="4" t="s">
         <v>251</v>
@@ -23056,8 +24358,8 @@
       </c>
     </row>
     <row r="65" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B65" s="43"/>
-      <c r="C65" s="40" t="s">
+      <c r="B65" s="165"/>
+      <c r="C65" s="162" t="s">
         <v>149</v>
       </c>
       <c r="D65" s="4"/>
@@ -23083,8 +24385,8 @@
       </c>
     </row>
     <row r="66" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B66" s="43"/>
-      <c r="C66" s="41"/>
+      <c r="B66" s="165"/>
+      <c r="C66" s="163"/>
       <c r="D66" s="4"/>
       <c r="E66" s="4" t="s">
         <v>210</v>
@@ -23108,7 +24410,7 @@
       </c>
     </row>
     <row r="67" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B67" s="43"/>
+      <c r="B67" s="165"/>
       <c r="C67" s="3" t="s">
         <v>14</v>
       </c>
@@ -23141,18 +24443,18 @@
       </c>
     </row>
     <row r="69" spans="2:12" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B69" s="42" t="s">
+      <c r="B69" s="164" t="s">
         <v>132</v>
       </c>
       <c r="C69" s="3"/>
-      <c r="D69" s="44" t="s">
+      <c r="D69" s="166" t="s">
         <v>0</v>
       </c>
-      <c r="E69" s="44"/>
-      <c r="F69" s="44" t="s">
+      <c r="E69" s="166"/>
+      <c r="F69" s="166" t="s">
         <v>1</v>
       </c>
-      <c r="G69" s="44"/>
+      <c r="G69" s="166"/>
       <c r="H69" s="8" t="s">
         <v>124</v>
       </c>
@@ -23162,14 +24464,14 @@
       <c r="J69" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="K69" s="44" t="s">
+      <c r="K69" s="166" t="s">
         <v>2</v>
       </c>
-      <c r="L69" s="44"/>
+      <c r="L69" s="166"/>
     </row>
     <row r="70" spans="2:12" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B70" s="43"/>
-      <c r="C70" s="40" t="s">
+      <c r="B70" s="165"/>
+      <c r="C70" s="162" t="s">
         <v>5</v>
       </c>
       <c r="D70" s="4" t="s">
@@ -23201,8 +24503,8 @@
       </c>
     </row>
     <row r="71" spans="2:12" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B71" s="43"/>
-      <c r="C71" s="41"/>
+      <c r="B71" s="165"/>
+      <c r="C71" s="163"/>
       <c r="D71" s="4" t="s">
         <v>16</v>
       </c>
@@ -23232,8 +24534,8 @@
       </c>
     </row>
     <row r="72" spans="2:12" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B72" s="43"/>
-      <c r="C72" s="40" t="s">
+      <c r="B72" s="165"/>
+      <c r="C72" s="162" t="s">
         <v>11</v>
       </c>
       <c r="D72" s="4"/>
@@ -23259,8 +24561,8 @@
       </c>
     </row>
     <row r="73" spans="2:12" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B73" s="43"/>
-      <c r="C73" s="41"/>
+      <c r="B73" s="165"/>
+      <c r="C73" s="163"/>
       <c r="D73" s="4"/>
       <c r="E73" s="4" t="s">
         <v>26</v>
@@ -23284,8 +24586,8 @@
       </c>
     </row>
     <row r="74" spans="2:12" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B74" s="43"/>
-      <c r="C74" s="40" t="s">
+      <c r="B74" s="165"/>
+      <c r="C74" s="162" t="s">
         <v>111</v>
       </c>
       <c r="D74" s="4"/>
@@ -23311,8 +24613,8 @@
       </c>
     </row>
     <row r="75" spans="2:12" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B75" s="43"/>
-      <c r="C75" s="41"/>
+      <c r="B75" s="165"/>
+      <c r="C75" s="163"/>
       <c r="D75" s="4"/>
       <c r="E75" s="4" t="s">
         <v>116</v>
@@ -23336,7 +24638,7 @@
       </c>
     </row>
     <row r="76" spans="2:12" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B76" s="43"/>
+      <c r="B76" s="165"/>
       <c r="C76" s="3" t="s">
         <v>14</v>
       </c>
@@ -23370,18 +24672,18 @@
     </row>
     <row r="77" spans="2:12" hidden="1" x14ac:dyDescent="0.2"/>
     <row r="78" spans="2:12" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B78" s="42" t="s">
+      <c r="B78" s="164" t="s">
         <v>133</v>
       </c>
       <c r="C78" s="3"/>
-      <c r="D78" s="44" t="s">
+      <c r="D78" s="166" t="s">
         <v>3</v>
       </c>
-      <c r="E78" s="44"/>
-      <c r="F78" s="44" t="s">
+      <c r="E78" s="166"/>
+      <c r="F78" s="166" t="s">
         <v>4</v>
       </c>
-      <c r="G78" s="44"/>
+      <c r="G78" s="166"/>
       <c r="H78" s="8" t="s">
         <v>124</v>
       </c>
@@ -23391,14 +24693,14 @@
       <c r="J78" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="K78" s="44" t="s">
+      <c r="K78" s="166" t="s">
         <v>127</v>
       </c>
-      <c r="L78" s="44"/>
+      <c r="L78" s="166"/>
     </row>
     <row r="79" spans="2:12" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B79" s="43"/>
-      <c r="C79" s="40" t="s">
+      <c r="B79" s="165"/>
+      <c r="C79" s="162" t="s">
         <v>5</v>
       </c>
       <c r="D79" s="4" t="s">
@@ -23430,8 +24732,8 @@
       </c>
     </row>
     <row r="80" spans="2:12" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B80" s="43"/>
-      <c r="C80" s="41"/>
+      <c r="B80" s="165"/>
+      <c r="C80" s="163"/>
       <c r="D80" s="4" t="s">
         <v>29</v>
       </c>
@@ -23461,8 +24763,8 @@
       </c>
     </row>
     <row r="81" spans="2:12" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B81" s="43"/>
-      <c r="C81" s="40" t="s">
+      <c r="B81" s="165"/>
+      <c r="C81" s="162" t="s">
         <v>186</v>
       </c>
       <c r="D81" s="4"/>
@@ -23488,8 +24790,8 @@
       </c>
     </row>
     <row r="82" spans="2:12" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B82" s="43"/>
-      <c r="C82" s="41"/>
+      <c r="B82" s="165"/>
+      <c r="C82" s="163"/>
       <c r="D82" s="4"/>
       <c r="E82" s="4" t="s">
         <v>16</v>
@@ -23513,8 +24815,8 @@
       </c>
     </row>
     <row r="83" spans="2:12" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B83" s="43"/>
-      <c r="C83" s="40" t="s">
+      <c r="B83" s="165"/>
+      <c r="C83" s="162" t="s">
         <v>230</v>
       </c>
       <c r="D83" s="4"/>
@@ -23540,8 +24842,8 @@
       </c>
     </row>
     <row r="84" spans="2:12" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B84" s="43"/>
-      <c r="C84" s="41"/>
+      <c r="B84" s="165"/>
+      <c r="C84" s="163"/>
       <c r="D84" s="4"/>
       <c r="E84" s="4" t="s">
         <v>21</v>
@@ -23565,8 +24867,8 @@
       </c>
     </row>
     <row r="85" spans="2:12" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B85" s="43"/>
-      <c r="C85" s="40" t="s">
+      <c r="B85" s="165"/>
+      <c r="C85" s="162" t="s">
         <v>134</v>
       </c>
       <c r="D85" s="4"/>
@@ -23592,8 +24894,8 @@
       </c>
     </row>
     <row r="86" spans="2:12" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B86" s="43"/>
-      <c r="C86" s="41"/>
+      <c r="B86" s="165"/>
+      <c r="C86" s="163"/>
       <c r="D86" s="4"/>
       <c r="E86" s="4" t="s">
         <v>251</v>
@@ -23617,8 +24919,8 @@
       </c>
     </row>
     <row r="87" spans="2:12" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B87" s="43"/>
-      <c r="C87" s="40" t="s">
+      <c r="B87" s="165"/>
+      <c r="C87" s="162" t="s">
         <v>141</v>
       </c>
       <c r="D87" s="4"/>
@@ -23644,8 +24946,8 @@
       </c>
     </row>
     <row r="88" spans="2:12" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B88" s="43"/>
-      <c r="C88" s="41"/>
+      <c r="B88" s="165"/>
+      <c r="C88" s="163"/>
       <c r="D88" s="4"/>
       <c r="E88" s="4" t="s">
         <v>258</v>
@@ -23669,7 +24971,7 @@
       </c>
     </row>
     <row r="89" spans="2:12" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B89" s="43"/>
+      <c r="B89" s="165"/>
       <c r="C89" s="3" t="s">
         <v>14</v>
       </c>
@@ -23704,54 +25006,6 @@
     <row r="90" spans="2:12" hidden="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="64">
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="B34:B45"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="K34:L34"/>
-    <mergeCell ref="C35:C36"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="C43:C44"/>
-    <mergeCell ref="C37:C38"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="K25:L25"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="D56:E56"/>
-    <mergeCell ref="F56:G56"/>
-    <mergeCell ref="K56:L56"/>
-    <mergeCell ref="D47:E47"/>
-    <mergeCell ref="F47:G47"/>
-    <mergeCell ref="K47:L47"/>
-    <mergeCell ref="B78:B89"/>
-    <mergeCell ref="D69:E69"/>
-    <mergeCell ref="F69:G69"/>
-    <mergeCell ref="K69:L69"/>
-    <mergeCell ref="D78:E78"/>
-    <mergeCell ref="F78:G78"/>
-    <mergeCell ref="K78:L78"/>
-    <mergeCell ref="C79:C80"/>
-    <mergeCell ref="C85:C86"/>
-    <mergeCell ref="C87:C88"/>
-    <mergeCell ref="C70:C71"/>
-    <mergeCell ref="C72:C73"/>
-    <mergeCell ref="C74:C75"/>
-    <mergeCell ref="C81:C82"/>
-    <mergeCell ref="C83:C84"/>
-    <mergeCell ref="B2:B9"/>
-    <mergeCell ref="B11:B22"/>
-    <mergeCell ref="B47:B54"/>
-    <mergeCell ref="B56:B67"/>
-    <mergeCell ref="B69:B76"/>
-    <mergeCell ref="B25:B32"/>
     <mergeCell ref="C65:C66"/>
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="C5:C6"/>
@@ -23768,12 +25022,60 @@
     <mergeCell ref="C16:C17"/>
     <mergeCell ref="C59:C60"/>
     <mergeCell ref="C61:C62"/>
+    <mergeCell ref="B2:B9"/>
+    <mergeCell ref="B11:B22"/>
+    <mergeCell ref="B47:B54"/>
+    <mergeCell ref="B56:B67"/>
+    <mergeCell ref="B69:B76"/>
+    <mergeCell ref="B25:B32"/>
+    <mergeCell ref="B78:B89"/>
+    <mergeCell ref="D69:E69"/>
+    <mergeCell ref="F69:G69"/>
+    <mergeCell ref="K69:L69"/>
+    <mergeCell ref="D78:E78"/>
+    <mergeCell ref="F78:G78"/>
+    <mergeCell ref="K78:L78"/>
+    <mergeCell ref="C79:C80"/>
+    <mergeCell ref="C85:C86"/>
+    <mergeCell ref="C87:C88"/>
+    <mergeCell ref="C70:C71"/>
+    <mergeCell ref="C72:C73"/>
+    <mergeCell ref="C74:C75"/>
+    <mergeCell ref="C81:C82"/>
+    <mergeCell ref="C83:C84"/>
+    <mergeCell ref="D56:E56"/>
+    <mergeCell ref="F56:G56"/>
+    <mergeCell ref="K56:L56"/>
+    <mergeCell ref="D47:E47"/>
+    <mergeCell ref="F47:G47"/>
+    <mergeCell ref="K47:L47"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="K25:L25"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="B34:B45"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="K34:L34"/>
+    <mergeCell ref="C35:C36"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="C43:C44"/>
+    <mergeCell ref="C37:C38"/>
+    <mergeCell ref="C39:C40"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C46079C1-F4F3-4E3A-8CE8-2113D4F28B6B}">
   <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -24006,7 +25308,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2D15DE7-CAF9-4A3C-99EC-AE501B1448E2}">
   <dimension ref="A1:M47"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>

--- a/Projects/MISQ/MISQ round 2/afterSEmeeting260624_results, theory and LR.xlsx
+++ b/Projects/MISQ/MISQ round 2/afterSEmeeting260624_results, theory and LR.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dylanchen/Desktop/geek-community/Projects/MISQ/MISQ round 2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EE90A10-09AB-9B47-8D30-D39EA99452E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2608270F-413F-6A4D-BACE-2FB84F46E895}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19420" activeTab="1" xr2:uid="{30F402B7-E6D8-E34B-8063-713AC97DE139}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19580" activeTab="2" xr2:uid="{30F402B7-E6D8-E34B-8063-713AC97DE139}"/>
   </bookViews>
   <sheets>
     <sheet name="Theory" sheetId="8" r:id="rId1"/>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1270" uniqueCount="546">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1343" uniqueCount="574">
   <si>
     <t>DV: # human answers</t>
   </si>
@@ -2291,6 +2291,90 @@
     <t>- Quality is a slow signal—inaccessible without deliberate reading. 
 - High quality triggers "surprise", forcing System 2 to override.
 - what's more, professional identity threat is "sufficiently important" to activate System 2</t>
+  </si>
+  <si>
+    <t>-0.198 *</t>
+  </si>
+  <si>
+    <t>0.304 **</t>
+  </si>
+  <si>
+    <t>-0.058 ***</t>
+  </si>
+  <si>
+    <t>0.029</t>
+  </si>
+  <si>
+    <t>(0.149)</t>
+  </si>
+  <si>
+    <t>(0.025)</t>
+  </si>
+  <si>
+    <t>-0.060</t>
+  </si>
+  <si>
+    <t>(0.064)</t>
+  </si>
+  <si>
+    <t>(0.088)</t>
+  </si>
+  <si>
+    <t>difficult questions</t>
+  </si>
+  <si>
+    <t>easy questions</t>
+  </si>
+  <si>
+    <t>2,373</t>
+  </si>
+  <si>
+    <t>1,230</t>
+  </si>
+  <si>
+    <t>-0.002</t>
+  </si>
+  <si>
+    <t>-0.031 *</t>
+  </si>
+  <si>
+    <t>0.382 ***</t>
+  </si>
+  <si>
+    <t>0.330 ***</t>
+  </si>
+  <si>
+    <t>1,365</t>
+  </si>
+  <si>
+    <t>1,320</t>
+  </si>
+  <si>
+    <t>expert first answer</t>
+  </si>
+  <si>
+    <t>rookie first answer</t>
+  </si>
+  <si>
+    <t>difficult question -&gt; AI weak competitor -&gt; let me answer</t>
+  </si>
+  <si>
+    <t>easy question -&gt; AI even weak still enough</t>
+  </si>
+  <si>
+    <t>difficult question + AI lengthy -&gt; may be comprehensive -&gt; deter</t>
+  </si>
+  <si>
+    <t>easy question + AI length -&gt; AI is enough</t>
+  </si>
+  <si>
+    <t>overconfidence</t>
+  </si>
+  <si>
+    <t>expert -&gt; facing surprise, stronger identity threat</t>
+  </si>
+  <si>
+    <t>Expert are not affected by length, rookie regard length as low-quality heuristic</t>
   </si>
 </sst>
 </file>
@@ -2668,7 +2752,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="168">
+  <cellXfs count="179">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -2984,12 +3068,6 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3005,26 +3083,56 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
@@ -3047,46 +3155,22 @@
     <xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3101,8 +3185,17 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3113,17 +3206,8 @@
     <xf numFmtId="49" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -3143,6 +3227,35 @@
     <xf numFmtId="49" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3166,2848 +3279,6 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout>
-        <c:manualLayout>
-          <c:layoutTarget val="inner"/>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="0.19658898783623088"/>
-          <c:y val="5.6745720814710666E-2"/>
-          <c:w val="0.75834536036245515"/>
-          <c:h val="0.75926640516999511"/>
-        </c:manualLayout>
-      </c:layout>
-      <c:scatterChart>
-        <c:scatterStyle val="lineMarker"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'interaction plot (20260608)'!$B$17</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>AI Answer</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="accent4"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-              <a:miter lim="800000"/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent4"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:dPt>
-            <c:idx val="2"/>
-            <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
-              <c:spPr>
-                <a:solidFill>
-                  <a:schemeClr val="accent4"/>
-                </a:solidFill>
-                <a:ln w="9525">
-                  <a:noFill/>
-                </a:ln>
-                <a:effectLst/>
-              </c:spPr>
-            </c:marker>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-                <a:solidFill>
-                  <a:schemeClr val="accent4"/>
-                </a:solidFill>
-                <a:prstDash val="dash"/>
-                <a:miter lim="800000"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-EE68-6544-A7C5-531FB802F206}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'interaction plot (20260608)'!$A$18:$A$22</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>6.2315934999999998</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>5.1203884999999998</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'interaction plot (20260608)'!$B$18:$B$22</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>-5.4421707499999999E-2</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>-4.4174824999999862E-3</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.22600000000000001</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-EE68-6544-A7C5-531FB802F206}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'interaction plot (20260608)'!$C$17</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>No Answer</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent2"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:dPt>
-            <c:idx val="0"/>
-            <c:marker>
-              <c:symbol val="none"/>
-            </c:marker>
-            <c:bubble3D val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-EE68-6544-A7C5-531FB802F206}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'interaction plot (20260608)'!$A$21:$A$22</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'interaction plot (20260608)'!$C$21:$C$22</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-EE68-6544-A7C5-531FB802F206}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:axId val="1273614864"/>
-        <c:axId val="1273614384"/>
-      </c:scatterChart>
-      <c:valAx>
-        <c:axId val="1273614384"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-          <c:max val="0.4"/>
-          <c:min val="-0.1"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-US" sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0" dirty="0">
-                    <a:solidFill>
-                      <a:prstClr val="black">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:prstClr>
-                    </a:solidFill>
-                  </a:rPr>
-                  <a:t>#</a:t>
-                </a:r>
-                <a:r>
-                  <a:rPr lang="zh-CN" altLang="en-US" sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0" dirty="0">
-                    <a:solidFill>
-                      <a:prstClr val="black">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:prstClr>
-                    </a:solidFill>
-                  </a:rPr>
-                  <a:t> </a:t>
-                </a:r>
-                <a:r>
-                  <a:rPr lang="en-US" sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0" dirty="0">
-                    <a:solidFill>
-                      <a:prstClr val="black">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:prstClr>
-                    </a:solidFill>
-                  </a:rPr>
-                  <a:t>Human</a:t>
-                </a:r>
-                <a:r>
-                  <a:rPr lang="zh-CN" altLang="en-US" sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0" dirty="0">
-                    <a:solidFill>
-                      <a:prstClr val="black">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:prstClr>
-                    </a:solidFill>
-                  </a:rPr>
-                  <a:t> </a:t>
-                </a:r>
-                <a:r>
-                  <a:rPr lang="en-US" sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0" dirty="0">
-                    <a:solidFill>
-                      <a:prstClr val="black">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:prstClr>
-                    </a:solidFill>
-                  </a:rPr>
-                  <a:t>Answer</a:t>
-                </a:r>
-                <a:r>
-                  <a:rPr lang="zh-CN" altLang="en-US" sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0" dirty="0">
-                    <a:solidFill>
-                      <a:prstClr val="black">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:prstClr>
-                    </a:solidFill>
-                  </a:rPr>
-                  <a:t> </a:t>
-                </a:r>
-                <a:r>
-                  <a:rPr lang="en-US" sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0" dirty="0">
-                    <a:solidFill>
-                      <a:prstClr val="black">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:prstClr>
-                    </a:solidFill>
-                  </a:rPr>
-                  <a:t>within</a:t>
-                </a:r>
-                <a:r>
-                  <a:rPr lang="zh-CN" altLang="en-US" sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0" dirty="0">
-                    <a:solidFill>
-                      <a:prstClr val="black">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:prstClr>
-                    </a:solidFill>
-                  </a:rPr>
-                  <a:t> </a:t>
-                </a:r>
-                <a:r>
-                  <a:rPr lang="en-US" sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0" dirty="0">
-                    <a:solidFill>
-                      <a:prstClr val="black">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:prstClr>
-                    </a:solidFill>
-                  </a:rPr>
-                  <a:t>7</a:t>
-                </a:r>
-                <a:r>
-                  <a:rPr lang="zh-CN" altLang="en-US" sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0" dirty="0">
-                    <a:solidFill>
-                      <a:prstClr val="black">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:prstClr>
-                    </a:solidFill>
-                  </a:rPr>
-                  <a:t> </a:t>
-                </a:r>
-                <a:r>
-                  <a:rPr lang="en-US" sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0" dirty="0">
-                    <a:solidFill>
-                      <a:prstClr val="black">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:prstClr>
-                    </a:solidFill>
-                  </a:rPr>
-                  <a:t>days</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1273614864"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-        <c:majorUnit val="0.2"/>
-      </c:valAx>
-      <c:valAx>
-        <c:axId val="1273614864"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-          <c:max val="7"/>
-          <c:min val="0"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-US"/>
-                  <a:t>AI</a:t>
-                </a:r>
-                <a:r>
-                  <a:rPr lang="zh-CN"/>
-                  <a:t> </a:t>
-                </a:r>
-                <a:r>
-                  <a:rPr lang="en-US"/>
-                  <a:t>answer</a:t>
-                </a:r>
-                <a:r>
-                  <a:rPr lang="zh-CN"/>
-                  <a:t> </a:t>
-                </a:r>
-                <a:r>
-                  <a:rPr lang="en-US"/>
-                  <a:t>Length</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:layout>
-            <c:manualLayout>
-              <c:xMode val="edge"/>
-              <c:yMode val="edge"/>
-              <c:x val="0.37847856559201215"/>
-              <c:y val="0.90839098154438758"/>
-            </c:manualLayout>
-          </c:layout>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1273614384"/>
-        <c:crossesAt val="-0.30000000000000004"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:layout>
-        <c:manualLayout>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="0.59825909791468757"/>
-          <c:y val="0.10924970324905096"/>
-          <c:w val="0.3334735333390908"/>
-          <c:h val="0.17773390683414819"/>
-        </c:manualLayout>
-      </c:layout>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr sz="1800"/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:scatterChart>
-        <c:scatterStyle val="lineMarker"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'interaction plot'!$C$34</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Human Answer</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'interaction plot'!$A$45:$A$46</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>0.25836000000000003</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.63216220000000001</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'interaction plot'!$C$45:$C$46</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>0.12762984000000002</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.31228812680000001</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-E8E4-4895-8FBF-6774C9D132F7}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'interaction plot'!$B$34</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>AI Answer</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'interaction plot'!$A$43:$A$44</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>0.40333040000000009</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.70744960000000001</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'interaction plot'!$B$43:$B$44</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>0.15528220400000003</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.272368096</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-E8E4-4895-8FBF-6774C9D132F7}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:axId val="1311726864"/>
-        <c:axId val="1273565424"/>
-      </c:scatterChart>
-      <c:valAx>
-        <c:axId val="1311726864"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="t"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-US"/>
-                  <a:t>Quality</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1273565424"/>
-        <c:crossesAt val="0.5"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:valAx>
-        <c:axId val="1273565424"/>
-        <c:scaling>
-          <c:orientation val="maxMin"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-US"/>
-                  <a:t>Similarity</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="low"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1311726864"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-        <c:majorUnit val="0.1"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout>
-        <c:manualLayout>
-          <c:layoutTarget val="inner"/>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="0.13831647104153175"/>
-          <c:y val="4.3437866128041271E-2"/>
-          <c:w val="0.8211485468131059"/>
-          <c:h val="0.85308113459581947"/>
-        </c:manualLayout>
-      </c:layout>
-      <c:scatterChart>
-        <c:scatterStyle val="lineMarker"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'interaction plot'!$B$16</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>AI Answer</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="accent4"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-              <a:miter lim="800000"/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent4"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:dPt>
-            <c:idx val="2"/>
-            <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
-              <c:spPr>
-                <a:solidFill>
-                  <a:schemeClr val="accent4"/>
-                </a:solidFill>
-                <a:ln w="9525">
-                  <a:solidFill>
-                    <a:schemeClr val="accent1"/>
-                  </a:solidFill>
-                </a:ln>
-                <a:effectLst/>
-              </c:spPr>
-            </c:marker>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-                <a:solidFill>
-                  <a:schemeClr val="accent4"/>
-                </a:solidFill>
-                <a:prstDash val="dash"/>
-                <a:miter lim="800000"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000000-7104-40F8-95BE-8E1EEF518DD6}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'interaction plot'!$A$17:$A$19</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>6.2315934999999998</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>5.1203884999999998</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'interaction plot'!$B$17:$B$19</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>-5.4421707499999999E-2</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>-4.4174824999999862E-3</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.22600000000000001</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-885A-4607-8931-2D78CBA2F14B}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'interaction plot'!$C$16</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>No Answer</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent2"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'interaction plot'!$A$17:$A$19</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>6.2315934999999998</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>5.1203884999999998</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'interaction plot'!$C$17:$C$19</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
-                <c:pt idx="2">
-                  <c:v>0</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-885A-4607-8931-2D78CBA2F14B}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:axId val="1273614864"/>
-        <c:axId val="1273614384"/>
-      </c:scatterChart>
-      <c:valAx>
-        <c:axId val="1273614384"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-          <c:max val="0.4"/>
-          <c:min val="-0.2"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-US"/>
-                  <a:t>#answer</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1273614864"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-        <c:majorUnit val="0.2"/>
-      </c:valAx>
-      <c:valAx>
-        <c:axId val="1273614864"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-US"/>
-                  <a:t>Length</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1273614384"/>
-        <c:crossesAt val="-0.30000000000000004"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:layout>
-        <c:manualLayout>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="0.35166708695010179"/>
-          <c:y val="0.10165455671610976"/>
-          <c:w val="0.18846405449128323"/>
-          <c:h val="0.13327620388496833"/>
-        </c:manualLayout>
-      </c:layout>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-  </c:chart>
-  <c:spPr>
-    <a:noFill/>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:scatterChart>
-        <c:scatterStyle val="lineMarker"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'interaction plot'!$B$23</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>AI Answer</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'interaction plot'!$A$24:$A$27</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>6.2315934999999998</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>5.1203884999999998</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'interaction plot'!$B$24:$B$27</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>-0.30157172450000003</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>-4.9328189499999953E-2</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-DAC9-F64E-B7E3-49212B2D3212}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'interaction plot'!$C$23</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Human Answer</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent2"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'interaction plot'!$A$24:$A$27</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>6.2315934999999998</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>5.1203884999999998</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'interaction plot'!$C$24:$C$27</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="2">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-DAC9-F64E-B7E3-49212B2D3212}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:axId val="1273614864"/>
-        <c:axId val="1273614384"/>
-      </c:scatterChart>
-      <c:valAx>
-        <c:axId val="1273614384"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-US"/>
-                  <a:t>#answer</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1273614864"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:valAx>
-        <c:axId val="1273614864"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-US"/>
-                  <a:t>Length</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1273614384"/>
-        <c:crossesAt val="-0.30000000000000004"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout>
-        <c:manualLayout>
-          <c:layoutTarget val="inner"/>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="0.18166413041912891"/>
-          <c:y val="4.3874636000693454E-2"/>
-          <c:w val="0.76843150800609039"/>
-          <c:h val="0.77262652213356342"/>
-        </c:manualLayout>
-      </c:layout>
-      <c:scatterChart>
-        <c:scatterStyle val="lineMarker"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'interaction plot (20260608)'!$B$25</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>AI Answer</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:srgbClr val="0F9FD5"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:dPt>
-            <c:idx val="0"/>
-            <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
-              <c:spPr>
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-                <a:ln w="9525">
-                  <a:noFill/>
-                </a:ln>
-                <a:effectLst/>
-              </c:spPr>
-            </c:marker>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:srgbClr val="0F9FD5"/>
-                </a:solidFill>
-                <a:prstDash val="dash"/>
-                <a:round/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-B5A6-104B-B051-7F492BE93299}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="1"/>
-            <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
-              <c:spPr>
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-                <a:ln w="9525">
-                  <a:noFill/>
-                </a:ln>
-                <a:effectLst/>
-              </c:spPr>
-            </c:marker>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:srgbClr val="0F9FD5"/>
-                </a:solidFill>
-                <a:prstDash val="dash"/>
-                <a:round/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-B5A6-104B-B051-7F492BE93299}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'interaction plot (20260608)'!$A$28:$A$30</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.40333040000000009</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.70744960000000001</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'interaction plot (20260608)'!$B$28:$B$30</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>-0.12</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2.1165640000000013E-2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.12760736</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-B5A6-104B-B051-7F492BE93299}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'interaction plot (20260608)'!$C$25</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>No Answer</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent2"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:dPt>
-            <c:idx val="0"/>
-            <c:marker>
-              <c:symbol val="none"/>
-            </c:marker>
-            <c:bubble3D val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-B5A6-104B-B051-7F492BE93299}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'interaction plot (20260608)'!$A$26:$A$27</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>0.8</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'interaction plot (20260608)'!$C$26:$C$27</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-B5A6-104B-B051-7F492BE93299}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:axId val="1273614864"/>
-        <c:axId val="1273614384"/>
-      </c:scatterChart>
-      <c:valAx>
-        <c:axId val="1273614384"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-          <c:min val="-0.2"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-US" sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0" dirty="0">
-                    <a:solidFill>
-                      <a:prstClr val="black">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:prstClr>
-                    </a:solidFill>
-                  </a:rPr>
-                  <a:t>First</a:t>
-                </a:r>
-                <a:r>
-                  <a:rPr lang="zh-CN" altLang="en-US" sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0" dirty="0">
-                    <a:solidFill>
-                      <a:prstClr val="black">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:prstClr>
-                    </a:solidFill>
-                  </a:rPr>
-                  <a:t> </a:t>
-                </a:r>
-                <a:r>
-                  <a:rPr lang="en-US" sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0" dirty="0">
-                    <a:solidFill>
-                      <a:prstClr val="black">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:prstClr>
-                    </a:solidFill>
-                  </a:rPr>
-                  <a:t>Human</a:t>
-                </a:r>
-                <a:r>
-                  <a:rPr lang="zh-CN" altLang="en-US" sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0" dirty="0">
-                    <a:solidFill>
-                      <a:prstClr val="black">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:prstClr>
-                    </a:solidFill>
-                  </a:rPr>
-                  <a:t> </a:t>
-                </a:r>
-                <a:r>
-                  <a:rPr lang="en-US" sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0" dirty="0">
-                    <a:solidFill>
-                      <a:prstClr val="black">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:prstClr>
-                    </a:solidFill>
-                  </a:rPr>
-                  <a:t>Answer</a:t>
-                </a:r>
-                <a:r>
-                  <a:rPr lang="zh-CN" altLang="en-US" sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0" dirty="0">
-                    <a:solidFill>
-                      <a:prstClr val="black">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:prstClr>
-                    </a:solidFill>
-                  </a:rPr>
-                  <a:t> </a:t>
-                </a:r>
-                <a:r>
-                  <a:rPr lang="en-US" sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0" dirty="0">
-                    <a:solidFill>
-                      <a:prstClr val="black">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:prstClr>
-                    </a:solidFill>
-                  </a:rPr>
-                  <a:t>Quality</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1273614864"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-        <c:majorUnit val="0.2"/>
-      </c:valAx>
-      <c:valAx>
-        <c:axId val="1273614864"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-          <c:max val="0.8"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-US"/>
-                  <a:t>AI</a:t>
-                </a:r>
-                <a:r>
-                  <a:rPr lang="zh-CN"/>
-                  <a:t> </a:t>
-                </a:r>
-                <a:r>
-                  <a:rPr lang="en-US"/>
-                  <a:t>answer</a:t>
-                </a:r>
-                <a:r>
-                  <a:rPr lang="zh-CN"/>
-                  <a:t> </a:t>
-                </a:r>
-                <a:r>
-                  <a:rPr lang="en-US"/>
-                  <a:t>Quality</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1273614384"/>
-        <c:crossesAt val="-0.30000000000000004"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:layout>
-        <c:manualLayout>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="0.59665699735930589"/>
-          <c:y val="0.60974883273512892"/>
-          <c:w val="0.35334525013277662"/>
-          <c:h val="0.16578553657770492"/>
-        </c:manualLayout>
-      </c:layout>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr sz="1800"/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -6607,7 +3878,489 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'interaction plot'!$B$23</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>AI Answer</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'interaction plot'!$A$24:$A$27</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>6.2315934999999998</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.1203884999999998</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'interaction plot'!$B$24:$B$27</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>-0.30157172450000003</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-4.9328189499999953E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-DAC9-F64E-B7E3-49212B2D3212}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'interaction plot'!$C$23</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Human Answer</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'interaction plot'!$A$24:$A$27</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>6.2315934999999998</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.1203884999999998</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'interaction plot'!$C$24:$C$27</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-DAC9-F64E-B7E3-49212B2D3212}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1273614864"/>
+        <c:axId val="1273614384"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1273614384"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>#answer</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1273614864"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1273614864"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Length</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1273614384"/>
+        <c:crossesAt val="-0.30000000000000004"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -7189,7 +4942,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -7880,7 +5633,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -8542,7 +6295,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -9235,7 +6988,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -9938,7 +7691,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -10538,6 +8291,1013 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'interaction plot'!$C$34</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Human Answer</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'interaction plot'!$A$45:$A$46</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0.25836000000000003</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.63216220000000001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'interaction plot'!$C$45:$C$46</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0.12762984000000002</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.31228812680000001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-E8E4-4895-8FBF-6774C9D132F7}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'interaction plot'!$B$34</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>AI Answer</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'interaction plot'!$A$43:$A$44</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0.40333040000000009</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.70744960000000001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'interaction plot'!$B$43:$B$44</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0.15528220400000003</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.272368096</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-E8E4-4895-8FBF-6774C9D132F7}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1311726864"/>
+        <c:axId val="1273565424"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1311726864"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="t"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Quality</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1273565424"/>
+        <c:crossesAt val="0.5"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1273565424"/>
+        <c:scaling>
+          <c:orientation val="maxMin"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Similarity</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="low"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1311726864"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+        <c:majorUnit val="0.1"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.13831647104153175"/>
+          <c:y val="4.3437866128041271E-2"/>
+          <c:w val="0.8211485468131059"/>
+          <c:h val="0.85308113459581947"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'interaction plot'!$B$16</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>AI Answer</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+              <a:miter lim="800000"/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:marker>
+              <c:symbol val="circle"/>
+              <c:size val="5"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+                <a:ln w="9525">
+                  <a:solidFill>
+                    <a:schemeClr val="accent1"/>
+                  </a:solidFill>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:marker>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+                <a:prstDash val="dash"/>
+                <a:miter lim="800000"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000000-7104-40F8-95BE-8E1EEF518DD6}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'interaction plot'!$A$17:$A$19</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>6.2315934999999998</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.1203884999999998</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'interaction plot'!$B$17:$B$19</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>-5.4421707499999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-4.4174824999999862E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.22600000000000001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-885A-4607-8931-2D78CBA2F14B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'interaction plot'!$C$16</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>No Answer</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'interaction plot'!$A$17:$A$19</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>6.2315934999999998</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.1203884999999998</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'interaction plot'!$C$17:$C$19</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-885A-4607-8931-2D78CBA2F14B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1273614864"/>
+        <c:axId val="1273614384"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1273614384"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="0.4"/>
+          <c:min val="-0.2"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>#answer</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1273614864"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+        <c:majorUnit val="0.2"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1273614864"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Length</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1273614384"/>
+        <c:crossesAt val="-0.30000000000000004"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.35166708695010179"/>
+          <c:y val="0.10165455671610976"/>
+          <c:w val="0.18846405449128323"/>
+          <c:h val="0.13327620388496833"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:noFill/>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -10579,86 +9339,6 @@
 </file>
 
 <file path=xl/charts/colors10.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/colors11.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/colors12.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -12050,7 +10730,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -12566,7 +11246,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -13082,7 +11762,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -13598,7 +12278,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -14114,7 +12794,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -14630,7 +13310,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -15146,7 +13826,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style8.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -15662,7 +14342,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style9.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -16178,1116 +14858,8 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style8.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/charts/style9.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>396875</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>673553</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>67582</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{18D98F9C-DBA7-6748-9B35-17F3FA29EBDB}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks/>
-        </xdr:cNvGraphicFramePr>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>1143000</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>238125</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>957036</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>4082</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Chart 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5BCA365D-B6D1-634A-ADFA-86DB922C97BC}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks/>
-        </xdr:cNvGraphicFramePr>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>10</xdr:col>
@@ -17315,7 +14887,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
           <a:clrChange>
             <a:clrFrom>
               <a:srgbClr val="FFFFFF"/>
@@ -17386,7 +14958,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
           <a:clrChange>
             <a:clrFrom>
               <a:srgbClr val="FFFFFF"/>
@@ -17457,7 +15029,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
           <a:clrChange>
             <a:clrFrom>
               <a:srgbClr val="FFFFFF"/>
@@ -17528,7 +15100,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
           <a:clrChange>
             <a:clrFrom>
               <a:srgbClr val="FFFFFF"/>
@@ -17599,7 +15171,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5">
           <a:clrChange>
             <a:clrFrom>
               <a:srgbClr val="FFFFFF"/>
@@ -17670,7 +15242,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6">
           <a:clrChange>
             <a:clrFrom>
               <a:srgbClr val="FFFFFF"/>
@@ -18837,7 +16409,7 @@
       </c>
     </row>
     <row r="6" spans="2:4" ht="22" x14ac:dyDescent="0.2">
-      <c r="B6" s="115" t="s">
+      <c r="B6" s="120" t="s">
         <v>391</v>
       </c>
       <c r="C6" s="28" t="s">
@@ -18848,7 +16420,7 @@
       </c>
     </row>
     <row r="7" spans="2:4" ht="111" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="116"/>
+      <c r="B7" s="121"/>
       <c r="C7" s="104" t="s">
         <v>543</v>
       </c>
@@ -18857,28 +16429,28 @@
       </c>
     </row>
     <row r="8" spans="2:4" ht="22" x14ac:dyDescent="0.2">
-      <c r="B8" s="115" t="s">
+      <c r="B8" s="120" t="s">
         <v>394</v>
       </c>
       <c r="C8" s="28" t="s">
         <v>398</v>
       </c>
-      <c r="D8" s="115" t="s">
+      <c r="D8" s="120" t="s">
         <v>395</v>
       </c>
     </row>
     <row r="9" spans="2:4" ht="89" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="116"/>
+      <c r="B9" s="121"/>
       <c r="C9" s="104" t="s">
         <v>542</v>
       </c>
-      <c r="D9" s="116"/>
+      <c r="D9" s="121"/>
     </row>
     <row r="10" spans="2:4" ht="22" x14ac:dyDescent="0.2">
-      <c r="B10" s="115" t="s">
+      <c r="B10" s="120" t="s">
         <v>396</v>
       </c>
-      <c r="C10" s="115" t="s">
+      <c r="C10" s="120" t="s">
         <v>395</v>
       </c>
       <c r="D10" s="28" t="s">
@@ -18886,8 +16458,8 @@
       </c>
     </row>
     <row r="11" spans="2:4" ht="89" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="116"/>
-      <c r="C11" s="116"/>
+      <c r="B11" s="121"/>
+      <c r="C11" s="121"/>
       <c r="D11" s="104" t="s">
         <v>545</v>
       </c>
@@ -18919,8 +16491,8 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B2" s="120"/>
-      <c r="C2" s="120"/>
+      <c r="B2" s="118"/>
+      <c r="C2" s="118"/>
       <c r="D2" s="103" t="s">
         <v>389</v>
       </c>
@@ -18932,10 +16504,10 @@
       </c>
     </row>
     <row r="3" spans="2:6" ht="46" x14ac:dyDescent="0.3">
-      <c r="B3" s="117" t="s">
+      <c r="B3" s="115" t="s">
         <v>462</v>
       </c>
-      <c r="C3" s="117"/>
+      <c r="C3" s="115"/>
       <c r="D3" s="98" t="s">
         <v>469</v>
       </c>
@@ -18945,7 +16517,7 @@
       <c r="F3" s="99"/>
     </row>
     <row r="4" spans="2:6" ht="46" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="119" t="s">
+      <c r="B4" s="117" t="s">
         <v>466</v>
       </c>
       <c r="C4" s="99" t="s">
@@ -18960,7 +16532,7 @@
       <c r="F4" s="99"/>
     </row>
     <row r="5" spans="2:6" ht="69" x14ac:dyDescent="0.3">
-      <c r="B5" s="119"/>
+      <c r="B5" s="117"/>
       <c r="C5" s="99" t="s">
         <v>468</v>
       </c>
@@ -18971,7 +16543,7 @@
       <c r="F5" s="99"/>
     </row>
     <row r="6" spans="2:6" ht="46" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="119"/>
+      <c r="B6" s="117"/>
       <c r="C6" s="100" t="s">
         <v>472</v>
       </c>
@@ -18982,10 +16554,10 @@
       <c r="F6" s="99"/>
     </row>
     <row r="7" spans="2:6" ht="23" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="121" t="s">
+      <c r="B7" s="119" t="s">
         <v>474</v>
       </c>
-      <c r="C7" s="118" t="s">
+      <c r="C7" s="116" t="s">
         <v>475</v>
       </c>
       <c r="D7" s="100"/>
@@ -18995,8 +16567,8 @@
       <c r="F7" s="99"/>
     </row>
     <row r="8" spans="2:6" ht="23" x14ac:dyDescent="0.3">
-      <c r="B8" s="121"/>
-      <c r="C8" s="118"/>
+      <c r="B8" s="119"/>
+      <c r="C8" s="116"/>
       <c r="D8" s="100"/>
       <c r="E8" s="98" t="s">
         <v>477</v>
@@ -19004,7 +16576,7 @@
       <c r="F8" s="99"/>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B9" s="121"/>
+      <c r="B9" s="119"/>
       <c r="C9" s="99" t="s">
         <v>478</v>
       </c>
@@ -19013,7 +16585,7 @@
       <c r="F9" s="99"/>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B10" s="121"/>
+      <c r="B10" s="119"/>
       <c r="C10" s="99" t="s">
         <v>479</v>
       </c>
@@ -19024,7 +16596,7 @@
       </c>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B11" s="121"/>
+      <c r="B11" s="119"/>
       <c r="C11" s="99" t="s">
         <v>483</v>
       </c>
@@ -19035,7 +16607,7 @@
       </c>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B12" s="121"/>
+      <c r="B12" s="119"/>
       <c r="C12" s="99"/>
       <c r="D12" s="106" t="s">
         <v>486</v>
@@ -19044,7 +16616,7 @@
       <c r="F12" s="99"/>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B13" s="121"/>
+      <c r="B13" s="119"/>
       <c r="C13" s="99"/>
       <c r="D13" s="100"/>
       <c r="E13" s="106" t="s">
@@ -19053,7 +16625,7 @@
       <c r="F13" s="99"/>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B14" s="121"/>
+      <c r="B14" s="119"/>
       <c r="C14" s="99"/>
       <c r="D14" s="100"/>
       <c r="E14" s="100"/>
@@ -19062,7 +16634,7 @@
       </c>
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B15" s="121"/>
+      <c r="B15" s="119"/>
       <c r="C15" s="99"/>
       <c r="D15" s="106" t="s">
         <v>489</v>
@@ -19111,40 +16683,40 @@
       <c r="B2" s="30" t="s">
         <v>388</v>
       </c>
-      <c r="C2" s="146" t="s">
+      <c r="C2" s="123" t="s">
         <v>389</v>
       </c>
-      <c r="D2" s="146"/>
-      <c r="E2" s="146"/>
-      <c r="F2" s="146"/>
-      <c r="G2" s="146"/>
-      <c r="H2" s="146"/>
-      <c r="I2" s="146"/>
-      <c r="J2" s="146"/>
-      <c r="K2" s="146"/>
-      <c r="L2" s="146"/>
-      <c r="M2" s="147" t="s">
+      <c r="D2" s="123"/>
+      <c r="E2" s="123"/>
+      <c r="F2" s="123"/>
+      <c r="G2" s="123"/>
+      <c r="H2" s="123"/>
+      <c r="I2" s="123"/>
+      <c r="J2" s="123"/>
+      <c r="K2" s="123"/>
+      <c r="L2" s="123"/>
+      <c r="M2" s="124" t="s">
         <v>390</v>
       </c>
-      <c r="N2" s="147"/>
-      <c r="O2" s="147"/>
-      <c r="P2" s="147"/>
-      <c r="Q2" s="147"/>
-      <c r="R2" s="147"/>
-      <c r="S2" s="129" t="s">
+      <c r="N2" s="124"/>
+      <c r="O2" s="124"/>
+      <c r="P2" s="124"/>
+      <c r="Q2" s="124"/>
+      <c r="R2" s="124"/>
+      <c r="S2" s="137" t="s">
         <v>461</v>
       </c>
-      <c r="T2" s="129"/>
-      <c r="U2" s="129"/>
-      <c r="V2" s="129"/>
-      <c r="W2" s="129"/>
-      <c r="X2" s="129"/>
-      <c r="Y2" s="129"/>
-      <c r="Z2" s="129"/>
-      <c r="AA2" s="129"/>
+      <c r="T2" s="137"/>
+      <c r="U2" s="137"/>
+      <c r="V2" s="137"/>
+      <c r="W2" s="137"/>
+      <c r="X2" s="137"/>
+      <c r="Y2" s="137"/>
+      <c r="Z2" s="137"/>
+      <c r="AA2" s="137"/>
     </row>
     <row r="3" spans="2:27" ht="21" x14ac:dyDescent="0.2">
-      <c r="B3" s="140" t="s">
+      <c r="B3" s="133" t="s">
         <v>462</v>
       </c>
       <c r="C3" s="37"/>
@@ -19165,7 +16737,7 @@
       <c r="R3" s="72"/>
     </row>
     <row r="4" spans="2:27" ht="21" x14ac:dyDescent="0.2">
-      <c r="B4" s="141"/>
+      <c r="B4" s="134"/>
       <c r="C4" s="37"/>
       <c r="D4" s="38"/>
       <c r="E4" s="38"/>
@@ -19188,7 +16760,7 @@
       </c>
     </row>
     <row r="5" spans="2:27" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="141"/>
+      <c r="B5" s="134"/>
       <c r="C5" s="37"/>
       <c r="D5" s="38"/>
       <c r="E5" s="38"/>
@@ -19230,7 +16802,7 @@
       </c>
     </row>
     <row r="6" spans="2:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="141"/>
+      <c r="B6" s="134"/>
       <c r="D6" s="38"/>
       <c r="E6" s="38"/>
       <c r="F6" s="38"/>
@@ -19239,22 +16811,22 @@
       <c r="J6" s="43" t="s">
         <v>388</v>
       </c>
-      <c r="K6" s="148" t="s">
+      <c r="K6" s="125" t="s">
         <v>399</v>
       </c>
-      <c r="L6" s="148"/>
-      <c r="M6" s="149" t="s">
+      <c r="L6" s="125"/>
+      <c r="M6" s="126" t="s">
         <v>400</v>
       </c>
-      <c r="N6" s="149"/>
-      <c r="T6" s="132" t="s">
+      <c r="N6" s="126"/>
+      <c r="T6" s="140" t="s">
         <v>345</v>
       </c>
-      <c r="U6" s="133" t="s">
+      <c r="U6" s="141" t="s">
         <v>458</v>
       </c>
-      <c r="V6" s="133"/>
-      <c r="W6" s="133"/>
+      <c r="V6" s="141"/>
+      <c r="W6" s="141"/>
       <c r="X6" s="86" t="s">
         <v>459</v>
       </c>
@@ -19263,13 +16835,13 @@
       </c>
     </row>
     <row r="7" spans="2:27" ht="16" x14ac:dyDescent="0.2">
-      <c r="B7" s="141"/>
+      <c r="B7" s="134"/>
       <c r="D7" s="38"/>
       <c r="E7" s="38"/>
       <c r="F7" s="38"/>
       <c r="G7" s="38"/>
       <c r="H7" s="38"/>
-      <c r="J7" s="144" t="s">
+      <c r="J7" s="122" t="s">
         <v>334</v>
       </c>
       <c r="K7" s="44" t="s">
@@ -19284,7 +16856,7 @@
       <c r="N7" s="76" t="s">
         <v>387</v>
       </c>
-      <c r="T7" s="132"/>
+      <c r="T7" s="140"/>
       <c r="U7" s="87" t="s">
         <v>449</v>
       </c>
@@ -19298,13 +16870,13 @@
       <c r="Y7" s="88"/>
     </row>
     <row r="8" spans="2:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="141"/>
+      <c r="B8" s="134"/>
       <c r="D8" s="38"/>
       <c r="E8" s="38"/>
       <c r="F8" s="38"/>
       <c r="G8" s="38"/>
       <c r="H8" s="38"/>
-      <c r="J8" s="144"/>
+      <c r="J8" s="122"/>
       <c r="K8" s="44" t="s">
         <v>16</v>
       </c>
@@ -19317,7 +16889,7 @@
       <c r="N8" s="76" t="s">
         <v>88</v>
       </c>
-      <c r="T8" s="134" t="s">
+      <c r="T8" s="142" t="s">
         <v>403</v>
       </c>
       <c r="U8" s="86">
@@ -19337,13 +16909,13 @@
       </c>
     </row>
     <row r="9" spans="2:27" ht="16" x14ac:dyDescent="0.2">
-      <c r="B9" s="141"/>
+      <c r="B9" s="134"/>
       <c r="D9" s="38"/>
       <c r="E9" s="38"/>
       <c r="F9" s="38"/>
       <c r="G9" s="38"/>
       <c r="H9" s="38"/>
-      <c r="J9" s="144" t="s">
+      <c r="J9" s="122" t="s">
         <v>401</v>
       </c>
       <c r="K9" s="44"/>
@@ -19354,7 +16926,7 @@
       <c r="N9" s="76" t="s">
         <v>384</v>
       </c>
-      <c r="T9" s="135"/>
+      <c r="T9" s="143"/>
       <c r="U9" s="90" t="s">
         <v>453</v>
       </c>
@@ -19372,13 +16944,13 @@
       </c>
     </row>
     <row r="10" spans="2:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="141"/>
+      <c r="B10" s="134"/>
       <c r="D10" s="38"/>
       <c r="E10" s="38"/>
       <c r="F10" s="38"/>
       <c r="G10" s="38"/>
       <c r="H10" s="38"/>
-      <c r="J10" s="144"/>
+      <c r="J10" s="122"/>
       <c r="K10" s="44"/>
       <c r="L10" s="44" t="s">
         <v>26</v>
@@ -19407,13 +16979,13 @@
       </c>
     </row>
     <row r="11" spans="2:27" ht="16" x14ac:dyDescent="0.2">
-      <c r="B11" s="141"/>
+      <c r="B11" s="134"/>
       <c r="D11" s="38"/>
       <c r="E11" s="38"/>
       <c r="F11" s="38"/>
       <c r="G11" s="38"/>
       <c r="H11" s="38"/>
-      <c r="J11" s="144" t="s">
+      <c r="J11" s="122" t="s">
         <v>402</v>
       </c>
       <c r="K11" s="44"/>
@@ -19444,13 +17016,13 @@
       </c>
     </row>
     <row r="12" spans="2:27" ht="16" x14ac:dyDescent="0.2">
-      <c r="B12" s="141"/>
+      <c r="B12" s="134"/>
       <c r="D12" s="38"/>
       <c r="E12" s="38"/>
       <c r="F12" s="38"/>
       <c r="G12" s="38"/>
       <c r="H12" s="38"/>
-      <c r="J12" s="145"/>
+      <c r="J12" s="127"/>
       <c r="K12" s="45"/>
       <c r="L12" s="45" t="s">
         <v>85</v>
@@ -19479,7 +17051,7 @@
       </c>
     </row>
     <row r="13" spans="2:27" ht="16" x14ac:dyDescent="0.2">
-      <c r="B13" s="141"/>
+      <c r="B13" s="134"/>
       <c r="D13" s="38"/>
       <c r="E13" s="38"/>
       <c r="F13" s="38"/>
@@ -19502,7 +17074,7 @@
       </c>
     </row>
     <row r="14" spans="2:27" ht="16" x14ac:dyDescent="0.2">
-      <c r="B14" s="141"/>
+      <c r="B14" s="134"/>
       <c r="D14" s="38"/>
       <c r="E14" s="38"/>
       <c r="F14" s="38"/>
@@ -19525,7 +17097,7 @@
       </c>
     </row>
     <row r="15" spans="2:27" ht="16" x14ac:dyDescent="0.2">
-      <c r="B15" s="141"/>
+      <c r="B15" s="134"/>
       <c r="D15" s="38"/>
       <c r="E15" s="38"/>
       <c r="F15" s="38"/>
@@ -19548,7 +17120,7 @@
       </c>
     </row>
     <row r="16" spans="2:27" ht="16" x14ac:dyDescent="0.2">
-      <c r="B16" s="141"/>
+      <c r="B16" s="134"/>
       <c r="J16" s="47" t="s">
         <v>339</v>
       </c>
@@ -19566,57 +17138,90 @@
       </c>
     </row>
     <row r="17" spans="2:35" ht="16" x14ac:dyDescent="0.2">
-      <c r="B17" s="141"/>
+      <c r="B17" s="134"/>
     </row>
     <row r="18" spans="2:35" ht="16" x14ac:dyDescent="0.2">
-      <c r="B18" s="141"/>
+      <c r="B18" s="134"/>
     </row>
     <row r="19" spans="2:35" ht="16" x14ac:dyDescent="0.2">
-      <c r="B19" s="141"/>
+      <c r="B19" s="134"/>
     </row>
     <row r="20" spans="2:35" ht="16" x14ac:dyDescent="0.2">
-      <c r="B20" s="141"/>
+      <c r="B20" s="134"/>
     </row>
     <row r="21" spans="2:35" ht="16" x14ac:dyDescent="0.2">
-      <c r="B21" s="141"/>
+      <c r="B21" s="134"/>
     </row>
     <row r="22" spans="2:35" ht="16" x14ac:dyDescent="0.2">
-      <c r="B22" s="141"/>
+      <c r="B22" s="134"/>
     </row>
     <row r="23" spans="2:35" ht="16" x14ac:dyDescent="0.2">
-      <c r="B23" s="141"/>
+      <c r="B23" s="134"/>
     </row>
     <row r="24" spans="2:35" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="142" t="s">
+      <c r="B24" s="135" t="s">
         <v>464</v>
       </c>
     </row>
     <row r="25" spans="2:35" ht="16" x14ac:dyDescent="0.2">
-      <c r="B25" s="142"/>
+      <c r="B25" s="135"/>
     </row>
     <row r="26" spans="2:35" ht="16" x14ac:dyDescent="0.2">
-      <c r="B26" s="142"/>
+      <c r="B26" s="135"/>
+      <c r="D26" s="41"/>
+      <c r="E26" s="42" t="s">
+        <v>340</v>
+      </c>
+      <c r="F26" s="42" t="s">
+        <v>341</v>
+      </c>
+      <c r="N26" s="170"/>
+      <c r="O26" s="74" t="s">
+        <v>340</v>
+      </c>
+      <c r="P26" s="74" t="s">
+        <v>341</v>
+      </c>
     </row>
     <row r="27" spans="2:35" ht="16" x14ac:dyDescent="0.2">
-      <c r="B27" s="142"/>
-      <c r="N27" s="73"/>
-    </row>
-    <row r="28" spans="2:35" s="26" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="B28" s="142"/>
+      <c r="B27" s="135"/>
+      <c r="E27" s="169" t="s">
+        <v>555</v>
+      </c>
+      <c r="F27" s="169" t="s">
+        <v>556</v>
+      </c>
+      <c r="O27" s="171" t="s">
+        <v>565</v>
+      </c>
+      <c r="P27" s="171" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="28" spans="2:35" s="26" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B28" s="135"/>
       <c r="C28" s="39"/>
-      <c r="D28" s="39"/>
-      <c r="E28" s="39"/>
-      <c r="F28" s="39"/>
-      <c r="G28" s="39"/>
-      <c r="H28" s="39"/>
-      <c r="I28" s="39"/>
+      <c r="D28" s="43" t="s">
+        <v>388</v>
+      </c>
+      <c r="E28" s="125" t="s">
+        <v>399</v>
+      </c>
+      <c r="F28" s="125"/>
+      <c r="G28" s="177"/>
+      <c r="H28" s="177"/>
+      <c r="I28" s="177"/>
       <c r="J28" s="39"/>
       <c r="K28" s="39"/>
       <c r="L28" s="39"/>
       <c r="M28" s="75"/>
-      <c r="N28" s="75"/>
-      <c r="O28" s="75"/>
-      <c r="P28" s="75"/>
+      <c r="N28" s="172" t="s">
+        <v>388</v>
+      </c>
+      <c r="O28" s="126" t="s">
+        <v>400</v>
+      </c>
+      <c r="P28" s="126"/>
       <c r="Q28" s="75"/>
       <c r="R28" s="75"/>
       <c r="S28" s="33"/>
@@ -19638,60 +17243,292 @@
       <c r="AI28" s="31"/>
     </row>
     <row r="29" spans="2:35" ht="16" x14ac:dyDescent="0.2">
-      <c r="B29" s="142"/>
-    </row>
-    <row r="30" spans="2:35" ht="16" x14ac:dyDescent="0.2">
-      <c r="B30" s="142"/>
+      <c r="B29" s="135"/>
+      <c r="D29" s="122" t="s">
+        <v>334</v>
+      </c>
+      <c r="E29" s="44" t="s">
+        <v>547</v>
+      </c>
+      <c r="F29" s="44" t="s">
+        <v>549</v>
+      </c>
+      <c r="G29" s="177" t="s">
+        <v>567</v>
+      </c>
+      <c r="H29" s="177"/>
+      <c r="I29" s="177"/>
+      <c r="N29" s="173" t="s">
+        <v>334</v>
+      </c>
+      <c r="O29" s="76" t="s">
+        <v>546</v>
+      </c>
+      <c r="P29" s="76" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q29" s="178" t="s">
+        <v>571</v>
+      </c>
+      <c r="R29" s="178"/>
+    </row>
+    <row r="30" spans="2:35" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B30" s="135"/>
+      <c r="D30" s="122"/>
+      <c r="E30" s="44" t="s">
+        <v>94</v>
+      </c>
+      <c r="F30" s="44" t="s">
+        <v>550</v>
+      </c>
+      <c r="G30" s="177" t="s">
+        <v>568</v>
+      </c>
+      <c r="H30" s="177"/>
+      <c r="I30" s="177"/>
+      <c r="N30" s="173"/>
+      <c r="O30" s="76" t="s">
+        <v>143</v>
+      </c>
+      <c r="P30" s="76" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q30" s="178"/>
+      <c r="R30" s="178"/>
     </row>
     <row r="31" spans="2:35" ht="16" x14ac:dyDescent="0.2">
-      <c r="B31" s="142"/>
-    </row>
-    <row r="32" spans="2:35" ht="16" x14ac:dyDescent="0.2">
-      <c r="B32" s="142"/>
-    </row>
-    <row r="33" spans="2:14" ht="16" x14ac:dyDescent="0.2">
-      <c r="B33" s="142"/>
-    </row>
-    <row r="34" spans="2:14" ht="16" x14ac:dyDescent="0.2">
-      <c r="B34" s="142"/>
-    </row>
-    <row r="35" spans="2:14" ht="16" x14ac:dyDescent="0.2">
-      <c r="B35" s="142"/>
-    </row>
-    <row r="36" spans="2:14" ht="16" x14ac:dyDescent="0.2">
-      <c r="B36" s="142"/>
-    </row>
-    <row r="37" spans="2:14" ht="16" x14ac:dyDescent="0.2">
-      <c r="B37" s="142"/>
-    </row>
-    <row r="38" spans="2:14" ht="16" x14ac:dyDescent="0.2">
-      <c r="B38" s="142"/>
-      <c r="N38" s="73"/>
-    </row>
-    <row r="39" spans="2:14" ht="16" x14ac:dyDescent="0.2">
-      <c r="B39" s="142"/>
-    </row>
-    <row r="40" spans="2:14" ht="16" x14ac:dyDescent="0.2">
-      <c r="B40" s="142"/>
-    </row>
-    <row r="41" spans="2:14" ht="16" x14ac:dyDescent="0.2">
-      <c r="B41" s="142"/>
-    </row>
-    <row r="42" spans="2:14" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B42" s="142" t="s">
+      <c r="B31" s="135"/>
+      <c r="D31" s="122" t="s">
+        <v>401</v>
+      </c>
+      <c r="E31" s="44" t="s">
+        <v>548</v>
+      </c>
+      <c r="F31" s="44" t="s">
+        <v>55</v>
+      </c>
+      <c r="G31" s="177" t="s">
+        <v>569</v>
+      </c>
+      <c r="H31" s="177"/>
+      <c r="I31" s="177"/>
+      <c r="N31" s="173" t="s">
+        <v>401</v>
+      </c>
+      <c r="O31" s="76" t="s">
+        <v>559</v>
+      </c>
+      <c r="P31" s="76" t="s">
+        <v>560</v>
+      </c>
+      <c r="Q31" s="178" t="s">
+        <v>573</v>
+      </c>
+      <c r="R31" s="178"/>
+    </row>
+    <row r="32" spans="2:35" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B32" s="135"/>
+      <c r="D32" s="122"/>
+      <c r="E32" s="44" t="s">
+        <v>57</v>
+      </c>
+      <c r="F32" s="44" t="s">
+        <v>551</v>
+      </c>
+      <c r="G32" s="177" t="s">
+        <v>570</v>
+      </c>
+      <c r="H32" s="177"/>
+      <c r="I32" s="177"/>
+      <c r="N32" s="173"/>
+      <c r="O32" s="76" t="s">
+        <v>456</v>
+      </c>
+      <c r="P32" s="76" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q32" s="178"/>
+      <c r="R32" s="178"/>
+    </row>
+    <row r="33" spans="2:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="B33" s="135"/>
+      <c r="D33" s="122" t="s">
+        <v>402</v>
+      </c>
+      <c r="E33" s="44" t="s">
+        <v>278</v>
+      </c>
+      <c r="F33" s="44" t="s">
+        <v>552</v>
+      </c>
+      <c r="G33" s="177"/>
+      <c r="H33" s="177"/>
+      <c r="I33" s="177"/>
+      <c r="N33" s="173" t="s">
+        <v>402</v>
+      </c>
+      <c r="O33" s="76" t="s">
+        <v>561</v>
+      </c>
+      <c r="P33" s="76" t="s">
+        <v>562</v>
+      </c>
+      <c r="Q33" s="178" t="s">
+        <v>572</v>
+      </c>
+      <c r="R33" s="178"/>
+    </row>
+    <row r="34" spans="2:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="B34" s="135"/>
+      <c r="D34" s="127"/>
+      <c r="E34" s="45" t="s">
+        <v>553</v>
+      </c>
+      <c r="F34" s="45" t="s">
+        <v>554</v>
+      </c>
+      <c r="G34" s="177"/>
+      <c r="H34" s="177"/>
+      <c r="I34" s="177"/>
+      <c r="N34" s="174"/>
+      <c r="O34" s="77" t="s">
+        <v>85</v>
+      </c>
+      <c r="P34" s="77" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q34" s="178"/>
+      <c r="R34" s="178"/>
+    </row>
+    <row r="35" spans="2:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="B35" s="135"/>
+      <c r="D35" s="46" t="s">
+        <v>335</v>
+      </c>
+      <c r="E35" s="44" t="s">
+        <v>336</v>
+      </c>
+      <c r="F35" s="44" t="s">
+        <v>336</v>
+      </c>
+      <c r="G35" s="177"/>
+      <c r="H35" s="177"/>
+      <c r="I35" s="177"/>
+      <c r="N35" s="175" t="s">
+        <v>335</v>
+      </c>
+      <c r="O35" s="76" t="s">
+        <v>336</v>
+      </c>
+      <c r="P35" s="76" t="s">
+        <v>336</v>
+      </c>
+      <c r="Q35" s="178"/>
+      <c r="R35" s="178"/>
+    </row>
+    <row r="36" spans="2:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="B36" s="135"/>
+      <c r="D36" s="46" t="s">
+        <v>337</v>
+      </c>
+      <c r="E36" s="44" t="s">
+        <v>336</v>
+      </c>
+      <c r="F36" s="44" t="s">
+        <v>336</v>
+      </c>
+      <c r="G36" s="177"/>
+      <c r="H36" s="177"/>
+      <c r="I36" s="177"/>
+      <c r="N36" s="175" t="s">
+        <v>337</v>
+      </c>
+      <c r="O36" s="76" t="s">
+        <v>336</v>
+      </c>
+      <c r="P36" s="76" t="s">
+        <v>336</v>
+      </c>
+      <c r="Q36" s="178"/>
+      <c r="R36" s="178"/>
+    </row>
+    <row r="37" spans="2:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="B37" s="135"/>
+      <c r="D37" s="46" t="s">
+        <v>338</v>
+      </c>
+      <c r="E37" s="44" t="s">
+        <v>336</v>
+      </c>
+      <c r="F37" s="44" t="s">
+        <v>336</v>
+      </c>
+      <c r="G37" s="177"/>
+      <c r="H37" s="177"/>
+      <c r="I37" s="177"/>
+      <c r="N37" s="175" t="s">
+        <v>338</v>
+      </c>
+      <c r="O37" s="76" t="s">
+        <v>336</v>
+      </c>
+      <c r="P37" s="76" t="s">
+        <v>336</v>
+      </c>
+      <c r="Q37" s="178"/>
+      <c r="R37" s="178"/>
+    </row>
+    <row r="38" spans="2:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="B38" s="135"/>
+      <c r="D38" s="47" t="s">
+        <v>339</v>
+      </c>
+      <c r="E38" s="45" t="s">
+        <v>557</v>
+      </c>
+      <c r="F38" s="45" t="s">
+        <v>558</v>
+      </c>
+      <c r="N38" s="176" t="s">
+        <v>339</v>
+      </c>
+      <c r="O38" s="77" t="s">
+        <v>563</v>
+      </c>
+      <c r="P38" s="77" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="39" spans="2:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="B39" s="135"/>
+    </row>
+    <row r="40" spans="2:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="B40" s="135"/>
+    </row>
+    <row r="41" spans="2:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="B41" s="135"/>
+    </row>
+    <row r="42" spans="2:18" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B42" s="135" t="s">
         <v>463</v>
       </c>
       <c r="D42" s="40" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="43" spans="2:14" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B43" s="142"/>
-      <c r="D43" s="137"/>
-      <c r="E43" s="137" t="s">
+      <c r="M42" s="168"/>
+      <c r="N42" s="168"/>
+      <c r="O42" s="168"/>
+      <c r="P42" s="168"/>
+      <c r="Q42" s="168"/>
+      <c r="R42" s="168"/>
+    </row>
+    <row r="43" spans="2:18" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B43" s="135"/>
+      <c r="D43" s="128"/>
+      <c r="E43" s="128" t="s">
         <v>404</v>
       </c>
-      <c r="F43" s="137"/>
+      <c r="F43" s="128"/>
       <c r="G43" s="48" t="s">
         <v>405</v>
       </c>
@@ -19701,10 +17538,16 @@
       <c r="I43" s="48" t="s">
         <v>407</v>
       </c>
-    </row>
-    <row r="44" spans="2:14" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B44" s="142"/>
-      <c r="D44" s="138"/>
+      <c r="M43" s="168"/>
+      <c r="N43" s="168"/>
+      <c r="O43" s="168"/>
+      <c r="P43" s="168"/>
+      <c r="Q43" s="168"/>
+      <c r="R43" s="168"/>
+    </row>
+    <row r="44" spans="2:18" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B44" s="135"/>
+      <c r="D44" s="129"/>
       <c r="E44" s="50" t="s">
         <v>340</v>
       </c>
@@ -19720,23 +17563,35 @@
       <c r="I44" s="51" t="s">
         <v>419</v>
       </c>
-    </row>
-    <row r="45" spans="2:14" ht="26" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B45" s="142"/>
-      <c r="D45" s="138"/>
-      <c r="E45" s="139" t="s">
+      <c r="M44" s="168"/>
+      <c r="N44" s="168"/>
+      <c r="O44" s="168"/>
+      <c r="P44" s="168"/>
+      <c r="Q44" s="168"/>
+      <c r="R44" s="168"/>
+    </row>
+    <row r="45" spans="2:18" ht="26" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B45" s="135"/>
+      <c r="D45" s="129"/>
+      <c r="E45" s="130" t="s">
         <v>408</v>
       </c>
-      <c r="F45" s="139"/>
-      <c r="G45" s="139" t="s">
+      <c r="F45" s="130"/>
+      <c r="G45" s="130" t="s">
         <v>409</v>
       </c>
-      <c r="H45" s="139"/>
-      <c r="I45" s="139"/>
-    </row>
-    <row r="46" spans="2:14" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B46" s="142"/>
-      <c r="D46" s="136" t="s">
+      <c r="H45" s="130"/>
+      <c r="I45" s="130"/>
+      <c r="M45" s="168"/>
+      <c r="N45" s="168"/>
+      <c r="O45" s="168"/>
+      <c r="P45" s="168"/>
+      <c r="Q45" s="168"/>
+      <c r="R45" s="168"/>
+    </row>
+    <row r="46" spans="2:18" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B46" s="135"/>
+      <c r="D46" s="131" t="s">
         <v>403</v>
       </c>
       <c r="E46" s="49" t="s">
@@ -19754,10 +17609,16 @@
       <c r="I46" s="49" t="s">
         <v>411</v>
       </c>
-    </row>
-    <row r="47" spans="2:14" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B47" s="142"/>
-      <c r="D47" s="136"/>
+      <c r="M46" s="168"/>
+      <c r="N46" s="168"/>
+      <c r="O46" s="168"/>
+      <c r="P46" s="168"/>
+      <c r="Q46" s="168"/>
+      <c r="R46" s="168"/>
+    </row>
+    <row r="47" spans="2:18" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B47" s="135"/>
+      <c r="D47" s="131"/>
       <c r="E47" s="44" t="s">
         <v>16</v>
       </c>
@@ -19773,9 +17634,15 @@
       <c r="I47" s="44" t="s">
         <v>457</v>
       </c>
-    </row>
-    <row r="48" spans="2:14" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B48" s="142"/>
+      <c r="M47" s="168"/>
+      <c r="N47" s="168"/>
+      <c r="O47" s="168"/>
+      <c r="P47" s="168"/>
+      <c r="Q47" s="168"/>
+      <c r="R47" s="168"/>
+    </row>
+    <row r="48" spans="2:18" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B48" s="135"/>
       <c r="D48" s="53" t="s">
         <v>412</v>
       </c>
@@ -19794,9 +17661,15 @@
       <c r="I48" s="50" t="s">
         <v>336</v>
       </c>
-    </row>
-    <row r="49" spans="2:11" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="142"/>
+      <c r="M48" s="168"/>
+      <c r="N48" s="168"/>
+      <c r="O48" s="168"/>
+      <c r="P48" s="168"/>
+      <c r="Q48" s="168"/>
+      <c r="R48" s="168"/>
+    </row>
+    <row r="49" spans="2:18" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B49" s="135"/>
       <c r="D49" s="53" t="s">
         <v>338</v>
       </c>
@@ -19815,9 +17688,15 @@
       <c r="I49" s="50" t="s">
         <v>336</v>
       </c>
-    </row>
-    <row r="50" spans="2:11" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B50" s="142"/>
+      <c r="M49" s="168"/>
+      <c r="N49" s="168"/>
+      <c r="O49" s="168"/>
+      <c r="P49" s="168"/>
+      <c r="Q49" s="168"/>
+      <c r="R49" s="168"/>
+    </row>
+    <row r="50" spans="2:18" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B50" s="135"/>
       <c r="D50" s="54" t="s">
         <v>413</v>
       </c>
@@ -19828,9 +17707,15 @@
       <c r="G50" s="55"/>
       <c r="H50" s="55"/>
       <c r="I50" s="55"/>
-    </row>
-    <row r="51" spans="2:11" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B51" s="142"/>
+      <c r="M50" s="168"/>
+      <c r="N50" s="168"/>
+      <c r="O50" s="168"/>
+      <c r="P50" s="168"/>
+      <c r="Q50" s="168"/>
+      <c r="R50" s="168"/>
+    </row>
+    <row r="51" spans="2:18" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B51" s="135"/>
       <c r="D51" s="57" t="s">
         <v>339</v>
       </c>
@@ -19849,9 +17734,15 @@
       <c r="I51" s="58">
         <v>3613</v>
       </c>
-    </row>
-    <row r="52" spans="2:11" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B52" s="142"/>
+      <c r="M51" s="168"/>
+      <c r="N51" s="168"/>
+      <c r="O51" s="168"/>
+      <c r="P51" s="168"/>
+      <c r="Q51" s="168"/>
+      <c r="R51" s="168"/>
+    </row>
+    <row r="52" spans="2:18" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B52" s="135"/>
       <c r="D52" s="57" t="s">
         <v>414</v>
       </c>
@@ -19866,9 +17757,15 @@
       <c r="I52" s="49">
         <v>10117.514999999999</v>
       </c>
-    </row>
-    <row r="53" spans="2:11" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B53" s="142"/>
+      <c r="M52" s="168"/>
+      <c r="N52" s="168"/>
+      <c r="O52" s="168"/>
+      <c r="P52" s="168"/>
+      <c r="Q52" s="168"/>
+      <c r="R52" s="168"/>
+    </row>
+    <row r="53" spans="2:18" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B53" s="135"/>
       <c r="D53" s="57" t="s">
         <v>415</v>
       </c>
@@ -19879,9 +17776,15 @@
       <c r="G53" s="59"/>
       <c r="H53" s="59"/>
       <c r="I53" s="59"/>
-    </row>
-    <row r="54" spans="2:11" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B54" s="142"/>
+      <c r="M53" s="168"/>
+      <c r="N53" s="168"/>
+      <c r="O53" s="168"/>
+      <c r="P53" s="168"/>
+      <c r="Q53" s="168"/>
+      <c r="R53" s="168"/>
+    </row>
+    <row r="54" spans="2:18" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B54" s="135"/>
       <c r="D54" s="57" t="s">
         <v>416</v>
       </c>
@@ -19898,9 +17801,15 @@
       <c r="I54" s="49">
         <v>-4869.7579999999998</v>
       </c>
-    </row>
-    <row r="55" spans="2:11" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B55" s="142"/>
+      <c r="M54" s="168"/>
+      <c r="N54" s="168"/>
+      <c r="O54" s="168"/>
+      <c r="P54" s="168"/>
+      <c r="Q54" s="168"/>
+      <c r="R54" s="168"/>
+    </row>
+    <row r="55" spans="2:18" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B55" s="135"/>
       <c r="D55" s="57" t="s">
         <v>417</v>
       </c>
@@ -19911,9 +17820,15 @@
       </c>
       <c r="H55" s="59"/>
       <c r="I55" s="59"/>
-    </row>
-    <row r="56" spans="2:11" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B56" s="142"/>
+      <c r="M55" s="168"/>
+      <c r="N55" s="168"/>
+      <c r="O55" s="168"/>
+      <c r="P55" s="168"/>
+      <c r="Q55" s="168"/>
+      <c r="R55" s="168"/>
+    </row>
+    <row r="56" spans="2:18" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B56" s="135"/>
       <c r="D56" s="54" t="s">
         <v>418</v>
       </c>
@@ -19924,9 +17839,15 @@
       </c>
       <c r="H56" s="55"/>
       <c r="I56" s="55"/>
-    </row>
-    <row r="57" spans="2:11" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B57" s="142"/>
+      <c r="M56" s="168"/>
+      <c r="N56" s="168"/>
+      <c r="O56" s="168"/>
+      <c r="P56" s="168"/>
+      <c r="Q56" s="168"/>
+      <c r="R56" s="168"/>
+    </row>
+    <row r="57" spans="2:18" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B57" s="135"/>
       <c r="D57" s="57"/>
       <c r="E57" s="49"/>
       <c r="F57" s="49"/>
@@ -19934,8 +17855,8 @@
       <c r="H57" s="49"/>
       <c r="I57" s="49"/>
     </row>
-    <row r="58" spans="2:11" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B58" s="142"/>
+    <row r="58" spans="2:18" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B58" s="135"/>
       <c r="D58" s="57"/>
       <c r="E58" s="49"/>
       <c r="F58" s="49"/>
@@ -19943,18 +17864,18 @@
       <c r="H58" s="49"/>
       <c r="I58" s="49"/>
     </row>
-    <row r="59" spans="2:11" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B59" s="142"/>
-    </row>
-    <row r="60" spans="2:11" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B60" s="142"/>
+    <row r="59" spans="2:18" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B59" s="135"/>
+    </row>
+    <row r="60" spans="2:18" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B60" s="135"/>
       <c r="D60" s="60" t="s">
         <v>435</v>
       </c>
     </row>
-    <row r="61" spans="2:11" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B61" s="142"/>
-      <c r="D61" s="137"/>
+    <row r="61" spans="2:18" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B61" s="135"/>
+      <c r="D61" s="128"/>
       <c r="E61" s="42" t="s">
         <v>340</v>
       </c>
@@ -19977,27 +17898,27 @@
         <v>434</v>
       </c>
     </row>
-    <row r="62" spans="2:11" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B62" s="142"/>
-      <c r="D62" s="138"/>
-      <c r="E62" s="122" t="s">
+    <row r="62" spans="2:18" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B62" s="135"/>
+      <c r="D62" s="129"/>
+      <c r="E62" s="132" t="s">
         <v>422</v>
       </c>
-      <c r="F62" s="122" t="s">
+      <c r="F62" s="132" t="s">
         <v>423</v>
       </c>
-      <c r="G62" s="122"/>
-      <c r="H62" s="122"/>
-      <c r="I62" s="122" t="s">
+      <c r="G62" s="132"/>
+      <c r="H62" s="132"/>
+      <c r="I62" s="132" t="s">
         <v>424</v>
       </c>
-      <c r="J62" s="122"/>
-      <c r="K62" s="122"/>
-    </row>
-    <row r="63" spans="2:11" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B63" s="142"/>
-      <c r="D63" s="138"/>
-      <c r="E63" s="139"/>
+      <c r="J62" s="132"/>
+      <c r="K62" s="132"/>
+    </row>
+    <row r="63" spans="2:18" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B63" s="135"/>
+      <c r="D63" s="129"/>
+      <c r="E63" s="130"/>
       <c r="F63" s="52" t="s">
         <v>425</v>
       </c>
@@ -20011,9 +17932,9 @@
       <c r="J63" s="61"/>
       <c r="K63" s="61"/>
     </row>
-    <row r="64" spans="2:11" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B64" s="142"/>
-      <c r="D64" s="136" t="s">
+    <row r="64" spans="2:18" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B64" s="135"/>
+      <c r="D64" s="131" t="s">
         <v>403</v>
       </c>
       <c r="E64" s="49" t="s">
@@ -20039,8 +17960,8 @@
       </c>
     </row>
     <row r="65" spans="2:13" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B65" s="142"/>
-      <c r="D65" s="143"/>
+      <c r="B65" s="135"/>
+      <c r="D65" s="136"/>
       <c r="E65" s="45" t="s">
         <v>29</v>
       </c>
@@ -20064,7 +17985,7 @@
       </c>
     </row>
     <row r="66" spans="2:13" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B66" s="142"/>
+      <c r="B66" s="135"/>
       <c r="D66" s="62" t="s">
         <v>338</v>
       </c>
@@ -20091,7 +18012,7 @@
       </c>
     </row>
     <row r="67" spans="2:13" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B67" s="142"/>
+      <c r="B67" s="135"/>
       <c r="D67" s="63" t="s">
         <v>412</v>
       </c>
@@ -20118,7 +18039,7 @@
       </c>
     </row>
     <row r="68" spans="2:13" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B68" s="142"/>
+      <c r="B68" s="135"/>
       <c r="D68" s="63" t="s">
         <v>339</v>
       </c>
@@ -20145,22 +18066,22 @@
       </c>
     </row>
     <row r="69" spans="2:13" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B69" s="142"/>
+      <c r="B69" s="135"/>
     </row>
     <row r="70" spans="2:13" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B70" s="142"/>
+      <c r="B70" s="135"/>
     </row>
     <row r="71" spans="2:13" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B71" s="142"/>
+      <c r="B71" s="135"/>
     </row>
     <row r="72" spans="2:13" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B72" s="142"/>
+      <c r="B72" s="135"/>
       <c r="K72" s="60" t="s">
         <v>448</v>
       </c>
     </row>
     <row r="73" spans="2:13" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B73" s="142"/>
+      <c r="B73" s="135"/>
       <c r="K73" s="66"/>
       <c r="L73" s="42" t="s">
         <v>340</v>
@@ -20170,7 +18091,7 @@
       </c>
     </row>
     <row r="74" spans="2:13" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B74" s="142"/>
+      <c r="B74" s="135"/>
       <c r="K74" s="50"/>
       <c r="L74" s="56" t="s">
         <v>436</v>
@@ -20180,8 +18101,8 @@
       </c>
     </row>
     <row r="75" spans="2:13" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B75" s="142"/>
-      <c r="K75" s="123" t="s">
+      <c r="B75" s="135"/>
+      <c r="K75" s="144" t="s">
         <v>438</v>
       </c>
       <c r="L75" s="50">
@@ -20192,8 +18113,8 @@
       </c>
     </row>
     <row r="76" spans="2:13" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B76" s="142"/>
-      <c r="K76" s="124"/>
+      <c r="B76" s="135"/>
+      <c r="K76" s="145"/>
       <c r="L76" s="67" t="s">
         <v>224</v>
       </c>
@@ -20202,7 +18123,7 @@
       </c>
     </row>
     <row r="77" spans="2:13" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B77" s="142"/>
+      <c r="B77" s="135"/>
       <c r="K77" s="53" t="s">
         <v>439</v>
       </c>
@@ -20214,7 +18135,7 @@
       </c>
     </row>
     <row r="78" spans="2:13" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B78" s="142"/>
+      <c r="B78" s="135"/>
       <c r="K78" s="63" t="s">
         <v>412</v>
       </c>
@@ -20226,7 +18147,7 @@
       </c>
     </row>
     <row r="79" spans="2:13" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B79" s="142"/>
+      <c r="B79" s="135"/>
       <c r="K79" s="63" t="s">
         <v>339</v>
       </c>
@@ -20238,50 +18159,50 @@
       </c>
     </row>
     <row r="80" spans="2:13" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B80" s="142"/>
+      <c r="B80" s="135"/>
     </row>
     <row r="81" spans="2:15" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B81" s="142"/>
+      <c r="B81" s="135"/>
     </row>
     <row r="82" spans="2:15" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B82" s="142"/>
+      <c r="B82" s="135"/>
     </row>
     <row r="83" spans="2:15" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B83" s="142"/>
+      <c r="B83" s="135"/>
       <c r="J83" s="60" t="s">
         <v>441</v>
       </c>
     </row>
     <row r="84" spans="2:15" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B84" s="142"/>
-      <c r="J84" s="125"/>
-      <c r="K84" s="127" t="s">
+      <c r="B84" s="135"/>
+      <c r="J84" s="146"/>
+      <c r="K84" s="148" t="s">
         <v>442</v>
       </c>
-      <c r="L84" s="127" t="s">
+      <c r="L84" s="148" t="s">
         <v>446</v>
       </c>
-      <c r="M84" s="130" t="s">
+      <c r="M84" s="138" t="s">
         <v>447</v>
       </c>
-      <c r="N84" s="130" t="s">
+      <c r="N84" s="138" t="s">
         <v>443</v>
       </c>
-      <c r="O84" s="130" t="s">
+      <c r="O84" s="138" t="s">
         <v>444</v>
       </c>
     </row>
     <row r="85" spans="2:15" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B85" s="142"/>
-      <c r="J85" s="126"/>
-      <c r="K85" s="128"/>
-      <c r="L85" s="128"/>
-      <c r="M85" s="131"/>
-      <c r="N85" s="131"/>
-      <c r="O85" s="131"/>
+      <c r="B85" s="135"/>
+      <c r="J85" s="147"/>
+      <c r="K85" s="149"/>
+      <c r="L85" s="149"/>
+      <c r="M85" s="139"/>
+      <c r="N85" s="139"/>
+      <c r="O85" s="139"/>
     </row>
     <row r="86" spans="2:15" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B86" s="142"/>
+      <c r="B86" s="135"/>
       <c r="J86" s="69" t="s">
         <v>445</v>
       </c>
@@ -20302,7 +18223,7 @@
       </c>
     </row>
     <row r="87" spans="2:15" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B87" s="142"/>
+      <c r="B87" s="135"/>
       <c r="J87" s="71" t="s">
         <v>437</v>
       </c>
@@ -20323,24 +18244,29 @@
       </c>
     </row>
     <row r="88" spans="2:15" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B88" s="142"/>
+      <c r="B88" s="135"/>
     </row>
     <row r="89" spans="2:15" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B89" s="142"/>
+      <c r="B89" s="135"/>
     </row>
   </sheetData>
-  <mergeCells count="31">
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="C2:L2"/>
-    <mergeCell ref="M2:R2"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="J11:J12"/>
-    <mergeCell ref="D43:D45"/>
-    <mergeCell ref="E43:F43"/>
-    <mergeCell ref="E45:F45"/>
-    <mergeCell ref="G45:I45"/>
+  <mergeCells count="39">
+    <mergeCell ref="I62:K62"/>
+    <mergeCell ref="K75:K76"/>
+    <mergeCell ref="J84:J85"/>
+    <mergeCell ref="K84:K85"/>
+    <mergeCell ref="L84:L85"/>
+    <mergeCell ref="S2:AA2"/>
+    <mergeCell ref="M84:M85"/>
+    <mergeCell ref="N84:N85"/>
+    <mergeCell ref="O84:O85"/>
+    <mergeCell ref="T6:T7"/>
+    <mergeCell ref="U6:W6"/>
+    <mergeCell ref="T8:T9"/>
+    <mergeCell ref="O28:P28"/>
+    <mergeCell ref="N29:N30"/>
+    <mergeCell ref="N31:N32"/>
+    <mergeCell ref="N33:N34"/>
     <mergeCell ref="D46:D47"/>
     <mergeCell ref="D61:D63"/>
     <mergeCell ref="E62:E63"/>
@@ -20349,18 +18275,21 @@
     <mergeCell ref="B24:B41"/>
     <mergeCell ref="B42:B89"/>
     <mergeCell ref="D64:D65"/>
-    <mergeCell ref="S2:AA2"/>
-    <mergeCell ref="M84:M85"/>
-    <mergeCell ref="N84:N85"/>
-    <mergeCell ref="O84:O85"/>
-    <mergeCell ref="T6:T7"/>
-    <mergeCell ref="U6:W6"/>
-    <mergeCell ref="T8:T9"/>
-    <mergeCell ref="I62:K62"/>
-    <mergeCell ref="K75:K76"/>
-    <mergeCell ref="J84:J85"/>
-    <mergeCell ref="K84:K85"/>
-    <mergeCell ref="L84:L85"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="D33:D34"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="D43:D45"/>
+    <mergeCell ref="E43:F43"/>
+    <mergeCell ref="E45:F45"/>
+    <mergeCell ref="G45:I45"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="C2:L2"/>
+    <mergeCell ref="M2:R2"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="J7:J8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -20377,7 +18306,7 @@
     <col min="5" max="5" width="13.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="19.83203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.5" customWidth="1"/>
     <col min="9" max="9" width="55" customWidth="1"/>
   </cols>
   <sheetData>
@@ -20805,25 +18734,6 @@
     </row>
   </sheetData>
   <mergeCells count="35">
-    <mergeCell ref="C19:C20"/>
-    <mergeCell ref="D19:D20"/>
-    <mergeCell ref="E19:E20"/>
-    <mergeCell ref="F19:F20"/>
-    <mergeCell ref="G19:G20"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="B8:B10"/>
-    <mergeCell ref="C8:C10"/>
-    <mergeCell ref="D8:D10"/>
-    <mergeCell ref="E8:E10"/>
-    <mergeCell ref="F8:F10"/>
-    <mergeCell ref="G8:G10"/>
-    <mergeCell ref="H8:H10"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="G3:G4"/>
     <mergeCell ref="H19:H20"/>
     <mergeCell ref="F16:F18"/>
     <mergeCell ref="G16:G18"/>
@@ -20840,6 +18750,25 @@
     <mergeCell ref="D16:D18"/>
     <mergeCell ref="E16:E18"/>
     <mergeCell ref="B19:B20"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="C8:C10"/>
+    <mergeCell ref="D8:D10"/>
+    <mergeCell ref="E8:E10"/>
+    <mergeCell ref="F8:F10"/>
+    <mergeCell ref="G8:G10"/>
+    <mergeCell ref="H8:H10"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="E19:E20"/>
+    <mergeCell ref="F19:F20"/>
+    <mergeCell ref="G19:G20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -21444,35 +19373,35 @@
       <c r="B3" s="15" t="s">
         <v>345</v>
       </c>
-      <c r="C3" s="154" t="s">
+      <c r="C3" s="161" t="s">
         <v>346</v>
       </c>
-      <c r="D3" s="154"/>
-      <c r="E3" s="154" t="s">
+      <c r="D3" s="161"/>
+      <c r="E3" s="161" t="s">
         <v>348</v>
       </c>
-      <c r="F3" s="154"/>
+      <c r="F3" s="161"/>
       <c r="H3" s="15" t="s">
         <v>345</v>
       </c>
-      <c r="I3" s="154" t="s">
+      <c r="I3" s="161" t="s">
         <v>349</v>
       </c>
-      <c r="J3" s="154"/>
-      <c r="K3" s="154" t="s">
+      <c r="J3" s="161"/>
+      <c r="K3" s="161" t="s">
         <v>350</v>
       </c>
-      <c r="L3" s="154"/>
+      <c r="L3" s="161"/>
       <c r="N3" s="15" t="s">
         <v>345</v>
       </c>
-      <c r="O3" s="154" t="s">
+      <c r="O3" s="161" t="s">
         <v>352</v>
       </c>
-      <c r="P3" s="154"/>
+      <c r="P3" s="161"/>
     </row>
     <row r="4" spans="2:16" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="155" t="s">
+      <c r="B4" s="158" t="s">
         <v>334</v>
       </c>
       <c r="C4" s="13" t="s">
@@ -21487,7 +19416,7 @@
       <c r="F4" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="H4" s="155" t="s">
+      <c r="H4" s="158" t="s">
         <v>334</v>
       </c>
       <c r="I4" s="13" t="s">
@@ -21502,7 +19431,7 @@
       <c r="L4" s="13" t="s">
         <v>260</v>
       </c>
-      <c r="N4" s="155" t="s">
+      <c r="N4" s="158" t="s">
         <v>334</v>
       </c>
       <c r="O4" s="13" t="s">
@@ -21513,7 +19442,7 @@
       </c>
     </row>
     <row r="5" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B5" s="155"/>
+      <c r="B5" s="158"/>
       <c r="C5" s="13" t="s">
         <v>16</v>
       </c>
@@ -21526,7 +19455,7 @@
       <c r="F5" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="H5" s="155"/>
+      <c r="H5" s="158"/>
       <c r="I5" s="13" t="s">
         <v>29</v>
       </c>
@@ -21539,7 +19468,7 @@
       <c r="L5" s="13" t="s">
         <v>263</v>
       </c>
-      <c r="N5" s="155"/>
+      <c r="N5" s="158"/>
       <c r="O5" s="13" t="s">
         <v>65</v>
       </c>
@@ -21548,7 +19477,7 @@
       </c>
     </row>
     <row r="6" spans="2:16" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="155" t="s">
+      <c r="B6" s="158" t="s">
         <v>364</v>
       </c>
       <c r="C6" s="13"/>
@@ -21559,7 +19488,7 @@
       <c r="F6" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="H6" s="155" t="s">
+      <c r="H6" s="158" t="s">
         <v>360</v>
       </c>
       <c r="J6" s="13" t="s">
@@ -21569,7 +19498,7 @@
       <c r="L6" s="13" t="s">
         <v>266</v>
       </c>
-      <c r="N6" s="155" t="s">
+      <c r="N6" s="158" t="s">
         <v>360</v>
       </c>
       <c r="P6" s="13" t="s">
@@ -21577,7 +19506,7 @@
       </c>
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B7" s="155"/>
+      <c r="B7" s="158"/>
       <c r="C7" s="13"/>
       <c r="D7" s="13" t="s">
         <v>26</v>
@@ -21586,7 +19515,7 @@
       <c r="F7" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="H7" s="155"/>
+      <c r="H7" s="158"/>
       <c r="J7" s="13" t="s">
         <v>213</v>
       </c>
@@ -21594,13 +19523,13 @@
       <c r="L7" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="N7" s="155"/>
+      <c r="N7" s="158"/>
       <c r="P7" s="13" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="8" spans="2:16" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="155" t="s">
+      <c r="B8" s="158" t="s">
         <v>365</v>
       </c>
       <c r="C8" s="13"/>
@@ -21611,7 +19540,7 @@
       <c r="F8" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="H8" s="155" t="s">
+      <c r="H8" s="158" t="s">
         <v>361</v>
       </c>
       <c r="J8" s="13" t="s">
@@ -21621,7 +19550,7 @@
       <c r="L8" s="13" t="s">
         <v>269</v>
       </c>
-      <c r="N8" s="155" t="s">
+      <c r="N8" s="158" t="s">
         <v>361</v>
       </c>
       <c r="P8" s="13" t="s">
@@ -21629,7 +19558,7 @@
       </c>
     </row>
     <row r="9" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B9" s="156"/>
+      <c r="B9" s="159"/>
       <c r="C9" s="16"/>
       <c r="D9" s="16" t="s">
         <v>85</v>
@@ -21638,7 +19567,7 @@
       <c r="F9" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="H9" s="155"/>
+      <c r="H9" s="158"/>
       <c r="J9" s="13" t="s">
         <v>163</v>
       </c>
@@ -21646,7 +19575,7 @@
       <c r="L9" s="13" t="s">
         <v>274</v>
       </c>
-      <c r="N9" s="155"/>
+      <c r="N9" s="158"/>
       <c r="P9" s="13" t="s">
         <v>217</v>
       </c>
@@ -21667,7 +19596,7 @@
       <c r="F10" s="13" t="s">
         <v>336</v>
       </c>
-      <c r="H10" s="155" t="s">
+      <c r="H10" s="158" t="s">
         <v>362</v>
       </c>
       <c r="I10" s="13"/>
@@ -21678,7 +19607,7 @@
       <c r="L10" s="13" t="s">
         <v>277</v>
       </c>
-      <c r="N10" s="155" t="s">
+      <c r="N10" s="158" t="s">
         <v>362</v>
       </c>
       <c r="O10" s="13"/>
@@ -21702,7 +19631,7 @@
       <c r="F11" s="13" t="s">
         <v>336</v>
       </c>
-      <c r="H11" s="155"/>
+      <c r="H11" s="158"/>
       <c r="I11" s="13"/>
       <c r="J11" s="13" t="s">
         <v>251</v>
@@ -21711,7 +19640,7 @@
       <c r="L11" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="N11" s="155"/>
+      <c r="N11" s="158"/>
       <c r="O11" s="13"/>
       <c r="P11" s="13" t="s">
         <v>213</v>
@@ -21733,7 +19662,7 @@
       <c r="F12" s="13" t="s">
         <v>336</v>
       </c>
-      <c r="H12" s="155" t="s">
+      <c r="H12" s="158" t="s">
         <v>363</v>
       </c>
       <c r="I12" s="13"/>
@@ -21744,7 +19673,7 @@
       <c r="L12" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="N12" s="155" t="s">
+      <c r="N12" s="158" t="s">
         <v>363</v>
       </c>
       <c r="O12" s="13"/>
@@ -21768,7 +19697,7 @@
       <c r="F13" s="16" t="s">
         <v>347</v>
       </c>
-      <c r="H13" s="156"/>
+      <c r="H13" s="159"/>
       <c r="I13" s="16"/>
       <c r="J13" s="16" t="s">
         <v>210</v>
@@ -21777,7 +19706,7 @@
       <c r="L13" s="16" t="s">
         <v>286</v>
       </c>
-      <c r="N13" s="156"/>
+      <c r="N13" s="159"/>
       <c r="O13" s="16"/>
       <c r="P13" s="16" t="s">
         <v>60</v>
@@ -21910,17 +19839,17 @@
       <c r="B20" s="29" t="s">
         <v>388</v>
       </c>
-      <c r="C20" s="154" t="s">
+      <c r="C20" s="161" t="s">
         <v>399</v>
       </c>
-      <c r="D20" s="154"/>
-      <c r="E20" s="154" t="s">
+      <c r="D20" s="161"/>
+      <c r="E20" s="161" t="s">
         <v>400</v>
       </c>
-      <c r="F20" s="154"/>
+      <c r="F20" s="161"/>
     </row>
     <row r="21" spans="2:16" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="155" t="s">
+      <c r="B21" s="158" t="s">
         <v>334</v>
       </c>
       <c r="C21" s="13" t="s">
@@ -21937,7 +19866,7 @@
       </c>
     </row>
     <row r="22" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B22" s="155"/>
+      <c r="B22" s="158"/>
       <c r="C22" s="13" t="s">
         <v>16</v>
       </c>
@@ -21952,7 +19881,7 @@
       </c>
     </row>
     <row r="23" spans="2:16" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="155" t="s">
+      <c r="B23" s="158" t="s">
         <v>401</v>
       </c>
       <c r="C23" s="13"/>
@@ -21965,7 +19894,7 @@
       </c>
     </row>
     <row r="24" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B24" s="155"/>
+      <c r="B24" s="158"/>
       <c r="C24" s="13"/>
       <c r="D24" s="13" t="s">
         <v>26</v>
@@ -21976,7 +19905,7 @@
       </c>
     </row>
     <row r="25" spans="2:16" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="155" t="s">
+      <c r="B25" s="158" t="s">
         <v>402</v>
       </c>
       <c r="C25" s="13"/>
@@ -21989,7 +19918,7 @@
       </c>
     </row>
     <row r="26" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B26" s="156"/>
+      <c r="B26" s="159"/>
       <c r="C26" s="16"/>
       <c r="D26" s="16" t="s">
         <v>85</v>
@@ -22070,23 +19999,23 @@
     <row r="32" spans="2:16" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="34" spans="2:7" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="44" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B44" s="157" t="s">
+      <c r="B44" s="160" t="s">
         <v>324</v>
       </c>
-      <c r="C44" s="157" t="s">
+      <c r="C44" s="160" t="s">
         <v>325</v>
       </c>
-      <c r="D44" s="157"/>
-      <c r="E44" s="157"/>
-      <c r="F44" s="157" t="s">
+      <c r="D44" s="160"/>
+      <c r="E44" s="160"/>
+      <c r="F44" s="160" t="s">
         <v>326</v>
       </c>
-      <c r="G44" s="157" t="s">
+      <c r="G44" s="160" t="s">
         <v>327</v>
       </c>
     </row>
     <row r="45" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B45" s="158"/>
+      <c r="B45" s="154"/>
       <c r="C45" s="19" t="s">
         <v>328</v>
       </c>
@@ -22096,11 +20025,11 @@
       <c r="E45" s="19" t="s">
         <v>330</v>
       </c>
-      <c r="F45" s="160"/>
-      <c r="G45" s="160"/>
+      <c r="F45" s="155"/>
+      <c r="G45" s="155"/>
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B46" s="159" t="s">
+      <c r="B46" s="156" t="s">
         <v>331</v>
       </c>
       <c r="C46" s="17" t="str">
@@ -22115,17 +20044,17 @@
         <f>"89.272"</f>
         <v>89.272</v>
       </c>
-      <c r="F46" s="158" t="str">
+      <c r="F46" s="154" t="str">
         <f>"0.000"</f>
         <v>0.000</v>
       </c>
-      <c r="G46" s="158" t="str">
+      <c r="G46" s="154" t="str">
         <f>"2702.000"</f>
         <v>2702.000</v>
       </c>
     </row>
     <row r="47" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B47" s="159"/>
+      <c r="B47" s="156"/>
       <c r="C47" s="17" t="str">
         <f>"(113.981)"</f>
         <v>(113.981)</v>
@@ -22138,11 +20067,11 @@
         <f>"(133.323)"</f>
         <v>(133.323)</v>
       </c>
-      <c r="F47" s="158"/>
-      <c r="G47" s="158"/>
+      <c r="F47" s="154"/>
+      <c r="G47" s="154"/>
     </row>
     <row r="48" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B48" s="159" t="s">
+      <c r="B48" s="156" t="s">
         <v>332</v>
       </c>
       <c r="C48" s="17" t="str">
@@ -22157,17 +20086,17 @@
         <f>"1.372"</f>
         <v>1.372</v>
       </c>
-      <c r="F48" s="158" t="str">
+      <c r="F48" s="154" t="str">
         <f>"0.000"</f>
         <v>0.000</v>
       </c>
-      <c r="G48" s="158" t="str">
+      <c r="G48" s="154" t="str">
         <f>"8.000"</f>
         <v>8.000</v>
       </c>
     </row>
     <row r="49" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B49" s="159"/>
+      <c r="B49" s="156"/>
       <c r="C49" s="17" t="str">
         <f>"(1.166)"</f>
         <v>(1.166)</v>
@@ -22180,11 +20109,11 @@
         <f>"(1.192)"</f>
         <v>(1.192)</v>
       </c>
-      <c r="F49" s="158"/>
-      <c r="G49" s="158"/>
+      <c r="F49" s="154"/>
+      <c r="G49" s="154"/>
     </row>
     <row r="50" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B50" s="159" t="s">
+      <c r="B50" s="156" t="s">
         <v>355</v>
       </c>
       <c r="C50" s="17" t="str">
@@ -22199,17 +20128,17 @@
         <f>"0.397"</f>
         <v>0.397</v>
       </c>
-      <c r="F50" s="158" t="str">
+      <c r="F50" s="154" t="str">
         <f>"-0.048"</f>
         <v>-0.048</v>
       </c>
-      <c r="G50" s="158" t="str">
+      <c r="G50" s="154" t="str">
         <f>"0.991"</f>
         <v>0.991</v>
       </c>
     </row>
     <row r="51" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B51" s="159"/>
+      <c r="B51" s="156"/>
       <c r="C51" s="17" t="str">
         <f>"(0.181)"</f>
         <v>(0.181)</v>
@@ -22222,11 +20151,11 @@
         <f>"(0.188)"</f>
         <v>(0.188)</v>
       </c>
-      <c r="F51" s="158"/>
-      <c r="G51" s="158"/>
+      <c r="F51" s="154"/>
+      <c r="G51" s="154"/>
     </row>
     <row r="52" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B52" s="159" t="s">
+      <c r="B52" s="156" t="s">
         <v>333</v>
       </c>
       <c r="C52" s="17" t="str">
@@ -22241,17 +20170,17 @@
         <f>"0.536"</f>
         <v>0.536</v>
       </c>
-      <c r="F52" s="158" t="str">
+      <c r="F52" s="154" t="str">
         <f>"-3.000"</f>
         <v>-3.000</v>
       </c>
-      <c r="G52" s="158" t="str">
+      <c r="G52" s="154" t="str">
         <f>"14.000"</f>
         <v>14.000</v>
       </c>
     </row>
     <row r="53" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B53" s="159"/>
+      <c r="B53" s="156"/>
       <c r="C53" s="17" t="str">
         <f>"(1.096)"</f>
         <v>(1.096)</v>
@@ -22264,11 +20193,11 @@
         <f>"(1.140)"</f>
         <v>(1.140)</v>
       </c>
-      <c r="F53" s="158"/>
-      <c r="G53" s="158"/>
+      <c r="F53" s="154"/>
+      <c r="G53" s="154"/>
     </row>
     <row r="54" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B54" s="159" t="s">
+      <c r="B54" s="156" t="s">
         <v>357</v>
       </c>
       <c r="C54" s="17" t="str">
@@ -22283,17 +20212,17 @@
         <f>"0.000"</f>
         <v>0.000</v>
       </c>
-      <c r="F54" s="158" t="str">
+      <c r="F54" s="154" t="str">
         <f>"0.000"</f>
         <v>0.000</v>
       </c>
-      <c r="G54" s="158" t="str">
+      <c r="G54" s="154" t="str">
         <f>"6.977"</f>
         <v>6.977</v>
       </c>
     </row>
     <row r="55" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B55" s="159"/>
+      <c r="B55" s="156"/>
       <c r="C55" s="17" t="str">
         <f>"(2.864)"</f>
         <v>(2.864)</v>
@@ -22306,11 +20235,11 @@
         <f>"(0.000)"</f>
         <v>(0.000)</v>
       </c>
-      <c r="F55" s="158"/>
-      <c r="G55" s="158"/>
+      <c r="F55" s="154"/>
+      <c r="G55" s="154"/>
     </row>
     <row r="56" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B56" s="159" t="s">
+      <c r="B56" s="156" t="s">
         <v>359</v>
       </c>
       <c r="C56" s="17" t="str">
@@ -22325,17 +20254,17 @@
         <f>"0.000"</f>
         <v>0.000</v>
       </c>
-      <c r="F56" s="158" t="str">
+      <c r="F56" s="154" t="str">
         <f>"0.000"</f>
         <v>0.000</v>
       </c>
-      <c r="G56" s="158" t="str">
+      <c r="G56" s="154" t="str">
         <f>"0.891"</f>
         <v>0.891</v>
       </c>
     </row>
     <row r="57" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B57" s="159"/>
+      <c r="B57" s="156"/>
       <c r="C57" s="17" t="str">
         <f>"(0.297)"</f>
         <v>(0.297)</v>
@@ -22348,11 +20277,11 @@
         <f>"(0.000)"</f>
         <v>(0.000)</v>
       </c>
-      <c r="F57" s="158"/>
-      <c r="G57" s="158"/>
+      <c r="F57" s="154"/>
+      <c r="G57" s="154"/>
     </row>
     <row r="58" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B58" s="159" t="s">
+      <c r="B58" s="156" t="s">
         <v>358</v>
       </c>
       <c r="C58" s="17" t="str">
@@ -22367,17 +20296,17 @@
         <f>"3.443"</f>
         <v>3.443</v>
       </c>
-      <c r="F58" s="158" t="str">
+      <c r="F58" s="154" t="str">
         <f>"0.000"</f>
         <v>0.000</v>
       </c>
-      <c r="G58" s="158" t="str">
+      <c r="G58" s="154" t="str">
         <f>"7.912"</f>
         <v>7.912</v>
       </c>
     </row>
     <row r="59" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B59" s="159"/>
+      <c r="B59" s="156"/>
       <c r="C59" s="17" t="str">
         <f>"(1.489)"</f>
         <v>(1.489)</v>
@@ -22390,11 +20319,11 @@
         <f>"(1.338)"</f>
         <v>(1.338)</v>
       </c>
-      <c r="F59" s="158"/>
-      <c r="G59" s="158"/>
+      <c r="F59" s="154"/>
+      <c r="G59" s="154"/>
     </row>
     <row r="60" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B60" s="159" t="s">
+      <c r="B60" s="156" t="s">
         <v>356</v>
       </c>
       <c r="C60" s="17" t="str">
@@ -22409,17 +20338,17 @@
         <f>"0.445"</f>
         <v>0.445</v>
       </c>
-      <c r="F60" s="158" t="str">
+      <c r="F60" s="154" t="str">
         <f>"-0.090"</f>
         <v>-0.090</v>
       </c>
-      <c r="G60" s="158" t="str">
+      <c r="G60" s="154" t="str">
         <f>"0.911"</f>
         <v>0.911</v>
       </c>
     </row>
     <row r="61" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B61" s="161"/>
+      <c r="B61" s="157"/>
       <c r="C61" s="18" t="str">
         <f>"(0.177)"</f>
         <v>(0.177)</v>
@@ -22432,29 +20361,28 @@
         <f>"(0.187)"</f>
         <v>(0.187)</v>
       </c>
-      <c r="F61" s="160"/>
-      <c r="G61" s="160"/>
+      <c r="F61" s="155"/>
+      <c r="G61" s="155"/>
     </row>
   </sheetData>
   <mergeCells count="51">
-    <mergeCell ref="G60:G61"/>
-    <mergeCell ref="G54:G55"/>
-    <mergeCell ref="B56:B57"/>
-    <mergeCell ref="F56:F57"/>
-    <mergeCell ref="G56:G57"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="F58:F59"/>
-    <mergeCell ref="G58:G59"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="F54:F55"/>
-    <mergeCell ref="B50:B51"/>
-    <mergeCell ref="F50:F51"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="F60:F61"/>
-    <mergeCell ref="G50:G51"/>
-    <mergeCell ref="B52:B53"/>
-    <mergeCell ref="F52:F53"/>
-    <mergeCell ref="G52:G53"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="O3:P3"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="N4:N5"/>
+    <mergeCell ref="N6:N7"/>
+    <mergeCell ref="N8:N9"/>
+    <mergeCell ref="H6:H7"/>
     <mergeCell ref="B48:B49"/>
     <mergeCell ref="F48:F49"/>
     <mergeCell ref="G48:G49"/>
@@ -22471,23 +20399,24 @@
     <mergeCell ref="H12:H13"/>
     <mergeCell ref="C20:D20"/>
     <mergeCell ref="E20:F20"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="O3:P3"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="N4:N5"/>
-    <mergeCell ref="N6:N7"/>
-    <mergeCell ref="N8:N9"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="B50:B51"/>
+    <mergeCell ref="F50:F51"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="F60:F61"/>
+    <mergeCell ref="G50:G51"/>
+    <mergeCell ref="B52:B53"/>
+    <mergeCell ref="F52:F53"/>
+    <mergeCell ref="G52:G53"/>
+    <mergeCell ref="G60:G61"/>
+    <mergeCell ref="G54:G55"/>
+    <mergeCell ref="B56:B57"/>
+    <mergeCell ref="F56:F57"/>
+    <mergeCell ref="G56:G57"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="F58:F59"/>
+    <mergeCell ref="G58:G59"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="F54:F55"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -25006,6 +22935,54 @@
     <row r="90" spans="2:12" hidden="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="64">
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="B34:B45"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="K34:L34"/>
+    <mergeCell ref="C35:C36"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="C43:C44"/>
+    <mergeCell ref="C37:C38"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="K25:L25"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="D56:E56"/>
+    <mergeCell ref="F56:G56"/>
+    <mergeCell ref="K56:L56"/>
+    <mergeCell ref="D47:E47"/>
+    <mergeCell ref="F47:G47"/>
+    <mergeCell ref="K47:L47"/>
+    <mergeCell ref="B78:B89"/>
+    <mergeCell ref="D69:E69"/>
+    <mergeCell ref="F69:G69"/>
+    <mergeCell ref="K69:L69"/>
+    <mergeCell ref="D78:E78"/>
+    <mergeCell ref="F78:G78"/>
+    <mergeCell ref="K78:L78"/>
+    <mergeCell ref="C79:C80"/>
+    <mergeCell ref="C85:C86"/>
+    <mergeCell ref="C87:C88"/>
+    <mergeCell ref="C70:C71"/>
+    <mergeCell ref="C72:C73"/>
+    <mergeCell ref="C74:C75"/>
+    <mergeCell ref="C81:C82"/>
+    <mergeCell ref="C83:C84"/>
+    <mergeCell ref="B2:B9"/>
+    <mergeCell ref="B11:B22"/>
+    <mergeCell ref="B47:B54"/>
+    <mergeCell ref="B56:B67"/>
+    <mergeCell ref="B69:B76"/>
+    <mergeCell ref="B25:B32"/>
     <mergeCell ref="C65:C66"/>
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="C5:C6"/>
@@ -25022,54 +22999,6 @@
     <mergeCell ref="C16:C17"/>
     <mergeCell ref="C59:C60"/>
     <mergeCell ref="C61:C62"/>
-    <mergeCell ref="B2:B9"/>
-    <mergeCell ref="B11:B22"/>
-    <mergeCell ref="B47:B54"/>
-    <mergeCell ref="B56:B67"/>
-    <mergeCell ref="B69:B76"/>
-    <mergeCell ref="B25:B32"/>
-    <mergeCell ref="B78:B89"/>
-    <mergeCell ref="D69:E69"/>
-    <mergeCell ref="F69:G69"/>
-    <mergeCell ref="K69:L69"/>
-    <mergeCell ref="D78:E78"/>
-    <mergeCell ref="F78:G78"/>
-    <mergeCell ref="K78:L78"/>
-    <mergeCell ref="C79:C80"/>
-    <mergeCell ref="C85:C86"/>
-    <mergeCell ref="C87:C88"/>
-    <mergeCell ref="C70:C71"/>
-    <mergeCell ref="C72:C73"/>
-    <mergeCell ref="C74:C75"/>
-    <mergeCell ref="C81:C82"/>
-    <mergeCell ref="C83:C84"/>
-    <mergeCell ref="D56:E56"/>
-    <mergeCell ref="F56:G56"/>
-    <mergeCell ref="K56:L56"/>
-    <mergeCell ref="D47:E47"/>
-    <mergeCell ref="F47:G47"/>
-    <mergeCell ref="K47:L47"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="K25:L25"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="B34:B45"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="K34:L34"/>
-    <mergeCell ref="C35:C36"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="C43:C44"/>
-    <mergeCell ref="C37:C38"/>
-    <mergeCell ref="C39:C40"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Projects/MISQ/MISQ round 2/afterSEmeeting260624_results, theory and LR.xlsx
+++ b/Projects/MISQ/MISQ round 2/afterSEmeeting260624_results, theory and LR.xlsx
@@ -8,25 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dylanchen/Desktop/geek-community/Projects/MISQ/MISQ round 2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2608270F-413F-6A4D-BACE-2FB84F46E895}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3239C758-9734-A047-8503-34D139DF2BA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19580" activeTab="2" xr2:uid="{30F402B7-E6D8-E34B-8063-713AC97DE139}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="38420" windowHeight="19540" xr2:uid="{30F402B7-E6D8-E34B-8063-713AC97DE139}"/>
   </bookViews>
   <sheets>
-    <sheet name="Theory" sheetId="8" r:id="rId1"/>
-    <sheet name="Result" sheetId="10" r:id="rId2"/>
-    <sheet name="Results (with table)" sheetId="7" r:id="rId3"/>
-    <sheet name="Literature Review" sheetId="9" r:id="rId4"/>
-    <sheet name="interaction plot (20260608)" sheetId="6" r:id="rId5"/>
-    <sheet name="table in paper" sheetId="3" r:id="rId6"/>
-    <sheet name="Sheet1" sheetId="1" r:id="rId7"/>
-    <sheet name="Sheet3" sheetId="5" r:id="rId8"/>
-    <sheet name="interaction plot" sheetId="2" r:id="rId9"/>
+    <sheet name="mechanism" sheetId="12" r:id="rId1"/>
+    <sheet name="robustness check" sheetId="13" r:id="rId2"/>
+    <sheet name="Theory" sheetId="8" r:id="rId3"/>
+    <sheet name="Result" sheetId="10" r:id="rId4"/>
+    <sheet name="Results (with table)" sheetId="7" r:id="rId5"/>
+    <sheet name="Literature Review" sheetId="9" r:id="rId6"/>
+    <sheet name="interaction plot (20260608)" sheetId="6" r:id="rId7"/>
+    <sheet name="table in paper" sheetId="3" r:id="rId8"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId9"/>
+    <sheet name="Sheet3" sheetId="5" r:id="rId10"/>
+    <sheet name="interaction plot" sheetId="2" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_Hlk194498603" localSheetId="3">'Literature Review'!$A$15</definedName>
-    <definedName name="_Ref194135344" localSheetId="2">'Results (with table)'!$N$26</definedName>
-    <definedName name="_Ref210225085" localSheetId="2">'Results (with table)'!$D$42</definedName>
+    <definedName name="_Hlk194498603" localSheetId="5">'Literature Review'!$A$15</definedName>
+    <definedName name="_Ref194135344" localSheetId="4">'Results (with table)'!$N$26</definedName>
+    <definedName name="_Ref210225085" localSheetId="4">'Results (with table)'!$D$42</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -52,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1343" uniqueCount="574">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1381" uniqueCount="606">
   <si>
     <t>DV: # human answers</t>
   </si>
@@ -2025,9 +2027,6 @@
     <t>Other DV</t>
   </si>
   <si>
-    <t>strength interpretation</t>
-  </si>
-  <si>
     <t>verify weak competitor</t>
   </si>
   <si>
@@ -2055,9 +2054,6 @@
 AI quality increase second human quality</t>
   </si>
   <si>
-    <t>Extend or Deepen Insights</t>
-  </si>
-  <si>
     <t>first human quality increase on what?</t>
   </si>
   <si>
@@ -2077,10 +2073,6 @@
   </si>
   <si>
     <t>AI lebel 更多地 increase high repuration expert contribution</t>
-  </si>
-  <si>
-    <t>AI label 更多地 decrease high repuration expert quality
-AI quality 更多地 increase  high repuration expert quality  (out of surprise)</t>
   </si>
   <si>
     <t>quality increase, how about recognition?</t>
@@ -2283,98 +2275,203 @@
 - what's more? "Overconfidence"</t>
   </si>
   <si>
-    <t>- AI label through system 1 output negative affect towards AI. Affect persists as continuous background "mood".
-- "Law of least effort" lowers the effort.
-- "Anchoring prevents sufficient adjustment", even for slow decision</t>
+    <t>-0.198 *</t>
+  </si>
+  <si>
+    <t>0.304 **</t>
+  </si>
+  <si>
+    <t>-0.058 ***</t>
+  </si>
+  <si>
+    <t>0.029</t>
+  </si>
+  <si>
+    <t>(0.149)</t>
+  </si>
+  <si>
+    <t>(0.025)</t>
+  </si>
+  <si>
+    <t>-0.060</t>
+  </si>
+  <si>
+    <t>(0.064)</t>
+  </si>
+  <si>
+    <t>(0.088)</t>
+  </si>
+  <si>
+    <t>difficult questions</t>
+  </si>
+  <si>
+    <t>easy questions</t>
+  </si>
+  <si>
+    <t>2,373</t>
+  </si>
+  <si>
+    <t>1,230</t>
+  </si>
+  <si>
+    <t>-0.002</t>
+  </si>
+  <si>
+    <t>-0.031 *</t>
+  </si>
+  <si>
+    <t>0.382 ***</t>
+  </si>
+  <si>
+    <t>0.330 ***</t>
+  </si>
+  <si>
+    <t>1,365</t>
+  </si>
+  <si>
+    <t>1,320</t>
+  </si>
+  <si>
+    <t>expert first answer</t>
+  </si>
+  <si>
+    <t>rookie first answer</t>
+  </si>
+  <si>
+    <t>difficult question -&gt; AI weak competitor -&gt; let me answer</t>
+  </si>
+  <si>
+    <t>easy question -&gt; AI even weak still enough</t>
+  </si>
+  <si>
+    <t>difficult question + AI lengthy -&gt; may be comprehensive -&gt; deter</t>
+  </si>
+  <si>
+    <t>easy question + AI length -&gt; AI is enough</t>
+  </si>
+  <si>
+    <t>overconfidence</t>
+  </si>
+  <si>
+    <t>expert -&gt; facing surprise, stronger identity threat</t>
+  </si>
+  <si>
+    <t>Expert are not affected by length, rookie regard length as low-quality heuristic</t>
+  </si>
+  <si>
+    <t>AI serve as benchmark</t>
+  </si>
+  <si>
+    <t>which subgroup can make effect concentrated</t>
+  </si>
+  <si>
+    <t>Test 5 — Effort-proxy outcome test</t>
+  </si>
+  <si>
+    <t>Identity-stakes / expertise moderation</t>
+  </si>
+  <si>
+    <t>Post hoc</t>
+  </si>
+  <si>
+    <t>mechnism</t>
+  </si>
+  <si>
+    <t>verify overconfidence</t>
+  </si>
+  <si>
+    <t>AI label 更多地 decrease high repuration expert quality</t>
+  </si>
+  <si>
+    <t>AI quality 更多地 increase  high repuration expert quality  (out of surprise)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">textual </t>
+  </si>
+  <si>
+    <t>AI label increase human contribution</t>
+  </si>
+  <si>
+    <t>AI length decrease human contribution</t>
+  </si>
+  <si>
+    <t>AI lael decrease first human quality</t>
+  </si>
+  <si>
+    <t>AI quality increase first human quality</t>
+  </si>
+  <si>
+    <t>mechanism</t>
+  </si>
+  <si>
+    <t>weak compatitor</t>
+  </si>
+  <si>
+    <t>textual analysis on comment</t>
+  </si>
+  <si>
+    <t>benchmark</t>
+  </si>
+  <si>
+    <t>include AI and more results</t>
   </si>
   <si>
     <t>- Quality is a slow signal—inaccessible without deliberate reading. 
 - High quality triggers "surprise", forcing System 2 to override.
-- what's more, professional identity threat is "sufficiently important" to activate System 2</t>
-  </si>
-  <si>
-    <t>-0.198 *</t>
-  </si>
-  <si>
-    <t>0.304 **</t>
-  </si>
-  <si>
-    <t>-0.058 ***</t>
-  </si>
-  <si>
-    <t>0.029</t>
-  </si>
-  <si>
-    <t>(0.149)</t>
-  </si>
-  <si>
-    <t>(0.025)</t>
-  </si>
-  <si>
-    <t>-0.060</t>
-  </si>
-  <si>
-    <t>(0.064)</t>
-  </si>
-  <si>
-    <t>(0.088)</t>
-  </si>
-  <si>
-    <t>difficult questions</t>
-  </si>
-  <si>
-    <t>easy questions</t>
-  </si>
-  <si>
-    <t>2,373</t>
-  </si>
-  <si>
-    <t>1,230</t>
-  </si>
-  <si>
-    <t>-0.002</t>
-  </si>
-  <si>
-    <t>-0.031 *</t>
-  </si>
-  <si>
-    <t>0.382 ***</t>
-  </si>
-  <si>
-    <t>0.330 ***</t>
-  </si>
-  <si>
-    <t>1,365</t>
-  </si>
-  <si>
-    <t>1,320</t>
-  </si>
-  <si>
-    <t>expert first answer</t>
-  </si>
-  <si>
-    <t>rookie first answer</t>
-  </si>
-  <si>
-    <t>difficult question -&gt; AI weak competitor -&gt; let me answer</t>
-  </si>
-  <si>
-    <t>easy question -&gt; AI even weak still enough</t>
-  </si>
-  <si>
-    <t>difficult question + AI lengthy -&gt; may be comprehensive -&gt; deter</t>
-  </si>
-  <si>
-    <t>easy question + AI length -&gt; AI is enough</t>
-  </si>
-  <si>
-    <t>overconfidence</t>
-  </si>
-  <si>
-    <t>expert -&gt; facing surprise, stronger identity threat</t>
-  </si>
-  <si>
-    <t>Expert are not affected by length, rookie regard length as low-quality heuristic</t>
+- what's more, professional identity threat is "sufficiently important" to activate System 2
+- benchmark</t>
+  </si>
+  <si>
+    <t>- AI label through system 1 output negative affect towards AI. Affect persists as continuous background "mood".
+- "Law of least effort" lowers the effort.</t>
+  </si>
+  <si>
+    <t>H1</t>
+  </si>
+  <si>
+    <t>H2</t>
+  </si>
+  <si>
+    <t>H3</t>
+  </si>
+  <si>
+    <t>H4</t>
+  </si>
+  <si>
+    <t>theory</t>
+  </si>
+  <si>
+    <t>weak competitor</t>
+  </si>
+  <si>
+    <t>question complexity subgroup analysis</t>
+  </si>
+  <si>
+    <t>textual analysis</t>
+  </si>
+  <si>
+    <t>supprot or not</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>length -&gt; comprehensiveness</t>
+  </si>
+  <si>
+    <t>comprehensiveness -&gt; stronger competition</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>weak competitor -&gt; least effort</t>
+  </si>
+  <si>
+    <t>top25% subgroup exptertise analysis</t>
+  </si>
+  <si>
+    <t>difficult and/or rookie subgroup</t>
   </si>
 </sst>
 </file>
@@ -2542,13 +2639,6 @@
     </font>
     <font>
       <sz val="16"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="16"/>
       <color rgb="FFFFC000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -2580,6 +2670,13 @@
       <color rgb="FFFF0000"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="9"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="7">
@@ -2620,7 +2717,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -2748,11 +2845,33 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="179">
+  <cellXfs count="187">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -3032,7 +3151,7 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3042,30 +3161,30 @@
     <xf numFmtId="49" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3075,13 +3194,7 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
@@ -3173,16 +3286,16 @@
     <xf numFmtId="0" fontId="17" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -3256,6 +3369,34 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -16380,6 +16521,858 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4619786A-464A-1C43-8F84-5024A3103C53}">
+  <dimension ref="B1:E8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="3" max="3" width="38" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="37.83203125" customWidth="1"/>
+    <col min="5" max="5" width="12.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="C1" t="s">
+        <v>594</v>
+      </c>
+      <c r="D1" t="s">
+        <v>583</v>
+      </c>
+      <c r="E1" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="2" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B2" t="s">
+        <v>590</v>
+      </c>
+      <c r="C2" t="s">
+        <v>595</v>
+      </c>
+      <c r="D2" t="s">
+        <v>596</v>
+      </c>
+      <c r="E2" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="C3" t="s">
+        <v>595</v>
+      </c>
+      <c r="D3" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B4" t="s">
+        <v>591</v>
+      </c>
+      <c r="C4" t="s">
+        <v>600</v>
+      </c>
+      <c r="D4" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="C5" t="s">
+        <v>601</v>
+      </c>
+      <c r="D5" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B6" t="s">
+        <v>592</v>
+      </c>
+      <c r="C6" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B7" t="s">
+        <v>593</v>
+      </c>
+      <c r="C7" t="s">
+        <v>586</v>
+      </c>
+      <c r="D7" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="D8" t="s">
+        <v>605</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C46079C1-F4F3-4E3A-8CE8-2113D4F28B6B}">
+  <dimension ref="A1:J15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="14.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" customWidth="1"/>
+    <col min="4" max="4" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.6640625" customWidth="1"/>
+    <col min="10" max="10" width="9.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B1" t="s">
+        <v>376</v>
+      </c>
+      <c r="H1" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>367</v>
+      </c>
+      <c r="B2">
+        <v>0.34200000000000003</v>
+      </c>
+      <c r="G2" t="s">
+        <v>367</v>
+      </c>
+      <c r="H2">
+        <v>5.4610000000000003</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>368</v>
+      </c>
+      <c r="B3">
+        <v>-1.6E-2</v>
+      </c>
+      <c r="G3" t="s">
+        <v>368</v>
+      </c>
+      <c r="H3">
+        <v>-0.188</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>369</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="G4" t="s">
+        <v>369</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>370</v>
+      </c>
+      <c r="B5">
+        <v>0.747</v>
+      </c>
+      <c r="G5" t="s">
+        <v>370</v>
+      </c>
+      <c r="H5">
+        <v>1.349</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>371</v>
+      </c>
+      <c r="B6">
+        <v>-6.6000000000000003E-2</v>
+      </c>
+      <c r="G6" t="s">
+        <v>371</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>372</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="G7" t="s">
+        <v>372</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>375</v>
+      </c>
+      <c r="B10" t="s">
+        <v>366</v>
+      </c>
+      <c r="C10" t="s">
+        <v>374</v>
+      </c>
+      <c r="D10" t="s">
+        <v>373</v>
+      </c>
+      <c r="G10" t="s">
+        <v>375</v>
+      </c>
+      <c r="H10" t="s">
+        <v>366</v>
+      </c>
+      <c r="I10" t="s">
+        <v>374</v>
+      </c>
+      <c r="J10" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>6.2315934999999998</v>
+      </c>
+      <c r="C11">
+        <f>$B$2+$B$5+($B$3+$B$6)*A11</f>
+        <v>0.57800933300000001</v>
+      </c>
+      <c r="G11">
+        <v>6.2315934999999998</v>
+      </c>
+      <c r="I11">
+        <f>$H$2+$H$5+($H$3+$H$6)*G11</f>
+        <v>5.6384604220000005</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>5.1203884999999998</v>
+      </c>
+      <c r="C12">
+        <f t="shared" ref="C12:C13" si="0">$B$2+$B$5+($B$3+$B$6)*A12</f>
+        <v>0.66912814300000001</v>
+      </c>
+      <c r="G12">
+        <v>5.1203884999999998</v>
+      </c>
+      <c r="I12">
+        <f t="shared" ref="I12:I13" si="1">$H$2+$H$5+($H$3+$H$6)*G12</f>
+        <v>5.8473669620000006</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>0</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+      <c r="C13">
+        <f t="shared" si="0"/>
+        <v>1.089</v>
+      </c>
+      <c r="D13">
+        <f>$B$2+$B$3*A13</f>
+        <v>0.34200000000000003</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <f t="shared" si="1"/>
+        <v>6.8100000000000005</v>
+      </c>
+      <c r="J13">
+        <f>$H$2+$H$3*G13</f>
+        <v>5.4610000000000003</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>2.1058599999999998</v>
+      </c>
+      <c r="D14">
+        <f t="shared" ref="D14:D15" si="2">$B$2+$B$3*A14</f>
+        <v>0.30830624000000001</v>
+      </c>
+      <c r="G14">
+        <v>2.1058599999999998</v>
+      </c>
+      <c r="J14">
+        <f t="shared" ref="J14:J15" si="3">$H$2+$H$3*G14</f>
+        <v>5.0650983200000006</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>4.780926</v>
+      </c>
+      <c r="D15">
+        <f t="shared" si="2"/>
+        <v>0.26550518400000001</v>
+      </c>
+      <c r="G15">
+        <v>4.780926</v>
+      </c>
+      <c r="J15">
+        <f t="shared" si="3"/>
+        <v>4.5621859120000003</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2D15DE7-CAF9-4A3C-99EC-AE501B1448E2}">
+  <dimension ref="A1:M47"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.33203125" customWidth="1"/>
+    <col min="4" max="4" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" t="s">
+        <v>321</v>
+      </c>
+      <c r="I1" t="s">
+        <v>322</v>
+      </c>
+      <c r="L1" t="s">
+        <v>321</v>
+      </c>
+      <c r="M1" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2">
+        <v>0.22600000000000001</v>
+      </c>
+      <c r="C2">
+        <v>1.113</v>
+      </c>
+      <c r="G2" t="s">
+        <v>316</v>
+      </c>
+      <c r="H2">
+        <v>2.7743699999999998</v>
+      </c>
+      <c r="I2">
+        <v>2.8641299999999998</v>
+      </c>
+      <c r="K2" t="s">
+        <v>319</v>
+      </c>
+      <c r="L2">
+        <v>5.6759909999999998</v>
+      </c>
+      <c r="M2">
+        <v>0.5556025</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3">
+        <v>-4.4999999999999998E-2</v>
+      </c>
+      <c r="C3">
+        <v>-0.22700000000000001</v>
+      </c>
+      <c r="K3" t="s">
+        <v>320</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="G4" t="s">
+        <v>323</v>
+      </c>
+      <c r="H4">
+        <v>0.27068130000000001</v>
+      </c>
+      <c r="I4">
+        <v>0.29724149999999999</v>
+      </c>
+      <c r="K4" t="s">
+        <v>319</v>
+      </c>
+      <c r="L4">
+        <v>0.55539000000000005</v>
+      </c>
+      <c r="M4">
+        <v>0.15205959999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" t="s">
+        <v>127</v>
+      </c>
+      <c r="K5" t="s">
+        <v>320</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="6">
+        <v>0.68400000000000005</v>
+      </c>
+      <c r="C6">
+        <v>1.2390000000000001</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="H6" t="s">
+        <v>321</v>
+      </c>
+      <c r="I6" t="s">
+        <v>322</v>
+      </c>
+      <c r="L6" t="s">
+        <v>321</v>
+      </c>
+      <c r="M6" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>186</v>
+      </c>
+      <c r="B7">
+        <v>-2.5999999999999999E-2</v>
+      </c>
+      <c r="C7">
+        <v>-0.20799999999999999</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="G7" t="s">
+        <v>186</v>
+      </c>
+      <c r="H7">
+        <f>4.662178- 1.488808</f>
+        <v>3.1733700000000002</v>
+      </c>
+      <c r="I7">
+        <f>4.662178+1.488808</f>
+        <v>6.1509859999999996</v>
+      </c>
+      <c r="K7" t="s">
+        <v>319</v>
+      </c>
+      <c r="L7">
+        <v>5.6759909999999998</v>
+      </c>
+      <c r="M7">
+        <v>0.5556025</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>134</v>
+      </c>
+      <c r="B8">
+        <v>-5.8000000000000003E-2</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="K8" t="s">
+        <v>320</v>
+      </c>
+      <c r="L8">
+        <v>3.4433929999999999</v>
+      </c>
+      <c r="M8">
+        <v>1.3375330000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>229</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0.49399999999999999</v>
+      </c>
+      <c r="G9" t="s">
+        <v>229</v>
+      </c>
+      <c r="H9">
+        <f>0.5062086-0.1771589</f>
+        <v>0.3290497</v>
+      </c>
+      <c r="I9">
+        <f>0.5062086+0.1771589</f>
+        <v>0.68336750000000002</v>
+      </c>
+      <c r="K9" t="s">
+        <v>319</v>
+      </c>
+      <c r="L9">
+        <v>0.55539000000000005</v>
+      </c>
+      <c r="M9">
+        <v>0.15205959999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>149</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>-0.109</v>
+      </c>
+      <c r="K10" t="s">
+        <v>320</v>
+      </c>
+      <c r="L10">
+        <v>0.44526110000000002</v>
+      </c>
+      <c r="M10">
+        <v>0.18690109999999999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B15" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>316</v>
+      </c>
+      <c r="B16" t="s">
+        <v>317</v>
+      </c>
+      <c r="C16" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <f>L2+M2</f>
+        <v>6.2315934999999998</v>
+      </c>
+      <c r="B17">
+        <f>$B$2+$B$3*A17</f>
+        <v>-5.4421707499999999E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <f>L2-M2</f>
+        <v>5.1203884999999998</v>
+      </c>
+      <c r="B18">
+        <f>$B$2+$B$3*A18</f>
+        <v>-4.4174824999999862E-3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>0</v>
+      </c>
+      <c r="B19">
+        <f>$B$2+$B$3*A19</f>
+        <v>0.22600000000000001</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>0</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B22" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>316</v>
+      </c>
+      <c r="B23" t="s">
+        <v>317</v>
+      </c>
+      <c r="C23" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <f>L7+M7</f>
+        <v>6.2315934999999998</v>
+      </c>
+      <c r="B24">
+        <f>$C$2+$C$3*A24</f>
+        <v>-0.30157172450000003</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <f>L7-M7</f>
+        <v>5.1203884999999998</v>
+      </c>
+      <c r="B25">
+        <f>$C$2+$C$3*A25</f>
+        <v>-4.9328189499999953E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>0</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>0</v>
+      </c>
+      <c r="C27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B33" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>186</v>
+      </c>
+      <c r="B34" t="s">
+        <v>317</v>
+      </c>
+      <c r="C34" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A35">
+        <f>L7-M7</f>
+        <v>5.1203884999999998</v>
+      </c>
+      <c r="B35">
+        <f>B6+B7*A35+B8*A35</f>
+        <v>0.25388736600000006</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A36">
+        <f>L7+M7</f>
+        <v>6.2315934999999998</v>
+      </c>
+      <c r="B36">
+        <f>B6+B7*A36+A36*B8</f>
+        <v>0.16054614600000006</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A37">
+        <v>0</v>
+      </c>
+      <c r="B37">
+        <f>B6+B7*A37+A37*B8</f>
+        <v>0.68400000000000005</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A38">
+        <f>L8-M8</f>
+        <v>2.1058599999999998</v>
+      </c>
+      <c r="C38">
+        <f>B7*(A38)</f>
+        <v>-5.4752359999999993E-2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A39">
+        <f>L8+M8</f>
+        <v>4.780926</v>
+      </c>
+      <c r="C39">
+        <f>B7*A39</f>
+        <v>-0.124304076</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A40">
+        <v>0</v>
+      </c>
+      <c r="C40">
+        <f>B7*A40</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B41" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>229</v>
+      </c>
+      <c r="B42" t="s">
+        <v>317</v>
+      </c>
+      <c r="C42" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A43">
+        <f>L9-M9</f>
+        <v>0.40333040000000009</v>
+      </c>
+      <c r="B43">
+        <f>D9*A43+D10*A43</f>
+        <v>0.15528220400000003</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A44">
+        <f>L9+M9</f>
+        <v>0.70744960000000001</v>
+      </c>
+      <c r="B44">
+        <f>D9*A44+D10*A44</f>
+        <v>0.272368096</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A45">
+        <f>L10-M10</f>
+        <v>0.25836000000000003</v>
+      </c>
+      <c r="C45">
+        <f>D9*A45</f>
+        <v>0.12762984000000002</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A46">
+        <f>L10+M10</f>
+        <v>0.63216220000000001</v>
+      </c>
+      <c r="C46">
+        <f>D9*A46</f>
+        <v>0.31228812680000001</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A47">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C3FA5B3-B001-5E4C-8923-ACBF510FEE8E}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{662C8392-57F3-DA44-A638-CAE1AE9DCA0E}">
   <dimension ref="B2:D11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -16393,7 +17386,7 @@
   <sheetData>
     <row r="2" spans="2:4" x14ac:dyDescent="0.2">
       <c r="C2" s="105" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="4" spans="2:4" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -16409,7 +17402,7 @@
       </c>
     </row>
     <row r="6" spans="2:4" ht="22" x14ac:dyDescent="0.2">
-      <c r="B6" s="120" t="s">
+      <c r="B6" s="118" t="s">
         <v>391</v>
       </c>
       <c r="C6" s="28" t="s">
@@ -16420,48 +17413,48 @@
       </c>
     </row>
     <row r="7" spans="2:4" ht="111" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="121"/>
+      <c r="B7" s="119"/>
       <c r="C7" s="104" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="D7" s="104" t="s">
-        <v>544</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8" spans="2:4" ht="22" x14ac:dyDescent="0.2">
-      <c r="B8" s="120" t="s">
+      <c r="B8" s="118" t="s">
         <v>394</v>
       </c>
       <c r="C8" s="28" t="s">
         <v>398</v>
       </c>
-      <c r="D8" s="120" t="s">
+      <c r="D8" s="118" t="s">
         <v>395</v>
       </c>
     </row>
     <row r="9" spans="2:4" ht="89" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="121"/>
+      <c r="B9" s="119"/>
       <c r="C9" s="104" t="s">
-        <v>542</v>
-      </c>
-      <c r="D9" s="121"/>
+        <v>539</v>
+      </c>
+      <c r="D9" s="119"/>
     </row>
     <row r="10" spans="2:4" ht="22" x14ac:dyDescent="0.2">
-      <c r="B10" s="120" t="s">
+      <c r="B10" s="118" t="s">
         <v>396</v>
       </c>
-      <c r="C10" s="120" t="s">
+      <c r="C10" s="118" t="s">
         <v>395</v>
       </c>
       <c r="D10" s="28" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="11" spans="2:4" ht="89" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="121"/>
-      <c r="C11" s="121"/>
+    <row r="11" spans="2:4" ht="111" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="119"/>
+      <c r="C11" s="119"/>
       <c r="D11" s="104" t="s">
-        <v>545</v>
+        <v>588</v>
       </c>
     </row>
   </sheetData>
@@ -16476,9 +17469,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8750E32-A59B-9548-9A1A-62B4C8E80AF6}">
-  <dimension ref="B2:F22"/>
+  <dimension ref="B2:F32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="22" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="97"/>
@@ -16491,8 +17484,8 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B2" s="118"/>
-      <c r="C2" s="118"/>
+      <c r="B2" s="117"/>
+      <c r="C2" s="117"/>
       <c r="D2" s="103" t="s">
         <v>389</v>
       </c>
@@ -16509,155 +17502,229 @@
       </c>
       <c r="C3" s="115"/>
       <c r="D3" s="98" t="s">
+        <v>468</v>
+      </c>
+      <c r="E3" s="98" t="s">
         <v>469</v>
       </c>
-      <c r="E3" s="98" t="s">
+      <c r="F3" s="99"/>
+    </row>
+    <row r="4" spans="2:6" ht="23" x14ac:dyDescent="0.3">
+      <c r="B4" s="180" t="s">
+        <v>574</v>
+      </c>
+      <c r="C4" s="178" t="s">
+        <v>466</v>
+      </c>
+      <c r="D4" s="177" t="s">
+        <v>479</v>
+      </c>
+      <c r="E4" s="177" t="s">
+        <v>576</v>
+      </c>
+      <c r="F4" s="99"/>
+    </row>
+    <row r="5" spans="2:6" ht="46" x14ac:dyDescent="0.3">
+      <c r="B5" s="181"/>
+      <c r="C5" s="186"/>
+      <c r="D5" s="177"/>
+      <c r="E5" s="177" t="s">
+        <v>577</v>
+      </c>
+      <c r="F5" s="99"/>
+    </row>
+    <row r="6" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B6" s="181"/>
+      <c r="C6" s="186"/>
+      <c r="D6" s="102" t="s">
+        <v>476</v>
+      </c>
+      <c r="E6" s="177"/>
+      <c r="F6" s="99"/>
+    </row>
+    <row r="7" spans="2:6" ht="46" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="181"/>
+      <c r="C7" s="179"/>
+      <c r="D7" s="102" t="s">
+        <v>578</v>
+      </c>
+      <c r="E7" s="177"/>
+      <c r="F7" s="99"/>
+    </row>
+    <row r="8" spans="2:6" ht="69" x14ac:dyDescent="0.3">
+      <c r="B8" s="181"/>
+      <c r="C8" s="99" t="s">
+        <v>467</v>
+      </c>
+      <c r="D8" s="98" t="s">
         <v>470</v>
       </c>
-      <c r="F3" s="99"/>
-    </row>
-    <row r="4" spans="2:6" ht="46" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="117" t="s">
-        <v>466</v>
-      </c>
-      <c r="C4" s="99" t="s">
-        <v>467</v>
-      </c>
-      <c r="D4" s="100" t="s">
+      <c r="E8" s="100"/>
+      <c r="F8" s="99"/>
+    </row>
+    <row r="9" spans="2:6" ht="46" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="181"/>
+      <c r="C9" s="100" t="s">
+        <v>471</v>
+      </c>
+      <c r="D9" s="100"/>
+      <c r="E9" s="177" t="s">
+        <v>472</v>
+      </c>
+      <c r="F9" s="99"/>
+    </row>
+    <row r="10" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B10" s="181"/>
+      <c r="C10" s="99"/>
+      <c r="D10" s="177"/>
+      <c r="E10" s="185" t="s">
+        <v>571</v>
+      </c>
+      <c r="F10" s="102"/>
+    </row>
+    <row r="11" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B11" s="182"/>
+      <c r="C11" s="99" t="s">
+        <v>575</v>
+      </c>
+      <c r="D11" s="185"/>
+      <c r="E11" s="185" t="s">
+        <v>572</v>
+      </c>
+      <c r="F11" s="102"/>
+    </row>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B12" s="183" t="s">
+        <v>573</v>
+      </c>
+      <c r="C12" s="99" t="s">
+        <v>477</v>
+      </c>
+      <c r="D12" s="100"/>
+      <c r="E12" s="100"/>
+      <c r="F12" s="102" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B13" s="184"/>
+      <c r="C13" s="99" t="s">
+        <v>480</v>
+      </c>
+      <c r="D13" s="100"/>
+      <c r="E13" s="100"/>
+      <c r="F13" s="102" t="s">
         <v>481</v>
       </c>
-      <c r="E4" s="100" t="s">
-        <v>482</v>
-      </c>
-      <c r="F4" s="99"/>
-    </row>
-    <row r="5" spans="2:6" ht="69" x14ac:dyDescent="0.3">
-      <c r="B5" s="117"/>
-      <c r="C5" s="99" t="s">
-        <v>468</v>
-      </c>
-      <c r="D5" s="98" t="s">
-        <v>471</v>
-      </c>
-      <c r="E5" s="100"/>
-      <c r="F5" s="99"/>
-    </row>
-    <row r="6" spans="2:6" ht="46" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="117"/>
-      <c r="C6" s="100" t="s">
-        <v>472</v>
-      </c>
-      <c r="D6" s="100"/>
-      <c r="E6" s="100" t="s">
+    </row>
+    <row r="14" spans="2:6" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="184"/>
+      <c r="C14" s="116" t="s">
         <v>473</v>
       </c>
-      <c r="F6" s="99"/>
-    </row>
-    <row r="7" spans="2:6" ht="23" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="119" t="s">
+      <c r="D14" s="100"/>
+      <c r="E14" s="101" t="s">
         <v>474</v>
       </c>
-      <c r="C7" s="116" t="s">
+      <c r="F14" s="99"/>
+    </row>
+    <row r="15" spans="2:6" ht="23" x14ac:dyDescent="0.3">
+      <c r="B15" s="184"/>
+      <c r="C15" s="116"/>
+      <c r="D15" s="100"/>
+      <c r="E15" s="98" t="s">
         <v>475</v>
       </c>
-      <c r="D7" s="100"/>
-      <c r="E7" s="101" t="s">
-        <v>476</v>
-      </c>
-      <c r="F7" s="99"/>
-    </row>
-    <row r="8" spans="2:6" ht="23" x14ac:dyDescent="0.3">
-      <c r="B8" s="119"/>
-      <c r="C8" s="116"/>
-      <c r="D8" s="100"/>
-      <c r="E8" s="98" t="s">
-        <v>477</v>
-      </c>
-      <c r="F8" s="99"/>
-    </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B9" s="119"/>
-      <c r="C9" s="99" t="s">
-        <v>478</v>
-      </c>
-      <c r="D9" s="100"/>
-      <c r="E9" s="100"/>
-      <c r="F9" s="99"/>
-    </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B10" s="119"/>
-      <c r="C10" s="99" t="s">
-        <v>479</v>
-      </c>
-      <c r="D10" s="100"/>
-      <c r="E10" s="100"/>
-      <c r="F10" s="102" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B11" s="119"/>
-      <c r="C11" s="99" t="s">
+      <c r="F15" s="99"/>
+    </row>
+    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="C19" s="97" t="s">
+        <v>462</v>
+      </c>
+      <c r="D19" s="96" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6" ht="23" x14ac:dyDescent="0.3">
+      <c r="D20" s="96" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="D21" s="96" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="D22" s="96" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6" ht="23" x14ac:dyDescent="0.3">
+      <c r="B23" s="97" t="s">
+        <v>583</v>
+      </c>
+      <c r="C23" s="97" t="s">
+        <v>584</v>
+      </c>
+      <c r="D23" s="96" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6" ht="23" x14ac:dyDescent="0.3">
+      <c r="C24" s="97" t="s">
+        <v>586</v>
+      </c>
+      <c r="D24" s="96" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="C29" s="99"/>
+      <c r="D29" s="106" t="s">
         <v>483</v>
       </c>
-      <c r="D11" s="100"/>
-      <c r="E11" s="100"/>
-      <c r="F11" s="102" t="s">
+      <c r="E29" s="100"/>
+      <c r="F29" s="99"/>
+    </row>
+    <row r="30" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="C30" s="99"/>
+      <c r="D30" s="100"/>
+      <c r="E30" s="106" t="s">
         <v>484</v>
       </c>
-    </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B12" s="119"/>
-      <c r="C12" s="99"/>
-      <c r="D12" s="106" t="s">
+      <c r="F30" s="99"/>
+    </row>
+    <row r="31" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="C31" s="99"/>
+      <c r="D31" s="100"/>
+      <c r="E31" s="100"/>
+      <c r="F31" s="106" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="C32" s="99"/>
+      <c r="D32" s="106" t="s">
         <v>486</v>
       </c>
-      <c r="E12" s="100"/>
-      <c r="F12" s="99"/>
-    </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B13" s="119"/>
-      <c r="C13" s="99"/>
-      <c r="D13" s="100"/>
-      <c r="E13" s="106" t="s">
-        <v>487</v>
-      </c>
-      <c r="F13" s="99"/>
-    </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B14" s="119"/>
-      <c r="C14" s="99"/>
-      <c r="D14" s="100"/>
-      <c r="E14" s="100"/>
-      <c r="F14" s="106" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B15" s="119"/>
-      <c r="C15" s="99"/>
-      <c r="D15" s="106" t="s">
-        <v>489</v>
-      </c>
-      <c r="E15" s="100"/>
-      <c r="F15" s="99"/>
-    </row>
-    <row r="22" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D22"/>
+      <c r="E32" s="100"/>
+      <c r="F32" s="99"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
+    <mergeCell ref="C4:C7"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="B4:B11"/>
+    <mergeCell ref="B12:B15"/>
     <mergeCell ref="B3:C3"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="B4:B6"/>
     <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B7:B15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FD1D18A-C464-364C-95F7-F927C76322D3}">
   <dimension ref="B2:AI89"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="22" x14ac:dyDescent="0.3"/>
@@ -16683,40 +17750,40 @@
       <c r="B2" s="30" t="s">
         <v>388</v>
       </c>
-      <c r="C2" s="123" t="s">
+      <c r="C2" s="121" t="s">
         <v>389</v>
       </c>
-      <c r="D2" s="123"/>
-      <c r="E2" s="123"/>
-      <c r="F2" s="123"/>
-      <c r="G2" s="123"/>
-      <c r="H2" s="123"/>
-      <c r="I2" s="123"/>
-      <c r="J2" s="123"/>
-      <c r="K2" s="123"/>
-      <c r="L2" s="123"/>
-      <c r="M2" s="124" t="s">
+      <c r="D2" s="121"/>
+      <c r="E2" s="121"/>
+      <c r="F2" s="121"/>
+      <c r="G2" s="121"/>
+      <c r="H2" s="121"/>
+      <c r="I2" s="121"/>
+      <c r="J2" s="121"/>
+      <c r="K2" s="121"/>
+      <c r="L2" s="121"/>
+      <c r="M2" s="122" t="s">
         <v>390</v>
       </c>
-      <c r="N2" s="124"/>
-      <c r="O2" s="124"/>
-      <c r="P2" s="124"/>
-      <c r="Q2" s="124"/>
-      <c r="R2" s="124"/>
-      <c r="S2" s="137" t="s">
+      <c r="N2" s="122"/>
+      <c r="O2" s="122"/>
+      <c r="P2" s="122"/>
+      <c r="Q2" s="122"/>
+      <c r="R2" s="122"/>
+      <c r="S2" s="135" t="s">
         <v>461</v>
       </c>
-      <c r="T2" s="137"/>
-      <c r="U2" s="137"/>
-      <c r="V2" s="137"/>
-      <c r="W2" s="137"/>
-      <c r="X2" s="137"/>
-      <c r="Y2" s="137"/>
-      <c r="Z2" s="137"/>
-      <c r="AA2" s="137"/>
+      <c r="T2" s="135"/>
+      <c r="U2" s="135"/>
+      <c r="V2" s="135"/>
+      <c r="W2" s="135"/>
+      <c r="X2" s="135"/>
+      <c r="Y2" s="135"/>
+      <c r="Z2" s="135"/>
+      <c r="AA2" s="135"/>
     </row>
     <row r="3" spans="2:27" ht="21" x14ac:dyDescent="0.2">
-      <c r="B3" s="133" t="s">
+      <c r="B3" s="131" t="s">
         <v>462</v>
       </c>
       <c r="C3" s="37"/>
@@ -16737,7 +17804,7 @@
       <c r="R3" s="72"/>
     </row>
     <row r="4" spans="2:27" ht="21" x14ac:dyDescent="0.2">
-      <c r="B4" s="134"/>
+      <c r="B4" s="132"/>
       <c r="C4" s="37"/>
       <c r="D4" s="38"/>
       <c r="E4" s="38"/>
@@ -16760,7 +17827,7 @@
       </c>
     </row>
     <row r="5" spans="2:27" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="134"/>
+      <c r="B5" s="132"/>
       <c r="C5" s="37"/>
       <c r="D5" s="38"/>
       <c r="E5" s="38"/>
@@ -16802,7 +17869,7 @@
       </c>
     </row>
     <row r="6" spans="2:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="134"/>
+      <c r="B6" s="132"/>
       <c r="D6" s="38"/>
       <c r="E6" s="38"/>
       <c r="F6" s="38"/>
@@ -16811,22 +17878,22 @@
       <c r="J6" s="43" t="s">
         <v>388</v>
       </c>
-      <c r="K6" s="125" t="s">
+      <c r="K6" s="123" t="s">
         <v>399</v>
       </c>
-      <c r="L6" s="125"/>
-      <c r="M6" s="126" t="s">
+      <c r="L6" s="123"/>
+      <c r="M6" s="124" t="s">
         <v>400</v>
       </c>
-      <c r="N6" s="126"/>
-      <c r="T6" s="140" t="s">
+      <c r="N6" s="124"/>
+      <c r="T6" s="138" t="s">
         <v>345</v>
       </c>
-      <c r="U6" s="141" t="s">
+      <c r="U6" s="139" t="s">
         <v>458</v>
       </c>
-      <c r="V6" s="141"/>
-      <c r="W6" s="141"/>
+      <c r="V6" s="139"/>
+      <c r="W6" s="139"/>
       <c r="X6" s="86" t="s">
         <v>459</v>
       </c>
@@ -16835,13 +17902,13 @@
       </c>
     </row>
     <row r="7" spans="2:27" ht="16" x14ac:dyDescent="0.2">
-      <c r="B7" s="134"/>
+      <c r="B7" s="132"/>
       <c r="D7" s="38"/>
       <c r="E7" s="38"/>
       <c r="F7" s="38"/>
       <c r="G7" s="38"/>
       <c r="H7" s="38"/>
-      <c r="J7" s="122" t="s">
+      <c r="J7" s="120" t="s">
         <v>334</v>
       </c>
       <c r="K7" s="44" t="s">
@@ -16856,7 +17923,7 @@
       <c r="N7" s="76" t="s">
         <v>387</v>
       </c>
-      <c r="T7" s="140"/>
+      <c r="T7" s="138"/>
       <c r="U7" s="87" t="s">
         <v>449</v>
       </c>
@@ -16870,13 +17937,13 @@
       <c r="Y7" s="88"/>
     </row>
     <row r="8" spans="2:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="134"/>
+      <c r="B8" s="132"/>
       <c r="D8" s="38"/>
       <c r="E8" s="38"/>
       <c r="F8" s="38"/>
       <c r="G8" s="38"/>
       <c r="H8" s="38"/>
-      <c r="J8" s="122"/>
+      <c r="J8" s="120"/>
       <c r="K8" s="44" t="s">
         <v>16</v>
       </c>
@@ -16889,7 +17956,7 @@
       <c r="N8" s="76" t="s">
         <v>88</v>
       </c>
-      <c r="T8" s="142" t="s">
+      <c r="T8" s="140" t="s">
         <v>403</v>
       </c>
       <c r="U8" s="86">
@@ -16909,13 +17976,13 @@
       </c>
     </row>
     <row r="9" spans="2:27" ht="16" x14ac:dyDescent="0.2">
-      <c r="B9" s="134"/>
+      <c r="B9" s="132"/>
       <c r="D9" s="38"/>
       <c r="E9" s="38"/>
       <c r="F9" s="38"/>
       <c r="G9" s="38"/>
       <c r="H9" s="38"/>
-      <c r="J9" s="122" t="s">
+      <c r="J9" s="120" t="s">
         <v>401</v>
       </c>
       <c r="K9" s="44"/>
@@ -16926,7 +17993,7 @@
       <c r="N9" s="76" t="s">
         <v>384</v>
       </c>
-      <c r="T9" s="143"/>
+      <c r="T9" s="141"/>
       <c r="U9" s="90" t="s">
         <v>453</v>
       </c>
@@ -16944,13 +18011,13 @@
       </c>
     </row>
     <row r="10" spans="2:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="134"/>
+      <c r="B10" s="132"/>
       <c r="D10" s="38"/>
       <c r="E10" s="38"/>
       <c r="F10" s="38"/>
       <c r="G10" s="38"/>
       <c r="H10" s="38"/>
-      <c r="J10" s="122"/>
+      <c r="J10" s="120"/>
       <c r="K10" s="44"/>
       <c r="L10" s="44" t="s">
         <v>26</v>
@@ -16979,13 +18046,13 @@
       </c>
     </row>
     <row r="11" spans="2:27" ht="16" x14ac:dyDescent="0.2">
-      <c r="B11" s="134"/>
+      <c r="B11" s="132"/>
       <c r="D11" s="38"/>
       <c r="E11" s="38"/>
       <c r="F11" s="38"/>
       <c r="G11" s="38"/>
       <c r="H11" s="38"/>
-      <c r="J11" s="122" t="s">
+      <c r="J11" s="120" t="s">
         <v>402</v>
       </c>
       <c r="K11" s="44"/>
@@ -17016,13 +18083,13 @@
       </c>
     </row>
     <row r="12" spans="2:27" ht="16" x14ac:dyDescent="0.2">
-      <c r="B12" s="134"/>
+      <c r="B12" s="132"/>
       <c r="D12" s="38"/>
       <c r="E12" s="38"/>
       <c r="F12" s="38"/>
       <c r="G12" s="38"/>
       <c r="H12" s="38"/>
-      <c r="J12" s="127"/>
+      <c r="J12" s="125"/>
       <c r="K12" s="45"/>
       <c r="L12" s="45" t="s">
         <v>85</v>
@@ -17051,7 +18118,7 @@
       </c>
     </row>
     <row r="13" spans="2:27" ht="16" x14ac:dyDescent="0.2">
-      <c r="B13" s="134"/>
+      <c r="B13" s="132"/>
       <c r="D13" s="38"/>
       <c r="E13" s="38"/>
       <c r="F13" s="38"/>
@@ -17074,7 +18141,7 @@
       </c>
     </row>
     <row r="14" spans="2:27" ht="16" x14ac:dyDescent="0.2">
-      <c r="B14" s="134"/>
+      <c r="B14" s="132"/>
       <c r="D14" s="38"/>
       <c r="E14" s="38"/>
       <c r="F14" s="38"/>
@@ -17097,7 +18164,7 @@
       </c>
     </row>
     <row r="15" spans="2:27" ht="16" x14ac:dyDescent="0.2">
-      <c r="B15" s="134"/>
+      <c r="B15" s="132"/>
       <c r="D15" s="38"/>
       <c r="E15" s="38"/>
       <c r="F15" s="38"/>
@@ -17120,7 +18187,7 @@
       </c>
     </row>
     <row r="16" spans="2:27" ht="16" x14ac:dyDescent="0.2">
-      <c r="B16" s="134"/>
+      <c r="B16" s="132"/>
       <c r="J16" s="47" t="s">
         <v>339</v>
       </c>
@@ -17138,36 +18205,36 @@
       </c>
     </row>
     <row r="17" spans="2:35" ht="16" x14ac:dyDescent="0.2">
-      <c r="B17" s="134"/>
+      <c r="B17" s="132"/>
     </row>
     <row r="18" spans="2:35" ht="16" x14ac:dyDescent="0.2">
-      <c r="B18" s="134"/>
+      <c r="B18" s="132"/>
     </row>
     <row r="19" spans="2:35" ht="16" x14ac:dyDescent="0.2">
-      <c r="B19" s="134"/>
+      <c r="B19" s="132"/>
     </row>
     <row r="20" spans="2:35" ht="16" x14ac:dyDescent="0.2">
-      <c r="B20" s="134"/>
+      <c r="B20" s="132"/>
     </row>
     <row r="21" spans="2:35" ht="16" x14ac:dyDescent="0.2">
-      <c r="B21" s="134"/>
+      <c r="B21" s="132"/>
     </row>
     <row r="22" spans="2:35" ht="16" x14ac:dyDescent="0.2">
-      <c r="B22" s="134"/>
+      <c r="B22" s="132"/>
     </row>
     <row r="23" spans="2:35" ht="16" x14ac:dyDescent="0.2">
-      <c r="B23" s="134"/>
+      <c r="B23" s="132"/>
     </row>
     <row r="24" spans="2:35" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="135" t="s">
+      <c r="B24" s="133" t="s">
         <v>464</v>
       </c>
     </row>
     <row r="25" spans="2:35" ht="16" x14ac:dyDescent="0.2">
-      <c r="B25" s="135"/>
+      <c r="B25" s="133"/>
     </row>
     <row r="26" spans="2:35" ht="16" x14ac:dyDescent="0.2">
-      <c r="B26" s="135"/>
+      <c r="B26" s="133"/>
       <c r="D26" s="41"/>
       <c r="E26" s="42" t="s">
         <v>340</v>
@@ -17175,7 +18242,7 @@
       <c r="F26" s="42" t="s">
         <v>341</v>
       </c>
-      <c r="N26" s="170"/>
+      <c r="N26" s="168"/>
       <c r="O26" s="74" t="s">
         <v>340</v>
       </c>
@@ -17184,44 +18251,44 @@
       </c>
     </row>
     <row r="27" spans="2:35" ht="16" x14ac:dyDescent="0.2">
-      <c r="B27" s="135"/>
-      <c r="E27" s="169" t="s">
-        <v>555</v>
-      </c>
-      <c r="F27" s="169" t="s">
-        <v>556</v>
-      </c>
-      <c r="O27" s="171" t="s">
-        <v>565</v>
-      </c>
-      <c r="P27" s="171" t="s">
-        <v>566</v>
+      <c r="B27" s="133"/>
+      <c r="E27" s="167" t="s">
+        <v>550</v>
+      </c>
+      <c r="F27" s="167" t="s">
+        <v>551</v>
+      </c>
+      <c r="O27" s="169" t="s">
+        <v>560</v>
+      </c>
+      <c r="P27" s="169" t="s">
+        <v>561</v>
       </c>
     </row>
     <row r="28" spans="2:35" s="26" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B28" s="135"/>
+      <c r="B28" s="133"/>
       <c r="C28" s="39"/>
       <c r="D28" s="43" t="s">
         <v>388</v>
       </c>
-      <c r="E28" s="125" t="s">
+      <c r="E28" s="123" t="s">
         <v>399</v>
       </c>
-      <c r="F28" s="125"/>
-      <c r="G28" s="177"/>
-      <c r="H28" s="177"/>
-      <c r="I28" s="177"/>
+      <c r="F28" s="123"/>
+      <c r="G28" s="175"/>
+      <c r="H28" s="175"/>
+      <c r="I28" s="175"/>
       <c r="J28" s="39"/>
       <c r="K28" s="39"/>
       <c r="L28" s="39"/>
       <c r="M28" s="75"/>
-      <c r="N28" s="172" t="s">
+      <c r="N28" s="170" t="s">
         <v>388</v>
       </c>
-      <c r="O28" s="126" t="s">
+      <c r="O28" s="124" t="s">
         <v>400</v>
       </c>
-      <c r="P28" s="126"/>
+      <c r="P28" s="124"/>
       <c r="Q28" s="75"/>
       <c r="R28" s="75"/>
       <c r="S28" s="33"/>
@@ -17243,165 +18310,165 @@
       <c r="AI28" s="31"/>
     </row>
     <row r="29" spans="2:35" ht="16" x14ac:dyDescent="0.2">
-      <c r="B29" s="135"/>
-      <c r="D29" s="122" t="s">
+      <c r="B29" s="133"/>
+      <c r="D29" s="120" t="s">
         <v>334</v>
       </c>
       <c r="E29" s="44" t="s">
-        <v>547</v>
+        <v>542</v>
       </c>
       <c r="F29" s="44" t="s">
-        <v>549</v>
-      </c>
-      <c r="G29" s="177" t="s">
-        <v>567</v>
-      </c>
-      <c r="H29" s="177"/>
-      <c r="I29" s="177"/>
-      <c r="N29" s="173" t="s">
+        <v>544</v>
+      </c>
+      <c r="G29" s="175" t="s">
+        <v>562</v>
+      </c>
+      <c r="H29" s="175"/>
+      <c r="I29" s="175"/>
+      <c r="N29" s="171" t="s">
         <v>334</v>
       </c>
       <c r="O29" s="76" t="s">
-        <v>546</v>
+        <v>541</v>
       </c>
       <c r="P29" s="76" t="s">
         <v>55</v>
       </c>
-      <c r="Q29" s="178" t="s">
-        <v>571</v>
-      </c>
-      <c r="R29" s="178"/>
+      <c r="Q29" s="176" t="s">
+        <v>566</v>
+      </c>
+      <c r="R29" s="176"/>
     </row>
     <row r="30" spans="2:35" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B30" s="135"/>
-      <c r="D30" s="122"/>
+      <c r="B30" s="133"/>
+      <c r="D30" s="120"/>
       <c r="E30" s="44" t="s">
         <v>94</v>
       </c>
       <c r="F30" s="44" t="s">
-        <v>550</v>
-      </c>
-      <c r="G30" s="177" t="s">
-        <v>568</v>
-      </c>
-      <c r="H30" s="177"/>
-      <c r="I30" s="177"/>
-      <c r="N30" s="173"/>
+        <v>545</v>
+      </c>
+      <c r="G30" s="175" t="s">
+        <v>563</v>
+      </c>
+      <c r="H30" s="175"/>
+      <c r="I30" s="175"/>
+      <c r="N30" s="171"/>
       <c r="O30" s="76" t="s">
         <v>143</v>
       </c>
       <c r="P30" s="76" t="s">
         <v>24</v>
       </c>
-      <c r="Q30" s="178"/>
-      <c r="R30" s="178"/>
+      <c r="Q30" s="176"/>
+      <c r="R30" s="176"/>
     </row>
     <row r="31" spans="2:35" ht="16" x14ac:dyDescent="0.2">
-      <c r="B31" s="135"/>
-      <c r="D31" s="122" t="s">
+      <c r="B31" s="133"/>
+      <c r="D31" s="120" t="s">
         <v>401</v>
       </c>
       <c r="E31" s="44" t="s">
-        <v>548</v>
+        <v>543</v>
       </c>
       <c r="F31" s="44" t="s">
         <v>55</v>
       </c>
-      <c r="G31" s="177" t="s">
-        <v>569</v>
-      </c>
-      <c r="H31" s="177"/>
-      <c r="I31" s="177"/>
-      <c r="N31" s="173" t="s">
+      <c r="G31" s="175" t="s">
+        <v>564</v>
+      </c>
+      <c r="H31" s="175"/>
+      <c r="I31" s="175"/>
+      <c r="N31" s="171" t="s">
         <v>401</v>
       </c>
       <c r="O31" s="76" t="s">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="P31" s="76" t="s">
-        <v>560</v>
-      </c>
-      <c r="Q31" s="178" t="s">
-        <v>573</v>
-      </c>
-      <c r="R31" s="178"/>
+        <v>555</v>
+      </c>
+      <c r="Q31" s="176" t="s">
+        <v>568</v>
+      </c>
+      <c r="R31" s="176"/>
     </row>
     <row r="32" spans="2:35" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B32" s="135"/>
-      <c r="D32" s="122"/>
+      <c r="B32" s="133"/>
+      <c r="D32" s="120"/>
       <c r="E32" s="44" t="s">
         <v>57</v>
       </c>
       <c r="F32" s="44" t="s">
-        <v>551</v>
-      </c>
-      <c r="G32" s="177" t="s">
-        <v>570</v>
-      </c>
-      <c r="H32" s="177"/>
-      <c r="I32" s="177"/>
-      <c r="N32" s="173"/>
+        <v>546</v>
+      </c>
+      <c r="G32" s="175" t="s">
+        <v>565</v>
+      </c>
+      <c r="H32" s="175"/>
+      <c r="I32" s="175"/>
+      <c r="N32" s="171"/>
       <c r="O32" s="76" t="s">
         <v>456</v>
       </c>
       <c r="P32" s="76" t="s">
         <v>26</v>
       </c>
-      <c r="Q32" s="178"/>
-      <c r="R32" s="178"/>
+      <c r="Q32" s="176"/>
+      <c r="R32" s="176"/>
     </row>
     <row r="33" spans="2:18" ht="16" x14ac:dyDescent="0.2">
-      <c r="B33" s="135"/>
-      <c r="D33" s="122" t="s">
+      <c r="B33" s="133"/>
+      <c r="D33" s="120" t="s">
         <v>402</v>
       </c>
       <c r="E33" s="44" t="s">
         <v>278</v>
       </c>
       <c r="F33" s="44" t="s">
-        <v>552</v>
-      </c>
-      <c r="G33" s="177"/>
-      <c r="H33" s="177"/>
-      <c r="I33" s="177"/>
-      <c r="N33" s="173" t="s">
+        <v>547</v>
+      </c>
+      <c r="G33" s="175"/>
+      <c r="H33" s="175"/>
+      <c r="I33" s="175"/>
+      <c r="N33" s="171" t="s">
         <v>402</v>
       </c>
       <c r="O33" s="76" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="P33" s="76" t="s">
-        <v>562</v>
-      </c>
-      <c r="Q33" s="178" t="s">
-        <v>572</v>
-      </c>
-      <c r="R33" s="178"/>
+        <v>557</v>
+      </c>
+      <c r="Q33" s="176" t="s">
+        <v>567</v>
+      </c>
+      <c r="R33" s="176"/>
     </row>
     <row r="34" spans="2:18" ht="16" x14ac:dyDescent="0.2">
-      <c r="B34" s="135"/>
-      <c r="D34" s="127"/>
+      <c r="B34" s="133"/>
+      <c r="D34" s="125"/>
       <c r="E34" s="45" t="s">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="F34" s="45" t="s">
-        <v>554</v>
-      </c>
-      <c r="G34" s="177"/>
-      <c r="H34" s="177"/>
-      <c r="I34" s="177"/>
-      <c r="N34" s="174"/>
+        <v>549</v>
+      </c>
+      <c r="G34" s="175"/>
+      <c r="H34" s="175"/>
+      <c r="I34" s="175"/>
+      <c r="N34" s="172"/>
       <c r="O34" s="77" t="s">
         <v>85</v>
       </c>
       <c r="P34" s="77" t="s">
         <v>85</v>
       </c>
-      <c r="Q34" s="178"/>
-      <c r="R34" s="178"/>
+      <c r="Q34" s="176"/>
+      <c r="R34" s="176"/>
     </row>
     <row r="35" spans="2:18" ht="16" x14ac:dyDescent="0.2">
-      <c r="B35" s="135"/>
+      <c r="B35" s="133"/>
       <c r="D35" s="46" t="s">
         <v>335</v>
       </c>
@@ -17411,10 +18478,10 @@
       <c r="F35" s="44" t="s">
         <v>336</v>
       </c>
-      <c r="G35" s="177"/>
-      <c r="H35" s="177"/>
-      <c r="I35" s="177"/>
-      <c r="N35" s="175" t="s">
+      <c r="G35" s="175"/>
+      <c r="H35" s="175"/>
+      <c r="I35" s="175"/>
+      <c r="N35" s="173" t="s">
         <v>335</v>
       </c>
       <c r="O35" s="76" t="s">
@@ -17423,11 +18490,13 @@
       <c r="P35" s="76" t="s">
         <v>336</v>
       </c>
-      <c r="Q35" s="178"/>
-      <c r="R35" s="178"/>
-    </row>
-    <row r="36" spans="2:18" ht="16" x14ac:dyDescent="0.2">
-      <c r="B36" s="135"/>
+      <c r="Q35" s="176" t="s">
+        <v>569</v>
+      </c>
+      <c r="R35" s="176"/>
+    </row>
+    <row r="36" spans="2:18" ht="17" x14ac:dyDescent="0.2">
+      <c r="B36" s="133"/>
       <c r="D36" s="46" t="s">
         <v>337</v>
       </c>
@@ -17437,10 +18506,10 @@
       <c r="F36" s="44" t="s">
         <v>336</v>
       </c>
-      <c r="G36" s="177"/>
-      <c r="H36" s="177"/>
-      <c r="I36" s="177"/>
-      <c r="N36" s="175" t="s">
+      <c r="G36" s="175"/>
+      <c r="H36" s="175"/>
+      <c r="I36" s="175"/>
+      <c r="N36" s="173" t="s">
         <v>337</v>
       </c>
       <c r="O36" s="76" t="s">
@@ -17449,11 +18518,13 @@
       <c r="P36" s="76" t="s">
         <v>336</v>
       </c>
-      <c r="Q36" s="178"/>
-      <c r="R36" s="178"/>
+      <c r="Q36" s="75" t="s">
+        <v>566</v>
+      </c>
+      <c r="R36" s="176"/>
     </row>
     <row r="37" spans="2:18" ht="16" x14ac:dyDescent="0.2">
-      <c r="B37" s="135"/>
+      <c r="B37" s="133"/>
       <c r="D37" s="46" t="s">
         <v>338</v>
       </c>
@@ -17463,10 +18534,10 @@
       <c r="F37" s="44" t="s">
         <v>336</v>
       </c>
-      <c r="G37" s="177"/>
-      <c r="H37" s="177"/>
-      <c r="I37" s="177"/>
-      <c r="N37" s="175" t="s">
+      <c r="G37" s="175"/>
+      <c r="H37" s="175"/>
+      <c r="I37" s="175"/>
+      <c r="N37" s="173" t="s">
         <v>338</v>
       </c>
       <c r="O37" s="76" t="s">
@@ -17475,60 +18546,62 @@
       <c r="P37" s="76" t="s">
         <v>336</v>
       </c>
-      <c r="Q37" s="178"/>
-      <c r="R37" s="178"/>
+      <c r="Q37" s="176" t="s">
+        <v>570</v>
+      </c>
+      <c r="R37" s="176"/>
     </row>
     <row r="38" spans="2:18" ht="16" x14ac:dyDescent="0.2">
-      <c r="B38" s="135"/>
+      <c r="B38" s="133"/>
       <c r="D38" s="47" t="s">
         <v>339</v>
       </c>
       <c r="E38" s="45" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="F38" s="45" t="s">
+        <v>553</v>
+      </c>
+      <c r="N38" s="174" t="s">
+        <v>339</v>
+      </c>
+      <c r="O38" s="77" t="s">
         <v>558</v>
       </c>
-      <c r="N38" s="176" t="s">
-        <v>339</v>
-      </c>
-      <c r="O38" s="77" t="s">
-        <v>563</v>
-      </c>
       <c r="P38" s="77" t="s">
-        <v>564</v>
+        <v>559</v>
       </c>
     </row>
     <row r="39" spans="2:18" ht="16" x14ac:dyDescent="0.2">
-      <c r="B39" s="135"/>
+      <c r="B39" s="133"/>
     </row>
     <row r="40" spans="2:18" ht="16" x14ac:dyDescent="0.2">
-      <c r="B40" s="135"/>
+      <c r="B40" s="133"/>
     </row>
     <row r="41" spans="2:18" ht="16" x14ac:dyDescent="0.2">
-      <c r="B41" s="135"/>
+      <c r="B41" s="133"/>
     </row>
     <row r="42" spans="2:18" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B42" s="135" t="s">
+      <c r="B42" s="133" t="s">
         <v>463</v>
       </c>
       <c r="D42" s="40" t="s">
         <v>420</v>
       </c>
-      <c r="M42" s="168"/>
-      <c r="N42" s="168"/>
-      <c r="O42" s="168"/>
-      <c r="P42" s="168"/>
-      <c r="Q42" s="168"/>
-      <c r="R42" s="168"/>
+      <c r="M42" s="166"/>
+      <c r="N42" s="166"/>
+      <c r="O42" s="166"/>
+      <c r="P42" s="166"/>
+      <c r="Q42" s="166"/>
+      <c r="R42" s="166"/>
     </row>
     <row r="43" spans="2:18" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B43" s="135"/>
-      <c r="D43" s="128"/>
-      <c r="E43" s="128" t="s">
+      <c r="B43" s="133"/>
+      <c r="D43" s="126"/>
+      <c r="E43" s="126" t="s">
         <v>404</v>
       </c>
-      <c r="F43" s="128"/>
+      <c r="F43" s="126"/>
       <c r="G43" s="48" t="s">
         <v>405</v>
       </c>
@@ -17538,16 +18611,16 @@
       <c r="I43" s="48" t="s">
         <v>407</v>
       </c>
-      <c r="M43" s="168"/>
-      <c r="N43" s="168"/>
-      <c r="O43" s="168"/>
-      <c r="P43" s="168"/>
-      <c r="Q43" s="168"/>
-      <c r="R43" s="168"/>
+      <c r="M43" s="166"/>
+      <c r="N43" s="166"/>
+      <c r="O43" s="166"/>
+      <c r="P43" s="166"/>
+      <c r="Q43" s="166"/>
+      <c r="R43" s="166"/>
     </row>
     <row r="44" spans="2:18" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B44" s="135"/>
-      <c r="D44" s="129"/>
+      <c r="B44" s="133"/>
+      <c r="D44" s="127"/>
       <c r="E44" s="50" t="s">
         <v>340</v>
       </c>
@@ -17563,35 +18636,35 @@
       <c r="I44" s="51" t="s">
         <v>419</v>
       </c>
-      <c r="M44" s="168"/>
-      <c r="N44" s="168"/>
-      <c r="O44" s="168"/>
-      <c r="P44" s="168"/>
-      <c r="Q44" s="168"/>
-      <c r="R44" s="168"/>
+      <c r="M44" s="166"/>
+      <c r="N44" s="166"/>
+      <c r="O44" s="166"/>
+      <c r="P44" s="166"/>
+      <c r="Q44" s="166"/>
+      <c r="R44" s="166"/>
     </row>
     <row r="45" spans="2:18" ht="26" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B45" s="135"/>
-      <c r="D45" s="129"/>
-      <c r="E45" s="130" t="s">
+      <c r="B45" s="133"/>
+      <c r="D45" s="127"/>
+      <c r="E45" s="128" t="s">
         <v>408</v>
       </c>
-      <c r="F45" s="130"/>
-      <c r="G45" s="130" t="s">
+      <c r="F45" s="128"/>
+      <c r="G45" s="128" t="s">
         <v>409</v>
       </c>
-      <c r="H45" s="130"/>
-      <c r="I45" s="130"/>
-      <c r="M45" s="168"/>
-      <c r="N45" s="168"/>
-      <c r="O45" s="168"/>
-      <c r="P45" s="168"/>
-      <c r="Q45" s="168"/>
-      <c r="R45" s="168"/>
+      <c r="H45" s="128"/>
+      <c r="I45" s="128"/>
+      <c r="M45" s="166"/>
+      <c r="N45" s="166"/>
+      <c r="O45" s="166"/>
+      <c r="P45" s="166"/>
+      <c r="Q45" s="166"/>
+      <c r="R45" s="166"/>
     </row>
     <row r="46" spans="2:18" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B46" s="135"/>
-      <c r="D46" s="131" t="s">
+      <c r="B46" s="133"/>
+      <c r="D46" s="129" t="s">
         <v>403</v>
       </c>
       <c r="E46" s="49" t="s">
@@ -17609,16 +18682,16 @@
       <c r="I46" s="49" t="s">
         <v>411</v>
       </c>
-      <c r="M46" s="168"/>
-      <c r="N46" s="168"/>
-      <c r="O46" s="168"/>
-      <c r="P46" s="168"/>
-      <c r="Q46" s="168"/>
-      <c r="R46" s="168"/>
+      <c r="M46" s="166"/>
+      <c r="N46" s="166"/>
+      <c r="O46" s="166"/>
+      <c r="P46" s="166"/>
+      <c r="Q46" s="166"/>
+      <c r="R46" s="166"/>
     </row>
     <row r="47" spans="2:18" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B47" s="135"/>
-      <c r="D47" s="131"/>
+      <c r="B47" s="133"/>
+      <c r="D47" s="129"/>
       <c r="E47" s="44" t="s">
         <v>16</v>
       </c>
@@ -17634,15 +18707,15 @@
       <c r="I47" s="44" t="s">
         <v>457</v>
       </c>
-      <c r="M47" s="168"/>
-      <c r="N47" s="168"/>
-      <c r="O47" s="168"/>
-      <c r="P47" s="168"/>
-      <c r="Q47" s="168"/>
-      <c r="R47" s="168"/>
+      <c r="M47" s="166"/>
+      <c r="N47" s="166"/>
+      <c r="O47" s="166"/>
+      <c r="P47" s="166"/>
+      <c r="Q47" s="166"/>
+      <c r="R47" s="166"/>
     </row>
     <row r="48" spans="2:18" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B48" s="135"/>
+      <c r="B48" s="133"/>
       <c r="D48" s="53" t="s">
         <v>412</v>
       </c>
@@ -17661,15 +18734,15 @@
       <c r="I48" s="50" t="s">
         <v>336</v>
       </c>
-      <c r="M48" s="168"/>
-      <c r="N48" s="168"/>
-      <c r="O48" s="168"/>
-      <c r="P48" s="168"/>
-      <c r="Q48" s="168"/>
-      <c r="R48" s="168"/>
+      <c r="M48" s="166"/>
+      <c r="N48" s="166"/>
+      <c r="O48" s="166"/>
+      <c r="P48" s="166"/>
+      <c r="Q48" s="166"/>
+      <c r="R48" s="166"/>
     </row>
     <row r="49" spans="2:18" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="135"/>
+      <c r="B49" s="133"/>
       <c r="D49" s="53" t="s">
         <v>338</v>
       </c>
@@ -17688,15 +18761,15 @@
       <c r="I49" s="50" t="s">
         <v>336</v>
       </c>
-      <c r="M49" s="168"/>
-      <c r="N49" s="168"/>
-      <c r="O49" s="168"/>
-      <c r="P49" s="168"/>
-      <c r="Q49" s="168"/>
-      <c r="R49" s="168"/>
+      <c r="M49" s="166"/>
+      <c r="N49" s="166"/>
+      <c r="O49" s="166"/>
+      <c r="P49" s="166"/>
+      <c r="Q49" s="166"/>
+      <c r="R49" s="166"/>
     </row>
     <row r="50" spans="2:18" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B50" s="135"/>
+      <c r="B50" s="133"/>
       <c r="D50" s="54" t="s">
         <v>413</v>
       </c>
@@ -17707,15 +18780,15 @@
       <c r="G50" s="55"/>
       <c r="H50" s="55"/>
       <c r="I50" s="55"/>
-      <c r="M50" s="168"/>
-      <c r="N50" s="168"/>
-      <c r="O50" s="168"/>
-      <c r="P50" s="168"/>
-      <c r="Q50" s="168"/>
-      <c r="R50" s="168"/>
+      <c r="M50" s="166"/>
+      <c r="N50" s="166"/>
+      <c r="O50" s="166"/>
+      <c r="P50" s="166"/>
+      <c r="Q50" s="166"/>
+      <c r="R50" s="166"/>
     </row>
     <row r="51" spans="2:18" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B51" s="135"/>
+      <c r="B51" s="133"/>
       <c r="D51" s="57" t="s">
         <v>339</v>
       </c>
@@ -17734,15 +18807,15 @@
       <c r="I51" s="58">
         <v>3613</v>
       </c>
-      <c r="M51" s="168"/>
-      <c r="N51" s="168"/>
-      <c r="O51" s="168"/>
-      <c r="P51" s="168"/>
-      <c r="Q51" s="168"/>
-      <c r="R51" s="168"/>
+      <c r="M51" s="166"/>
+      <c r="N51" s="166"/>
+      <c r="O51" s="166"/>
+      <c r="P51" s="166"/>
+      <c r="Q51" s="166"/>
+      <c r="R51" s="166"/>
     </row>
     <row r="52" spans="2:18" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B52" s="135"/>
+      <c r="B52" s="133"/>
       <c r="D52" s="57" t="s">
         <v>414</v>
       </c>
@@ -17757,15 +18830,15 @@
       <c r="I52" s="49">
         <v>10117.514999999999</v>
       </c>
-      <c r="M52" s="168"/>
-      <c r="N52" s="168"/>
-      <c r="O52" s="168"/>
-      <c r="P52" s="168"/>
-      <c r="Q52" s="168"/>
-      <c r="R52" s="168"/>
+      <c r="M52" s="166"/>
+      <c r="N52" s="166"/>
+      <c r="O52" s="166"/>
+      <c r="P52" s="166"/>
+      <c r="Q52" s="166"/>
+      <c r="R52" s="166"/>
     </row>
     <row r="53" spans="2:18" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B53" s="135"/>
+      <c r="B53" s="133"/>
       <c r="D53" s="57" t="s">
         <v>415</v>
       </c>
@@ -17776,15 +18849,15 @@
       <c r="G53" s="59"/>
       <c r="H53" s="59"/>
       <c r="I53" s="59"/>
-      <c r="M53" s="168"/>
-      <c r="N53" s="168"/>
-      <c r="O53" s="168"/>
-      <c r="P53" s="168"/>
-      <c r="Q53" s="168"/>
-      <c r="R53" s="168"/>
+      <c r="M53" s="166"/>
+      <c r="N53" s="166"/>
+      <c r="O53" s="166"/>
+      <c r="P53" s="166"/>
+      <c r="Q53" s="166"/>
+      <c r="R53" s="166"/>
     </row>
     <row r="54" spans="2:18" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B54" s="135"/>
+      <c r="B54" s="133"/>
       <c r="D54" s="57" t="s">
         <v>416</v>
       </c>
@@ -17801,15 +18874,15 @@
       <c r="I54" s="49">
         <v>-4869.7579999999998</v>
       </c>
-      <c r="M54" s="168"/>
-      <c r="N54" s="168"/>
-      <c r="O54" s="168"/>
-      <c r="P54" s="168"/>
-      <c r="Q54" s="168"/>
-      <c r="R54" s="168"/>
+      <c r="M54" s="166"/>
+      <c r="N54" s="166"/>
+      <c r="O54" s="166"/>
+      <c r="P54" s="166"/>
+      <c r="Q54" s="166"/>
+      <c r="R54" s="166"/>
     </row>
     <row r="55" spans="2:18" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B55" s="135"/>
+      <c r="B55" s="133"/>
       <c r="D55" s="57" t="s">
         <v>417</v>
       </c>
@@ -17820,15 +18893,15 @@
       </c>
       <c r="H55" s="59"/>
       <c r="I55" s="59"/>
-      <c r="M55" s="168"/>
-      <c r="N55" s="168"/>
-      <c r="O55" s="168"/>
-      <c r="P55" s="168"/>
-      <c r="Q55" s="168"/>
-      <c r="R55" s="168"/>
+      <c r="M55" s="166"/>
+      <c r="N55" s="166"/>
+      <c r="O55" s="166"/>
+      <c r="P55" s="166"/>
+      <c r="Q55" s="166"/>
+      <c r="R55" s="166"/>
     </row>
     <row r="56" spans="2:18" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B56" s="135"/>
+      <c r="B56" s="133"/>
       <c r="D56" s="54" t="s">
         <v>418</v>
       </c>
@@ -17839,15 +18912,15 @@
       </c>
       <c r="H56" s="55"/>
       <c r="I56" s="55"/>
-      <c r="M56" s="168"/>
-      <c r="N56" s="168"/>
-      <c r="O56" s="168"/>
-      <c r="P56" s="168"/>
-      <c r="Q56" s="168"/>
-      <c r="R56" s="168"/>
+      <c r="M56" s="166"/>
+      <c r="N56" s="166"/>
+      <c r="O56" s="166"/>
+      <c r="P56" s="166"/>
+      <c r="Q56" s="166"/>
+      <c r="R56" s="166"/>
     </row>
     <row r="57" spans="2:18" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B57" s="135"/>
+      <c r="B57" s="133"/>
       <c r="D57" s="57"/>
       <c r="E57" s="49"/>
       <c r="F57" s="49"/>
@@ -17856,7 +18929,7 @@
       <c r="I57" s="49"/>
     </row>
     <row r="58" spans="2:18" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B58" s="135"/>
+      <c r="B58" s="133"/>
       <c r="D58" s="57"/>
       <c r="E58" s="49"/>
       <c r="F58" s="49"/>
@@ -17865,17 +18938,17 @@
       <c r="I58" s="49"/>
     </row>
     <row r="59" spans="2:18" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B59" s="135"/>
+      <c r="B59" s="133"/>
     </row>
     <row r="60" spans="2:18" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B60" s="135"/>
+      <c r="B60" s="133"/>
       <c r="D60" s="60" t="s">
         <v>435</v>
       </c>
     </row>
     <row r="61" spans="2:18" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B61" s="135"/>
-      <c r="D61" s="128"/>
+      <c r="B61" s="133"/>
+      <c r="D61" s="126"/>
       <c r="E61" s="42" t="s">
         <v>340</v>
       </c>
@@ -17899,26 +18972,26 @@
       </c>
     </row>
     <row r="62" spans="2:18" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B62" s="135"/>
-      <c r="D62" s="129"/>
-      <c r="E62" s="132" t="s">
+      <c r="B62" s="133"/>
+      <c r="D62" s="127"/>
+      <c r="E62" s="130" t="s">
         <v>422</v>
       </c>
-      <c r="F62" s="132" t="s">
+      <c r="F62" s="130" t="s">
         <v>423</v>
       </c>
-      <c r="G62" s="132"/>
-      <c r="H62" s="132"/>
-      <c r="I62" s="132" t="s">
+      <c r="G62" s="130"/>
+      <c r="H62" s="130"/>
+      <c r="I62" s="130" t="s">
         <v>424</v>
       </c>
-      <c r="J62" s="132"/>
-      <c r="K62" s="132"/>
+      <c r="J62" s="130"/>
+      <c r="K62" s="130"/>
     </row>
     <row r="63" spans="2:18" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B63" s="135"/>
-      <c r="D63" s="129"/>
-      <c r="E63" s="130"/>
+      <c r="B63" s="133"/>
+      <c r="D63" s="127"/>
+      <c r="E63" s="128"/>
       <c r="F63" s="52" t="s">
         <v>425</v>
       </c>
@@ -17933,8 +19006,8 @@
       <c r="K63" s="61"/>
     </row>
     <row r="64" spans="2:18" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B64" s="135"/>
-      <c r="D64" s="131" t="s">
+      <c r="B64" s="133"/>
+      <c r="D64" s="129" t="s">
         <v>403</v>
       </c>
       <c r="E64" s="49" t="s">
@@ -17960,8 +19033,8 @@
       </c>
     </row>
     <row r="65" spans="2:13" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B65" s="135"/>
-      <c r="D65" s="136"/>
+      <c r="B65" s="133"/>
+      <c r="D65" s="134"/>
       <c r="E65" s="45" t="s">
         <v>29</v>
       </c>
@@ -17985,7 +19058,7 @@
       </c>
     </row>
     <row r="66" spans="2:13" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B66" s="135"/>
+      <c r="B66" s="133"/>
       <c r="D66" s="62" t="s">
         <v>338</v>
       </c>
@@ -18012,7 +19085,7 @@
       </c>
     </row>
     <row r="67" spans="2:13" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B67" s="135"/>
+      <c r="B67" s="133"/>
       <c r="D67" s="63" t="s">
         <v>412</v>
       </c>
@@ -18039,7 +19112,7 @@
       </c>
     </row>
     <row r="68" spans="2:13" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B68" s="135"/>
+      <c r="B68" s="133"/>
       <c r="D68" s="63" t="s">
         <v>339</v>
       </c>
@@ -18066,22 +19139,22 @@
       </c>
     </row>
     <row r="69" spans="2:13" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B69" s="135"/>
+      <c r="B69" s="133"/>
     </row>
     <row r="70" spans="2:13" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B70" s="135"/>
+      <c r="B70" s="133"/>
     </row>
     <row r="71" spans="2:13" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B71" s="135"/>
+      <c r="B71" s="133"/>
     </row>
     <row r="72" spans="2:13" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B72" s="135"/>
+      <c r="B72" s="133"/>
       <c r="K72" s="60" t="s">
         <v>448</v>
       </c>
     </row>
     <row r="73" spans="2:13" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B73" s="135"/>
+      <c r="B73" s="133"/>
       <c r="K73" s="66"/>
       <c r="L73" s="42" t="s">
         <v>340</v>
@@ -18091,7 +19164,7 @@
       </c>
     </row>
     <row r="74" spans="2:13" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B74" s="135"/>
+      <c r="B74" s="133"/>
       <c r="K74" s="50"/>
       <c r="L74" s="56" t="s">
         <v>436</v>
@@ -18101,8 +19174,8 @@
       </c>
     </row>
     <row r="75" spans="2:13" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B75" s="135"/>
-      <c r="K75" s="144" t="s">
+      <c r="B75" s="133"/>
+      <c r="K75" s="142" t="s">
         <v>438</v>
       </c>
       <c r="L75" s="50">
@@ -18113,8 +19186,8 @@
       </c>
     </row>
     <row r="76" spans="2:13" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B76" s="135"/>
-      <c r="K76" s="145"/>
+      <c r="B76" s="133"/>
+      <c r="K76" s="143"/>
       <c r="L76" s="67" t="s">
         <v>224</v>
       </c>
@@ -18123,7 +19196,7 @@
       </c>
     </row>
     <row r="77" spans="2:13" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B77" s="135"/>
+      <c r="B77" s="133"/>
       <c r="K77" s="53" t="s">
         <v>439</v>
       </c>
@@ -18135,7 +19208,7 @@
       </c>
     </row>
     <row r="78" spans="2:13" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B78" s="135"/>
+      <c r="B78" s="133"/>
       <c r="K78" s="63" t="s">
         <v>412</v>
       </c>
@@ -18147,7 +19220,7 @@
       </c>
     </row>
     <row r="79" spans="2:13" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B79" s="135"/>
+      <c r="B79" s="133"/>
       <c r="K79" s="63" t="s">
         <v>339</v>
       </c>
@@ -18159,50 +19232,50 @@
       </c>
     </row>
     <row r="80" spans="2:13" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B80" s="135"/>
+      <c r="B80" s="133"/>
     </row>
     <row r="81" spans="2:15" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B81" s="135"/>
+      <c r="B81" s="133"/>
     </row>
     <row r="82" spans="2:15" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B82" s="135"/>
+      <c r="B82" s="133"/>
     </row>
     <row r="83" spans="2:15" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B83" s="135"/>
+      <c r="B83" s="133"/>
       <c r="J83" s="60" t="s">
         <v>441</v>
       </c>
     </row>
     <row r="84" spans="2:15" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B84" s="135"/>
-      <c r="J84" s="146"/>
-      <c r="K84" s="148" t="s">
+      <c r="B84" s="133"/>
+      <c r="J84" s="144"/>
+      <c r="K84" s="146" t="s">
         <v>442</v>
       </c>
-      <c r="L84" s="148" t="s">
+      <c r="L84" s="146" t="s">
         <v>446</v>
       </c>
-      <c r="M84" s="138" t="s">
+      <c r="M84" s="136" t="s">
         <v>447</v>
       </c>
-      <c r="N84" s="138" t="s">
+      <c r="N84" s="136" t="s">
         <v>443</v>
       </c>
-      <c r="O84" s="138" t="s">
+      <c r="O84" s="136" t="s">
         <v>444</v>
       </c>
     </row>
     <row r="85" spans="2:15" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B85" s="135"/>
-      <c r="J85" s="147"/>
-      <c r="K85" s="149"/>
-      <c r="L85" s="149"/>
-      <c r="M85" s="139"/>
-      <c r="N85" s="139"/>
-      <c r="O85" s="139"/>
+      <c r="B85" s="133"/>
+      <c r="J85" s="145"/>
+      <c r="K85" s="147"/>
+      <c r="L85" s="147"/>
+      <c r="M85" s="137"/>
+      <c r="N85" s="137"/>
+      <c r="O85" s="137"/>
     </row>
     <row r="86" spans="2:15" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B86" s="135"/>
+      <c r="B86" s="133"/>
       <c r="J86" s="69" t="s">
         <v>445</v>
       </c>
@@ -18223,7 +19296,7 @@
       </c>
     </row>
     <row r="87" spans="2:15" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B87" s="135"/>
+      <c r="B87" s="133"/>
       <c r="J87" s="71" t="s">
         <v>437</v>
       </c>
@@ -18244,10 +19317,10 @@
       </c>
     </row>
     <row r="88" spans="2:15" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B88" s="135"/>
+      <c r="B88" s="133"/>
     </row>
     <row r="89" spans="2:15" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B89" s="135"/>
+      <c r="B89" s="133"/>
     </row>
   </sheetData>
   <mergeCells count="39">
@@ -18297,7 +19370,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06B7323D-B2F5-BD40-8E81-C2419FFBC224}">
   <dimension ref="B2:I21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -18312,424 +19385,424 @@
   <sheetData>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B2" s="110" t="s">
+        <v>487</v>
+      </c>
+      <c r="C2" s="110" t="s">
+        <v>488</v>
+      </c>
+      <c r="D2" s="110" t="s">
+        <v>489</v>
+      </c>
+      <c r="E2" s="110" t="s">
         <v>490</v>
       </c>
-      <c r="C2" s="110" t="s">
+      <c r="F2" s="110" t="s">
         <v>491</v>
       </c>
-      <c r="D2" s="110" t="s">
+      <c r="G2" s="110" t="s">
         <v>492</v>
       </c>
-      <c r="E2" s="110" t="s">
+      <c r="H2" s="110" t="s">
         <v>493</v>
       </c>
-      <c r="F2" s="110" t="s">
+      <c r="I2" s="110" t="s">
         <v>494</v>
       </c>
-      <c r="G2" s="110" t="s">
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B3" s="150" t="s">
         <v>495</v>
       </c>
-      <c r="H2" s="110" t="s">
+      <c r="C3" s="149" t="s">
         <v>496</v>
       </c>
-      <c r="I2" s="110" t="s">
+      <c r="D3" s="149" t="s">
         <v>497</v>
       </c>
-    </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B3" s="152" t="s">
+      <c r="E3" s="149" t="s">
         <v>498</v>
       </c>
-      <c r="C3" s="151" t="s">
+      <c r="F3" s="149" t="s">
         <v>499</v>
       </c>
-      <c r="D3" s="151" t="s">
+      <c r="G3" s="149" t="s">
         <v>500</v>
       </c>
-      <c r="E3" s="151" t="s">
+      <c r="H3" s="149" t="s">
         <v>501</v>
       </c>
-      <c r="F3" s="151" t="s">
+      <c r="I3" s="107" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B4" s="150"/>
+      <c r="C4" s="149"/>
+      <c r="D4" s="149"/>
+      <c r="E4" s="149"/>
+      <c r="F4" s="149"/>
+      <c r="G4" s="149"/>
+      <c r="H4" s="149"/>
+      <c r="I4" s="107" t="s">
         <v>502</v>
-      </c>
-      <c r="G3" s="151" t="s">
-        <v>503</v>
-      </c>
-      <c r="H3" s="151" t="s">
-        <v>504</v>
-      </c>
-      <c r="I3" s="107" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B4" s="152"/>
-      <c r="C4" s="151"/>
-      <c r="D4" s="151"/>
-      <c r="E4" s="151"/>
-      <c r="F4" s="151"/>
-      <c r="G4" s="151"/>
-      <c r="H4" s="151"/>
-      <c r="I4" s="107" t="s">
-        <v>505</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B5" s="108" t="s">
+        <v>503</v>
+      </c>
+      <c r="C5" s="109" t="s">
+        <v>496</v>
+      </c>
+      <c r="D5" s="109" t="s">
+        <v>497</v>
+      </c>
+      <c r="E5" s="109" t="s">
+        <v>504</v>
+      </c>
+      <c r="F5" s="109" t="s">
+        <v>499</v>
+      </c>
+      <c r="G5" s="109" t="s">
+        <v>505</v>
+      </c>
+      <c r="H5" s="109" t="s">
         <v>506</v>
       </c>
-      <c r="C5" s="109" t="s">
-        <v>499</v>
-      </c>
-      <c r="D5" s="109" t="s">
-        <v>500</v>
-      </c>
-      <c r="E5" s="109" t="s">
+      <c r="I5" s="107" t="s">
         <v>507</v>
-      </c>
-      <c r="F5" s="109" t="s">
-        <v>502</v>
-      </c>
-      <c r="G5" s="109" t="s">
-        <v>508</v>
-      </c>
-      <c r="H5" s="109" t="s">
-        <v>509</v>
-      </c>
-      <c r="I5" s="107" t="s">
-        <v>510</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B6" s="108" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="C6" s="109" t="s">
+        <v>496</v>
+      </c>
+      <c r="D6" s="109" t="s">
+        <v>497</v>
+      </c>
+      <c r="E6" s="109" t="s">
+        <v>504</v>
+      </c>
+      <c r="F6" s="109" t="s">
         <v>499</v>
       </c>
-      <c r="D6" s="109" t="s">
-        <v>500</v>
-      </c>
-      <c r="E6" s="109" t="s">
+      <c r="G6" s="109" t="s">
+        <v>505</v>
+      </c>
+      <c r="H6" s="109" t="s">
+        <v>506</v>
+      </c>
+      <c r="I6" s="107" t="s">
         <v>507</v>
-      </c>
-      <c r="F6" s="109" t="s">
-        <v>502</v>
-      </c>
-      <c r="G6" s="109" t="s">
-        <v>508</v>
-      </c>
-      <c r="H6" s="109" t="s">
-        <v>509</v>
-      </c>
-      <c r="I6" s="107" t="s">
-        <v>510</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B7" s="108" t="s">
+        <v>509</v>
+      </c>
+      <c r="C7" s="109" t="s">
+        <v>510</v>
+      </c>
+      <c r="D7" s="109" t="s">
+        <v>497</v>
+      </c>
+      <c r="E7" s="109" t="s">
+        <v>504</v>
+      </c>
+      <c r="F7" s="109" t="s">
+        <v>499</v>
+      </c>
+      <c r="G7" s="109" t="s">
+        <v>505</v>
+      </c>
+      <c r="H7" s="109" t="s">
+        <v>506</v>
+      </c>
+      <c r="I7" s="107" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B8" s="150" t="s">
+        <v>511</v>
+      </c>
+      <c r="C8" s="149" t="s">
+        <v>510</v>
+      </c>
+      <c r="D8" s="149" t="s">
+        <v>497</v>
+      </c>
+      <c r="E8" s="149" t="s">
+        <v>504</v>
+      </c>
+      <c r="F8" s="149" t="s">
+        <v>499</v>
+      </c>
+      <c r="G8" s="149" t="s">
         <v>512</v>
       </c>
-      <c r="C7" s="109" t="s">
+      <c r="H8" s="149" t="s">
         <v>513</v>
       </c>
-      <c r="D7" s="109" t="s">
-        <v>500</v>
-      </c>
-      <c r="E7" s="109" t="s">
-        <v>507</v>
-      </c>
-      <c r="F7" s="109" t="s">
-        <v>502</v>
-      </c>
-      <c r="G7" s="109" t="s">
-        <v>508</v>
-      </c>
-      <c r="H7" s="109" t="s">
-        <v>509</v>
-      </c>
-      <c r="I7" s="107" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B8" s="152" t="s">
+      <c r="I8" s="107" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B9" s="150"/>
+      <c r="C9" s="149"/>
+      <c r="D9" s="149"/>
+      <c r="E9" s="149"/>
+      <c r="F9" s="149"/>
+      <c r="G9" s="149"/>
+      <c r="H9" s="149"/>
+      <c r="I9" s="107" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B10" s="150"/>
+      <c r="C10" s="149"/>
+      <c r="D10" s="149"/>
+      <c r="E10" s="149"/>
+      <c r="F10" s="149"/>
+      <c r="G10" s="149"/>
+      <c r="H10" s="149"/>
+      <c r="I10" s="107" t="s">
         <v>514</v>
-      </c>
-      <c r="C8" s="151" t="s">
-        <v>513</v>
-      </c>
-      <c r="D8" s="151" t="s">
-        <v>500</v>
-      </c>
-      <c r="E8" s="151" t="s">
-        <v>507</v>
-      </c>
-      <c r="F8" s="151" t="s">
-        <v>502</v>
-      </c>
-      <c r="G8" s="151" t="s">
-        <v>515</v>
-      </c>
-      <c r="H8" s="151" t="s">
-        <v>516</v>
-      </c>
-      <c r="I8" s="107" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B9" s="152"/>
-      <c r="C9" s="151"/>
-      <c r="D9" s="151"/>
-      <c r="E9" s="151"/>
-      <c r="F9" s="151"/>
-      <c r="G9" s="151"/>
-      <c r="H9" s="151"/>
-      <c r="I9" s="107" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B10" s="152"/>
-      <c r="C10" s="151"/>
-      <c r="D10" s="151"/>
-      <c r="E10" s="151"/>
-      <c r="F10" s="151"/>
-      <c r="G10" s="151"/>
-      <c r="H10" s="151"/>
-      <c r="I10" s="107" t="s">
-        <v>517</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B11" s="108" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="C11" s="109" t="s">
+        <v>496</v>
+      </c>
+      <c r="D11" s="109" t="s">
+        <v>497</v>
+      </c>
+      <c r="E11" s="109" t="s">
+        <v>504</v>
+      </c>
+      <c r="F11" s="109" t="s">
         <v>499</v>
       </c>
-      <c r="D11" s="109" t="s">
-        <v>500</v>
-      </c>
-      <c r="E11" s="109" t="s">
-        <v>507</v>
-      </c>
-      <c r="F11" s="109" t="s">
-        <v>502</v>
-      </c>
       <c r="G11" s="109" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="H11" s="109" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="I11" s="107" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B12" s="108" t="s">
+        <v>518</v>
+      </c>
+      <c r="C12" s="109" t="s">
+        <v>519</v>
+      </c>
+      <c r="D12" s="109" t="s">
+        <v>520</v>
+      </c>
+      <c r="E12" s="109" t="s">
+        <v>504</v>
+      </c>
+      <c r="F12" s="109" t="s">
+        <v>499</v>
+      </c>
+      <c r="G12" s="109" t="s">
+        <v>516</v>
+      </c>
+      <c r="H12" s="109" t="s">
         <v>521</v>
       </c>
-      <c r="C12" s="109" t="s">
-        <v>522</v>
-      </c>
-      <c r="D12" s="109" t="s">
-        <v>523</v>
-      </c>
-      <c r="E12" s="109" t="s">
-        <v>507</v>
-      </c>
-      <c r="F12" s="109" t="s">
-        <v>502</v>
-      </c>
-      <c r="G12" s="109" t="s">
-        <v>519</v>
-      </c>
-      <c r="H12" s="109" t="s">
-        <v>524</v>
-      </c>
       <c r="I12" s="107" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B13" s="108" t="s">
+        <v>522</v>
+      </c>
+      <c r="C13" s="109" t="s">
+        <v>496</v>
+      </c>
+      <c r="D13" s="109" t="s">
+        <v>497</v>
+      </c>
+      <c r="E13" s="109" t="s">
+        <v>504</v>
+      </c>
+      <c r="F13" s="109" t="s">
+        <v>499</v>
+      </c>
+      <c r="G13" s="109" t="s">
+        <v>505</v>
+      </c>
+      <c r="H13" s="109" t="s">
+        <v>523</v>
+      </c>
+      <c r="I13" s="107" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B14" s="150" t="s">
+        <v>524</v>
+      </c>
+      <c r="C14" s="149" t="s">
+        <v>510</v>
+      </c>
+      <c r="D14" s="149" t="s">
+        <v>497</v>
+      </c>
+      <c r="E14" s="149" t="s">
+        <v>504</v>
+      </c>
+      <c r="F14" s="149" t="s">
+        <v>499</v>
+      </c>
+      <c r="G14" s="149" t="s">
+        <v>500</v>
+      </c>
+      <c r="H14" s="149" t="s">
+        <v>517</v>
+      </c>
+      <c r="I14" s="107" t="s">
         <v>525</v>
       </c>
-      <c r="C13" s="109" t="s">
+    </row>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B15" s="150"/>
+      <c r="C15" s="149"/>
+      <c r="D15" s="149"/>
+      <c r="E15" s="149"/>
+      <c r="F15" s="149"/>
+      <c r="G15" s="149"/>
+      <c r="H15" s="149"/>
+      <c r="I15" s="107" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B16" s="150" t="s">
+        <v>527</v>
+      </c>
+      <c r="C16" s="149" t="s">
+        <v>510</v>
+      </c>
+      <c r="D16" s="149" t="s">
+        <v>497</v>
+      </c>
+      <c r="E16" s="149" t="s">
+        <v>498</v>
+      </c>
+      <c r="F16" s="149" t="s">
         <v>499</v>
       </c>
-      <c r="D13" s="109" t="s">
-        <v>500</v>
-      </c>
-      <c r="E13" s="109" t="s">
-        <v>507</v>
-      </c>
-      <c r="F13" s="109" t="s">
-        <v>502</v>
-      </c>
-      <c r="G13" s="109" t="s">
-        <v>508</v>
-      </c>
-      <c r="H13" s="109" t="s">
-        <v>526</v>
-      </c>
-      <c r="I13" s="107" t="s">
+      <c r="G16" s="149" t="s">
+        <v>512</v>
+      </c>
+      <c r="H16" s="149" t="s">
+        <v>506</v>
+      </c>
+      <c r="I16" s="107" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B17" s="150"/>
+      <c r="C17" s="149"/>
+      <c r="D17" s="149"/>
+      <c r="E17" s="149"/>
+      <c r="F17" s="149"/>
+      <c r="G17" s="149"/>
+      <c r="H17" s="149"/>
+      <c r="I17" s="107" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B18" s="150"/>
+      <c r="C18" s="149"/>
+      <c r="D18" s="149"/>
+      <c r="E18" s="149"/>
+      <c r="F18" s="149"/>
+      <c r="G18" s="149"/>
+      <c r="H18" s="149"/>
+      <c r="I18" s="107" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B19" s="151" t="s">
+        <v>522</v>
+      </c>
+      <c r="C19" s="148" t="s">
+        <v>496</v>
+      </c>
+      <c r="D19" s="148" t="s">
+        <v>497</v>
+      </c>
+      <c r="E19" s="148" t="s">
+        <v>504</v>
+      </c>
+      <c r="F19" s="148" t="s">
+        <v>499</v>
+      </c>
+      <c r="G19" s="148" t="s">
+        <v>505</v>
+      </c>
+      <c r="H19" s="148" t="s">
+        <v>523</v>
+      </c>
+      <c r="I19" s="111" t="s">
         <v>537</v>
       </c>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B14" s="152" t="s">
-        <v>527</v>
-      </c>
-      <c r="C14" s="151" t="s">
-        <v>513</v>
-      </c>
-      <c r="D14" s="151" t="s">
-        <v>500</v>
-      </c>
-      <c r="E14" s="151" t="s">
-        <v>507</v>
-      </c>
-      <c r="F14" s="151" t="s">
-        <v>502</v>
-      </c>
-      <c r="G14" s="151" t="s">
-        <v>503</v>
-      </c>
-      <c r="H14" s="151" t="s">
-        <v>520</v>
-      </c>
-      <c r="I14" s="107" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B15" s="152"/>
-      <c r="C15" s="151"/>
-      <c r="D15" s="151"/>
-      <c r="E15" s="151"/>
-      <c r="F15" s="151"/>
-      <c r="G15" s="151"/>
-      <c r="H15" s="151"/>
-      <c r="I15" s="107" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B16" s="152" t="s">
-        <v>530</v>
-      </c>
-      <c r="C16" s="151" t="s">
-        <v>513</v>
-      </c>
-      <c r="D16" s="151" t="s">
-        <v>500</v>
-      </c>
-      <c r="E16" s="151" t="s">
-        <v>501</v>
-      </c>
-      <c r="F16" s="151" t="s">
-        <v>502</v>
-      </c>
-      <c r="G16" s="151" t="s">
-        <v>515</v>
-      </c>
-      <c r="H16" s="151" t="s">
-        <v>509</v>
-      </c>
-      <c r="I16" s="107" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="152"/>
-      <c r="C17" s="151"/>
-      <c r="D17" s="151"/>
-      <c r="E17" s="151"/>
-      <c r="F17" s="151"/>
-      <c r="G17" s="151"/>
-      <c r="H17" s="151"/>
-      <c r="I17" s="107" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B18" s="152"/>
-      <c r="C18" s="151"/>
-      <c r="D18" s="151"/>
-      <c r="E18" s="151"/>
-      <c r="F18" s="151"/>
-      <c r="G18" s="151"/>
-      <c r="H18" s="151"/>
-      <c r="I18" s="107" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="153" t="s">
-        <v>525</v>
-      </c>
-      <c r="C19" s="150" t="s">
-        <v>499</v>
-      </c>
-      <c r="D19" s="150" t="s">
-        <v>500</v>
-      </c>
-      <c r="E19" s="150" t="s">
-        <v>507</v>
-      </c>
-      <c r="F19" s="150" t="s">
-        <v>502</v>
-      </c>
-      <c r="G19" s="150" t="s">
-        <v>508</v>
-      </c>
-      <c r="H19" s="150" t="s">
-        <v>526</v>
-      </c>
-      <c r="I19" s="111" t="s">
-        <v>540</v>
-      </c>
-    </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B20" s="153"/>
-      <c r="C20" s="150"/>
-      <c r="D20" s="150"/>
-      <c r="E20" s="150"/>
-      <c r="F20" s="150"/>
-      <c r="G20" s="150"/>
-      <c r="H20" s="150"/>
+      <c r="B20" s="151"/>
+      <c r="C20" s="148"/>
+      <c r="D20" s="148"/>
+      <c r="E20" s="148"/>
+      <c r="F20" s="148"/>
+      <c r="G20" s="148"/>
+      <c r="H20" s="148"/>
       <c r="I20" s="111" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
     </row>
     <row r="21" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B21" s="112" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="C21" s="113" t="s">
+        <v>496</v>
+      </c>
+      <c r="D21" s="113" t="s">
+        <v>497</v>
+      </c>
+      <c r="E21" s="113" t="s">
+        <v>504</v>
+      </c>
+      <c r="F21" s="113" t="s">
         <v>499</v>
       </c>
-      <c r="D21" s="113" t="s">
-        <v>500</v>
-      </c>
-      <c r="E21" s="113" t="s">
-        <v>507</v>
-      </c>
-      <c r="F21" s="113" t="s">
-        <v>502</v>
-      </c>
       <c r="G21" s="113" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="H21" s="113" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="I21" s="114" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
     </row>
   </sheetData>
@@ -18775,7 +19848,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8DD9CDF-8D3B-4C4F-9F1C-C65D2EB3343E}">
   <dimension ref="A1:M49"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -19314,7 +20387,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2940A11-14E0-5242-BAF0-2DDD4FA2A627}">
   <dimension ref="B2:P61"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -19373,35 +20446,35 @@
       <c r="B3" s="15" t="s">
         <v>345</v>
       </c>
-      <c r="C3" s="161" t="s">
+      <c r="C3" s="159" t="s">
         <v>346</v>
       </c>
-      <c r="D3" s="161"/>
-      <c r="E3" s="161" t="s">
+      <c r="D3" s="159"/>
+      <c r="E3" s="159" t="s">
         <v>348</v>
       </c>
-      <c r="F3" s="161"/>
+      <c r="F3" s="159"/>
       <c r="H3" s="15" t="s">
         <v>345</v>
       </c>
-      <c r="I3" s="161" t="s">
+      <c r="I3" s="159" t="s">
         <v>349</v>
       </c>
-      <c r="J3" s="161"/>
-      <c r="K3" s="161" t="s">
+      <c r="J3" s="159"/>
+      <c r="K3" s="159" t="s">
         <v>350</v>
       </c>
-      <c r="L3" s="161"/>
+      <c r="L3" s="159"/>
       <c r="N3" s="15" t="s">
         <v>345</v>
       </c>
-      <c r="O3" s="161" t="s">
+      <c r="O3" s="159" t="s">
         <v>352</v>
       </c>
-      <c r="P3" s="161"/>
+      <c r="P3" s="159"/>
     </row>
     <row r="4" spans="2:16" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="158" t="s">
+      <c r="B4" s="156" t="s">
         <v>334</v>
       </c>
       <c r="C4" s="13" t="s">
@@ -19416,7 +20489,7 @@
       <c r="F4" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="H4" s="158" t="s">
+      <c r="H4" s="156" t="s">
         <v>334</v>
       </c>
       <c r="I4" s="13" t="s">
@@ -19431,7 +20504,7 @@
       <c r="L4" s="13" t="s">
         <v>260</v>
       </c>
-      <c r="N4" s="158" t="s">
+      <c r="N4" s="156" t="s">
         <v>334</v>
       </c>
       <c r="O4" s="13" t="s">
@@ -19442,7 +20515,7 @@
       </c>
     </row>
     <row r="5" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B5" s="158"/>
+      <c r="B5" s="156"/>
       <c r="C5" s="13" t="s">
         <v>16</v>
       </c>
@@ -19455,7 +20528,7 @@
       <c r="F5" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="H5" s="158"/>
+      <c r="H5" s="156"/>
       <c r="I5" s="13" t="s">
         <v>29</v>
       </c>
@@ -19468,7 +20541,7 @@
       <c r="L5" s="13" t="s">
         <v>263</v>
       </c>
-      <c r="N5" s="158"/>
+      <c r="N5" s="156"/>
       <c r="O5" s="13" t="s">
         <v>65</v>
       </c>
@@ -19477,7 +20550,7 @@
       </c>
     </row>
     <row r="6" spans="2:16" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="158" t="s">
+      <c r="B6" s="156" t="s">
         <v>364</v>
       </c>
       <c r="C6" s="13"/>
@@ -19488,7 +20561,7 @@
       <c r="F6" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="H6" s="158" t="s">
+      <c r="H6" s="156" t="s">
         <v>360</v>
       </c>
       <c r="J6" s="13" t="s">
@@ -19498,7 +20571,7 @@
       <c r="L6" s="13" t="s">
         <v>266</v>
       </c>
-      <c r="N6" s="158" t="s">
+      <c r="N6" s="156" t="s">
         <v>360</v>
       </c>
       <c r="P6" s="13" t="s">
@@ -19506,7 +20579,7 @@
       </c>
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B7" s="158"/>
+      <c r="B7" s="156"/>
       <c r="C7" s="13"/>
       <c r="D7" s="13" t="s">
         <v>26</v>
@@ -19515,7 +20588,7 @@
       <c r="F7" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="H7" s="158"/>
+      <c r="H7" s="156"/>
       <c r="J7" s="13" t="s">
         <v>213</v>
       </c>
@@ -19523,13 +20596,13 @@
       <c r="L7" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="N7" s="158"/>
+      <c r="N7" s="156"/>
       <c r="P7" s="13" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="8" spans="2:16" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="158" t="s">
+      <c r="B8" s="156" t="s">
         <v>365</v>
       </c>
       <c r="C8" s="13"/>
@@ -19540,7 +20613,7 @@
       <c r="F8" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="H8" s="158" t="s">
+      <c r="H8" s="156" t="s">
         <v>361</v>
       </c>
       <c r="J8" s="13" t="s">
@@ -19550,7 +20623,7 @@
       <c r="L8" s="13" t="s">
         <v>269</v>
       </c>
-      <c r="N8" s="158" t="s">
+      <c r="N8" s="156" t="s">
         <v>361</v>
       </c>
       <c r="P8" s="13" t="s">
@@ -19558,7 +20631,7 @@
       </c>
     </row>
     <row r="9" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B9" s="159"/>
+      <c r="B9" s="157"/>
       <c r="C9" s="16"/>
       <c r="D9" s="16" t="s">
         <v>85</v>
@@ -19567,7 +20640,7 @@
       <c r="F9" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="H9" s="158"/>
+      <c r="H9" s="156"/>
       <c r="J9" s="13" t="s">
         <v>163</v>
       </c>
@@ -19575,7 +20648,7 @@
       <c r="L9" s="13" t="s">
         <v>274</v>
       </c>
-      <c r="N9" s="158"/>
+      <c r="N9" s="156"/>
       <c r="P9" s="13" t="s">
         <v>217</v>
       </c>
@@ -19596,7 +20669,7 @@
       <c r="F10" s="13" t="s">
         <v>336</v>
       </c>
-      <c r="H10" s="158" t="s">
+      <c r="H10" s="156" t="s">
         <v>362</v>
       </c>
       <c r="I10" s="13"/>
@@ -19607,7 +20680,7 @@
       <c r="L10" s="13" t="s">
         <v>277</v>
       </c>
-      <c r="N10" s="158" t="s">
+      <c r="N10" s="156" t="s">
         <v>362</v>
       </c>
       <c r="O10" s="13"/>
@@ -19631,7 +20704,7 @@
       <c r="F11" s="13" t="s">
         <v>336</v>
       </c>
-      <c r="H11" s="158"/>
+      <c r="H11" s="156"/>
       <c r="I11" s="13"/>
       <c r="J11" s="13" t="s">
         <v>251</v>
@@ -19640,7 +20713,7 @@
       <c r="L11" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="N11" s="158"/>
+      <c r="N11" s="156"/>
       <c r="O11" s="13"/>
       <c r="P11" s="13" t="s">
         <v>213</v>
@@ -19662,7 +20735,7 @@
       <c r="F12" s="13" t="s">
         <v>336</v>
       </c>
-      <c r="H12" s="158" t="s">
+      <c r="H12" s="156" t="s">
         <v>363</v>
       </c>
       <c r="I12" s="13"/>
@@ -19673,7 +20746,7 @@
       <c r="L12" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="N12" s="158" t="s">
+      <c r="N12" s="156" t="s">
         <v>363</v>
       </c>
       <c r="O12" s="13"/>
@@ -19697,7 +20770,7 @@
       <c r="F13" s="16" t="s">
         <v>347</v>
       </c>
-      <c r="H13" s="159"/>
+      <c r="H13" s="157"/>
       <c r="I13" s="16"/>
       <c r="J13" s="16" t="s">
         <v>210</v>
@@ -19706,7 +20779,7 @@
       <c r="L13" s="16" t="s">
         <v>286</v>
       </c>
-      <c r="N13" s="159"/>
+      <c r="N13" s="157"/>
       <c r="O13" s="16"/>
       <c r="P13" s="16" t="s">
         <v>60</v>
@@ -19839,17 +20912,17 @@
       <c r="B20" s="29" t="s">
         <v>388</v>
       </c>
-      <c r="C20" s="161" t="s">
+      <c r="C20" s="159" t="s">
         <v>399</v>
       </c>
-      <c r="D20" s="161"/>
-      <c r="E20" s="161" t="s">
+      <c r="D20" s="159"/>
+      <c r="E20" s="159" t="s">
         <v>400</v>
       </c>
-      <c r="F20" s="161"/>
+      <c r="F20" s="159"/>
     </row>
     <row r="21" spans="2:16" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="158" t="s">
+      <c r="B21" s="156" t="s">
         <v>334</v>
       </c>
       <c r="C21" s="13" t="s">
@@ -19866,7 +20939,7 @@
       </c>
     </row>
     <row r="22" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B22" s="158"/>
+      <c r="B22" s="156"/>
       <c r="C22" s="13" t="s">
         <v>16</v>
       </c>
@@ -19881,7 +20954,7 @@
       </c>
     </row>
     <row r="23" spans="2:16" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="158" t="s">
+      <c r="B23" s="156" t="s">
         <v>401</v>
       </c>
       <c r="C23" s="13"/>
@@ -19894,7 +20967,7 @@
       </c>
     </row>
     <row r="24" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B24" s="158"/>
+      <c r="B24" s="156"/>
       <c r="C24" s="13"/>
       <c r="D24" s="13" t="s">
         <v>26</v>
@@ -19905,7 +20978,7 @@
       </c>
     </row>
     <row r="25" spans="2:16" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="158" t="s">
+      <c r="B25" s="156" t="s">
         <v>402</v>
       </c>
       <c r="C25" s="13"/>
@@ -19918,7 +20991,7 @@
       </c>
     </row>
     <row r="26" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B26" s="159"/>
+      <c r="B26" s="157"/>
       <c r="C26" s="16"/>
       <c r="D26" s="16" t="s">
         <v>85</v>
@@ -19999,23 +21072,23 @@
     <row r="32" spans="2:16" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="34" spans="2:7" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="44" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B44" s="160" t="s">
+      <c r="B44" s="158" t="s">
         <v>324</v>
       </c>
-      <c r="C44" s="160" t="s">
+      <c r="C44" s="158" t="s">
         <v>325</v>
       </c>
-      <c r="D44" s="160"/>
-      <c r="E44" s="160"/>
-      <c r="F44" s="160" t="s">
+      <c r="D44" s="158"/>
+      <c r="E44" s="158"/>
+      <c r="F44" s="158" t="s">
         <v>326</v>
       </c>
-      <c r="G44" s="160" t="s">
+      <c r="G44" s="158" t="s">
         <v>327</v>
       </c>
     </row>
     <row r="45" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B45" s="154"/>
+      <c r="B45" s="152"/>
       <c r="C45" s="19" t="s">
         <v>328</v>
       </c>
@@ -20025,11 +21098,11 @@
       <c r="E45" s="19" t="s">
         <v>330</v>
       </c>
-      <c r="F45" s="155"/>
-      <c r="G45" s="155"/>
+      <c r="F45" s="153"/>
+      <c r="G45" s="153"/>
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B46" s="156" t="s">
+      <c r="B46" s="154" t="s">
         <v>331</v>
       </c>
       <c r="C46" s="17" t="str">
@@ -20044,17 +21117,17 @@
         <f>"89.272"</f>
         <v>89.272</v>
       </c>
-      <c r="F46" s="154" t="str">
+      <c r="F46" s="152" t="str">
         <f>"0.000"</f>
         <v>0.000</v>
       </c>
-      <c r="G46" s="154" t="str">
+      <c r="G46" s="152" t="str">
         <f>"2702.000"</f>
         <v>2702.000</v>
       </c>
     </row>
     <row r="47" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B47" s="156"/>
+      <c r="B47" s="154"/>
       <c r="C47" s="17" t="str">
         <f>"(113.981)"</f>
         <v>(113.981)</v>
@@ -20067,11 +21140,11 @@
         <f>"(133.323)"</f>
         <v>(133.323)</v>
       </c>
-      <c r="F47" s="154"/>
-      <c r="G47" s="154"/>
+      <c r="F47" s="152"/>
+      <c r="G47" s="152"/>
     </row>
     <row r="48" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B48" s="156" t="s">
+      <c r="B48" s="154" t="s">
         <v>332</v>
       </c>
       <c r="C48" s="17" t="str">
@@ -20086,17 +21159,17 @@
         <f>"1.372"</f>
         <v>1.372</v>
       </c>
-      <c r="F48" s="154" t="str">
+      <c r="F48" s="152" t="str">
         <f>"0.000"</f>
         <v>0.000</v>
       </c>
-      <c r="G48" s="154" t="str">
+      <c r="G48" s="152" t="str">
         <f>"8.000"</f>
         <v>8.000</v>
       </c>
     </row>
     <row r="49" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B49" s="156"/>
+      <c r="B49" s="154"/>
       <c r="C49" s="17" t="str">
         <f>"(1.166)"</f>
         <v>(1.166)</v>
@@ -20109,11 +21182,11 @@
         <f>"(1.192)"</f>
         <v>(1.192)</v>
       </c>
-      <c r="F49" s="154"/>
-      <c r="G49" s="154"/>
+      <c r="F49" s="152"/>
+      <c r="G49" s="152"/>
     </row>
     <row r="50" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B50" s="156" t="s">
+      <c r="B50" s="154" t="s">
         <v>355</v>
       </c>
       <c r="C50" s="17" t="str">
@@ -20128,17 +21201,17 @@
         <f>"0.397"</f>
         <v>0.397</v>
       </c>
-      <c r="F50" s="154" t="str">
+      <c r="F50" s="152" t="str">
         <f>"-0.048"</f>
         <v>-0.048</v>
       </c>
-      <c r="G50" s="154" t="str">
+      <c r="G50" s="152" t="str">
         <f>"0.991"</f>
         <v>0.991</v>
       </c>
     </row>
     <row r="51" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B51" s="156"/>
+      <c r="B51" s="154"/>
       <c r="C51" s="17" t="str">
         <f>"(0.181)"</f>
         <v>(0.181)</v>
@@ -20151,11 +21224,11 @@
         <f>"(0.188)"</f>
         <v>(0.188)</v>
       </c>
-      <c r="F51" s="154"/>
-      <c r="G51" s="154"/>
+      <c r="F51" s="152"/>
+      <c r="G51" s="152"/>
     </row>
     <row r="52" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B52" s="156" t="s">
+      <c r="B52" s="154" t="s">
         <v>333</v>
       </c>
       <c r="C52" s="17" t="str">
@@ -20170,17 +21243,17 @@
         <f>"0.536"</f>
         <v>0.536</v>
       </c>
-      <c r="F52" s="154" t="str">
+      <c r="F52" s="152" t="str">
         <f>"-3.000"</f>
         <v>-3.000</v>
       </c>
-      <c r="G52" s="154" t="str">
+      <c r="G52" s="152" t="str">
         <f>"14.000"</f>
         <v>14.000</v>
       </c>
     </row>
     <row r="53" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B53" s="156"/>
+      <c r="B53" s="154"/>
       <c r="C53" s="17" t="str">
         <f>"(1.096)"</f>
         <v>(1.096)</v>
@@ -20193,11 +21266,11 @@
         <f>"(1.140)"</f>
         <v>(1.140)</v>
       </c>
-      <c r="F53" s="154"/>
-      <c r="G53" s="154"/>
+      <c r="F53" s="152"/>
+      <c r="G53" s="152"/>
     </row>
     <row r="54" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B54" s="156" t="s">
+      <c r="B54" s="154" t="s">
         <v>357</v>
       </c>
       <c r="C54" s="17" t="str">
@@ -20212,17 +21285,17 @@
         <f>"0.000"</f>
         <v>0.000</v>
       </c>
-      <c r="F54" s="154" t="str">
+      <c r="F54" s="152" t="str">
         <f>"0.000"</f>
         <v>0.000</v>
       </c>
-      <c r="G54" s="154" t="str">
+      <c r="G54" s="152" t="str">
         <f>"6.977"</f>
         <v>6.977</v>
       </c>
     </row>
     <row r="55" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B55" s="156"/>
+      <c r="B55" s="154"/>
       <c r="C55" s="17" t="str">
         <f>"(2.864)"</f>
         <v>(2.864)</v>
@@ -20235,11 +21308,11 @@
         <f>"(0.000)"</f>
         <v>(0.000)</v>
       </c>
-      <c r="F55" s="154"/>
-      <c r="G55" s="154"/>
+      <c r="F55" s="152"/>
+      <c r="G55" s="152"/>
     </row>
     <row r="56" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B56" s="156" t="s">
+      <c r="B56" s="154" t="s">
         <v>359</v>
       </c>
       <c r="C56" s="17" t="str">
@@ -20254,17 +21327,17 @@
         <f>"0.000"</f>
         <v>0.000</v>
       </c>
-      <c r="F56" s="154" t="str">
+      <c r="F56" s="152" t="str">
         <f>"0.000"</f>
         <v>0.000</v>
       </c>
-      <c r="G56" s="154" t="str">
+      <c r="G56" s="152" t="str">
         <f>"0.891"</f>
         <v>0.891</v>
       </c>
     </row>
     <row r="57" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B57" s="156"/>
+      <c r="B57" s="154"/>
       <c r="C57" s="17" t="str">
         <f>"(0.297)"</f>
         <v>(0.297)</v>
@@ -20277,11 +21350,11 @@
         <f>"(0.000)"</f>
         <v>(0.000)</v>
       </c>
-      <c r="F57" s="154"/>
-      <c r="G57" s="154"/>
+      <c r="F57" s="152"/>
+      <c r="G57" s="152"/>
     </row>
     <row r="58" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B58" s="156" t="s">
+      <c r="B58" s="154" t="s">
         <v>358</v>
       </c>
       <c r="C58" s="17" t="str">
@@ -20296,17 +21369,17 @@
         <f>"3.443"</f>
         <v>3.443</v>
       </c>
-      <c r="F58" s="154" t="str">
+      <c r="F58" s="152" t="str">
         <f>"0.000"</f>
         <v>0.000</v>
       </c>
-      <c r="G58" s="154" t="str">
+      <c r="G58" s="152" t="str">
         <f>"7.912"</f>
         <v>7.912</v>
       </c>
     </row>
     <row r="59" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B59" s="156"/>
+      <c r="B59" s="154"/>
       <c r="C59" s="17" t="str">
         <f>"(1.489)"</f>
         <v>(1.489)</v>
@@ -20319,11 +21392,11 @@
         <f>"(1.338)"</f>
         <v>(1.338)</v>
       </c>
-      <c r="F59" s="154"/>
-      <c r="G59" s="154"/>
+      <c r="F59" s="152"/>
+      <c r="G59" s="152"/>
     </row>
     <row r="60" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B60" s="156" t="s">
+      <c r="B60" s="154" t="s">
         <v>356</v>
       </c>
       <c r="C60" s="17" t="str">
@@ -20338,17 +21411,17 @@
         <f>"0.445"</f>
         <v>0.445</v>
       </c>
-      <c r="F60" s="154" t="str">
+      <c r="F60" s="152" t="str">
         <f>"-0.090"</f>
         <v>-0.090</v>
       </c>
-      <c r="G60" s="154" t="str">
+      <c r="G60" s="152" t="str">
         <f>"0.911"</f>
         <v>0.911</v>
       </c>
     </row>
     <row r="61" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B61" s="157"/>
+      <c r="B61" s="155"/>
       <c r="C61" s="18" t="str">
         <f>"(0.177)"</f>
         <v>(0.177)</v>
@@ -20361,8 +21434,8 @@
         <f>"(0.187)"</f>
         <v>(0.187)</v>
       </c>
-      <c r="F61" s="155"/>
-      <c r="G61" s="155"/>
+      <c r="F61" s="153"/>
+      <c r="G61" s="153"/>
     </row>
   </sheetData>
   <mergeCells count="51">
@@ -20423,7 +21496,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{985AFA23-5DA6-564F-ADE6-19391318ACD9}">
   <dimension ref="B1:X90"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -20452,18 +21525,18 @@
   <sheetData>
     <row r="1" spans="2:12" hidden="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:12" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="164" t="s">
+      <c r="B2" s="162" t="s">
         <v>179</v>
       </c>
       <c r="C2" s="3"/>
-      <c r="D2" s="166" t="s">
+      <c r="D2" s="164" t="s">
         <v>0</v>
       </c>
-      <c r="E2" s="166"/>
-      <c r="F2" s="166" t="s">
+      <c r="E2" s="164"/>
+      <c r="F2" s="164" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="166"/>
+      <c r="G2" s="164"/>
       <c r="H2" s="8" t="s">
         <v>124</v>
       </c>
@@ -20473,14 +21546,14 @@
       <c r="J2" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="K2" s="166" t="s">
+      <c r="K2" s="164" t="s">
         <v>2</v>
       </c>
-      <c r="L2" s="166"/>
+      <c r="L2" s="164"/>
     </row>
     <row r="3" spans="2:12" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="165"/>
-      <c r="C3" s="162" t="s">
+      <c r="B3" s="163"/>
+      <c r="C3" s="160" t="s">
         <v>5</v>
       </c>
       <c r="D3" s="4" t="s">
@@ -20512,8 +21585,8 @@
       </c>
     </row>
     <row r="4" spans="2:12" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="165"/>
-      <c r="C4" s="163"/>
+      <c r="B4" s="163"/>
+      <c r="C4" s="161"/>
       <c r="D4" s="4" t="s">
         <v>16</v>
       </c>
@@ -20543,8 +21616,8 @@
       </c>
     </row>
     <row r="5" spans="2:12" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="165"/>
-      <c r="C5" s="162" t="s">
+      <c r="B5" s="163"/>
+      <c r="C5" s="160" t="s">
         <v>11</v>
       </c>
       <c r="D5" s="4"/>
@@ -20570,8 +21643,8 @@
       </c>
     </row>
     <row r="6" spans="2:12" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="165"/>
-      <c r="C6" s="163"/>
+      <c r="B6" s="163"/>
+      <c r="C6" s="161"/>
       <c r="D6" s="4"/>
       <c r="E6" s="4" t="s">
         <v>26</v>
@@ -20595,8 +21668,8 @@
       </c>
     </row>
     <row r="7" spans="2:12" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="165"/>
-      <c r="C7" s="162" t="s">
+      <c r="B7" s="163"/>
+      <c r="C7" s="160" t="s">
         <v>13</v>
       </c>
       <c r="D7" s="4"/>
@@ -20622,8 +21695,8 @@
       </c>
     </row>
     <row r="8" spans="2:12" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="165"/>
-      <c r="C8" s="163"/>
+      <c r="B8" s="163"/>
+      <c r="C8" s="161"/>
       <c r="D8" s="4"/>
       <c r="E8" s="4" t="s">
         <v>33</v>
@@ -20647,7 +21720,7 @@
       </c>
     </row>
     <row r="9" spans="2:12" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="165"/>
+      <c r="B9" s="163"/>
       <c r="C9" s="3" t="s">
         <v>14</v>
       </c>
@@ -20681,18 +21754,18 @@
     </row>
     <row r="10" spans="2:12" hidden="1" x14ac:dyDescent="0.2"/>
     <row r="11" spans="2:12" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="164" t="s">
+      <c r="B11" s="162" t="s">
         <v>180</v>
       </c>
       <c r="C11" s="3"/>
-      <c r="D11" s="166" t="s">
+      <c r="D11" s="164" t="s">
         <v>3</v>
       </c>
-      <c r="E11" s="166"/>
-      <c r="F11" s="166" t="s">
+      <c r="E11" s="164"/>
+      <c r="F11" s="164" t="s">
         <v>4</v>
       </c>
-      <c r="G11" s="166"/>
+      <c r="G11" s="164"/>
       <c r="H11" s="8" t="s">
         <v>124</v>
       </c>
@@ -20702,14 +21775,14 @@
       <c r="J11" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="K11" s="166" t="s">
+      <c r="K11" s="164" t="s">
         <v>127</v>
       </c>
-      <c r="L11" s="166"/>
+      <c r="L11" s="164"/>
     </row>
     <row r="12" spans="2:12" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="165"/>
-      <c r="C12" s="162" t="s">
+      <c r="B12" s="163"/>
+      <c r="C12" s="160" t="s">
         <v>5</v>
       </c>
       <c r="D12" s="4" t="s">
@@ -20741,8 +21814,8 @@
       </c>
     </row>
     <row r="13" spans="2:12" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="165"/>
-      <c r="C13" s="163"/>
+      <c r="B13" s="163"/>
+      <c r="C13" s="161"/>
       <c r="D13" s="4" t="s">
         <v>29</v>
       </c>
@@ -20772,8 +21845,8 @@
       </c>
     </row>
     <row r="14" spans="2:12" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="165"/>
-      <c r="C14" s="162" t="s">
+      <c r="B14" s="163"/>
+      <c r="C14" s="160" t="s">
         <v>186</v>
       </c>
       <c r="D14" s="4"/>
@@ -20799,8 +21872,8 @@
       </c>
     </row>
     <row r="15" spans="2:12" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="165"/>
-      <c r="C15" s="163"/>
+      <c r="B15" s="163"/>
+      <c r="C15" s="161"/>
       <c r="D15" s="4"/>
       <c r="E15" s="4" t="s">
         <v>211</v>
@@ -20824,8 +21897,8 @@
       </c>
     </row>
     <row r="16" spans="2:12" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="165"/>
-      <c r="C16" s="162" t="s">
+      <c r="B16" s="163"/>
+      <c r="C16" s="160" t="s">
         <v>228</v>
       </c>
       <c r="D16" s="4"/>
@@ -20851,8 +21924,8 @@
       </c>
     </row>
     <row r="17" spans="2:24" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="165"/>
-      <c r="C17" s="163"/>
+      <c r="B17" s="163"/>
+      <c r="C17" s="161"/>
       <c r="D17" s="4"/>
       <c r="E17" s="4" t="s">
         <v>215</v>
@@ -20876,8 +21949,8 @@
       </c>
     </row>
     <row r="18" spans="2:24" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="165"/>
-      <c r="C18" s="162" t="s">
+      <c r="B18" s="163"/>
+      <c r="C18" s="160" t="s">
         <v>134</v>
       </c>
       <c r="D18" s="4"/>
@@ -20903,8 +21976,8 @@
       </c>
     </row>
     <row r="19" spans="2:24" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="165"/>
-      <c r="C19" s="163"/>
+      <c r="B19" s="163"/>
+      <c r="C19" s="161"/>
       <c r="D19" s="4"/>
       <c r="E19" s="4" t="s">
         <v>222</v>
@@ -20928,8 +22001,8 @@
       </c>
     </row>
     <row r="20" spans="2:24" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="165"/>
-      <c r="C20" s="162" t="s">
+      <c r="B20" s="163"/>
+      <c r="C20" s="160" t="s">
         <v>139</v>
       </c>
       <c r="D20" s="4"/>
@@ -20955,8 +22028,8 @@
       </c>
     </row>
     <row r="21" spans="2:24" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="165"/>
-      <c r="C21" s="163"/>
+      <c r="B21" s="163"/>
+      <c r="C21" s="161"/>
       <c r="D21" s="4"/>
       <c r="E21" s="4" t="s">
         <v>143</v>
@@ -20980,7 +22053,7 @@
       </c>
     </row>
     <row r="22" spans="2:24" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="165"/>
+      <c r="B22" s="163"/>
       <c r="C22" s="3" t="s">
         <v>14</v>
       </c>
@@ -21039,18 +22112,18 @@
       <c r="X24" s="11"/>
     </row>
     <row r="25" spans="2:24" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="164" t="s">
+      <c r="B25" s="162" t="s">
         <v>177</v>
       </c>
       <c r="C25" s="3"/>
-      <c r="D25" s="166" t="s">
+      <c r="D25" s="164" t="s">
         <v>0</v>
       </c>
-      <c r="E25" s="166"/>
-      <c r="F25" s="166" t="s">
+      <c r="E25" s="164"/>
+      <c r="F25" s="164" t="s">
         <v>1</v>
       </c>
-      <c r="G25" s="166"/>
+      <c r="G25" s="164"/>
       <c r="H25" s="8" t="s">
         <v>124</v>
       </c>
@@ -21060,10 +22133,10 @@
       <c r="J25" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="K25" s="166" t="s">
+      <c r="K25" s="164" t="s">
         <v>2</v>
       </c>
-      <c r="L25" s="166"/>
+      <c r="L25" s="164"/>
       <c r="N25" s="10"/>
       <c r="P25" s="2"/>
       <c r="Q25" s="2"/>
@@ -21076,8 +22149,8 @@
       <c r="X25" s="11"/>
     </row>
     <row r="26" spans="2:24" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="165"/>
-      <c r="C26" s="162" t="s">
+      <c r="B26" s="163"/>
+      <c r="C26" s="160" t="s">
         <v>5</v>
       </c>
       <c r="D26" s="4" t="s">
@@ -21119,8 +22192,8 @@
       <c r="X26" s="11"/>
     </row>
     <row r="27" spans="2:24" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B27" s="165"/>
-      <c r="C27" s="163"/>
+      <c r="B27" s="163"/>
+      <c r="C27" s="161"/>
       <c r="D27" s="4" t="s">
         <v>16</v>
       </c>
@@ -21160,8 +22233,8 @@
       <c r="X27" s="11"/>
     </row>
     <row r="28" spans="2:24" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B28" s="165"/>
-      <c r="C28" s="162" t="s">
+      <c r="B28" s="163"/>
+      <c r="C28" s="160" t="s">
         <v>11</v>
       </c>
       <c r="D28" s="4"/>
@@ -21197,8 +22270,8 @@
       <c r="X28" s="11"/>
     </row>
     <row r="29" spans="2:24" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B29" s="165"/>
-      <c r="C29" s="163"/>
+      <c r="B29" s="163"/>
+      <c r="C29" s="161"/>
       <c r="D29" s="4"/>
       <c r="E29" s="4" t="s">
         <v>26</v>
@@ -21232,8 +22305,8 @@
       <c r="X29" s="11"/>
     </row>
     <row r="30" spans="2:24" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B30" s="165"/>
-      <c r="C30" s="162" t="s">
+      <c r="B30" s="163"/>
+      <c r="C30" s="160" t="s">
         <v>13</v>
       </c>
       <c r="D30" s="4"/>
@@ -21269,8 +22342,8 @@
       <c r="X30" s="11"/>
     </row>
     <row r="31" spans="2:24" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B31" s="165"/>
-      <c r="C31" s="163"/>
+      <c r="B31" s="163"/>
+      <c r="C31" s="161"/>
       <c r="D31" s="4"/>
       <c r="E31" s="4" t="s">
         <v>33</v>
@@ -21304,7 +22377,7 @@
       <c r="X31" s="11"/>
     </row>
     <row r="32" spans="2:24" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B32" s="165"/>
+      <c r="B32" s="163"/>
       <c r="C32" s="3" t="s">
         <v>14</v>
       </c>
@@ -21359,18 +22432,18 @@
       <c r="X33" s="11"/>
     </row>
     <row r="34" spans="2:24" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B34" s="164" t="s">
+      <c r="B34" s="162" t="s">
         <v>178</v>
       </c>
       <c r="C34" s="3"/>
-      <c r="D34" s="166" t="s">
+      <c r="D34" s="164" t="s">
         <v>3</v>
       </c>
-      <c r="E34" s="166"/>
-      <c r="F34" s="166" t="s">
+      <c r="E34" s="164"/>
+      <c r="F34" s="164" t="s">
         <v>4</v>
       </c>
-      <c r="G34" s="166"/>
+      <c r="G34" s="164"/>
       <c r="H34" s="8" t="s">
         <v>124</v>
       </c>
@@ -21380,10 +22453,10 @@
       <c r="J34" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="K34" s="166" t="s">
+      <c r="K34" s="164" t="s">
         <v>127</v>
       </c>
-      <c r="L34" s="166"/>
+      <c r="L34" s="164"/>
       <c r="N34" s="10"/>
       <c r="P34" s="2"/>
       <c r="Q34" s="2"/>
@@ -21396,8 +22469,8 @@
       <c r="X34" s="11"/>
     </row>
     <row r="35" spans="2:24" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B35" s="165"/>
-      <c r="C35" s="162" t="s">
+      <c r="B35" s="163"/>
+      <c r="C35" s="160" t="s">
         <v>5</v>
       </c>
       <c r="D35" s="4" t="s">
@@ -21439,8 +22512,8 @@
       <c r="X35" s="11"/>
     </row>
     <row r="36" spans="2:24" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B36" s="165"/>
-      <c r="C36" s="163"/>
+      <c r="B36" s="163"/>
+      <c r="C36" s="161"/>
       <c r="D36" s="4" t="s">
         <v>29</v>
       </c>
@@ -21480,8 +22553,8 @@
       <c r="X36" s="11"/>
     </row>
     <row r="37" spans="2:24" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B37" s="165"/>
-      <c r="C37" s="162" t="s">
+      <c r="B37" s="163"/>
+      <c r="C37" s="160" t="s">
         <v>186</v>
       </c>
       <c r="D37" s="4"/>
@@ -21517,8 +22590,8 @@
       <c r="X37" s="11"/>
     </row>
     <row r="38" spans="2:24" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B38" s="165"/>
-      <c r="C38" s="163"/>
+      <c r="B38" s="163"/>
+      <c r="C38" s="161"/>
       <c r="D38" s="4"/>
       <c r="E38" s="4" t="s">
         <v>211</v>
@@ -21552,8 +22625,8 @@
       <c r="X38" s="11"/>
     </row>
     <row r="39" spans="2:24" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="165"/>
-      <c r="C39" s="162" t="s">
+      <c r="B39" s="163"/>
+      <c r="C39" s="160" t="s">
         <v>228</v>
       </c>
       <c r="D39" s="4"/>
@@ -21589,8 +22662,8 @@
       <c r="X39" s="11"/>
     </row>
     <row r="40" spans="2:24" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B40" s="165"/>
-      <c r="C40" s="163"/>
+      <c r="B40" s="163"/>
+      <c r="C40" s="161"/>
       <c r="D40" s="4"/>
       <c r="E40" s="4" t="s">
         <v>215</v>
@@ -21624,8 +22697,8 @@
       <c r="X40" s="11"/>
     </row>
     <row r="41" spans="2:24" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B41" s="165"/>
-      <c r="C41" s="162" t="s">
+      <c r="B41" s="163"/>
+      <c r="C41" s="160" t="s">
         <v>134</v>
       </c>
       <c r="D41" s="4"/>
@@ -21661,8 +22734,8 @@
       <c r="X41" s="11"/>
     </row>
     <row r="42" spans="2:24" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B42" s="165"/>
-      <c r="C42" s="163"/>
+      <c r="B42" s="163"/>
+      <c r="C42" s="161"/>
       <c r="D42" s="4"/>
       <c r="E42" s="4" t="s">
         <v>222</v>
@@ -21696,8 +22769,8 @@
       <c r="X42" s="11"/>
     </row>
     <row r="43" spans="2:24" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B43" s="165"/>
-      <c r="C43" s="162" t="s">
+      <c r="B43" s="163"/>
+      <c r="C43" s="160" t="s">
         <v>139</v>
       </c>
       <c r="D43" s="4"/>
@@ -21733,8 +22806,8 @@
       <c r="X43" s="11"/>
     </row>
     <row r="44" spans="2:24" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B44" s="165"/>
-      <c r="C44" s="163"/>
+      <c r="B44" s="163"/>
+      <c r="C44" s="161"/>
       <c r="D44" s="4"/>
       <c r="E44" s="4" t="s">
         <v>143</v>
@@ -21768,7 +22841,7 @@
       <c r="X44" s="11"/>
     </row>
     <row r="45" spans="2:24" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B45" s="165"/>
+      <c r="B45" s="163"/>
       <c r="C45" s="3" t="s">
         <v>14</v>
       </c>
@@ -21812,18 +22885,18 @@
     </row>
     <row r="46" spans="2:24" hidden="1" x14ac:dyDescent="0.2"/>
     <row r="47" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B47" s="164" t="s">
+      <c r="B47" s="162" t="s">
         <v>130</v>
       </c>
       <c r="C47" s="3"/>
-      <c r="D47" s="166" t="s">
+      <c r="D47" s="164" t="s">
         <v>0</v>
       </c>
-      <c r="E47" s="166"/>
-      <c r="F47" s="166" t="s">
+      <c r="E47" s="164"/>
+      <c r="F47" s="164" t="s">
         <v>1</v>
       </c>
-      <c r="G47" s="166"/>
+      <c r="G47" s="164"/>
       <c r="H47" s="24" t="s">
         <v>124</v>
       </c>
@@ -21833,14 +22906,14 @@
       <c r="J47" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="K47" s="167" t="s">
+      <c r="K47" s="165" t="s">
         <v>2</v>
       </c>
-      <c r="L47" s="167"/>
+      <c r="L47" s="165"/>
     </row>
     <row r="48" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B48" s="165"/>
-      <c r="C48" s="162" t="s">
+      <c r="B48" s="163"/>
+      <c r="C48" s="160" t="s">
         <v>5</v>
       </c>
       <c r="D48" s="7" t="s">
@@ -21872,8 +22945,8 @@
       </c>
     </row>
     <row r="49" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B49" s="165"/>
-      <c r="C49" s="163"/>
+      <c r="B49" s="163"/>
+      <c r="C49" s="161"/>
       <c r="D49" s="4" t="s">
         <v>16</v>
       </c>
@@ -21903,8 +22976,8 @@
       </c>
     </row>
     <row r="50" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B50" s="165"/>
-      <c r="C50" s="162" t="s">
+      <c r="B50" s="163"/>
+      <c r="C50" s="160" t="s">
         <v>11</v>
       </c>
       <c r="D50" s="4"/>
@@ -21930,8 +23003,8 @@
       </c>
     </row>
     <row r="51" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B51" s="165"/>
-      <c r="C51" s="163"/>
+      <c r="B51" s="163"/>
+      <c r="C51" s="161"/>
       <c r="D51" s="4"/>
       <c r="E51" s="4" t="s">
         <v>26</v>
@@ -21955,8 +23028,8 @@
       </c>
     </row>
     <row r="52" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B52" s="165"/>
-      <c r="C52" s="162" t="s">
+      <c r="B52" s="163"/>
+      <c r="C52" s="160" t="s">
         <v>79</v>
       </c>
       <c r="D52" s="4"/>
@@ -21982,8 +23055,8 @@
       </c>
     </row>
     <row r="53" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B53" s="165"/>
-      <c r="C53" s="163"/>
+      <c r="B53" s="163"/>
+      <c r="C53" s="161"/>
       <c r="D53" s="4"/>
       <c r="E53" s="4" t="s">
         <v>85</v>
@@ -22007,7 +23080,7 @@
       </c>
     </row>
     <row r="54" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B54" s="165"/>
+      <c r="B54" s="163"/>
       <c r="C54" s="3" t="s">
         <v>14</v>
       </c>
@@ -22040,18 +23113,18 @@
       </c>
     </row>
     <row r="56" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B56" s="164" t="s">
+      <c r="B56" s="162" t="s">
         <v>131</v>
       </c>
       <c r="C56" s="3"/>
-      <c r="D56" s="166" t="s">
+      <c r="D56" s="164" t="s">
         <v>3</v>
       </c>
-      <c r="E56" s="166"/>
-      <c r="F56" s="166" t="s">
+      <c r="E56" s="164"/>
+      <c r="F56" s="164" t="s">
         <v>4</v>
       </c>
-      <c r="G56" s="166"/>
+      <c r="G56" s="164"/>
       <c r="H56" s="8" t="s">
         <v>124</v>
       </c>
@@ -22061,14 +23134,14 @@
       <c r="J56" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="K56" s="166" t="s">
+      <c r="K56" s="164" t="s">
         <v>127</v>
       </c>
-      <c r="L56" s="166"/>
+      <c r="L56" s="164"/>
     </row>
     <row r="57" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B57" s="165"/>
-      <c r="C57" s="162" t="s">
+      <c r="B57" s="163"/>
+      <c r="C57" s="160" t="s">
         <v>5</v>
       </c>
       <c r="D57" s="7" t="s">
@@ -22100,8 +23173,8 @@
       </c>
     </row>
     <row r="58" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B58" s="165"/>
-      <c r="C58" s="163"/>
+      <c r="B58" s="163"/>
+      <c r="C58" s="161"/>
       <c r="D58" s="4" t="s">
         <v>29</v>
       </c>
@@ -22131,8 +23204,8 @@
       </c>
     </row>
     <row r="59" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B59" s="165"/>
-      <c r="C59" s="162" t="s">
+      <c r="B59" s="163"/>
+      <c r="C59" s="160" t="s">
         <v>186</v>
       </c>
       <c r="D59" s="4"/>
@@ -22158,8 +23231,8 @@
       </c>
     </row>
     <row r="60" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B60" s="165"/>
-      <c r="C60" s="163"/>
+      <c r="B60" s="163"/>
+      <c r="C60" s="161"/>
       <c r="D60" s="4"/>
       <c r="E60" s="4" t="s">
         <v>213</v>
@@ -22183,8 +23256,8 @@
       </c>
     </row>
     <row r="61" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B61" s="165"/>
-      <c r="C61" s="162" t="s">
+      <c r="B61" s="163"/>
+      <c r="C61" s="160" t="s">
         <v>229</v>
       </c>
       <c r="D61" s="4"/>
@@ -22210,8 +23283,8 @@
       </c>
     </row>
     <row r="62" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B62" s="165"/>
-      <c r="C62" s="163"/>
+      <c r="B62" s="163"/>
+      <c r="C62" s="161"/>
       <c r="D62" s="4"/>
       <c r="E62" s="4" t="s">
         <v>163</v>
@@ -22235,8 +23308,8 @@
       </c>
     </row>
     <row r="63" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B63" s="165"/>
-      <c r="C63" s="162" t="s">
+      <c r="B63" s="163"/>
+      <c r="C63" s="160" t="s">
         <v>134</v>
       </c>
       <c r="D63" s="4"/>
@@ -22262,8 +23335,8 @@
       </c>
     </row>
     <row r="64" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B64" s="165"/>
-      <c r="C64" s="163"/>
+      <c r="B64" s="163"/>
+      <c r="C64" s="161"/>
       <c r="D64" s="4"/>
       <c r="E64" s="4" t="s">
         <v>251</v>
@@ -22287,8 +23360,8 @@
       </c>
     </row>
     <row r="65" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B65" s="165"/>
-      <c r="C65" s="162" t="s">
+      <c r="B65" s="163"/>
+      <c r="C65" s="160" t="s">
         <v>149</v>
       </c>
       <c r="D65" s="4"/>
@@ -22314,8 +23387,8 @@
       </c>
     </row>
     <row r="66" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B66" s="165"/>
-      <c r="C66" s="163"/>
+      <c r="B66" s="163"/>
+      <c r="C66" s="161"/>
       <c r="D66" s="4"/>
       <c r="E66" s="4" t="s">
         <v>210</v>
@@ -22339,7 +23412,7 @@
       </c>
     </row>
     <row r="67" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B67" s="165"/>
+      <c r="B67" s="163"/>
       <c r="C67" s="3" t="s">
         <v>14</v>
       </c>
@@ -22372,18 +23445,18 @@
       </c>
     </row>
     <row r="69" spans="2:12" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B69" s="164" t="s">
+      <c r="B69" s="162" t="s">
         <v>132</v>
       </c>
       <c r="C69" s="3"/>
-      <c r="D69" s="166" t="s">
+      <c r="D69" s="164" t="s">
         <v>0</v>
       </c>
-      <c r="E69" s="166"/>
-      <c r="F69" s="166" t="s">
+      <c r="E69" s="164"/>
+      <c r="F69" s="164" t="s">
         <v>1</v>
       </c>
-      <c r="G69" s="166"/>
+      <c r="G69" s="164"/>
       <c r="H69" s="8" t="s">
         <v>124</v>
       </c>
@@ -22393,14 +23466,14 @@
       <c r="J69" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="K69" s="166" t="s">
+      <c r="K69" s="164" t="s">
         <v>2</v>
       </c>
-      <c r="L69" s="166"/>
+      <c r="L69" s="164"/>
     </row>
     <row r="70" spans="2:12" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B70" s="165"/>
-      <c r="C70" s="162" t="s">
+      <c r="B70" s="163"/>
+      <c r="C70" s="160" t="s">
         <v>5</v>
       </c>
       <c r="D70" s="4" t="s">
@@ -22432,8 +23505,8 @@
       </c>
     </row>
     <row r="71" spans="2:12" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B71" s="165"/>
-      <c r="C71" s="163"/>
+      <c r="B71" s="163"/>
+      <c r="C71" s="161"/>
       <c r="D71" s="4" t="s">
         <v>16</v>
       </c>
@@ -22463,8 +23536,8 @@
       </c>
     </row>
     <row r="72" spans="2:12" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B72" s="165"/>
-      <c r="C72" s="162" t="s">
+      <c r="B72" s="163"/>
+      <c r="C72" s="160" t="s">
         <v>11</v>
       </c>
       <c r="D72" s="4"/>
@@ -22490,8 +23563,8 @@
       </c>
     </row>
     <row r="73" spans="2:12" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B73" s="165"/>
-      <c r="C73" s="163"/>
+      <c r="B73" s="163"/>
+      <c r="C73" s="161"/>
       <c r="D73" s="4"/>
       <c r="E73" s="4" t="s">
         <v>26</v>
@@ -22515,8 +23588,8 @@
       </c>
     </row>
     <row r="74" spans="2:12" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B74" s="165"/>
-      <c r="C74" s="162" t="s">
+      <c r="B74" s="163"/>
+      <c r="C74" s="160" t="s">
         <v>111</v>
       </c>
       <c r="D74" s="4"/>
@@ -22542,8 +23615,8 @@
       </c>
     </row>
     <row r="75" spans="2:12" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B75" s="165"/>
-      <c r="C75" s="163"/>
+      <c r="B75" s="163"/>
+      <c r="C75" s="161"/>
       <c r="D75" s="4"/>
       <c r="E75" s="4" t="s">
         <v>116</v>
@@ -22567,7 +23640,7 @@
       </c>
     </row>
     <row r="76" spans="2:12" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B76" s="165"/>
+      <c r="B76" s="163"/>
       <c r="C76" s="3" t="s">
         <v>14</v>
       </c>
@@ -22601,18 +23674,18 @@
     </row>
     <row r="77" spans="2:12" hidden="1" x14ac:dyDescent="0.2"/>
     <row r="78" spans="2:12" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B78" s="164" t="s">
+      <c r="B78" s="162" t="s">
         <v>133</v>
       </c>
       <c r="C78" s="3"/>
-      <c r="D78" s="166" t="s">
+      <c r="D78" s="164" t="s">
         <v>3</v>
       </c>
-      <c r="E78" s="166"/>
-      <c r="F78" s="166" t="s">
+      <c r="E78" s="164"/>
+      <c r="F78" s="164" t="s">
         <v>4</v>
       </c>
-      <c r="G78" s="166"/>
+      <c r="G78" s="164"/>
       <c r="H78" s="8" t="s">
         <v>124</v>
       </c>
@@ -22622,14 +23695,14 @@
       <c r="J78" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="K78" s="166" t="s">
+      <c r="K78" s="164" t="s">
         <v>127</v>
       </c>
-      <c r="L78" s="166"/>
+      <c r="L78" s="164"/>
     </row>
     <row r="79" spans="2:12" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B79" s="165"/>
-      <c r="C79" s="162" t="s">
+      <c r="B79" s="163"/>
+      <c r="C79" s="160" t="s">
         <v>5</v>
       </c>
       <c r="D79" s="4" t="s">
@@ -22661,8 +23734,8 @@
       </c>
     </row>
     <row r="80" spans="2:12" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B80" s="165"/>
-      <c r="C80" s="163"/>
+      <c r="B80" s="163"/>
+      <c r="C80" s="161"/>
       <c r="D80" s="4" t="s">
         <v>29</v>
       </c>
@@ -22692,8 +23765,8 @@
       </c>
     </row>
     <row r="81" spans="2:12" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B81" s="165"/>
-      <c r="C81" s="162" t="s">
+      <c r="B81" s="163"/>
+      <c r="C81" s="160" t="s">
         <v>186</v>
       </c>
       <c r="D81" s="4"/>
@@ -22719,8 +23792,8 @@
       </c>
     </row>
     <row r="82" spans="2:12" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B82" s="165"/>
-      <c r="C82" s="163"/>
+      <c r="B82" s="163"/>
+      <c r="C82" s="161"/>
       <c r="D82" s="4"/>
       <c r="E82" s="4" t="s">
         <v>16</v>
@@ -22744,8 +23817,8 @@
       </c>
     </row>
     <row r="83" spans="2:12" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B83" s="165"/>
-      <c r="C83" s="162" t="s">
+      <c r="B83" s="163"/>
+      <c r="C83" s="160" t="s">
         <v>230</v>
       </c>
       <c r="D83" s="4"/>
@@ -22771,8 +23844,8 @@
       </c>
     </row>
     <row r="84" spans="2:12" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B84" s="165"/>
-      <c r="C84" s="163"/>
+      <c r="B84" s="163"/>
+      <c r="C84" s="161"/>
       <c r="D84" s="4"/>
       <c r="E84" s="4" t="s">
         <v>21</v>
@@ -22796,8 +23869,8 @@
       </c>
     </row>
     <row r="85" spans="2:12" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B85" s="165"/>
-      <c r="C85" s="162" t="s">
+      <c r="B85" s="163"/>
+      <c r="C85" s="160" t="s">
         <v>134</v>
       </c>
       <c r="D85" s="4"/>
@@ -22823,8 +23896,8 @@
       </c>
     </row>
     <row r="86" spans="2:12" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B86" s="165"/>
-      <c r="C86" s="163"/>
+      <c r="B86" s="163"/>
+      <c r="C86" s="161"/>
       <c r="D86" s="4"/>
       <c r="E86" s="4" t="s">
         <v>251</v>
@@ -22848,8 +23921,8 @@
       </c>
     </row>
     <row r="87" spans="2:12" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B87" s="165"/>
-      <c r="C87" s="162" t="s">
+      <c r="B87" s="163"/>
+      <c r="C87" s="160" t="s">
         <v>141</v>
       </c>
       <c r="D87" s="4"/>
@@ -22875,8 +23948,8 @@
       </c>
     </row>
     <row r="88" spans="2:12" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B88" s="165"/>
-      <c r="C88" s="163"/>
+      <c r="B88" s="163"/>
+      <c r="C88" s="161"/>
       <c r="D88" s="4"/>
       <c r="E88" s="4" t="s">
         <v>258</v>
@@ -22900,7 +23973,7 @@
       </c>
     </row>
     <row r="89" spans="2:12" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B89" s="165"/>
+      <c r="B89" s="163"/>
       <c r="C89" s="3" t="s">
         <v>14</v>
       </c>
@@ -23002,756 +24075,4 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C46079C1-F4F3-4E3A-8CE8-2113D4F28B6B}">
-  <dimension ref="A1:J15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="14.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.1640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.6640625" customWidth="1"/>
-    <col min="4" max="4" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.83203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.1640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.6640625" customWidth="1"/>
-    <col min="10" max="10" width="9.5" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B1" t="s">
-        <v>376</v>
-      </c>
-      <c r="H1" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>367</v>
-      </c>
-      <c r="B2">
-        <v>0.34200000000000003</v>
-      </c>
-      <c r="G2" t="s">
-        <v>367</v>
-      </c>
-      <c r="H2">
-        <v>5.4610000000000003</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>368</v>
-      </c>
-      <c r="B3">
-        <v>-1.6E-2</v>
-      </c>
-      <c r="G3" t="s">
-        <v>368</v>
-      </c>
-      <c r="H3">
-        <v>-0.188</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>369</v>
-      </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-      <c r="G4" t="s">
-        <v>369</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>370</v>
-      </c>
-      <c r="B5">
-        <v>0.747</v>
-      </c>
-      <c r="G5" t="s">
-        <v>370</v>
-      </c>
-      <c r="H5">
-        <v>1.349</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>371</v>
-      </c>
-      <c r="B6">
-        <v>-6.6000000000000003E-2</v>
-      </c>
-      <c r="G6" t="s">
-        <v>371</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>372</v>
-      </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
-      <c r="G7" t="s">
-        <v>372</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>375</v>
-      </c>
-      <c r="B10" t="s">
-        <v>366</v>
-      </c>
-      <c r="C10" t="s">
-        <v>374</v>
-      </c>
-      <c r="D10" t="s">
-        <v>373</v>
-      </c>
-      <c r="G10" t="s">
-        <v>375</v>
-      </c>
-      <c r="H10" t="s">
-        <v>366</v>
-      </c>
-      <c r="I10" t="s">
-        <v>374</v>
-      </c>
-      <c r="J10" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A11">
-        <v>6.2315934999999998</v>
-      </c>
-      <c r="C11">
-        <f>$B$2+$B$5+($B$3+$B$6)*A11</f>
-        <v>0.57800933300000001</v>
-      </c>
-      <c r="G11">
-        <v>6.2315934999999998</v>
-      </c>
-      <c r="I11">
-        <f>$H$2+$H$5+($H$3+$H$6)*G11</f>
-        <v>5.6384604220000005</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A12">
-        <v>5.1203884999999998</v>
-      </c>
-      <c r="C12">
-        <f t="shared" ref="C12:C13" si="0">$B$2+$B$5+($B$3+$B$6)*A12</f>
-        <v>0.66912814300000001</v>
-      </c>
-      <c r="G12">
-        <v>5.1203884999999998</v>
-      </c>
-      <c r="I12">
-        <f t="shared" ref="I12:I13" si="1">$H$2+$H$5+($H$3+$H$6)*G12</f>
-        <v>5.8473669620000006</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A13">
-        <v>0</v>
-      </c>
-      <c r="B13">
-        <v>0</v>
-      </c>
-      <c r="C13">
-        <f t="shared" si="0"/>
-        <v>1.089</v>
-      </c>
-      <c r="D13">
-        <f>$B$2+$B$3*A13</f>
-        <v>0.34200000000000003</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <f t="shared" si="1"/>
-        <v>6.8100000000000005</v>
-      </c>
-      <c r="J13">
-        <f>$H$2+$H$3*G13</f>
-        <v>5.4610000000000003</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A14">
-        <v>2.1058599999999998</v>
-      </c>
-      <c r="D14">
-        <f t="shared" ref="D14:D15" si="2">$B$2+$B$3*A14</f>
-        <v>0.30830624000000001</v>
-      </c>
-      <c r="G14">
-        <v>2.1058599999999998</v>
-      </c>
-      <c r="J14">
-        <f t="shared" ref="J14:J15" si="3">$H$2+$H$3*G14</f>
-        <v>5.0650983200000006</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A15">
-        <v>4.780926</v>
-      </c>
-      <c r="D15">
-        <f t="shared" si="2"/>
-        <v>0.26550518400000001</v>
-      </c>
-      <c r="G15">
-        <v>4.780926</v>
-      </c>
-      <c r="J15">
-        <f t="shared" si="3"/>
-        <v>4.5621859120000003</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2D15DE7-CAF9-4A3C-99EC-AE501B1448E2}">
-  <dimension ref="A1:M47"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="27.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.33203125" customWidth="1"/>
-    <col min="4" max="4" width="27.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H1" t="s">
-        <v>321</v>
-      </c>
-      <c r="I1" t="s">
-        <v>322</v>
-      </c>
-      <c r="L1" t="s">
-        <v>321</v>
-      </c>
-      <c r="M1" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2">
-        <v>0.22600000000000001</v>
-      </c>
-      <c r="C2">
-        <v>1.113</v>
-      </c>
-      <c r="G2" t="s">
-        <v>316</v>
-      </c>
-      <c r="H2">
-        <v>2.7743699999999998</v>
-      </c>
-      <c r="I2">
-        <v>2.8641299999999998</v>
-      </c>
-      <c r="K2" t="s">
-        <v>319</v>
-      </c>
-      <c r="L2">
-        <v>5.6759909999999998</v>
-      </c>
-      <c r="M2">
-        <v>0.5556025</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3">
-        <v>-4.4999999999999998E-2</v>
-      </c>
-      <c r="C3">
-        <v>-0.22700000000000001</v>
-      </c>
-      <c r="K3" t="s">
-        <v>320</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>79</v>
-      </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="G4" t="s">
-        <v>323</v>
-      </c>
-      <c r="H4">
-        <v>0.27068130000000001</v>
-      </c>
-      <c r="I4">
-        <v>0.29724149999999999</v>
-      </c>
-      <c r="K4" t="s">
-        <v>319</v>
-      </c>
-      <c r="L4">
-        <v>0.55539000000000005</v>
-      </c>
-      <c r="M4">
-        <v>0.15205959999999999</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="B5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D5" t="s">
-        <v>127</v>
-      </c>
-      <c r="K5" t="s">
-        <v>320</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="6">
-        <v>0.68400000000000005</v>
-      </c>
-      <c r="C6">
-        <v>1.2390000000000001</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="H6" t="s">
-        <v>321</v>
-      </c>
-      <c r="I6" t="s">
-        <v>322</v>
-      </c>
-      <c r="L6" t="s">
-        <v>321</v>
-      </c>
-      <c r="M6" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>186</v>
-      </c>
-      <c r="B7">
-        <v>-2.5999999999999999E-2</v>
-      </c>
-      <c r="C7">
-        <v>-0.20799999999999999</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="G7" t="s">
-        <v>186</v>
-      </c>
-      <c r="H7">
-        <f>4.662178- 1.488808</f>
-        <v>3.1733700000000002</v>
-      </c>
-      <c r="I7">
-        <f>4.662178+1.488808</f>
-        <v>6.1509859999999996</v>
-      </c>
-      <c r="K7" t="s">
-        <v>319</v>
-      </c>
-      <c r="L7">
-        <v>5.6759909999999998</v>
-      </c>
-      <c r="M7">
-        <v>0.5556025</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>134</v>
-      </c>
-      <c r="B8">
-        <v>-5.8000000000000003E-2</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="K8" t="s">
-        <v>320</v>
-      </c>
-      <c r="L8">
-        <v>3.4433929999999999</v>
-      </c>
-      <c r="M8">
-        <v>1.3375330000000001</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>229</v>
-      </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9">
-        <v>0.49399999999999999</v>
-      </c>
-      <c r="G9" t="s">
-        <v>229</v>
-      </c>
-      <c r="H9">
-        <f>0.5062086-0.1771589</f>
-        <v>0.3290497</v>
-      </c>
-      <c r="I9">
-        <f>0.5062086+0.1771589</f>
-        <v>0.68336750000000002</v>
-      </c>
-      <c r="K9" t="s">
-        <v>319</v>
-      </c>
-      <c r="L9">
-        <v>0.55539000000000005</v>
-      </c>
-      <c r="M9">
-        <v>0.15205959999999999</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>149</v>
-      </c>
-      <c r="B10">
-        <v>0</v>
-      </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-      <c r="D10">
-        <v>-0.109</v>
-      </c>
-      <c r="K10" t="s">
-        <v>320</v>
-      </c>
-      <c r="L10">
-        <v>0.44526110000000002</v>
-      </c>
-      <c r="M10">
-        <v>0.18690109999999999</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="B15" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>316</v>
-      </c>
-      <c r="B16" t="s">
-        <v>317</v>
-      </c>
-      <c r="C16" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17">
-        <f>L2+M2</f>
-        <v>6.2315934999999998</v>
-      </c>
-      <c r="B17">
-        <f>$B$2+$B$3*A17</f>
-        <v>-5.4421707499999999E-2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18">
-        <f>L2-M2</f>
-        <v>5.1203884999999998</v>
-      </c>
-      <c r="B18">
-        <f>$B$2+$B$3*A18</f>
-        <v>-4.4174824999999862E-3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A19">
-        <v>0</v>
-      </c>
-      <c r="B19">
-        <f>$B$2+$B$3*A19</f>
-        <v>0.22600000000000001</v>
-      </c>
-      <c r="C19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A20">
-        <v>0</v>
-      </c>
-      <c r="C20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B22" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>316</v>
-      </c>
-      <c r="B23" t="s">
-        <v>317</v>
-      </c>
-      <c r="C23" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A24">
-        <f>L7+M7</f>
-        <v>6.2315934999999998</v>
-      </c>
-      <c r="B24">
-        <f>$C$2+$C$3*A24</f>
-        <v>-0.30157172450000003</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A25">
-        <f>L7-M7</f>
-        <v>5.1203884999999998</v>
-      </c>
-      <c r="B25">
-        <f>$C$2+$C$3*A25</f>
-        <v>-4.9328189499999953E-2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A26">
-        <v>0</v>
-      </c>
-      <c r="C26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A27">
-        <v>0</v>
-      </c>
-      <c r="C27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B33" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
-        <v>186</v>
-      </c>
-      <c r="B34" t="s">
-        <v>317</v>
-      </c>
-      <c r="C34" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A35">
-        <f>L7-M7</f>
-        <v>5.1203884999999998</v>
-      </c>
-      <c r="B35">
-        <f>B6+B7*A35+B8*A35</f>
-        <v>0.25388736600000006</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A36">
-        <f>L7+M7</f>
-        <v>6.2315934999999998</v>
-      </c>
-      <c r="B36">
-        <f>B6+B7*A36+A36*B8</f>
-        <v>0.16054614600000006</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A37">
-        <v>0</v>
-      </c>
-      <c r="B37">
-        <f>B6+B7*A37+A37*B8</f>
-        <v>0.68400000000000005</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A38">
-        <f>L8-M8</f>
-        <v>2.1058599999999998</v>
-      </c>
-      <c r="C38">
-        <f>B7*(A38)</f>
-        <v>-5.4752359999999993E-2</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A39">
-        <f>L8+M8</f>
-        <v>4.780926</v>
-      </c>
-      <c r="C39">
-        <f>B7*A39</f>
-        <v>-0.124304076</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A40">
-        <v>0</v>
-      </c>
-      <c r="C40">
-        <f>B7*A40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B41" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A42" t="s">
-        <v>229</v>
-      </c>
-      <c r="B42" t="s">
-        <v>317</v>
-      </c>
-      <c r="C42" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A43">
-        <f>L9-M9</f>
-        <v>0.40333040000000009</v>
-      </c>
-      <c r="B43">
-        <f>D9*A43+D10*A43</f>
-        <v>0.15528220400000003</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A44">
-        <f>L9+M9</f>
-        <v>0.70744960000000001</v>
-      </c>
-      <c r="B44">
-        <f>D9*A44+D10*A44</f>
-        <v>0.272368096</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A45">
-        <f>L10-M10</f>
-        <v>0.25836000000000003</v>
-      </c>
-      <c r="C45">
-        <f>D9*A45</f>
-        <v>0.12762984000000002</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A46">
-        <f>L10+M10</f>
-        <v>0.63216220000000001</v>
-      </c>
-      <c r="C46">
-        <f>D9*A46</f>
-        <v>0.31228812680000001</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A47">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
 </file>